--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.9 → 49.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>49.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -761,8 +789,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -902,10 +929,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>628.5</v>
+        <v>629.5</v>
       </c>
       <c r="D2">
-        <v>1.37</v>
+        <v>0.16</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -914,46 +941,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-37.62</v>
+        <v>-37.52</v>
       </c>
       <c r="H2">
-        <v>71.16</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I2">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J2">
-        <v>-12.5</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="K2">
-        <v>-11.68</v>
+        <v>-10.26</v>
       </c>
       <c r="L2">
-        <v>12.39</v>
+        <v>14.1</v>
       </c>
       <c r="M2">
-        <v>-8.460000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P2">
-        <v>626.5</v>
+        <v>627.4400000000001</v>
       </c>
       <c r="Q2">
-        <v>643.52</v>
+        <v>641.37</v>
       </c>
       <c r="R2">
-        <v>657.62</v>
+        <v>656.87</v>
       </c>
       <c r="S2">
-        <v>614.6</v>
+        <v>614.91</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +995,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>43.8</v>
+        <v>44.25</v>
       </c>
       <c r="Z2">
-        <v>-10.58</v>
+        <v>-10.04</v>
       </c>
       <c r="AA2">
-        <v>-9.890000000000001</v>
+        <v>-9.92</v>
       </c>
       <c r="AB2">
-        <v>-0.6899999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>36.7</v>
+        <v>57.9</v>
       </c>
       <c r="AD2">
-        <v>21.98</v>
+        <v>36.41</v>
       </c>
       <c r="AE2">
-        <v>20.79</v>
+        <v>20.3</v>
       </c>
       <c r="AF2">
-        <v>-71.89</v>
+        <v>-66.98999999999999</v>
       </c>
       <c r="AG2">
-        <v>682.71</v>
+        <v>678.55</v>
       </c>
       <c r="AH2">
-        <v>604.33</v>
+        <v>604.2</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1004,7 +1031,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>20.77</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1042,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>279.05</v>
+        <v>273.55</v>
       </c>
       <c r="D3">
-        <v>2.82</v>
+        <v>-1.97</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1027,46 +1054,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-1.97</v>
       </c>
       <c r="H3">
-        <v>82.11</v>
+        <v>78.52</v>
       </c>
       <c r="I3">
-        <v>7.62</v>
+        <v>3.46</v>
       </c>
       <c r="J3">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="K3">
-        <v>22.64</v>
+        <v>18.06</v>
       </c>
       <c r="L3">
-        <v>33.77</v>
+        <v>30.57</v>
       </c>
       <c r="M3">
-        <v>37.63</v>
+        <v>35.06</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>269.14</v>
+        <v>270.97</v>
       </c>
       <c r="Q3">
-        <v>262.17</v>
+        <v>262.91</v>
       </c>
       <c r="R3">
-        <v>257.26</v>
+        <v>257.92</v>
       </c>
       <c r="S3">
-        <v>204.78</v>
+        <v>205.2</v>
       </c>
       <c r="T3">
-        <v>36.27</v>
+        <v>33.31</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,43 +1108,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>65.92</v>
+        <v>59.88</v>
       </c>
       <c r="Z3">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="AA3">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AB3">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC3">
-        <v>99</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="AD3">
-        <v>92.89</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="AE3">
         <v>8.81</v>
       </c>
       <c r="AF3">
-        <v>42.94</v>
+        <v>-40.85</v>
       </c>
       <c r="AG3">
-        <v>275.79</v>
+        <v>277.34</v>
       </c>
       <c r="AH3">
-        <v>248.55</v>
+        <v>248.47</v>
       </c>
       <c r="AI3">
-        <v>249.08</v>
+        <v>250.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>23.09</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1155,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1125</v>
+        <v>1095</v>
       </c>
       <c r="D4">
-        <v>1.99</v>
+        <v>-2.67</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1140,46 +1167,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-12.71</v>
+        <v>-15.04</v>
       </c>
       <c r="H4">
-        <v>18.95</v>
+        <v>15.78</v>
       </c>
       <c r="I4">
-        <v>1.8</v>
+        <v>-2.58</v>
       </c>
       <c r="J4">
-        <v>7.01</v>
+        <v>6.43</v>
       </c>
       <c r="K4">
-        <v>-7.35</v>
+        <v>-11.9</v>
       </c>
       <c r="L4">
-        <v>15</v>
+        <v>9.74</v>
       </c>
       <c r="M4">
-        <v>23.3</v>
+        <v>21.39</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P4">
-        <v>1113.28</v>
+        <v>1107.48</v>
       </c>
       <c r="Q4">
-        <v>1070.62</v>
+        <v>1073.36</v>
       </c>
       <c r="R4">
-        <v>1093.04</v>
+        <v>1090.75</v>
       </c>
       <c r="S4">
-        <v>1121.23</v>
+        <v>1121.66</v>
       </c>
       <c r="T4">
-        <v>0.34</v>
+        <v>-2.38</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1191,37 +1218,37 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>62.28</v>
+        <v>52.49</v>
       </c>
       <c r="Z4">
-        <v>10.02</v>
+        <v>9.25</v>
       </c>
       <c r="AA4">
-        <v>0.96</v>
+        <v>2.62</v>
       </c>
       <c r="AB4">
-        <v>9.06</v>
+        <v>6.63</v>
       </c>
       <c r="AC4">
-        <v>76.31</v>
+        <v>70.63</v>
       </c>
       <c r="AD4">
-        <v>78.8</v>
+        <v>73.94</v>
       </c>
       <c r="AE4">
-        <v>24.62</v>
+        <v>25.11</v>
       </c>
       <c r="AF4">
-        <v>-23.94</v>
+        <v>-30.65</v>
       </c>
       <c r="AG4">
-        <v>1140.73</v>
+        <v>1142.74</v>
       </c>
       <c r="AH4">
-        <v>1000.51</v>
+        <v>1003.99</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1230,7 +1257,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>36.11</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1268,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>732.75</v>
+        <v>725.1</v>
       </c>
       <c r="D5">
-        <v>-0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1253,46 +1280,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.25</v>
+        <v>-16.13</v>
       </c>
       <c r="H5">
-        <v>10.7</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I5">
-        <v>0.14</v>
+        <v>-1.43</v>
       </c>
       <c r="J5">
-        <v>2.28</v>
+        <v>3.09</v>
       </c>
       <c r="K5">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="L5">
-        <v>1.03</v>
+        <v>0.31</v>
       </c>
       <c r="M5">
-        <v>38.48</v>
+        <v>37.22</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>736.01</v>
+        <v>733.9</v>
       </c>
       <c r="Q5">
-        <v>732.02</v>
+        <v>732.1900000000001</v>
       </c>
       <c r="R5">
-        <v>709.23</v>
+        <v>709.8200000000001</v>
       </c>
       <c r="S5">
-        <v>752.62</v>
+        <v>752.26</v>
       </c>
       <c r="T5">
-        <v>-2.64</v>
+        <v>-3.61</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1334,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>53.91</v>
+        <v>49.61</v>
       </c>
       <c r="Z5">
-        <v>6.28</v>
+        <v>5.23</v>
       </c>
       <c r="AA5">
-        <v>6.73</v>
+        <v>6.43</v>
       </c>
       <c r="AB5">
-        <v>-0.45</v>
+        <v>-1.2</v>
       </c>
       <c r="AC5">
-        <v>42.38</v>
+        <v>30.51</v>
       </c>
       <c r="AD5">
-        <v>55.42</v>
+        <v>44.13</v>
       </c>
       <c r="AE5">
-        <v>16.78</v>
+        <v>16.65</v>
       </c>
       <c r="AF5">
-        <v>-59.95</v>
+        <v>-28.19</v>
       </c>
       <c r="AG5">
-        <v>746.54</v>
+        <v>746.28</v>
       </c>
       <c r="AH5">
-        <v>717.51</v>
+        <v>718.09</v>
       </c>
       <c r="AI5">
         <v>690.96</v>
@@ -1343,7 +1370,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>27.11</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1381,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="D6">
-        <v>2.41</v>
+        <v>-2.6</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1366,46 +1393,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-3.67</v>
+        <v>-6.17</v>
       </c>
       <c r="H6">
-        <v>31.79</v>
+        <v>28.37</v>
       </c>
       <c r="I6">
-        <v>1.58</v>
+        <v>-0.88</v>
       </c>
       <c r="J6">
-        <v>4.44</v>
+        <v>1.69</v>
       </c>
       <c r="K6">
-        <v>11.97</v>
+        <v>10.94</v>
       </c>
       <c r="L6">
-        <v>7.84</v>
+        <v>5.06</v>
       </c>
       <c r="M6">
-        <v>20.35</v>
+        <v>20.4</v>
       </c>
       <c r="N6">
         <v>55</v>
       </c>
       <c r="O6">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>567.58</v>
+        <v>566.58</v>
       </c>
       <c r="Q6">
-        <v>557.0599999999999</v>
+        <v>557.35</v>
       </c>
       <c r="R6">
-        <v>562.83</v>
+        <v>562.46</v>
       </c>
       <c r="S6">
-        <v>518.5</v>
+        <v>518.6900000000001</v>
       </c>
       <c r="T6">
-        <v>11.47</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1447,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>61.12</v>
+        <v>51.82</v>
       </c>
       <c r="Z6">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AA6">
-        <v>-0.01</v>
+        <v>0.5</v>
       </c>
       <c r="AB6">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC6">
-        <v>81.28</v>
+        <v>75.39</v>
       </c>
       <c r="AD6">
-        <v>80.61</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="AE6">
-        <v>12.56</v>
+        <v>13.19</v>
       </c>
       <c r="AF6">
-        <v>-6.84</v>
+        <v>10.46</v>
       </c>
       <c r="AG6">
-        <v>578.2</v>
+        <v>578.66</v>
       </c>
       <c r="AH6">
-        <v>535.92</v>
+        <v>536.04</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1456,7 +1483,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.15</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1494,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11852</v>
+        <v>11941</v>
       </c>
       <c r="D7">
-        <v>-1.44</v>
+        <v>0.75</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1479,46 +1506,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-46.53</v>
+        <v>-46.13</v>
       </c>
       <c r="H7">
-        <v>11.23</v>
+        <v>12.07</v>
       </c>
       <c r="I7">
-        <v>-1.36</v>
+        <v>-1.92</v>
       </c>
       <c r="J7">
-        <v>5.37</v>
+        <v>4.56</v>
       </c>
       <c r="K7">
-        <v>-3.95</v>
+        <v>-4.49</v>
       </c>
       <c r="L7">
-        <v>-37.82</v>
+        <v>-37.27</v>
       </c>
       <c r="M7">
-        <v>18.92</v>
+        <v>19.45</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>12092.2</v>
+        <v>12045.4</v>
       </c>
       <c r="Q7">
-        <v>11354.75</v>
+        <v>11391.2</v>
       </c>
       <c r="R7">
-        <v>11872.64</v>
+        <v>11853.8</v>
       </c>
       <c r="S7">
-        <v>15289.72</v>
+        <v>15263.4</v>
       </c>
       <c r="T7">
-        <v>-22.48</v>
+        <v>-21.77</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1560,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>54.48</v>
+        <v>56.22</v>
       </c>
       <c r="Z7">
-        <v>72.38</v>
+        <v>84.89</v>
       </c>
       <c r="AA7">
-        <v>-75.64</v>
+        <v>-43.54</v>
       </c>
       <c r="AB7">
-        <v>148.02</v>
+        <v>128.42</v>
       </c>
       <c r="AC7">
-        <v>78</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="AD7">
-        <v>86.90000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="AE7">
-        <v>378.09</v>
+        <v>376.01</v>
       </c>
       <c r="AF7">
-        <v>-34.97</v>
+        <v>34.49</v>
       </c>
       <c r="AG7">
-        <v>12380.14</v>
+        <v>12446.61</v>
       </c>
       <c r="AH7">
-        <v>10329.36</v>
+        <v>10335.79</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1569,7 +1596,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>40.1</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1607,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>342</v>
+        <v>341.85</v>
       </c>
       <c r="D8">
-        <v>1.86</v>
+        <v>-0.04</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1592,46 +1619,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.62</v>
+        <v>-2.66</v>
       </c>
       <c r="H8">
-        <v>45.96</v>
+        <v>45.9</v>
       </c>
       <c r="I8">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="J8">
-        <v>3.62</v>
+        <v>-2.66</v>
       </c>
       <c r="K8">
-        <v>25.71</v>
+        <v>27.58</v>
       </c>
       <c r="L8">
-        <v>12.02</v>
+        <v>12.1</v>
       </c>
       <c r="M8">
-        <v>31.48</v>
+        <v>31.43</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P8">
-        <v>333.78</v>
+        <v>336.3</v>
       </c>
       <c r="Q8">
-        <v>331.11</v>
+        <v>330.84</v>
       </c>
       <c r="R8">
-        <v>315.53</v>
+        <v>316.88</v>
       </c>
       <c r="S8">
-        <v>281</v>
+        <v>281.22</v>
       </c>
       <c r="T8">
-        <v>21.71</v>
+        <v>21.56</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1646,34 +1673,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>60.29</v>
+        <v>60.18</v>
       </c>
       <c r="Z8">
-        <v>3.84</v>
+        <v>4.48</v>
       </c>
       <c r="AA8">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AB8">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="AC8">
-        <v>69.7</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AD8">
-        <v>58.67</v>
+        <v>71.97</v>
       </c>
       <c r="AE8">
-        <v>11.11</v>
+        <v>10.77</v>
       </c>
       <c r="AF8">
-        <v>18.99</v>
+        <v>-34.3</v>
       </c>
       <c r="AG8">
-        <v>352.72</v>
+        <v>351.72</v>
       </c>
       <c r="AH8">
-        <v>309.5</v>
+        <v>309.95</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1682,7 +1709,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>24.1</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1720,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1302</v>
+        <v>1283.4</v>
       </c>
       <c r="D9">
-        <v>0.19</v>
+        <v>-1.43</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1705,46 +1732,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-2.11</v>
+        <v>-3.5</v>
       </c>
       <c r="H9">
-        <v>26.83</v>
+        <v>25.01</v>
       </c>
       <c r="I9">
-        <v>0.75</v>
+        <v>-1.28</v>
       </c>
       <c r="J9">
-        <v>4.54</v>
+        <v>3.72</v>
       </c>
       <c r="K9">
-        <v>3.97</v>
+        <v>0.67</v>
       </c>
       <c r="L9">
-        <v>23.31</v>
+        <v>21.83</v>
       </c>
       <c r="M9">
-        <v>13.53</v>
+        <v>12.38</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P9">
-        <v>1307.88</v>
+        <v>1304.56</v>
       </c>
       <c r="Q9">
-        <v>1267.62</v>
+        <v>1269.41</v>
       </c>
       <c r="R9">
-        <v>1264.12</v>
+        <v>1263.8</v>
       </c>
       <c r="S9">
-        <v>1213.51</v>
+        <v>1214.16</v>
       </c>
       <c r="T9">
-        <v>7.29</v>
+        <v>5.7</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1759,34 +1786,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>59.59</v>
+        <v>53.28</v>
       </c>
       <c r="Z9">
-        <v>14.95</v>
+        <v>13.53</v>
       </c>
       <c r="AA9">
-        <v>9.25</v>
+        <v>10.1</v>
       </c>
       <c r="AB9">
-        <v>5.7</v>
+        <v>3.42</v>
       </c>
       <c r="AC9">
-        <v>55.73</v>
+        <v>43.24</v>
       </c>
       <c r="AD9">
-        <v>71.59</v>
+        <v>56.76</v>
       </c>
       <c r="AE9">
-        <v>26.19</v>
+        <v>26.3</v>
       </c>
       <c r="AF9">
-        <v>-13.96</v>
+        <v>-14.31</v>
       </c>
       <c r="AG9">
-        <v>1327.16</v>
+        <v>1328.57</v>
       </c>
       <c r="AH9">
-        <v>1208.08</v>
+        <v>1210.24</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1795,7 +1822,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>46.24</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1833,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>84.37</v>
+        <v>83.87</v>
       </c>
       <c r="D10">
-        <v>-0.12</v>
+        <v>-0.59</v>
       </c>
       <c r="E10">
         <v>88.17</v>
@@ -1818,25 +1845,25 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-4.31</v>
+        <v>-4.88</v>
       </c>
       <c r="H10">
-        <v>133.84</v>
+        <v>132.46</v>
       </c>
       <c r="I10">
-        <v>5.45</v>
+        <v>1.61</v>
       </c>
       <c r="J10">
-        <v>65.72</v>
+        <v>58.39</v>
       </c>
       <c r="K10">
-        <v>61.44</v>
+        <v>61.66</v>
       </c>
       <c r="L10">
-        <v>7.59</v>
+        <v>7.14</v>
       </c>
       <c r="M10">
-        <v>-3.81</v>
+        <v>-3.91</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1845,19 +1872,19 @@
         <v>91</v>
       </c>
       <c r="P10">
-        <v>85.15000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="Q10">
-        <v>68.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="R10">
-        <v>58.45</v>
+        <v>59.13</v>
       </c>
       <c r="S10">
-        <v>59.16</v>
+        <v>59.18</v>
       </c>
       <c r="T10">
-        <v>42.6</v>
+        <v>41.73</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1899,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>71.63</v>
+        <v>70.66</v>
       </c>
       <c r="Z10">
-        <v>8.220000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="AA10">
-        <v>6.47</v>
+        <v>6.81</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="AC10">
-        <v>72</v>
+        <v>55.88</v>
       </c>
       <c r="AD10">
-        <v>85.47</v>
+        <v>71.36</v>
       </c>
       <c r="AE10">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="AF10">
-        <v>-81.52</v>
+        <v>-73.20999999999999</v>
       </c>
       <c r="AG10">
-        <v>93.73999999999999</v>
+        <v>94.89</v>
       </c>
       <c r="AH10">
-        <v>43.76</v>
+        <v>45.81</v>
       </c>
       <c r="AI10">
         <v>71.40000000000001</v>
@@ -1908,7 +1935,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>53.1</v>
+        <v>52.72</v>
       </c>
     </row>
   </sheetData>
@@ -2069,12 +2096,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1278 +2144,1278 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-12.5</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.13</v>
+      <c r="D7" s="6">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.05</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-0.33</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>1.18</v>
       </c>
+      <c r="D8" s="6">
+        <v>1.84</v>
+      </c>
       <c r="E8" s="7">
-        <v>1.51</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>7.11</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>7.01</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.1</v>
+      <c r="D9" s="6">
+        <v>6.43</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>3.53</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>2.28</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.25</v>
+      <c r="D10" s="6">
+        <v>3.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>4.44</v>
       </c>
-      <c r="E11" s="6">
+      <c r="D11" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5.37</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-6.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.54</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3.72</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>65.72</v>
+      </c>
+      <c r="D15" s="6">
+        <v>58.39</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-7.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>7.62</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3.46</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-4.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.58</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.43</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.88</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
         <v>-1.36</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-1.92</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3.83</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>5.45</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.61</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-3.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>12.39</v>
+      </c>
+      <c r="D25" s="6">
+        <v>14.1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>33.77</v>
+      </c>
+      <c r="D26" s="6">
+        <v>30.57</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>15</v>
+      </c>
+      <c r="D27" s="6">
+        <v>9.74</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1.03</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>7.84</v>
+      </c>
+      <c r="D29" s="6">
+        <v>5.06</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>8.09</v>
-      </c>
-      <c r="D12" s="5">
-        <v>5.37</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-37.82</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-37.27</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>3.66</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>12.02</v>
+      </c>
+      <c r="D31" s="6">
+        <v>12.1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>23.31</v>
+      </c>
+      <c r="D32" s="6">
+        <v>21.83</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>7.59</v>
+      </c>
+      <c r="D33" s="6">
+        <v>7.14</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-11.68</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-10.26</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>22.64</v>
+      </c>
+      <c r="D35" s="6">
+        <v>18.06</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-7.35</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-11.9</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>11.97</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.94</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>25.71</v>
+      </c>
+      <c r="D40" s="6">
+        <v>27.58</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>3.97</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>61.44</v>
+      </c>
+      <c r="D42" s="6">
+        <v>61.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-37.62</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-37.52</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-1.97</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-12.71</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-15.04</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-15.25</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-16.13</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-6.17</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-46.53</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-46.13</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-2.62</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="E49" s="8">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6.01</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4.54</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>66.8</v>
-      </c>
-      <c r="D15" s="5">
-        <v>65.72</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-4.31</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-4.88</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.1</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>628.5</v>
+      </c>
+      <c r="D52" s="6">
+        <v>629.5</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>5.62</v>
-      </c>
-      <c r="D17" s="5">
-        <v>7.62</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="C53" s="6">
+        <v>279.05</v>
+      </c>
+      <c r="D53" s="6">
+        <v>273.55</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1125</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1095</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-0.02</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>732.75</v>
+      </c>
+      <c r="D55" s="6">
+        <v>725.1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-7.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.76</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>578</v>
+      </c>
+      <c r="D56" s="6">
+        <v>563</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>6.82</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.36</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-8.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11852</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11941</v>
+      </c>
+      <c r="E57" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>7.47</v>
-      </c>
-      <c r="D22" s="5">
-        <v>3.95</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>342</v>
+      </c>
+      <c r="D58" s="6">
+        <v>341.85</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2.32</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1302</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1283.4</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-18.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>26.68</v>
-      </c>
-      <c r="D24" s="5">
-        <v>5.45</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-21.23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>84.37</v>
+      </c>
+      <c r="D60" s="6">
+        <v>83.87</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>34</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>12.46</v>
-      </c>
-      <c r="D25" s="5">
-        <v>12.39</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>43.8</v>
+      </c>
+      <c r="D63" s="6">
+        <v>44.25</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>33.35</v>
-      </c>
-      <c r="D26" s="5">
-        <v>33.77</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>65.92</v>
+      </c>
+      <c r="D64" s="6">
+        <v>59.88</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-6.04</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>16.89</v>
-      </c>
-      <c r="D27" s="5">
-        <v>15</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>62.28</v>
+      </c>
+      <c r="D65" s="6">
+        <v>52.49</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-9.789999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>53.91</v>
+      </c>
+      <c r="D66" s="6">
+        <v>49.61</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>10.68</v>
-      </c>
-      <c r="D29" s="5">
-        <v>7.84</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>61.12</v>
+      </c>
+      <c r="D67" s="6">
+        <v>51.82</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-9.300000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-37.24</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-37.82</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>54.48</v>
+      </c>
+      <c r="D68" s="6">
+        <v>56.22</v>
+      </c>
+      <c r="E68" s="7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>10.43</v>
-      </c>
-      <c r="D31" s="5">
-        <v>12.02</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>60.29</v>
+      </c>
+      <c r="D69" s="6">
+        <v>60.18</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>26.44</v>
-      </c>
-      <c r="D32" s="5">
-        <v>23.31</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>59.59</v>
+      </c>
+      <c r="D70" s="6">
+        <v>53.28</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>7.96</v>
-      </c>
-      <c r="D33" s="5">
-        <v>7.59</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>71.63</v>
+      </c>
+      <c r="D71" s="6">
+        <v>70.66</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-13.02</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-11.68</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-71.89</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-66.98999999999999</v>
+      </c>
+      <c r="E72" s="7">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>15.04</v>
-      </c>
-      <c r="D35" s="5">
-        <v>22.64</v>
-      </c>
-      <c r="E35" s="7">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>42.94</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-40.85</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-83.79000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-10.47</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-7.35</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-23.94</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-30.65</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-6.71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-59.95</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-28.19</v>
+      </c>
+      <c r="E75" s="7">
+        <v>31.76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1.74</v>
-      </c>
-      <c r="D38" s="5">
-        <v>11.97</v>
-      </c>
-      <c r="E38" s="7">
-        <v>10.23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="D76" s="6">
+        <v>10.46</v>
+      </c>
+      <c r="E76" s="7">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-4.06</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-3.95</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-34.97</v>
+      </c>
+      <c r="D77" s="6">
+        <v>34.49</v>
+      </c>
+      <c r="E77" s="7">
+        <v>69.45999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>16.84</v>
-      </c>
-      <c r="D40" s="5">
-        <v>25.71</v>
-      </c>
-      <c r="E40" s="7">
-        <v>8.869999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>18.99</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-34.3</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-53.29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>2.92</v>
-      </c>
-      <c r="D41" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-13.96</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-14.31</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>56.37</v>
-      </c>
-      <c r="D42" s="5">
-        <v>61.44</v>
-      </c>
-      <c r="E42" s="7">
-        <v>5.07</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-38.47</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-37.62</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="D44" s="5">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-12.71</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-15.03</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-15.25</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-5.93</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-3.67</v>
-      </c>
-      <c r="E47" s="7">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-45.75</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-46.53</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-4.4</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-2.62</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-2.29</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-4.2</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-4.31</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>620</v>
-      </c>
-      <c r="D52" s="5">
-        <v>628.5</v>
-      </c>
-      <c r="E52" s="7">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>271.4</v>
-      </c>
-      <c r="D53" s="5">
-        <v>279.05</v>
-      </c>
-      <c r="E53" s="7">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1103</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1125</v>
-      </c>
-      <c r="E54" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>734.65</v>
-      </c>
-      <c r="D55" s="5">
-        <v>732.75</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>564.4</v>
-      </c>
-      <c r="D56" s="5">
-        <v>578</v>
-      </c>
-      <c r="E56" s="7">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>12025</v>
-      </c>
-      <c r="D57" s="5">
-        <v>11852</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>335.75</v>
-      </c>
-      <c r="D58" s="5">
-        <v>342</v>
-      </c>
-      <c r="E58" s="7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1299.5</v>
-      </c>
-      <c r="D59" s="5">
-        <v>1302</v>
-      </c>
-      <c r="E59" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>84.47</v>
-      </c>
-      <c r="D60" s="5">
-        <v>84.37</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>66</v>
-      </c>
-      <c r="D61" s="5">
-        <v>77</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>77</v>
-      </c>
-      <c r="D62" s="5">
-        <v>66</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>39.97</v>
-      </c>
-      <c r="D63" s="5">
-        <v>43.8</v>
-      </c>
-      <c r="E63" s="7">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>60.82</v>
-      </c>
-      <c r="D64" s="5">
-        <v>65.92</v>
-      </c>
-      <c r="E64" s="7">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>56.79</v>
-      </c>
-      <c r="D65" s="5">
-        <v>62.28</v>
-      </c>
-      <c r="E65" s="7">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>55.01</v>
-      </c>
-      <c r="D66" s="5">
-        <v>53.91</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>54.2</v>
-      </c>
-      <c r="D67" s="5">
-        <v>61.12</v>
-      </c>
-      <c r="E67" s="7">
-        <v>6.92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>58.67</v>
-      </c>
-      <c r="D68" s="5">
-        <v>54.48</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>57.07</v>
-      </c>
-      <c r="D69" s="5">
-        <v>60.29</v>
-      </c>
-      <c r="E69" s="7">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>58.98</v>
-      </c>
-      <c r="D70" s="5">
-        <v>59.59</v>
-      </c>
-      <c r="E70" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>71.81</v>
-      </c>
-      <c r="D71" s="5">
-        <v>71.63</v>
-      </c>
-      <c r="E71" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="5">
-        <v>-38.92</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-71.89</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-32.97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-13.64</v>
-      </c>
-      <c r="D73" s="5">
-        <v>42.94</v>
-      </c>
-      <c r="E73" s="7">
-        <v>56.58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-67.02</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-23.94</v>
-      </c>
-      <c r="E74" s="7">
-        <v>43.08</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-71.91</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-59.95</v>
-      </c>
-      <c r="E75" s="7">
-        <v>11.96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-27.6</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-6.84</v>
-      </c>
-      <c r="E76" s="7">
-        <v>20.76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-34.97</v>
-      </c>
-      <c r="E77" s="6">
-        <v>-43.09</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-36.77</v>
-      </c>
-      <c r="D78" s="5">
-        <v>18.99</v>
-      </c>
-      <c r="E78" s="7">
-        <v>55.76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-59.69</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-13.96</v>
-      </c>
-      <c r="E79" s="7">
-        <v>45.73</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-86.84999999999999</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C80" s="6">
         <v>-81.52</v>
       </c>
+      <c r="D80" s="6">
+        <v>-73.20999999999999</v>
+      </c>
       <c r="E80" s="7">
-        <v>5.33</v>
+        <v>8.31</v>
       </c>
     </row>
   </sheetData>
@@ -3379,60 +3441,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>59.2</v>
-      </c>
-      <c r="E2" s="10">
-        <v>80</v>
-      </c>
-      <c r="F2" s="10">
-        <v>9.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>11.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>10.2</v>
+      </c>
+      <c r="H2" s="11">
+        <v>55.4</v>
+      </c>
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3534,61 +3596,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3848</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3763</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.3148</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.233</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.2035</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1892</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.1353</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0381</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.08460000000000001</v>
+      <c r="A2" s="14">
+        <v>0.3722</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3506</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3143</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2139</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.204</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1945</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1238</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0391</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.08929999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="106">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,112 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.7% → -1.3%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.7%</t>
+  </si>
+  <si>
+    <t>-1.3%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.9 → 49.6</t>
+    <t>44.2 → 57.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.2</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>49.6 → 55.9</t>
+  </si>
+  <si>
+    <t>49.6</t>
+  </si>
+  <si>
+    <t>55.9</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>70.7 → 68.7</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>68.7</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-2.0% → -3.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-2.0%</t>
+  </si>
+  <si>
+    <t>-3.4%</t>
+  </si>
+  <si>
+    <t>51.8 → 49.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>53.9</t>
-  </si>
-  <si>
-    <t>49.6</t>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>56.2 → 48.0</t>
+  </si>
+  <si>
+    <t>56.2</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>53.3 → 49.0</t>
+  </si>
+  <si>
+    <t>53.3</t>
+  </si>
+  <si>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +350,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,20 +384,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,13 +431,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +521,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -789,14 +897,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -929,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>629.5</v>
+        <v>666.55</v>
       </c>
       <c r="D2">
-        <v>0.16</v>
+        <v>5.89</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -941,46 +1049,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-37.52</v>
+        <v>-33.85</v>
       </c>
       <c r="H2">
-        <v>71.43000000000001</v>
+        <v>81.52</v>
       </c>
       <c r="I2">
-        <v>0.75</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>-8.449999999999999</v>
+        <v>-0.87</v>
       </c>
       <c r="K2">
-        <v>-10.26</v>
+        <v>-4.59</v>
       </c>
       <c r="L2">
-        <v>14.1</v>
+        <v>22.63</v>
       </c>
       <c r="M2">
-        <v>-8.93</v>
+        <v>-8.84</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>627.4400000000001</v>
+        <v>635.46</v>
       </c>
       <c r="Q2">
-        <v>641.37</v>
+        <v>640.92</v>
       </c>
       <c r="R2">
-        <v>656.87</v>
+        <v>657.1</v>
       </c>
       <c r="S2">
-        <v>614.91</v>
+        <v>615.41</v>
       </c>
       <c r="T2">
-        <v>2.37</v>
+        <v>8.31</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -995,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.25</v>
+        <v>57.78</v>
       </c>
       <c r="Z2">
-        <v>-10.04</v>
+        <v>-6.55</v>
       </c>
       <c r="AA2">
-        <v>-9.92</v>
+        <v>-9.24</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>2.7</v>
       </c>
       <c r="AC2">
-        <v>57.9</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="AD2">
-        <v>36.41</v>
+        <v>61.95</v>
       </c>
       <c r="AE2">
-        <v>20.3</v>
+        <v>23.35</v>
       </c>
       <c r="AF2">
-        <v>-66.98999999999999</v>
+        <v>1703.29</v>
       </c>
       <c r="AG2">
-        <v>678.55</v>
+        <v>676.53</v>
       </c>
       <c r="AH2">
-        <v>604.2</v>
+        <v>605.3099999999999</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1031,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>18.56</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1042,10 +1150,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>273.55</v>
+        <v>269.55</v>
       </c>
       <c r="D3">
-        <v>-1.97</v>
+        <v>-1.46</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1054,46 +1162,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-1.97</v>
+        <v>-3.4</v>
       </c>
       <c r="H3">
-        <v>78.52</v>
+        <v>75.91</v>
       </c>
       <c r="I3">
-        <v>3.46</v>
+        <v>1.49</v>
       </c>
       <c r="J3">
-        <v>1.84</v>
+        <v>4.13</v>
       </c>
       <c r="K3">
-        <v>18.06</v>
+        <v>16.42</v>
       </c>
       <c r="L3">
-        <v>30.57</v>
+        <v>32.29</v>
       </c>
       <c r="M3">
-        <v>35.06</v>
+        <v>34.58</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>270.97</v>
+        <v>271.76</v>
       </c>
       <c r="Q3">
-        <v>262.91</v>
+        <v>263.6</v>
       </c>
       <c r="R3">
-        <v>257.92</v>
+        <v>258.49</v>
       </c>
       <c r="S3">
-        <v>205.2</v>
+        <v>205.63</v>
       </c>
       <c r="T3">
-        <v>33.31</v>
+        <v>31.09</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1108,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>59.88</v>
+        <v>55.87</v>
       </c>
       <c r="Z3">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="AA3">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AB3">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="AC3">
-        <v>90.93000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="AD3">
-        <v>94.51000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="AE3">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="AF3">
-        <v>-40.85</v>
+        <v>-47.71</v>
       </c>
       <c r="AG3">
-        <v>277.34</v>
+        <v>277.89</v>
       </c>
       <c r="AH3">
-        <v>248.47</v>
+        <v>249.32</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1144,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>26.44</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1155,10 +1263,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="D4">
-        <v>-2.67</v>
+        <v>1.55</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1167,46 +1275,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-15.04</v>
+        <v>-13.72</v>
       </c>
       <c r="H4">
-        <v>15.78</v>
+        <v>17.57</v>
       </c>
       <c r="I4">
-        <v>-2.58</v>
+        <v>-0.13</v>
       </c>
       <c r="J4">
-        <v>6.43</v>
+        <v>6.91</v>
       </c>
       <c r="K4">
-        <v>-11.9</v>
+        <v>-11.24</v>
       </c>
       <c r="L4">
-        <v>9.74</v>
+        <v>13.01</v>
       </c>
       <c r="M4">
-        <v>21.39</v>
+        <v>21.6</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P4">
-        <v>1107.48</v>
+        <v>1107.2</v>
       </c>
       <c r="Q4">
-        <v>1073.36</v>
+        <v>1076.85</v>
       </c>
       <c r="R4">
-        <v>1090.75</v>
+        <v>1088.92</v>
       </c>
       <c r="S4">
-        <v>1121.66</v>
+        <v>1122.17</v>
       </c>
       <c r="T4">
-        <v>-2.38</v>
+        <v>-0.91</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1221,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>52.49</v>
+        <v>56.65</v>
       </c>
       <c r="Z4">
-        <v>9.25</v>
+        <v>9.9</v>
       </c>
       <c r="AA4">
-        <v>2.62</v>
+        <v>4.08</v>
       </c>
       <c r="AB4">
-        <v>6.63</v>
+        <v>5.83</v>
       </c>
       <c r="AC4">
-        <v>70.63</v>
+        <v>70.44</v>
       </c>
       <c r="AD4">
-        <v>73.94</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="AE4">
-        <v>25.11</v>
+        <v>24.66</v>
       </c>
       <c r="AF4">
-        <v>-30.65</v>
+        <v>-64.37</v>
       </c>
       <c r="AG4">
-        <v>1142.74</v>
+        <v>1146.65</v>
       </c>
       <c r="AH4">
-        <v>1003.99</v>
+        <v>1007.06</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1257,7 +1365,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>34.82</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1268,10 +1376,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>725.1</v>
+        <v>737.9</v>
       </c>
       <c r="D5">
-        <v>-1.04</v>
+        <v>1.77</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1280,46 +1388,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.13</v>
+        <v>-14.65</v>
       </c>
       <c r="H5">
-        <v>9.550000000000001</v>
+        <v>11.48</v>
       </c>
       <c r="I5">
-        <v>-1.43</v>
+        <v>-0.89</v>
       </c>
       <c r="J5">
-        <v>3.09</v>
+        <v>2.23</v>
       </c>
       <c r="K5">
-        <v>-0.02</v>
+        <v>-1.44</v>
       </c>
       <c r="L5">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="M5">
-        <v>37.22</v>
+        <v>37.08</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>733.9</v>
+        <v>732.58</v>
       </c>
       <c r="Q5">
-        <v>732.1900000000001</v>
+        <v>732.87</v>
       </c>
       <c r="R5">
-        <v>709.8200000000001</v>
+        <v>710.85</v>
       </c>
       <c r="S5">
-        <v>752.26</v>
+        <v>751.95</v>
       </c>
       <c r="T5">
-        <v>-3.61</v>
+        <v>-1.87</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1334,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>49.61</v>
+        <v>55.94</v>
       </c>
       <c r="Z5">
-        <v>5.23</v>
+        <v>5.37</v>
       </c>
       <c r="AA5">
-        <v>6.43</v>
+        <v>6.22</v>
       </c>
       <c r="AB5">
-        <v>-1.2</v>
+        <v>-0.85</v>
       </c>
       <c r="AC5">
-        <v>30.51</v>
+        <v>33.85</v>
       </c>
       <c r="AD5">
-        <v>44.13</v>
+        <v>35.58</v>
       </c>
       <c r="AE5">
-        <v>16.65</v>
+        <v>17.58</v>
       </c>
       <c r="AF5">
-        <v>-28.19</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AG5">
-        <v>746.28</v>
+        <v>746.66</v>
       </c>
       <c r="AH5">
-        <v>718.09</v>
+        <v>719.08</v>
       </c>
       <c r="AI5">
         <v>690.96</v>
@@ -1370,7 +1478,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.39</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1381,10 +1489,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>563</v>
+        <v>558.75</v>
       </c>
       <c r="D6">
-        <v>-2.6</v>
+        <v>-0.75</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1393,46 +1501,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-6.17</v>
+        <v>-6.88</v>
       </c>
       <c r="H6">
-        <v>28.37</v>
+        <v>27.41</v>
       </c>
       <c r="I6">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="J6">
-        <v>1.69</v>
+        <v>0.27</v>
       </c>
       <c r="K6">
-        <v>10.94</v>
+        <v>9.33</v>
       </c>
       <c r="L6">
-        <v>5.06</v>
+        <v>4.98</v>
       </c>
       <c r="M6">
-        <v>20.4</v>
+        <v>19.08</v>
       </c>
       <c r="N6">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>566.58</v>
+        <v>565.13</v>
       </c>
       <c r="Q6">
-        <v>557.35</v>
+        <v>557.79</v>
       </c>
       <c r="R6">
-        <v>562.46</v>
+        <v>561.91</v>
       </c>
       <c r="S6">
-        <v>518.6900000000001</v>
+        <v>518.8200000000001</v>
       </c>
       <c r="T6">
-        <v>8.539999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1447,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.82</v>
+        <v>49.52</v>
       </c>
       <c r="Z6">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AA6">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB6">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="AC6">
-        <v>75.39</v>
+        <v>61.34</v>
       </c>
       <c r="AD6">
-        <v>77.95999999999999</v>
+        <v>72.67</v>
       </c>
       <c r="AE6">
-        <v>13.19</v>
+        <v>13.02</v>
       </c>
       <c r="AF6">
-        <v>10.46</v>
+        <v>-32.45</v>
       </c>
       <c r="AG6">
-        <v>578.66</v>
+        <v>578.8099999999999</v>
       </c>
       <c r="AH6">
-        <v>536.04</v>
+        <v>536.77</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1483,7 +1591,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.32</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1494,10 +1602,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11941</v>
+        <v>11572</v>
       </c>
       <c r="D7">
-        <v>0.75</v>
+        <v>-3.09</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1506,46 +1614,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-46.13</v>
+        <v>-47.79</v>
       </c>
       <c r="H7">
-        <v>12.07</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I7">
-        <v>-1.92</v>
+        <v>-6.12</v>
       </c>
       <c r="J7">
-        <v>4.56</v>
+        <v>3.21</v>
       </c>
       <c r="K7">
-        <v>-4.49</v>
+        <v>-7.3</v>
       </c>
       <c r="L7">
-        <v>-37.27</v>
+        <v>-38.89</v>
       </c>
       <c r="M7">
-        <v>19.45</v>
+        <v>18.15</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P7">
-        <v>12045.4</v>
+        <v>11894.4</v>
       </c>
       <c r="Q7">
-        <v>11391.2</v>
+        <v>11411.55</v>
       </c>
       <c r="R7">
-        <v>11853.8</v>
+        <v>11834.82</v>
       </c>
       <c r="S7">
-        <v>15263.4</v>
+        <v>15235.42</v>
       </c>
       <c r="T7">
-        <v>-21.77</v>
+        <v>-24.05</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1560,34 +1668,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>56.22</v>
+        <v>48.05</v>
       </c>
       <c r="Z7">
-        <v>84.89</v>
+        <v>64.28</v>
       </c>
       <c r="AA7">
-        <v>-43.54</v>
+        <v>-21.97</v>
       </c>
       <c r="AB7">
-        <v>128.42</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="AC7">
-        <v>74.73999999999999</v>
+        <v>62.58</v>
       </c>
       <c r="AD7">
-        <v>80.27</v>
+        <v>71.77</v>
       </c>
       <c r="AE7">
-        <v>376.01</v>
+        <v>378.44</v>
       </c>
       <c r="AF7">
-        <v>34.49</v>
+        <v>-11.91</v>
       </c>
       <c r="AG7">
-        <v>12446.61</v>
+        <v>12464.29</v>
       </c>
       <c r="AH7">
-        <v>10335.79</v>
+        <v>10358.81</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1596,7 +1704,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>37.07</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1607,10 +1715,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>341.85</v>
+        <v>346.6</v>
       </c>
       <c r="D8">
-        <v>-0.04</v>
+        <v>1.39</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1619,46 +1727,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.66</v>
+        <v>-1.31</v>
       </c>
       <c r="H8">
-        <v>45.9</v>
+        <v>47.92</v>
       </c>
       <c r="I8">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
-        <v>-2.66</v>
+        <v>-0.19</v>
       </c>
       <c r="K8">
-        <v>27.58</v>
+        <v>29.55</v>
       </c>
       <c r="L8">
-        <v>12.1</v>
+        <v>15.38</v>
       </c>
       <c r="M8">
-        <v>31.43</v>
+        <v>32.03</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P8">
-        <v>336.3</v>
+        <v>338.74</v>
       </c>
       <c r="Q8">
-        <v>330.84</v>
+        <v>331.3</v>
       </c>
       <c r="R8">
-        <v>316.88</v>
+        <v>318.3</v>
       </c>
       <c r="S8">
-        <v>281.22</v>
+        <v>281.45</v>
       </c>
       <c r="T8">
-        <v>21.56</v>
+        <v>23.15</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1673,34 +1781,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>60.18</v>
+        <v>62.64</v>
       </c>
       <c r="Z8">
-        <v>4.48</v>
+        <v>5.3</v>
       </c>
       <c r="AA8">
-        <v>3.76</v>
+        <v>4.07</v>
       </c>
       <c r="AB8">
-        <v>0.72</v>
+        <v>1.24</v>
       </c>
       <c r="AC8">
-        <v>89.54000000000001</v>
+        <v>99.77</v>
       </c>
       <c r="AD8">
-        <v>71.97</v>
+        <v>86.34</v>
       </c>
       <c r="AE8">
-        <v>10.77</v>
+        <v>11.14</v>
       </c>
       <c r="AF8">
-        <v>-34.3</v>
+        <v>165.76</v>
       </c>
       <c r="AG8">
-        <v>351.72</v>
+        <v>353.18</v>
       </c>
       <c r="AH8">
-        <v>309.95</v>
+        <v>309.42</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1709,7 +1817,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>25.52</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1720,10 +1828,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1283.4</v>
+        <v>1269.1</v>
       </c>
       <c r="D9">
-        <v>-1.43</v>
+        <v>-1.11</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1732,46 +1840,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-3.5</v>
+        <v>-4.58</v>
       </c>
       <c r="H9">
-        <v>25.01</v>
+        <v>23.62</v>
       </c>
       <c r="I9">
-        <v>-1.28</v>
+        <v>-4.58</v>
       </c>
       <c r="J9">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="K9">
-        <v>0.67</v>
+        <v>-2.14</v>
       </c>
       <c r="L9">
-        <v>21.83</v>
+        <v>20.57</v>
       </c>
       <c r="M9">
-        <v>12.38</v>
+        <v>12.13</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P9">
-        <v>1304.56</v>
+        <v>1292.38</v>
       </c>
       <c r="Q9">
-        <v>1269.41</v>
+        <v>1271.52</v>
       </c>
       <c r="R9">
-        <v>1263.8</v>
+        <v>1262.96</v>
       </c>
       <c r="S9">
-        <v>1214.16</v>
+        <v>1214.81</v>
       </c>
       <c r="T9">
-        <v>5.7</v>
+        <v>4.47</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1786,34 +1894,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>53.28</v>
+        <v>48.99</v>
       </c>
       <c r="Z9">
-        <v>13.53</v>
+        <v>11.12</v>
       </c>
       <c r="AA9">
-        <v>10.1</v>
+        <v>10.31</v>
       </c>
       <c r="AB9">
-        <v>3.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC9">
-        <v>43.24</v>
+        <v>28.71</v>
       </c>
       <c r="AD9">
-        <v>56.76</v>
+        <v>42.56</v>
       </c>
       <c r="AE9">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="AF9">
-        <v>-14.31</v>
+        <v>-51.35</v>
       </c>
       <c r="AG9">
-        <v>1328.57</v>
+        <v>1327.21</v>
       </c>
       <c r="AH9">
-        <v>1210.24</v>
+        <v>1215.82</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1822,7 +1930,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>42.39</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1833,10 +1941,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>83.87</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.59</v>
+        <v>-1.16</v>
       </c>
       <c r="E10">
         <v>88.17</v>
@@ -1845,25 +1953,25 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-4.88</v>
+        <v>-5.98</v>
       </c>
       <c r="H10">
-        <v>132.46</v>
+        <v>129.77</v>
       </c>
       <c r="I10">
-        <v>1.61</v>
+        <v>-3.82</v>
       </c>
       <c r="J10">
-        <v>58.39</v>
+        <v>59.73</v>
       </c>
       <c r="K10">
-        <v>61.66</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="L10">
-        <v>7.14</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M10">
-        <v>-3.91</v>
+        <v>-4.54</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1872,61 +1980,61 @@
         <v>91</v>
       </c>
       <c r="P10">
-        <v>85.41</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="Q10">
-        <v>70.34999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="R10">
-        <v>59.13</v>
+        <v>59.79</v>
       </c>
       <c r="S10">
-        <v>59.18</v>
+        <v>59.2</v>
       </c>
       <c r="T10">
-        <v>41.73</v>
+        <v>40.05</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
       </c>
       <c r="V10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10">
-        <v>70.66</v>
+        <v>68.73</v>
       </c>
       <c r="Z10">
-        <v>8.15</v>
+        <v>7.92</v>
       </c>
       <c r="AA10">
-        <v>6.81</v>
+        <v>7.03</v>
       </c>
       <c r="AB10">
-        <v>1.34</v>
+        <v>0.89</v>
       </c>
       <c r="AC10">
-        <v>55.88</v>
+        <v>49.69</v>
       </c>
       <c r="AD10">
-        <v>71.36</v>
+        <v>59.19</v>
       </c>
       <c r="AE10">
-        <v>5.29</v>
+        <v>5.15</v>
       </c>
       <c r="AF10">
-        <v>-73.20999999999999</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="AG10">
-        <v>94.89</v>
+        <v>95.3</v>
       </c>
       <c r="AH10">
-        <v>45.81</v>
+        <v>48.6</v>
       </c>
       <c r="AI10">
         <v>71.40000000000001</v>
@@ -1935,7 +2043,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>52.72</v>
+        <v>52.39</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2116,7 +2224,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2128,1300 +2236,1497 @@
         <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="C6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-12.5</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="E7" s="7">
-        <v>4.05</v>
+      <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1.84</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.66</v>
+        <v>73</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-0.87</v>
+      </c>
+      <c r="E16" s="9">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1.84</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4.13</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>7.01</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C18" s="8">
         <v>6.43</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D18" s="8">
+        <v>6.91</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>2.28</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C19" s="8">
         <v>3.09</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D19" s="8">
+        <v>2.23</v>
+      </c>
+      <c r="E19" s="10">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>4.44</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C20" s="8">
         <v>1.69</v>
       </c>
-      <c r="E11" s="8">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D20" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="E20" s="10">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>5.37</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C21" s="8">
         <v>4.56</v>
       </c>
-      <c r="E12" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D21" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="E21" s="10">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C22" s="8">
         <v>-2.66</v>
       </c>
-      <c r="E13" s="8">
-        <v>-6.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D22" s="8">
+        <v>-0.19</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>4.54</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C23" s="8">
         <v>3.72</v>
       </c>
-      <c r="E14" s="8">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D23" s="8">
+        <v>1.72</v>
+      </c>
+      <c r="E23" s="10">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>65.72</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C24" s="8">
         <v>58.39</v>
       </c>
-      <c r="E15" s="8">
-        <v>-7.33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D24" s="8">
+        <v>59.73</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C25" s="8">
         <v>0.75</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D25" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="E25" s="9">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>7.62</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C26" s="8">
         <v>3.46</v>
       </c>
-      <c r="E17" s="8">
-        <v>-4.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D26" s="8">
+        <v>1.49</v>
+      </c>
+      <c r="E26" s="10">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C27" s="8">
         <v>-2.58</v>
       </c>
-      <c r="E18" s="8">
-        <v>-4.38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D27" s="8">
+        <v>-0.13</v>
+      </c>
+      <c r="E27" s="9">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>0.14</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C28" s="8">
         <v>-1.43</v>
       </c>
-      <c r="E19" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D28" s="8">
+        <v>-0.89</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>1.58</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C29" s="8">
         <v>-0.88</v>
       </c>
-      <c r="E20" s="8">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D29" s="8">
+        <v>-1.28</v>
+      </c>
+      <c r="E29" s="10">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C30" s="8">
         <v>-1.92</v>
       </c>
-      <c r="E21" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D30" s="8">
+        <v>-6.12</v>
+      </c>
+      <c r="E30" s="10">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="6">
-        <v>3.95</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C31" s="8">
         <v>3.83</v>
       </c>
-      <c r="E22" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D31" s="8">
+        <v>3.65</v>
+      </c>
+      <c r="E31" s="10">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C32" s="8">
         <v>-1.28</v>
       </c>
-      <c r="E23" s="8">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D32" s="8">
+        <v>-4.58</v>
+      </c>
+      <c r="E32" s="10">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="6">
-        <v>5.45</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C33" s="8">
         <v>1.61</v>
       </c>
-      <c r="E24" s="8">
-        <v>-3.84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D33" s="8">
+        <v>-3.82</v>
+      </c>
+      <c r="E33" s="10">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>12.39</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C34" s="8">
         <v>14.1</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D34" s="8">
+        <v>22.63</v>
+      </c>
+      <c r="E34" s="9">
+        <v>8.529999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>33.77</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C35" s="8">
         <v>30.57</v>
       </c>
-      <c r="E26" s="8">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D35" s="8">
+        <v>32.29</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>15</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C36" s="8">
         <v>9.74</v>
       </c>
-      <c r="E27" s="8">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D36" s="8">
+        <v>13.01</v>
+      </c>
+      <c r="E36" s="9">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C37" s="8">
         <v>0.31</v>
       </c>
-      <c r="E28" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D37" s="8">
+        <v>0.92</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6">
-        <v>7.84</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C38" s="8">
         <v>5.06</v>
       </c>
-      <c r="E29" s="8">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D38" s="8">
+        <v>4.98</v>
+      </c>
+      <c r="E38" s="10">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B39" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="6">
-        <v>-37.82</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C39" s="8">
         <v>-37.27</v>
       </c>
-      <c r="E30" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="D39" s="8">
+        <v>-38.89</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="6">
-        <v>12.02</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C40" s="8">
         <v>12.1</v>
       </c>
-      <c r="E31" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="D40" s="8">
+        <v>15.38</v>
+      </c>
+      <c r="E40" s="9">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B41" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="6">
-        <v>23.31</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C41" s="8">
         <v>21.83</v>
       </c>
-      <c r="E32" s="8">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="D41" s="8">
+        <v>20.57</v>
+      </c>
+      <c r="E41" s="10">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B42" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="6">
-        <v>7.59</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C42" s="8">
         <v>7.14</v>
       </c>
-      <c r="E33" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="D42" s="8">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>-11.68</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C43" s="8">
         <v>-10.26</v>
       </c>
-      <c r="E34" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="D43" s="8">
+        <v>-4.59</v>
+      </c>
+      <c r="E43" s="9">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B44" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="6">
-        <v>22.64</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C44" s="8">
         <v>18.06</v>
       </c>
-      <c r="E35" s="8">
+      <c r="D44" s="8">
+        <v>16.42</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-11.9</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-11.24</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-0.02</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-1.44</v>
+      </c>
+      <c r="E46" s="10">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8">
+        <v>10.94</v>
+      </c>
+      <c r="D47" s="8">
+        <v>9.33</v>
+      </c>
+      <c r="E47" s="10">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-4.49</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-7.3</v>
+      </c>
+      <c r="E48" s="10">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="8">
+        <v>27.58</v>
+      </c>
+      <c r="D49" s="8">
+        <v>29.55</v>
+      </c>
+      <c r="E49" s="9">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="8">
+        <v>0.67</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-2.14</v>
+      </c>
+      <c r="E50" s="10">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="8">
+        <v>61.66</v>
+      </c>
+      <c r="D51" s="8">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-37.52</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-33.85</v>
+      </c>
+      <c r="E52" s="9">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>-1.97</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-3.4</v>
+      </c>
+      <c r="E53" s="10">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-15.04</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-13.72</v>
+      </c>
+      <c r="E54" s="9">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-16.13</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-14.65</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="8">
+        <v>-6.17</v>
+      </c>
+      <c r="D56" s="8">
+        <v>-6.88</v>
+      </c>
+      <c r="E56" s="10">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="8">
+        <v>-46.13</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-47.79</v>
+      </c>
+      <c r="E57" s="10">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="8">
+        <v>-2.66</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-1.31</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="8">
+        <v>-3.5</v>
+      </c>
+      <c r="D59" s="8">
         <v>-4.58</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="E59" s="10">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="8">
+        <v>-4.88</v>
+      </c>
+      <c r="D60" s="8">
+        <v>-5.98</v>
+      </c>
+      <c r="E60" s="10">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>629.5</v>
+      </c>
+      <c r="D61" s="8">
+        <v>666.55</v>
+      </c>
+      <c r="E61" s="9">
+        <v>37.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>273.55</v>
+      </c>
+      <c r="D62" s="8">
+        <v>269.55</v>
+      </c>
+      <c r="E62" s="10">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-7.35</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>1095</v>
+      </c>
+      <c r="D63" s="8">
+        <v>1112</v>
+      </c>
+      <c r="E63" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B64" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8">
+        <v>725.1</v>
+      </c>
+      <c r="D64" s="8">
+        <v>737.9</v>
+      </c>
+      <c r="E64" s="9">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>11.97</v>
-      </c>
-      <c r="D38" s="6">
-        <v>10.94</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B65" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="8">
+        <v>563</v>
+      </c>
+      <c r="D65" s="8">
+        <v>558.75</v>
+      </c>
+      <c r="E65" s="10">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-3.95</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B66" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="8">
+        <v>11941</v>
+      </c>
+      <c r="D66" s="8">
+        <v>11572</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>25.71</v>
-      </c>
-      <c r="D40" s="6">
-        <v>27.58</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B67" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="8">
+        <v>341.85</v>
+      </c>
+      <c r="D67" s="8">
+        <v>346.6</v>
+      </c>
+      <c r="E67" s="9">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3.97</v>
-      </c>
-      <c r="D41" s="6">
-        <v>0.67</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B68" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="8">
+        <v>1283.4</v>
+      </c>
+      <c r="D68" s="8">
+        <v>1269.1</v>
+      </c>
+      <c r="E68" s="10">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>61.44</v>
-      </c>
-      <c r="D42" s="6">
-        <v>61.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="8">
+        <v>83.87</v>
+      </c>
+      <c r="D69" s="8">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E69" s="10">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-37.62</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-37.52</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="8">
+        <v>23</v>
+      </c>
+      <c r="D70" s="8">
+        <v>55</v>
+      </c>
+      <c r="E70" s="9">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="8">
+        <v>45</v>
+      </c>
+      <c r="D71" s="8">
+        <v>23</v>
+      </c>
+      <c r="E71" s="10">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="8">
+        <v>55</v>
+      </c>
+      <c r="D72" s="8">
+        <v>45</v>
+      </c>
+      <c r="E72" s="10">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>44.25</v>
+      </c>
+      <c r="D73" s="8">
+        <v>57.78</v>
+      </c>
+      <c r="E73" s="9">
+        <v>13.53</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>0</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-1.97</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>59.88</v>
+      </c>
+      <c r="D74" s="8">
+        <v>55.87</v>
+      </c>
+      <c r="E74" s="10">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-12.71</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-15.04</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>52.49</v>
+      </c>
+      <c r="D75" s="8">
+        <v>56.65</v>
+      </c>
+      <c r="E75" s="9">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-16.13</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="8">
+        <v>49.61</v>
+      </c>
+      <c r="D76" s="8">
+        <v>55.94</v>
+      </c>
+      <c r="E76" s="9">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B77" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="8">
+        <v>51.82</v>
+      </c>
+      <c r="D77" s="8">
+        <v>49.52</v>
+      </c>
+      <c r="E77" s="10">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-46.53</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-46.13</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="8">
+        <v>56.22</v>
+      </c>
+      <c r="D78" s="8">
+        <v>48.05</v>
+      </c>
+      <c r="E78" s="10">
+        <v>-8.17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="8">
+        <v>60.18</v>
+      </c>
+      <c r="D79" s="8">
+        <v>62.64</v>
+      </c>
+      <c r="E79" s="9">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B80" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" s="8">
+        <v>53.28</v>
+      </c>
+      <c r="D80" s="8">
+        <v>48.99</v>
+      </c>
+      <c r="E80" s="10">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-4.31</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-4.88</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="B81" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="8">
+        <v>70.66</v>
+      </c>
+      <c r="D81" s="8">
+        <v>68.73</v>
+      </c>
+      <c r="E81" s="10">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>628.5</v>
-      </c>
-      <c r="D52" s="6">
-        <v>629.5</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>-66.98999999999999</v>
+      </c>
+      <c r="D82" s="8">
+        <v>1703.29</v>
+      </c>
+      <c r="E82" s="9">
+        <v>1770.28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>279.05</v>
-      </c>
-      <c r="D53" s="6">
-        <v>273.55</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-40.85</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-47.71</v>
+      </c>
+      <c r="E83" s="10">
+        <v>-6.86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1125</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1095</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="B84" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="8">
+        <v>-30.65</v>
+      </c>
+      <c r="D84" s="8">
+        <v>-64.37</v>
+      </c>
+      <c r="E84" s="10">
+        <v>-33.72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>732.75</v>
-      </c>
-      <c r="D55" s="6">
-        <v>725.1</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-7.65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="B85" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="8">
+        <v>-28.19</v>
+      </c>
+      <c r="D85" s="8">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E85" s="9">
+        <v>37.58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>578</v>
-      </c>
-      <c r="D56" s="6">
-        <v>563</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="B86" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="8">
+        <v>10.46</v>
+      </c>
+      <c r="D86" s="8">
+        <v>-32.45</v>
+      </c>
+      <c r="E86" s="10">
+        <v>-42.91</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11852</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11941</v>
-      </c>
-      <c r="E57" s="7">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
+      <c r="B87" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="8">
+        <v>34.49</v>
+      </c>
+      <c r="D87" s="8">
+        <v>-11.91</v>
+      </c>
+      <c r="E87" s="10">
+        <v>-46.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>342</v>
-      </c>
-      <c r="D58" s="6">
-        <v>341.85</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
+      <c r="B88" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="8">
+        <v>-34.3</v>
+      </c>
+      <c r="D88" s="8">
+        <v>165.76</v>
+      </c>
+      <c r="E88" s="9">
+        <v>200.06</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1302</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1283.4</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-18.6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
+      <c r="B89" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="8">
+        <v>-14.31</v>
+      </c>
+      <c r="D89" s="8">
+        <v>-51.35</v>
+      </c>
+      <c r="E89" s="10">
+        <v>-37.04</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>84.37</v>
-      </c>
-      <c r="D60" s="6">
-        <v>83.87</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>43.8</v>
-      </c>
-      <c r="D63" s="6">
-        <v>44.25</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>65.92</v>
-      </c>
-      <c r="D64" s="6">
-        <v>59.88</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-6.04</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>62.28</v>
-      </c>
-      <c r="D65" s="6">
-        <v>52.49</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-9.789999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>53.91</v>
-      </c>
-      <c r="D66" s="6">
-        <v>49.61</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>61.12</v>
-      </c>
-      <c r="D67" s="6">
-        <v>51.82</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-9.300000000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>54.48</v>
-      </c>
-      <c r="D68" s="6">
-        <v>56.22</v>
-      </c>
-      <c r="E68" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>60.29</v>
-      </c>
-      <c r="D69" s="6">
-        <v>60.18</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>59.59</v>
-      </c>
-      <c r="D70" s="6">
-        <v>53.28</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>71.63</v>
-      </c>
-      <c r="D71" s="6">
-        <v>70.66</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B90" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-71.89</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-66.98999999999999</v>
-      </c>
-      <c r="E72" s="7">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>42.94</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-40.85</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-83.79000000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-23.94</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-30.65</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-6.71</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-59.95</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-28.19</v>
-      </c>
-      <c r="E75" s="7">
-        <v>31.76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-6.84</v>
-      </c>
-      <c r="D76" s="6">
-        <v>10.46</v>
-      </c>
-      <c r="E76" s="7">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-34.97</v>
-      </c>
-      <c r="D77" s="6">
-        <v>34.49</v>
-      </c>
-      <c r="E77" s="7">
-        <v>69.45999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>18.99</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-34.3</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-53.29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-13.96</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-14.31</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-81.52</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C90" s="8">
         <v>-73.20999999999999</v>
       </c>
-      <c r="E80" s="7">
-        <v>8.31</v>
+      <c r="D90" s="8">
+        <v>-91.23999999999999</v>
+      </c>
+      <c r="E90" s="10">
+        <v>-18.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3441,61 +3746,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="13">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="14">
+        <v>9</v>
+      </c>
+      <c r="D2" s="13">
+        <v>56</v>
+      </c>
+      <c r="E2" s="13">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="12">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="F2" s="13">
+        <v>8.6</v>
+      </c>
+      <c r="G2" s="13">
+        <v>10.3</v>
+      </c>
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>7.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>10.2</v>
-      </c>
-      <c r="H2" s="11">
-        <v>55.4</v>
-      </c>
-      <c r="I2" s="11">
-        <v>30</v>
+      <c r="I2" s="13">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3596,61 +3901,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3722</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3506</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3143</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2139</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.204</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1238</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0391</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.08929999999999999</v>
+      <c r="A2" s="16">
+        <v>0.3708</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3458</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.3203</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.216</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1908</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1815</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1213</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.0454</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.08839999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,25 +193,16 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
     <t>Near 52W High</t>
   </si>
   <si>
-    <t>-2.7% → -1.3%</t>
+    <t>-6.0% → -1.3%</t>
   </si>
   <si>
     <t>🟢 BREAKOUT WATCH</t>
   </si>
   <si>
-    <t>-2.7%</t>
+    <t>-6.0%</t>
   </si>
   <si>
     <t>-1.3%</t>
@@ -220,85 +211,52 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.2 → 57.8</t>
+    <t>48.0 → 50.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>44.2</t>
-  </si>
-  <si>
-    <t>57.8</t>
-  </si>
-  <si>
-    <t>49.6 → 55.9</t>
-  </si>
-  <si>
-    <t>49.6</t>
-  </si>
-  <si>
-    <t>55.9</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>70.7 → 68.7</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>70.7</t>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>49.0 → 50.8</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.3% → -2.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-2.8%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>68.7 → 72.2</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>68.7</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-2.0% → -3.4%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-2.0%</t>
-  </si>
-  <si>
-    <t>-3.4%</t>
-  </si>
-  <si>
-    <t>51.8 → 49.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>56.2 → 48.0</t>
-  </si>
-  <si>
-    <t>56.2</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>53.3 → 49.0</t>
-  </si>
-  <si>
-    <t>53.3</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>72.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -350,7 +308,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,13 +356,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -438,6 +403,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -525,12 +496,12 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -539,7 +510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -897,8 +868,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -1037,10 +1008,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>666.55</v>
+        <v>651.5</v>
       </c>
       <c r="D2">
-        <v>5.89</v>
+        <v>-2.26</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -1049,46 +1020,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.85</v>
+        <v>-35.34</v>
       </c>
       <c r="H2">
-        <v>81.52</v>
+        <v>77.42</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="J2">
-        <v>-0.87</v>
+        <v>-3.57</v>
       </c>
       <c r="K2">
-        <v>-4.59</v>
+        <v>-6.84</v>
       </c>
       <c r="L2">
-        <v>22.63</v>
+        <v>23.29</v>
       </c>
       <c r="M2">
-        <v>-8.84</v>
+        <v>-9.16</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>635.46</v>
+        <v>639.21</v>
       </c>
       <c r="Q2">
-        <v>640.92</v>
+        <v>639.4299999999999</v>
       </c>
       <c r="R2">
         <v>657.1</v>
       </c>
       <c r="S2">
-        <v>615.41</v>
+        <v>615.87</v>
       </c>
       <c r="T2">
-        <v>8.31</v>
+        <v>5.79</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1103,34 +1074,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.78</v>
+        <v>52.23</v>
       </c>
       <c r="Z2">
-        <v>-6.55</v>
+        <v>-4.94</v>
       </c>
       <c r="AA2">
-        <v>-9.24</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AB2">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AC2">
-        <v>91.23999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="AD2">
-        <v>61.95</v>
+        <v>79.59</v>
       </c>
       <c r="AE2">
-        <v>23.35</v>
+        <v>24.54</v>
       </c>
       <c r="AF2">
-        <v>1703.29</v>
+        <v>44.64</v>
       </c>
       <c r="AG2">
-        <v>676.53</v>
+        <v>670.0599999999999</v>
       </c>
       <c r="AH2">
-        <v>605.3099999999999</v>
+        <v>608.8</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1139,7 +1110,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>23.85</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1150,10 +1121,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>269.55</v>
+        <v>264.4</v>
       </c>
       <c r="D3">
-        <v>-1.46</v>
+        <v>-1.91</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1162,25 +1133,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-3.4</v>
+        <v>-5.25</v>
       </c>
       <c r="H3">
-        <v>75.91</v>
+        <v>72.55</v>
       </c>
       <c r="I3">
-        <v>1.49</v>
+        <v>-0.32</v>
       </c>
       <c r="J3">
-        <v>4.13</v>
+        <v>3.46</v>
       </c>
       <c r="K3">
-        <v>16.42</v>
+        <v>16.48</v>
       </c>
       <c r="L3">
-        <v>32.29</v>
+        <v>27.16</v>
       </c>
       <c r="M3">
-        <v>34.58</v>
+        <v>34.18</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1189,19 +1160,19 @@
         <v>80</v>
       </c>
       <c r="P3">
-        <v>271.76</v>
+        <v>271.59</v>
       </c>
       <c r="Q3">
-        <v>263.6</v>
+        <v>263.42</v>
       </c>
       <c r="R3">
-        <v>258.49</v>
+        <v>258.76</v>
       </c>
       <c r="S3">
-        <v>205.63</v>
+        <v>206.05</v>
       </c>
       <c r="T3">
-        <v>31.09</v>
+        <v>28.32</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1216,34 +1187,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.87</v>
+        <v>51.12</v>
       </c>
       <c r="Z3">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="AA3">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB3">
-        <v>1.1</v>
+        <v>0.49</v>
       </c>
       <c r="AC3">
-        <v>75.83</v>
+        <v>53.6</v>
       </c>
       <c r="AD3">
-        <v>88.59</v>
+        <v>73.45</v>
       </c>
       <c r="AE3">
-        <v>8.77</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AF3">
-        <v>-47.71</v>
+        <v>-46.64</v>
       </c>
       <c r="AG3">
-        <v>277.89</v>
+        <v>277.56</v>
       </c>
       <c r="AH3">
-        <v>249.32</v>
+        <v>249.28</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1252,7 +1223,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>26.3</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1263,10 +1234,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1112</v>
+        <v>1099.9</v>
       </c>
       <c r="D4">
-        <v>1.55</v>
+        <v>-1.09</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1275,46 +1246,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-13.72</v>
+        <v>-14.66</v>
       </c>
       <c r="H4">
-        <v>17.57</v>
+        <v>16.29</v>
       </c>
       <c r="I4">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="J4">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="K4">
-        <v>-11.24</v>
+        <v>-10.72</v>
       </c>
       <c r="L4">
-        <v>13.01</v>
+        <v>10.26</v>
       </c>
       <c r="M4">
-        <v>21.6</v>
+        <v>21.33</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P4">
-        <v>1107.2</v>
+        <v>1106.98</v>
       </c>
       <c r="Q4">
-        <v>1076.85</v>
+        <v>1080.45</v>
       </c>
       <c r="R4">
-        <v>1088.92</v>
+        <v>1086.69</v>
       </c>
       <c r="S4">
-        <v>1122.17</v>
+        <v>1122.63</v>
       </c>
       <c r="T4">
-        <v>-0.91</v>
+        <v>-2.02</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1329,34 +1300,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>56.65</v>
+        <v>53.09</v>
       </c>
       <c r="Z4">
-        <v>9.9</v>
+        <v>9.33</v>
       </c>
       <c r="AA4">
-        <v>4.08</v>
+        <v>5.13</v>
       </c>
       <c r="AB4">
-        <v>5.83</v>
+        <v>4.21</v>
       </c>
       <c r="AC4">
-        <v>70.44</v>
+        <v>51.93</v>
       </c>
       <c r="AD4">
-        <v>72.45999999999999</v>
+        <v>64.33</v>
       </c>
       <c r="AE4">
-        <v>24.66</v>
+        <v>24.43</v>
       </c>
       <c r="AF4">
-        <v>-64.37</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="AG4">
-        <v>1146.65</v>
+        <v>1146.98</v>
       </c>
       <c r="AH4">
-        <v>1007.06</v>
+        <v>1013.92</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1365,7 +1336,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>33.4</v>
+        <v>31.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1376,10 +1347,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>737.9</v>
+        <v>735.4</v>
       </c>
       <c r="D5">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1388,46 +1359,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.65</v>
+        <v>-14.94</v>
       </c>
       <c r="H5">
-        <v>11.48</v>
+        <v>11.1</v>
       </c>
       <c r="I5">
-        <v>-0.89</v>
+        <v>0.4</v>
       </c>
       <c r="J5">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="K5">
-        <v>-1.44</v>
+        <v>-1.88</v>
       </c>
       <c r="L5">
-        <v>0.92</v>
+        <v>1.88</v>
       </c>
       <c r="M5">
-        <v>37.08</v>
+        <v>36.26</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>732.58</v>
+        <v>733.16</v>
       </c>
       <c r="Q5">
-        <v>732.87</v>
+        <v>732.77</v>
       </c>
       <c r="R5">
-        <v>710.85</v>
+        <v>711.9299999999999</v>
       </c>
       <c r="S5">
-        <v>751.95</v>
+        <v>751.62</v>
       </c>
       <c r="T5">
-        <v>-1.87</v>
+        <v>-2.16</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1442,34 +1413,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>55.94</v>
+        <v>54.5</v>
       </c>
       <c r="Z5">
-        <v>5.37</v>
+        <v>5.21</v>
       </c>
       <c r="AA5">
-        <v>6.22</v>
+        <v>6.02</v>
       </c>
       <c r="AB5">
-        <v>-0.85</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AC5">
-        <v>33.85</v>
+        <v>34.95</v>
       </c>
       <c r="AD5">
-        <v>35.58</v>
+        <v>33.1</v>
       </c>
       <c r="AE5">
-        <v>17.58</v>
+        <v>17.04</v>
       </c>
       <c r="AF5">
-        <v>9.390000000000001</v>
+        <v>-59.57</v>
       </c>
       <c r="AG5">
-        <v>746.66</v>
+        <v>746.4400000000001</v>
       </c>
       <c r="AH5">
-        <v>719.08</v>
+        <v>719.09</v>
       </c>
       <c r="AI5">
         <v>690.96</v>
@@ -1478,7 +1449,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.81</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1489,10 +1460,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>558.75</v>
+        <v>558.6</v>
       </c>
       <c r="D6">
-        <v>-0.75</v>
+        <v>-0.03</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1501,46 +1472,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-6.88</v>
+        <v>-6.9</v>
       </c>
       <c r="H6">
-        <v>27.41</v>
+        <v>27.37</v>
       </c>
       <c r="I6">
-        <v>-1.28</v>
+        <v>-0.52</v>
       </c>
       <c r="J6">
-        <v>0.27</v>
+        <v>1.58</v>
       </c>
       <c r="K6">
-        <v>9.33</v>
+        <v>8.83</v>
       </c>
       <c r="L6">
-        <v>4.98</v>
+        <v>5.18</v>
       </c>
       <c r="M6">
-        <v>19.08</v>
+        <v>19.04</v>
       </c>
       <c r="N6">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O6">
         <v>62</v>
       </c>
       <c r="P6">
-        <v>565.13</v>
+        <v>564.55</v>
       </c>
       <c r="Q6">
-        <v>557.79</v>
+        <v>558.55</v>
       </c>
       <c r="R6">
-        <v>561.91</v>
+        <v>561.52</v>
       </c>
       <c r="S6">
-        <v>518.8200000000001</v>
+        <v>518.97</v>
       </c>
       <c r="T6">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1555,34 +1526,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>49.52</v>
+        <v>49.44</v>
       </c>
       <c r="Z6">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AA6">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="AB6">
-        <v>1.24</v>
+        <v>0.68</v>
       </c>
       <c r="AC6">
-        <v>61.34</v>
+        <v>39.73</v>
       </c>
       <c r="AD6">
-        <v>72.67</v>
+        <v>58.82</v>
       </c>
       <c r="AE6">
-        <v>13.02</v>
+        <v>12.91</v>
       </c>
       <c r="AF6">
-        <v>-32.45</v>
+        <v>-12.96</v>
       </c>
       <c r="AG6">
-        <v>578.8099999999999</v>
+        <v>578.45</v>
       </c>
       <c r="AH6">
-        <v>536.77</v>
+        <v>538.65</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1591,7 +1562,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.79</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1602,10 +1573,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11572</v>
+        <v>11670</v>
       </c>
       <c r="D7">
-        <v>-3.09</v>
+        <v>0.85</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1614,46 +1585,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.79</v>
+        <v>-47.35</v>
       </c>
       <c r="H7">
-        <v>8.609999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I7">
-        <v>-6.12</v>
+        <v>-3.41</v>
       </c>
       <c r="J7">
-        <v>3.21</v>
+        <v>4.52</v>
       </c>
       <c r="K7">
-        <v>-7.3</v>
+        <v>-5.74</v>
       </c>
       <c r="L7">
-        <v>-38.89</v>
+        <v>-35.9</v>
       </c>
       <c r="M7">
-        <v>18.15</v>
+        <v>18.17</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>11894.4</v>
+        <v>11812</v>
       </c>
       <c r="Q7">
-        <v>11411.55</v>
+        <v>11435.2</v>
       </c>
       <c r="R7">
-        <v>11834.82</v>
+        <v>11819.76</v>
       </c>
       <c r="S7">
-        <v>15235.42</v>
+        <v>15208.26</v>
       </c>
       <c r="T7">
-        <v>-24.05</v>
+        <v>-23.27</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1668,34 +1639,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.05</v>
+        <v>50.13</v>
       </c>
       <c r="Z7">
-        <v>64.28</v>
+        <v>55.23</v>
       </c>
       <c r="AA7">
-        <v>-21.97</v>
+        <v>-6.53</v>
       </c>
       <c r="AB7">
-        <v>86.26000000000001</v>
+        <v>61.76</v>
       </c>
       <c r="AC7">
-        <v>62.58</v>
+        <v>53.93</v>
       </c>
       <c r="AD7">
-        <v>71.77</v>
+        <v>63.75</v>
       </c>
       <c r="AE7">
-        <v>378.44</v>
+        <v>368.41</v>
       </c>
       <c r="AF7">
-        <v>-11.91</v>
+        <v>-16.11</v>
       </c>
       <c r="AG7">
-        <v>12464.29</v>
+        <v>12488.9</v>
       </c>
       <c r="AH7">
-        <v>10358.81</v>
+        <v>10381.5</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1704,7 +1675,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.82</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1715,10 +1686,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>346.6</v>
+        <v>341.35</v>
       </c>
       <c r="D8">
-        <v>1.39</v>
+        <v>-1.51</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1727,46 +1698,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.31</v>
+        <v>-2.8</v>
       </c>
       <c r="H8">
-        <v>47.92</v>
+        <v>45.68</v>
       </c>
       <c r="I8">
-        <v>3.65</v>
+        <v>4.23</v>
       </c>
       <c r="J8">
-        <v>-0.19</v>
+        <v>1.19</v>
       </c>
       <c r="K8">
-        <v>29.55</v>
+        <v>27.8</v>
       </c>
       <c r="L8">
-        <v>15.38</v>
+        <v>12.81</v>
       </c>
       <c r="M8">
-        <v>32.03</v>
+        <v>31.29</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P8">
-        <v>338.74</v>
+        <v>341.51</v>
       </c>
       <c r="Q8">
-        <v>331.3</v>
+        <v>331.4</v>
       </c>
       <c r="R8">
-        <v>318.3</v>
+        <v>319.72</v>
       </c>
       <c r="S8">
-        <v>281.45</v>
+        <v>281.69</v>
       </c>
       <c r="T8">
-        <v>23.15</v>
+        <v>21.18</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1781,34 +1752,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>62.64</v>
+        <v>58.34</v>
       </c>
       <c r="Z8">
-        <v>5.3</v>
+        <v>5.47</v>
       </c>
       <c r="AA8">
-        <v>4.07</v>
+        <v>4.35</v>
       </c>
       <c r="AB8">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AC8">
-        <v>99.77</v>
+        <v>92.44</v>
       </c>
       <c r="AD8">
-        <v>86.34</v>
+        <v>93.92</v>
       </c>
       <c r="AE8">
-        <v>11.14</v>
+        <v>11.2</v>
       </c>
       <c r="AF8">
-        <v>165.76</v>
+        <v>-27.82</v>
       </c>
       <c r="AG8">
-        <v>353.18</v>
+        <v>353.46</v>
       </c>
       <c r="AH8">
-        <v>309.42</v>
+        <v>309.35</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1817,7 +1788,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>29.01</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1828,10 +1799,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1269.1</v>
+        <v>1275</v>
       </c>
       <c r="D9">
-        <v>-1.11</v>
+        <v>0.46</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1840,25 +1811,25 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-4.58</v>
+        <v>-4.14</v>
       </c>
       <c r="H9">
-        <v>23.62</v>
+        <v>24.2</v>
       </c>
       <c r="I9">
-        <v>-4.58</v>
+        <v>-2.52</v>
       </c>
       <c r="J9">
-        <v>1.72</v>
+        <v>3.92</v>
       </c>
       <c r="K9">
-        <v>-2.14</v>
+        <v>-0.3</v>
       </c>
       <c r="L9">
-        <v>20.57</v>
+        <v>19.74</v>
       </c>
       <c r="M9">
-        <v>12.13</v>
+        <v>12.23</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1867,19 +1838,19 @@
         <v>66</v>
       </c>
       <c r="P9">
-        <v>1292.38</v>
+        <v>1285.8</v>
       </c>
       <c r="Q9">
-        <v>1271.52</v>
+        <v>1274.22</v>
       </c>
       <c r="R9">
-        <v>1262.96</v>
+        <v>1262.2</v>
       </c>
       <c r="S9">
-        <v>1214.81</v>
+        <v>1215.48</v>
       </c>
       <c r="T9">
-        <v>4.47</v>
+        <v>4.9</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1894,34 +1865,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>48.99</v>
+        <v>50.76</v>
       </c>
       <c r="Z9">
-        <v>11.12</v>
+        <v>9.57</v>
       </c>
       <c r="AA9">
-        <v>10.31</v>
+        <v>10.16</v>
       </c>
       <c r="AB9">
-        <v>0.8100000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="AC9">
+        <v>14.16</v>
+      </c>
+      <c r="AD9">
         <v>28.71</v>
       </c>
-      <c r="AD9">
-        <v>42.56</v>
-      </c>
       <c r="AE9">
-        <v>25.9</v>
+        <v>24.89</v>
       </c>
       <c r="AF9">
-        <v>-51.35</v>
+        <v>-4.03</v>
       </c>
       <c r="AG9">
-        <v>1327.21</v>
+        <v>1324.57</v>
       </c>
       <c r="AH9">
-        <v>1215.82</v>
+        <v>1223.86</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1930,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>37.65</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1941,10 +1912,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>82.90000000000001</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="D10">
-        <v>-1.16</v>
+        <v>4.99</v>
       </c>
       <c r="E10">
         <v>88.17</v>
@@ -1953,46 +1924,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-5.98</v>
+        <v>-1.28</v>
       </c>
       <c r="H10">
-        <v>129.77</v>
+        <v>141.24</v>
       </c>
       <c r="I10">
-        <v>-3.82</v>
+        <v>-1.28</v>
       </c>
       <c r="J10">
-        <v>59.73</v>
+        <v>70.83</v>
       </c>
       <c r="K10">
-        <v>64.34999999999999</v>
+        <v>73.66</v>
       </c>
       <c r="L10">
-        <v>8.109999999999999</v>
+        <v>14.72</v>
       </c>
       <c r="M10">
-        <v>-4.54</v>
+        <v>-3.01</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P10">
-        <v>84.76000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="Q10">
-        <v>71.95</v>
+        <v>73.78</v>
       </c>
       <c r="R10">
-        <v>59.79</v>
+        <v>60.56</v>
       </c>
       <c r="S10">
-        <v>59.2</v>
+        <v>59.24</v>
       </c>
       <c r="T10">
-        <v>40.05</v>
+        <v>46.94</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -2007,43 +1978,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>68.73</v>
+        <v>72.22</v>
       </c>
       <c r="Z10">
-        <v>7.92</v>
+        <v>7.99</v>
       </c>
       <c r="AA10">
-        <v>7.03</v>
+        <v>7.22</v>
       </c>
       <c r="AB10">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="AC10">
-        <v>49.69</v>
+        <v>50.89</v>
       </c>
       <c r="AD10">
-        <v>59.19</v>
+        <v>52.15</v>
       </c>
       <c r="AE10">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
       <c r="AF10">
-        <v>-91.23999999999999</v>
+        <v>-81.23999999999999</v>
       </c>
       <c r="AG10">
-        <v>95.3</v>
+        <v>95.72</v>
       </c>
       <c r="AH10">
-        <v>48.6</v>
+        <v>51.84</v>
       </c>
       <c r="AI10">
-        <v>71.40000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>52.39</v>
+        <v>52.52</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2236,44 +2207,44 @@
         <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>68</v>
@@ -2283,1450 +2254,1333 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-0.87</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-3.57</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4.13</v>
+      </c>
+      <c r="D12" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>6.91</v>
+      </c>
+      <c r="D13" s="8">
+        <v>5.54</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.23</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.54</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>97</v>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.58</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.31</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="8">
-        <v>-8.449999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="D16" s="8">
-        <v>-0.87</v>
-      </c>
-      <c r="E16" s="9">
-        <v>7.58</v>
+        <v>4.52</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <v>1.84</v>
+        <v>-0.19</v>
       </c>
       <c r="D17" s="8">
-        <v>4.13</v>
-      </c>
-      <c r="E17" s="9">
-        <v>2.29</v>
+        <v>1.19</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="8">
-        <v>6.43</v>
+        <v>1.72</v>
       </c>
       <c r="D18" s="8">
-        <v>6.91</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.48</v>
+        <v>3.92</v>
+      </c>
+      <c r="E18" s="10">
+        <v>2.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="8">
-        <v>3.09</v>
+        <v>59.73</v>
       </c>
       <c r="D19" s="8">
-        <v>2.23</v>
+        <v>70.83</v>
       </c>
       <c r="E19" s="10">
-        <v>-0.86</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="8">
-        <v>1.69</v>
+        <v>6.4</v>
       </c>
       <c r="D20" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-1.42</v>
+        <v>2.96</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="8">
-        <v>4.56</v>
+        <v>1.49</v>
       </c>
       <c r="D21" s="8">
-        <v>3.21</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-1.35</v>
+        <v>-0.32</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="8">
-        <v>-2.66</v>
+        <v>-0.13</v>
       </c>
       <c r="D22" s="8">
-        <v>-0.19</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.47</v>
+        <v>-0.1</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0.03</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="8">
-        <v>3.72</v>
+        <v>-0.89</v>
       </c>
       <c r="D23" s="8">
-        <v>1.72</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="10">
-        <v>-2</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="8">
-        <v>58.39</v>
+        <v>-1.28</v>
       </c>
       <c r="D24" s="8">
-        <v>59.73</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.34</v>
+        <v>-0.52</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.76</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="8">
-        <v>0.75</v>
+        <v>-6.12</v>
       </c>
       <c r="D25" s="8">
-        <v>6.4</v>
-      </c>
-      <c r="E25" s="9">
-        <v>5.65</v>
+        <v>-3.41</v>
+      </c>
+      <c r="E25" s="10">
+        <v>2.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="8">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="D26" s="8">
-        <v>1.49</v>
+        <v>4.23</v>
       </c>
       <c r="E26" s="10">
-        <v>-1.97</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="8">
-        <v>-2.58</v>
+        <v>-4.58</v>
       </c>
       <c r="D27" s="8">
-        <v>-0.13</v>
-      </c>
-      <c r="E27" s="9">
-        <v>2.45</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E27" s="10">
+        <v>2.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="8">
-        <v>-1.43</v>
+        <v>-3.82</v>
       </c>
       <c r="D28" s="8">
-        <v>-0.89</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.54</v>
+        <v>-1.28</v>
+      </c>
+      <c r="E28" s="10">
+        <v>2.54</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C29" s="8">
-        <v>-0.88</v>
+        <v>22.63</v>
       </c>
       <c r="D29" s="8">
-        <v>-1.28</v>
+        <v>23.29</v>
       </c>
       <c r="E29" s="10">
-        <v>-0.4</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C30" s="8">
-        <v>-1.92</v>
+        <v>32.29</v>
       </c>
       <c r="D30" s="8">
-        <v>-6.12</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-4.2</v>
+        <v>27.16</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-5.13</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C31" s="8">
-        <v>3.83</v>
+        <v>13.01</v>
       </c>
       <c r="D31" s="8">
-        <v>3.65</v>
-      </c>
-      <c r="E31" s="10">
-        <v>-0.18</v>
+        <v>10.26</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C32" s="8">
-        <v>-1.28</v>
+        <v>0.92</v>
       </c>
       <c r="D32" s="8">
-        <v>-4.58</v>
+        <v>1.88</v>
       </c>
       <c r="E32" s="10">
-        <v>-3.3</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C33" s="8">
-        <v>1.61</v>
+        <v>4.98</v>
       </c>
       <c r="D33" s="8">
-        <v>-3.82</v>
+        <v>5.18</v>
       </c>
       <c r="E33" s="10">
-        <v>-5.43</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="8">
-        <v>14.1</v>
+        <v>-38.89</v>
       </c>
       <c r="D34" s="8">
-        <v>22.63</v>
-      </c>
-      <c r="E34" s="9">
-        <v>8.529999999999999</v>
+        <v>-35.9</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="8">
-        <v>30.57</v>
+        <v>15.38</v>
       </c>
       <c r="D35" s="8">
-        <v>32.29</v>
+        <v>12.81</v>
       </c>
       <c r="E35" s="9">
-        <v>1.72</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="8">
-        <v>9.74</v>
+        <v>20.57</v>
       </c>
       <c r="D36" s="8">
-        <v>13.01</v>
+        <v>19.74</v>
       </c>
       <c r="E36" s="9">
-        <v>3.27</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="8">
-        <v>0.31</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D37" s="8">
-        <v>0.92</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.61</v>
+        <v>14.72</v>
+      </c>
+      <c r="E37" s="10">
+        <v>6.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="8">
-        <v>5.06</v>
+        <v>-4.59</v>
       </c>
       <c r="D38" s="8">
-        <v>4.98</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-0.08</v>
+        <v>-6.84</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="8">
-        <v>-37.27</v>
+        <v>16.42</v>
       </c>
       <c r="D39" s="8">
-        <v>-38.89</v>
+        <v>16.48</v>
       </c>
       <c r="E39" s="10">
-        <v>-1.62</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" s="8">
-        <v>12.1</v>
+        <v>-11.24</v>
       </c>
       <c r="D40" s="8">
-        <v>15.38</v>
-      </c>
-      <c r="E40" s="9">
-        <v>3.28</v>
+        <v>-10.72</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" s="8">
-        <v>21.83</v>
+        <v>-1.44</v>
       </c>
       <c r="D41" s="8">
-        <v>20.57</v>
-      </c>
-      <c r="E41" s="10">
-        <v>-1.26</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42" s="8">
-        <v>7.14</v>
+        <v>9.33</v>
       </c>
       <c r="D42" s="8">
-        <v>8.109999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="E42" s="9">
-        <v>0.97</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="8">
-        <v>-10.26</v>
+        <v>-7.3</v>
       </c>
       <c r="D43" s="8">
-        <v>-4.59</v>
-      </c>
-      <c r="E43" s="9">
-        <v>5.67</v>
+        <v>-5.74</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1.56</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="8">
-        <v>18.06</v>
+        <v>29.55</v>
       </c>
       <c r="D44" s="8">
-        <v>16.42</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-1.64</v>
+        <v>27.8</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="8">
-        <v>-11.9</v>
+        <v>-2.14</v>
       </c>
       <c r="D45" s="8">
-        <v>-11.24</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.66</v>
+        <v>-0.3</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1.84</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="8">
-        <v>-0.02</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="D46" s="8">
-        <v>-1.44</v>
+        <v>73.66</v>
       </c>
       <c r="E46" s="10">
-        <v>-1.42</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C47" s="8">
-        <v>10.94</v>
+        <v>-33.85</v>
       </c>
       <c r="D47" s="8">
-        <v>9.33</v>
-      </c>
-      <c r="E47" s="10">
-        <v>-1.61</v>
+        <v>-35.34</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C48" s="8">
-        <v>-4.49</v>
+        <v>-3.4</v>
       </c>
       <c r="D48" s="8">
-        <v>-7.3</v>
-      </c>
-      <c r="E48" s="10">
-        <v>-2.81</v>
+        <v>-5.25</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C49" s="8">
-        <v>27.58</v>
+        <v>-13.72</v>
       </c>
       <c r="D49" s="8">
-        <v>29.55</v>
+        <v>-14.66</v>
       </c>
       <c r="E49" s="9">
-        <v>1.97</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C50" s="8">
-        <v>0.67</v>
+        <v>-14.65</v>
       </c>
       <c r="D50" s="8">
-        <v>-2.14</v>
-      </c>
-      <c r="E50" s="10">
-        <v>-2.81</v>
+        <v>-14.94</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C51" s="8">
-        <v>61.66</v>
+        <v>-6.88</v>
       </c>
       <c r="D51" s="8">
-        <v>64.34999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="E51" s="9">
-        <v>2.69</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="8">
-        <v>-37.52</v>
+        <v>-47.79</v>
       </c>
       <c r="D52" s="8">
-        <v>-33.85</v>
-      </c>
-      <c r="E52" s="9">
-        <v>3.67</v>
+        <v>-47.35</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.44</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="8">
-        <v>-1.97</v>
+        <v>-1.31</v>
       </c>
       <c r="D53" s="8">
-        <v>-3.4</v>
-      </c>
-      <c r="E53" s="10">
-        <v>-1.43</v>
+        <v>-2.8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C54" s="8">
-        <v>-15.04</v>
+        <v>-4.58</v>
       </c>
       <c r="D54" s="8">
-        <v>-13.72</v>
-      </c>
-      <c r="E54" s="9">
-        <v>1.32</v>
+        <v>-4.14</v>
+      </c>
+      <c r="E54" s="10">
+        <v>0.44</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="8">
-        <v>-16.13</v>
+        <v>-5.98</v>
       </c>
       <c r="D55" s="8">
-        <v>-14.65</v>
-      </c>
-      <c r="E55" s="9">
-        <v>1.48</v>
+        <v>-1.28</v>
+      </c>
+      <c r="E55" s="10">
+        <v>4.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C56" s="8">
-        <v>-6.17</v>
+        <v>666.55</v>
       </c>
       <c r="D56" s="8">
-        <v>-6.88</v>
-      </c>
-      <c r="E56" s="10">
-        <v>-0.71</v>
+        <v>651.5</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-15.05</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C57" s="8">
-        <v>-46.13</v>
+        <v>269.55</v>
       </c>
       <c r="D57" s="8">
-        <v>-47.79</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-1.66</v>
+        <v>264.4</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-5.15</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C58" s="8">
-        <v>-2.66</v>
+        <v>1112</v>
       </c>
       <c r="D58" s="8">
-        <v>-1.31</v>
+        <v>1099.9</v>
       </c>
       <c r="E58" s="9">
-        <v>1.35</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C59" s="8">
-        <v>-3.5</v>
+        <v>737.9</v>
       </c>
       <c r="D59" s="8">
-        <v>-4.58</v>
-      </c>
-      <c r="E59" s="10">
-        <v>-1.08</v>
+        <v>735.4</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C60" s="8">
-        <v>-4.88</v>
+        <v>558.75</v>
       </c>
       <c r="D60" s="8">
-        <v>-5.98</v>
-      </c>
-      <c r="E60" s="10">
-        <v>-1.1</v>
+        <v>558.6</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="8">
-        <v>629.5</v>
+        <v>11572</v>
       </c>
       <c r="D61" s="8">
-        <v>666.55</v>
-      </c>
-      <c r="E61" s="9">
-        <v>37.05</v>
+        <v>11670</v>
+      </c>
+      <c r="E61" s="10">
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C62" s="8">
-        <v>273.55</v>
+        <v>346.6</v>
       </c>
       <c r="D62" s="8">
-        <v>269.55</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-4</v>
+        <v>341.35</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-5.25</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C63" s="8">
-        <v>1095</v>
+        <v>1269.1</v>
       </c>
       <c r="D63" s="8">
-        <v>1112</v>
-      </c>
-      <c r="E63" s="9">
-        <v>17</v>
+        <v>1275</v>
+      </c>
+      <c r="E63" s="10">
+        <v>5.9</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C64" s="8">
-        <v>725.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D64" s="8">
-        <v>737.9</v>
-      </c>
-      <c r="E64" s="9">
-        <v>12.8</v>
+        <v>87.04000000000001</v>
+      </c>
+      <c r="E64" s="10">
+        <v>4.14</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C65" s="8">
-        <v>563</v>
+        <v>55</v>
       </c>
       <c r="D65" s="8">
-        <v>558.75</v>
-      </c>
-      <c r="E65" s="10">
-        <v>-4.25</v>
+        <v>45</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-10</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C66" s="8">
-        <v>11941</v>
+        <v>45</v>
       </c>
       <c r="D66" s="8">
-        <v>11572</v>
+        <v>55</v>
       </c>
       <c r="E66" s="10">
-        <v>-369</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C67" s="8">
-        <v>341.85</v>
+        <v>57.78</v>
       </c>
       <c r="D67" s="8">
-        <v>346.6</v>
+        <v>52.23</v>
       </c>
       <c r="E67" s="9">
-        <v>4.75</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C68" s="8">
-        <v>1283.4</v>
+        <v>55.87</v>
       </c>
       <c r="D68" s="8">
-        <v>1269.1</v>
-      </c>
-      <c r="E68" s="10">
-        <v>-14.3</v>
+        <v>51.12</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C69" s="8">
-        <v>83.87</v>
+        <v>56.65</v>
       </c>
       <c r="D69" s="8">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="E69" s="10">
-        <v>-0.97</v>
+        <v>53.09</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C70" s="8">
-        <v>23</v>
+        <v>55.94</v>
       </c>
       <c r="D70" s="8">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="E70" s="9">
-        <v>32</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C71" s="8">
-        <v>45</v>
+        <v>49.52</v>
       </c>
       <c r="D71" s="8">
-        <v>23</v>
-      </c>
-      <c r="E71" s="10">
-        <v>-22</v>
+        <v>49.44</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C72" s="8">
-        <v>55</v>
+        <v>48.05</v>
       </c>
       <c r="D72" s="8">
-        <v>45</v>
+        <v>50.13</v>
       </c>
       <c r="E72" s="10">
-        <v>-10</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="8">
-        <v>44.25</v>
+        <v>62.64</v>
       </c>
       <c r="D73" s="8">
-        <v>57.78</v>
+        <v>58.34</v>
       </c>
       <c r="E73" s="9">
-        <v>13.53</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="8">
-        <v>59.88</v>
+        <v>48.99</v>
       </c>
       <c r="D74" s="8">
-        <v>55.87</v>
+        <v>50.76</v>
       </c>
       <c r="E74" s="10">
-        <v>-4.01</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="8">
-        <v>52.49</v>
+        <v>68.73</v>
       </c>
       <c r="D75" s="8">
-        <v>56.65</v>
-      </c>
-      <c r="E75" s="9">
-        <v>4.16</v>
+        <v>72.22</v>
+      </c>
+      <c r="E75" s="10">
+        <v>3.49</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C76" s="8">
-        <v>49.61</v>
+        <v>1703.29</v>
       </c>
       <c r="D76" s="8">
-        <v>55.94</v>
+        <v>44.64</v>
       </c>
       <c r="E76" s="9">
-        <v>6.33</v>
+        <v>-1658.65</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C77" s="8">
-        <v>51.82</v>
+        <v>-47.71</v>
       </c>
       <c r="D77" s="8">
-        <v>49.52</v>
+        <v>-46.64</v>
       </c>
       <c r="E77" s="10">
-        <v>-2.3</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C78" s="8">
-        <v>56.22</v>
+        <v>-64.37</v>
       </c>
       <c r="D78" s="8">
-        <v>48.05</v>
-      </c>
-      <c r="E78" s="10">
-        <v>-8.17</v>
+        <v>-71.76000000000001</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-7.39</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C79" s="8">
-        <v>60.18</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D79" s="8">
-        <v>62.64</v>
+        <v>-59.57</v>
       </c>
       <c r="E79" s="9">
-        <v>2.46</v>
+        <v>-68.95999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C80" s="8">
-        <v>53.28</v>
+        <v>-32.45</v>
       </c>
       <c r="D80" s="8">
-        <v>48.99</v>
+        <v>-12.96</v>
       </c>
       <c r="E80" s="10">
-        <v>-4.29</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C81" s="8">
-        <v>70.66</v>
+        <v>-11.91</v>
       </c>
       <c r="D81" s="8">
-        <v>68.73</v>
-      </c>
-      <c r="E81" s="10">
-        <v>-1.93</v>
+        <v>-16.11</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-4.2</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="8">
-        <v>-66.98999999999999</v>
+        <v>165.76</v>
       </c>
       <c r="D82" s="8">
-        <v>1703.29</v>
+        <v>-27.82</v>
       </c>
       <c r="E82" s="9">
-        <v>1770.28</v>
+        <v>-193.58</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C83" s="8">
-        <v>-40.85</v>
+        <v>-51.35</v>
       </c>
       <c r="D83" s="8">
-        <v>-47.71</v>
+        <v>-4.03</v>
       </c>
       <c r="E83" s="10">
-        <v>-6.86</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C84" s="8">
-        <v>-30.65</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="D84" s="8">
-        <v>-64.37</v>
+        <v>-81.23999999999999</v>
       </c>
       <c r="E84" s="10">
-        <v>-33.72</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="8">
-        <v>-28.19</v>
-      </c>
-      <c r="D85" s="8">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="E85" s="9">
-        <v>37.58</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="8">
-        <v>10.46</v>
-      </c>
-      <c r="D86" s="8">
-        <v>-32.45</v>
-      </c>
-      <c r="E86" s="10">
-        <v>-42.91</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C87" s="8">
-        <v>34.49</v>
-      </c>
-      <c r="D87" s="8">
-        <v>-11.91</v>
-      </c>
-      <c r="E87" s="10">
-        <v>-46.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88" s="8">
-        <v>-34.3</v>
-      </c>
-      <c r="D88" s="8">
-        <v>165.76</v>
-      </c>
-      <c r="E88" s="9">
-        <v>200.06</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C89" s="8">
-        <v>-14.31</v>
-      </c>
-      <c r="D89" s="8">
-        <v>-51.35</v>
-      </c>
-      <c r="E89" s="10">
-        <v>-37.04</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C90" s="8">
-        <v>-73.20999999999999</v>
-      </c>
-      <c r="D90" s="8">
-        <v>-91.23999999999999</v>
-      </c>
-      <c r="E90" s="10">
-        <v>-18.03</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3750,28 +3604,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3785,16 +3639,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="13">
-        <v>56</v>
+        <v>54.6</v>
       </c>
       <c r="E2" s="13">
         <v>70</v>
       </c>
       <c r="F2" s="13">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="G2" s="13">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="H2" s="13">
         <v>55.4</v>
@@ -3931,31 +3785,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="16">
-        <v>0.3708</v>
+        <v>0.3626</v>
       </c>
       <c r="B2" s="16">
-        <v>0.3458</v>
+        <v>0.3418</v>
       </c>
       <c r="C2" s="16">
-        <v>0.3203</v>
+        <v>0.3129</v>
       </c>
       <c r="D2" s="16">
-        <v>0.216</v>
+        <v>0.2133</v>
       </c>
       <c r="E2" s="16">
-        <v>0.1908</v>
+        <v>0.1904</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1815</v>
+        <v>0.1817</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1213</v>
+        <v>0.1223</v>
       </c>
       <c r="H2" s="16">
-        <v>-0.0454</v>
+        <v>-0.0301</v>
       </c>
       <c r="I2" s="16">
-        <v>-0.08839999999999999</v>
+        <v>-0.0916</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,70 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-6.0% → -1.3%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-6.0%</t>
-  </si>
-  <si>
-    <t>-1.3%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.0 → 50.1</t>
+    <t>49.4 → 50.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>49.0 → 50.8</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>52.2 → 47.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>50.8 → 49.2</t>
   </si>
   <si>
     <t>50.8</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.3% → -2.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-2.8%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.7 → 72.2</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.7</t>
-  </si>
-  <si>
-    <t>72.2</t>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -308,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,27 +319,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,18 +353,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -493,15 +437,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -510,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -868,8 +811,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -1008,10 +951,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>651.5</v>
+        <v>636.3</v>
       </c>
       <c r="D2">
-        <v>-2.26</v>
+        <v>-2.33</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -1020,46 +963,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.34</v>
+        <v>-36.85</v>
       </c>
       <c r="H2">
-        <v>77.42</v>
+        <v>73.28</v>
       </c>
       <c r="I2">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="J2">
-        <v>-3.57</v>
+        <v>-6.61</v>
       </c>
       <c r="K2">
-        <v>-6.84</v>
+        <v>-7.66</v>
       </c>
       <c r="L2">
-        <v>23.29</v>
+        <v>21.03</v>
       </c>
       <c r="M2">
-        <v>-9.16</v>
+        <v>-8.65</v>
       </c>
       <c r="N2">
         <v>45</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>639.21</v>
+        <v>642.47</v>
       </c>
       <c r="Q2">
-        <v>639.4299999999999</v>
+        <v>638.29</v>
       </c>
       <c r="R2">
-        <v>657.1</v>
+        <v>656.63</v>
       </c>
       <c r="S2">
-        <v>615.87</v>
+        <v>616.25</v>
       </c>
       <c r="T2">
-        <v>5.79</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1074,34 +1017,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.23</v>
+        <v>47.3</v>
       </c>
       <c r="Z2">
-        <v>-4.94</v>
+        <v>-4.83</v>
       </c>
       <c r="AA2">
-        <v>-8.380000000000001</v>
+        <v>-7.67</v>
       </c>
       <c r="AB2">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="AC2">
-        <v>89.62</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="AD2">
-        <v>79.59</v>
+        <v>83.62</v>
       </c>
       <c r="AE2">
-        <v>24.54</v>
+        <v>24.41</v>
       </c>
       <c r="AF2">
-        <v>44.64</v>
+        <v>-17.1</v>
       </c>
       <c r="AG2">
-        <v>670.0599999999999</v>
+        <v>667.51</v>
       </c>
       <c r="AH2">
-        <v>608.8</v>
+        <v>609.0700000000001</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1110,7 +1053,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.44</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1121,10 +1064,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>264.4</v>
+        <v>267.1</v>
       </c>
       <c r="D3">
-        <v>-1.91</v>
+        <v>1.02</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1133,25 +1076,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-5.25</v>
+        <v>-4.28</v>
       </c>
       <c r="H3">
-        <v>72.55</v>
+        <v>74.31</v>
       </c>
       <c r="I3">
-        <v>-0.32</v>
+        <v>-1.58</v>
       </c>
       <c r="J3">
-        <v>3.46</v>
+        <v>-0.35</v>
       </c>
       <c r="K3">
-        <v>16.48</v>
+        <v>22.11</v>
       </c>
       <c r="L3">
-        <v>27.16</v>
+        <v>30.53</v>
       </c>
       <c r="M3">
-        <v>34.18</v>
+        <v>35.16</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1160,19 +1103,19 @@
         <v>80</v>
       </c>
       <c r="P3">
-        <v>271.59</v>
+        <v>270.73</v>
       </c>
       <c r="Q3">
-        <v>263.42</v>
+        <v>263.3</v>
       </c>
       <c r="R3">
-        <v>258.76</v>
+        <v>258.9</v>
       </c>
       <c r="S3">
-        <v>206.05</v>
+        <v>206.5</v>
       </c>
       <c r="T3">
-        <v>28.32</v>
+        <v>29.34</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1187,34 +1130,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>51.12</v>
+        <v>53.36</v>
       </c>
       <c r="Z3">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA3">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB3">
-        <v>0.49</v>
+        <v>0.23</v>
       </c>
       <c r="AC3">
-        <v>53.6</v>
+        <v>40.89</v>
       </c>
       <c r="AD3">
-        <v>73.45</v>
+        <v>56.77</v>
       </c>
       <c r="AE3">
-        <v>8.640000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AF3">
-        <v>-46.64</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="AG3">
-        <v>277.56</v>
+        <v>277.27</v>
       </c>
       <c r="AH3">
-        <v>249.28</v>
+        <v>249.34</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1223,7 +1166,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>23.42</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1234,10 +1177,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1099.9</v>
+        <v>1091.5</v>
       </c>
       <c r="D4">
-        <v>-1.09</v>
+        <v>-0.76</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1246,46 +1189,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-14.66</v>
+        <v>-15.31</v>
       </c>
       <c r="H4">
-        <v>16.29</v>
+        <v>15.4</v>
       </c>
       <c r="I4">
-        <v>-0.1</v>
+        <v>-1.04</v>
       </c>
       <c r="J4">
-        <v>5.54</v>
+        <v>6.18</v>
       </c>
       <c r="K4">
-        <v>-10.72</v>
+        <v>-11.39</v>
       </c>
       <c r="L4">
-        <v>10.26</v>
+        <v>12.27</v>
       </c>
       <c r="M4">
-        <v>21.33</v>
+        <v>20.83</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O4">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>1106.98</v>
+        <v>1104.68</v>
       </c>
       <c r="Q4">
-        <v>1080.45</v>
+        <v>1083.78</v>
       </c>
       <c r="R4">
-        <v>1086.69</v>
+        <v>1084.58</v>
       </c>
       <c r="S4">
-        <v>1122.63</v>
+        <v>1122.91</v>
       </c>
       <c r="T4">
-        <v>-2.02</v>
+        <v>-2.8</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1300,34 +1243,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>53.09</v>
+        <v>50.7</v>
       </c>
       <c r="Z4">
-        <v>9.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AA4">
-        <v>5.13</v>
+        <v>5.73</v>
       </c>
       <c r="AB4">
-        <v>4.21</v>
+        <v>2.39</v>
       </c>
       <c r="AC4">
-        <v>51.93</v>
+        <v>41.98</v>
       </c>
       <c r="AD4">
-        <v>64.33</v>
+        <v>54.78</v>
       </c>
       <c r="AE4">
-        <v>24.43</v>
+        <v>24.08</v>
       </c>
       <c r="AF4">
-        <v>-71.76000000000001</v>
+        <v>-48.21</v>
       </c>
       <c r="AG4">
-        <v>1146.98</v>
+        <v>1145.08</v>
       </c>
       <c r="AH4">
-        <v>1013.92</v>
+        <v>1022.47</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1336,7 +1279,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.49</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1347,10 +1290,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>735.4</v>
+        <v>737.85</v>
       </c>
       <c r="D5">
-        <v>-0.34</v>
+        <v>0.33</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1359,46 +1302,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.94</v>
+        <v>-14.66</v>
       </c>
       <c r="H5">
-        <v>11.1</v>
+        <v>11.47</v>
       </c>
       <c r="I5">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="J5">
-        <v>1.54</v>
+        <v>0.05</v>
       </c>
       <c r="K5">
-        <v>-1.88</v>
+        <v>-1.44</v>
       </c>
       <c r="L5">
-        <v>1.88</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M5">
-        <v>36.26</v>
+        <v>36.96</v>
       </c>
       <c r="N5">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>733.16</v>
+        <v>733.8</v>
       </c>
       <c r="Q5">
-        <v>732.77</v>
+        <v>732.78</v>
       </c>
       <c r="R5">
-        <v>711.9299999999999</v>
+        <v>712.75</v>
       </c>
       <c r="S5">
-        <v>751.62</v>
+        <v>751.26</v>
       </c>
       <c r="T5">
-        <v>-2.16</v>
+        <v>-1.79</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1413,34 +1356,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>54.5</v>
+        <v>55.71</v>
       </c>
       <c r="Z5">
-        <v>5.21</v>
+        <v>5.23</v>
       </c>
       <c r="AA5">
-        <v>6.02</v>
+        <v>5.86</v>
       </c>
       <c r="AB5">
-        <v>-0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="AC5">
-        <v>34.95</v>
+        <v>51.53</v>
       </c>
       <c r="AD5">
-        <v>33.1</v>
+        <v>40.11</v>
       </c>
       <c r="AE5">
-        <v>17.04</v>
+        <v>16.37</v>
       </c>
       <c r="AF5">
-        <v>-59.57</v>
+        <v>-36.24</v>
       </c>
       <c r="AG5">
-        <v>746.4400000000001</v>
+        <v>746.49</v>
       </c>
       <c r="AH5">
-        <v>719.09</v>
+        <v>719.08</v>
       </c>
       <c r="AI5">
         <v>690.96</v>
@@ -1449,7 +1392,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>21.04</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1460,10 +1403,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>558.6</v>
+        <v>560</v>
       </c>
       <c r="D6">
-        <v>-0.03</v>
+        <v>0.25</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1472,46 +1415,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-6.9</v>
+        <v>-6.67</v>
       </c>
       <c r="H6">
-        <v>27.37</v>
+        <v>27.69</v>
       </c>
       <c r="I6">
-        <v>-0.52</v>
+        <v>-0.78</v>
       </c>
       <c r="J6">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
-        <v>8.83</v>
+        <v>6.21</v>
       </c>
       <c r="L6">
-        <v>5.18</v>
+        <v>8.41</v>
       </c>
       <c r="M6">
-        <v>19.04</v>
+        <v>18.39</v>
       </c>
       <c r="N6">
         <v>55</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P6">
-        <v>564.55</v>
+        <v>563.67</v>
       </c>
       <c r="Q6">
-        <v>558.55</v>
+        <v>559.49</v>
       </c>
       <c r="R6">
-        <v>561.52</v>
+        <v>560.95</v>
       </c>
       <c r="S6">
-        <v>518.97</v>
+        <v>519.13</v>
       </c>
       <c r="T6">
-        <v>7.64</v>
+        <v>7.87</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1526,34 +1469,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>49.44</v>
+        <v>50.28</v>
       </c>
       <c r="Z6">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AA6">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="AB6">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AC6">
-        <v>39.73</v>
+        <v>36.87</v>
       </c>
       <c r="AD6">
-        <v>58.82</v>
+        <v>45.98</v>
       </c>
       <c r="AE6">
-        <v>12.91</v>
+        <v>12.47</v>
       </c>
       <c r="AF6">
-        <v>-12.96</v>
+        <v>-37.68</v>
       </c>
       <c r="AG6">
-        <v>578.45</v>
+        <v>577.64</v>
       </c>
       <c r="AH6">
-        <v>538.65</v>
+        <v>541.35</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1562,7 +1505,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.9</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1573,10 +1516,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11670</v>
+        <v>11874</v>
       </c>
       <c r="D7">
-        <v>0.85</v>
+        <v>1.75</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1585,46 +1528,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.35</v>
+        <v>-46.43</v>
       </c>
       <c r="H7">
-        <v>9.529999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="I7">
-        <v>-3.41</v>
+        <v>-1.26</v>
       </c>
       <c r="J7">
-        <v>4.52</v>
+        <v>6.05</v>
       </c>
       <c r="K7">
-        <v>-5.74</v>
+        <v>-6.3</v>
       </c>
       <c r="L7">
-        <v>-35.9</v>
+        <v>-35.73</v>
       </c>
       <c r="M7">
-        <v>18.17</v>
+        <v>18.86</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>11812</v>
+        <v>11781.8</v>
       </c>
       <c r="Q7">
-        <v>11435.2</v>
+        <v>11479.85</v>
       </c>
       <c r="R7">
-        <v>11819.76</v>
+        <v>11808.48</v>
       </c>
       <c r="S7">
-        <v>15208.26</v>
+        <v>15184.36</v>
       </c>
       <c r="T7">
-        <v>-23.27</v>
+        <v>-21.8</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1639,34 +1582,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.13</v>
+        <v>54.22</v>
       </c>
       <c r="Z7">
-        <v>55.23</v>
+        <v>63.78</v>
       </c>
       <c r="AA7">
-        <v>-6.53</v>
+        <v>7.53</v>
       </c>
       <c r="AB7">
-        <v>61.76</v>
+        <v>56.25</v>
       </c>
       <c r="AC7">
-        <v>53.93</v>
+        <v>48.51</v>
       </c>
       <c r="AD7">
-        <v>63.75</v>
+        <v>55.01</v>
       </c>
       <c r="AE7">
-        <v>368.41</v>
+        <v>374.24</v>
       </c>
       <c r="AF7">
-        <v>-16.11</v>
+        <v>67.27</v>
       </c>
       <c r="AG7">
-        <v>12488.9</v>
+        <v>12528.18</v>
       </c>
       <c r="AH7">
-        <v>10381.5</v>
+        <v>10431.52</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1675,7 +1618,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.13</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1686,10 +1629,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>341.35</v>
+        <v>339.15</v>
       </c>
       <c r="D8">
-        <v>-1.51</v>
+        <v>-0.64</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1698,25 +1641,25 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.8</v>
+        <v>-3.43</v>
       </c>
       <c r="H8">
-        <v>45.68</v>
+        <v>44.74</v>
       </c>
       <c r="I8">
-        <v>4.23</v>
+        <v>1.01</v>
       </c>
       <c r="J8">
-        <v>1.19</v>
+        <v>-0.04</v>
       </c>
       <c r="K8">
-        <v>27.8</v>
+        <v>25.4</v>
       </c>
       <c r="L8">
-        <v>12.81</v>
+        <v>14.12</v>
       </c>
       <c r="M8">
-        <v>31.29</v>
+        <v>30.96</v>
       </c>
       <c r="N8">
         <v>77</v>
@@ -1725,19 +1668,19 @@
         <v>76</v>
       </c>
       <c r="P8">
-        <v>341.51</v>
+        <v>342.19</v>
       </c>
       <c r="Q8">
-        <v>331.4</v>
+        <v>331.25</v>
       </c>
       <c r="R8">
-        <v>319.72</v>
+        <v>321.05</v>
       </c>
       <c r="S8">
-        <v>281.69</v>
+        <v>281.9</v>
       </c>
       <c r="T8">
-        <v>21.18</v>
+        <v>20.31</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1752,34 +1695,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.34</v>
+        <v>56.59</v>
       </c>
       <c r="Z8">
-        <v>5.47</v>
+        <v>5.37</v>
       </c>
       <c r="AA8">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="AB8">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="AC8">
-        <v>92.44</v>
+        <v>82.34</v>
       </c>
       <c r="AD8">
-        <v>93.92</v>
+        <v>91.52</v>
       </c>
       <c r="AE8">
-        <v>11.2</v>
+        <v>10.77</v>
       </c>
       <c r="AF8">
-        <v>-27.82</v>
+        <v>-38.77</v>
       </c>
       <c r="AG8">
-        <v>353.46</v>
+        <v>353.04</v>
       </c>
       <c r="AH8">
-        <v>309.35</v>
+        <v>309.47</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1788,7 +1731,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>31.94</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1799,10 +1742,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="D9">
-        <v>0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1811,25 +1754,25 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-4.14</v>
+        <v>-4.51</v>
       </c>
       <c r="H9">
-        <v>24.2</v>
+        <v>23.71</v>
       </c>
       <c r="I9">
-        <v>-2.52</v>
+        <v>-2.27</v>
       </c>
       <c r="J9">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="K9">
-        <v>-0.3</v>
+        <v>-1.76</v>
       </c>
       <c r="L9">
-        <v>19.74</v>
+        <v>21.04</v>
       </c>
       <c r="M9">
-        <v>12.23</v>
+        <v>11.79</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1838,19 +1781,19 @@
         <v>66</v>
       </c>
       <c r="P9">
-        <v>1285.8</v>
+        <v>1279.9</v>
       </c>
       <c r="Q9">
-        <v>1274.22</v>
+        <v>1275.85</v>
       </c>
       <c r="R9">
-        <v>1262.2</v>
+        <v>1261.58</v>
       </c>
       <c r="S9">
-        <v>1215.48</v>
+        <v>1216.08</v>
       </c>
       <c r="T9">
-        <v>4.9</v>
+        <v>4.43</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1865,34 +1808,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>50.76</v>
+        <v>49.2</v>
       </c>
       <c r="Z9">
-        <v>9.57</v>
+        <v>7.86</v>
       </c>
       <c r="AA9">
-        <v>10.16</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB9">
-        <v>-0.58</v>
+        <v>-1.84</v>
       </c>
       <c r="AC9">
-        <v>14.16</v>
+        <v>5.9</v>
       </c>
       <c r="AD9">
-        <v>28.71</v>
+        <v>16.26</v>
       </c>
       <c r="AE9">
-        <v>24.89</v>
+        <v>24.28</v>
       </c>
       <c r="AF9">
-        <v>-4.03</v>
+        <v>-45.97</v>
       </c>
       <c r="AG9">
-        <v>1324.57</v>
+        <v>1323.2</v>
       </c>
       <c r="AH9">
-        <v>1223.86</v>
+        <v>1228.5</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1901,7 +1844,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.79</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1912,58 +1855,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>87.04000000000001</v>
+        <v>91.39</v>
       </c>
       <c r="D10">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>88.17</v>
+        <v>91.39</v>
       </c>
       <c r="F10">
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>141.24</v>
+        <v>153.3</v>
       </c>
       <c r="I10">
-        <v>-1.28</v>
+        <v>8.19</v>
       </c>
       <c r="J10">
-        <v>70.83</v>
+        <v>81.37</v>
       </c>
       <c r="K10">
-        <v>73.66</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="L10">
-        <v>14.72</v>
+        <v>21.63</v>
       </c>
       <c r="M10">
-        <v>-3.01</v>
+        <v>-1.63</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>84.53</v>
+        <v>85.91</v>
       </c>
       <c r="Q10">
-        <v>73.78</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R10">
-        <v>60.56</v>
+        <v>61.39</v>
       </c>
       <c r="S10">
-        <v>59.24</v>
+        <v>59.3</v>
       </c>
       <c r="T10">
-        <v>46.94</v>
+        <v>54.11</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1978,43 +1921,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>72.22</v>
+        <v>75.34</v>
       </c>
       <c r="Z10">
-        <v>7.99</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AA10">
-        <v>7.22</v>
+        <v>7.44</v>
       </c>
       <c r="AB10">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AC10">
-        <v>50.89</v>
+        <v>60.29</v>
       </c>
       <c r="AD10">
-        <v>52.15</v>
+        <v>53.62</v>
       </c>
       <c r="AE10">
-        <v>5.08</v>
+        <v>5.03</v>
       </c>
       <c r="AF10">
-        <v>-81.23999999999999</v>
+        <v>-84.15000000000001</v>
       </c>
       <c r="AG10">
-        <v>95.72</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="AH10">
-        <v>51.84</v>
+        <v>55.95</v>
       </c>
       <c r="AI10">
-        <v>71.81</v>
+        <v>76.31</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>52.52</v>
+        <v>53.95</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2195,7 +2138,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2214,1373 +2157,1333 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-3.57</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-6.61</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3.46</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-0.35</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5.54</v>
+      </c>
+      <c r="D11" s="7">
+        <v>6.18</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.54</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>4.52</v>
+      </c>
+      <c r="D14" s="7">
+        <v>6.05</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.19</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.04</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="D16" s="7">
+        <v>4.01</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>70.83</v>
+      </c>
+      <c r="D17" s="7">
+        <v>81.37</v>
+      </c>
+      <c r="E17" s="9">
+        <v>10.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.96</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2.63</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.32</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.58</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.04</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.44</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.41</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-1.26</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4.23</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.01</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-2.52</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.27</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-1.28</v>
+      </c>
+      <c r="D26" s="7">
+        <v>8.19</v>
+      </c>
+      <c r="E26" s="9">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>23.29</v>
+      </c>
+      <c r="D27" s="7">
+        <v>21.03</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>27.16</v>
+      </c>
+      <c r="D28" s="7">
+        <v>30.53</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>10.26</v>
+      </c>
+      <c r="D29" s="7">
+        <v>12.27</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="D30" s="7">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="E30" s="9">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>5.18</v>
+      </c>
+      <c r="D31" s="7">
+        <v>8.41</v>
+      </c>
+      <c r="E31" s="9">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-35.9</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-35.73</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>12.81</v>
+      </c>
+      <c r="D33" s="7">
+        <v>14.12</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>19.74</v>
+      </c>
+      <c r="D34" s="7">
+        <v>21.04</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>14.72</v>
+      </c>
+      <c r="D35" s="7">
+        <v>21.63</v>
+      </c>
+      <c r="E35" s="9">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-6.84</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-7.66</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>16.48</v>
+      </c>
+      <c r="D37" s="7">
+        <v>22.11</v>
+      </c>
+      <c r="E37" s="9">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-10.72</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-11.39</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.88</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-1.44</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>8.83</v>
+      </c>
+      <c r="D40" s="7">
+        <v>6.21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-5.74</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-6.3</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>27.8</v>
+      </c>
+      <c r="D42" s="7">
+        <v>25.4</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-1.76</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>73.66</v>
+      </c>
+      <c r="D44" s="7">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="E44" s="9">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-35.34</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-36.85</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-5.25</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-4.28</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-14.66</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-15.31</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-14.94</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-14.66</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-6.9</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-6.67</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-47.35</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-46.43</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-3.43</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-4.14</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-4.51</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-1.28</v>
+      </c>
+      <c r="D53" s="7">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="E53" s="9">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-0.87</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-3.57</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>651.5</v>
+      </c>
+      <c r="D54" s="7">
+        <v>636.3</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-15.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>4.13</v>
-      </c>
-      <c r="D12" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>264.4</v>
+      </c>
+      <c r="D55" s="7">
+        <v>267.1</v>
+      </c>
+      <c r="E55" s="9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>6.91</v>
-      </c>
-      <c r="D13" s="8">
-        <v>5.54</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1099.9</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1091.5</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>2.23</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.54</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>735.4</v>
+      </c>
+      <c r="D57" s="7">
+        <v>737.85</v>
+      </c>
+      <c r="E57" s="9">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.58</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>558.6</v>
+      </c>
+      <c r="D58" s="7">
+        <v>560</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>3.21</v>
-      </c>
-      <c r="D16" s="8">
-        <v>4.52</v>
-      </c>
-      <c r="E16" s="10">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>11670</v>
+      </c>
+      <c r="D59" s="7">
+        <v>11874</v>
+      </c>
+      <c r="E59" s="9">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-0.19</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1.19</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>341.35</v>
+      </c>
+      <c r="D60" s="7">
+        <v>339.15</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1.72</v>
-      </c>
-      <c r="D18" s="8">
-        <v>3.92</v>
-      </c>
-      <c r="E18" s="10">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1275</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1270</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>59.73</v>
-      </c>
-      <c r="D19" s="8">
-        <v>70.83</v>
-      </c>
-      <c r="E19" s="10">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="D62" s="7">
+        <v>91.39</v>
+      </c>
+      <c r="E62" s="9">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>34</v>
+      </c>
+      <c r="D63" s="7">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>34</v>
+      </c>
+      <c r="E64" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>6.4</v>
-      </c>
-      <c r="D20" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>52.23</v>
+      </c>
+      <c r="D65" s="7">
+        <v>47.3</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-4.93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1.49</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-0.32</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>51.12</v>
+      </c>
+      <c r="D66" s="7">
+        <v>53.36</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-0.13</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-0.1</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>53.09</v>
+      </c>
+      <c r="D67" s="7">
+        <v>50.7</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-0.89</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>54.5</v>
+      </c>
+      <c r="D68" s="7">
+        <v>55.71</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>-1.28</v>
-      </c>
-      <c r="D24" s="8">
-        <v>-0.52</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>49.44</v>
+      </c>
+      <c r="D69" s="7">
+        <v>50.28</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-6.12</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-3.41</v>
-      </c>
-      <c r="E25" s="10">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>50.13</v>
+      </c>
+      <c r="D70" s="7">
+        <v>54.22</v>
+      </c>
+      <c r="E70" s="9">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>3.65</v>
-      </c>
-      <c r="D26" s="8">
-        <v>4.23</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>58.34</v>
+      </c>
+      <c r="D71" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-4.58</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-2.52</v>
-      </c>
-      <c r="E27" s="10">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>50.76</v>
+      </c>
+      <c r="D72" s="7">
+        <v>49.2</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-3.82</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-1.28</v>
-      </c>
-      <c r="E28" s="10">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>72.22</v>
+      </c>
+      <c r="D73" s="7">
+        <v>75.34</v>
+      </c>
+      <c r="E73" s="9">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>22.63</v>
-      </c>
-      <c r="D29" s="8">
-        <v>23.29</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>44.64</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-17.1</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-61.74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>32.29</v>
-      </c>
-      <c r="D30" s="8">
-        <v>27.16</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-5.13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-46.64</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-23.68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>13.01</v>
-      </c>
-      <c r="D31" s="8">
-        <v>10.26</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-71.76000000000001</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-48.21</v>
+      </c>
+      <c r="E76" s="9">
+        <v>23.55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0.92</v>
-      </c>
-      <c r="D32" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-59.57</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-36.24</v>
+      </c>
+      <c r="E77" s="9">
+        <v>23.33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>4.98</v>
-      </c>
-      <c r="D33" s="8">
-        <v>5.18</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-12.96</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-37.68</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-24.72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>-38.89</v>
-      </c>
-      <c r="D34" s="8">
-        <v>-35.9</v>
-      </c>
-      <c r="E34" s="10">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-16.11</v>
+      </c>
+      <c r="D79" s="7">
+        <v>67.27</v>
+      </c>
+      <c r="E79" s="9">
+        <v>83.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>15.38</v>
-      </c>
-      <c r="D35" s="8">
-        <v>12.81</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-27.82</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-38.77</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-10.95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>20.57</v>
-      </c>
-      <c r="D36" s="8">
-        <v>19.74</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-4.03</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-45.97</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-41.94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="8">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="D37" s="8">
-        <v>14.72</v>
-      </c>
-      <c r="E37" s="10">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-4.59</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-6.84</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>16.42</v>
-      </c>
-      <c r="D39" s="8">
-        <v>16.48</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-11.24</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-10.72</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>-1.44</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-1.88</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>9.33</v>
-      </c>
-      <c r="D42" s="8">
-        <v>8.83</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-7.3</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-5.74</v>
-      </c>
-      <c r="E43" s="10">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>29.55</v>
-      </c>
-      <c r="D44" s="8">
-        <v>27.8</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-2.14</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-0.3</v>
-      </c>
-      <c r="E45" s="10">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="8">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="D46" s="8">
-        <v>73.66</v>
-      </c>
-      <c r="E46" s="10">
-        <v>9.31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-33.85</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-35.34</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-3.4</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-5.25</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-13.72</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-14.66</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-14.65</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-14.94</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-6.88</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-6.9</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-47.79</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-47.35</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>-1.31</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-2.8</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-4.58</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-4.14</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="8">
-        <v>-5.98</v>
-      </c>
-      <c r="D55" s="8">
-        <v>-1.28</v>
-      </c>
-      <c r="E55" s="10">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>666.55</v>
-      </c>
-      <c r="D56" s="8">
-        <v>651.5</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-15.05</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>269.55</v>
-      </c>
-      <c r="D57" s="8">
-        <v>264.4</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-5.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>1112</v>
-      </c>
-      <c r="D58" s="8">
-        <v>1099.9</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-12.1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>737.9</v>
-      </c>
-      <c r="D59" s="8">
-        <v>735.4</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>558.75</v>
-      </c>
-      <c r="D60" s="8">
-        <v>558.6</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>11572</v>
-      </c>
-      <c r="D61" s="8">
-        <v>11670</v>
-      </c>
-      <c r="E61" s="10">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>346.6</v>
-      </c>
-      <c r="D62" s="8">
-        <v>341.35</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>1269.1</v>
-      </c>
-      <c r="D63" s="8">
-        <v>1275</v>
-      </c>
-      <c r="E63" s="10">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="8">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="D64" s="8">
-        <v>87.04000000000001</v>
-      </c>
-      <c r="E64" s="10">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="8">
-        <v>55</v>
-      </c>
-      <c r="D65" s="8">
-        <v>45</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="8">
-        <v>45</v>
-      </c>
-      <c r="D66" s="8">
-        <v>55</v>
-      </c>
-      <c r="E66" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="8">
-        <v>57.78</v>
-      </c>
-      <c r="D67" s="8">
-        <v>52.23</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="8">
-        <v>55.87</v>
-      </c>
-      <c r="D68" s="8">
-        <v>51.12</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-4.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="8">
-        <v>56.65</v>
-      </c>
-      <c r="D69" s="8">
-        <v>53.09</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-3.56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="8">
-        <v>55.94</v>
-      </c>
-      <c r="D70" s="8">
-        <v>54.5</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>49.52</v>
-      </c>
-      <c r="D71" s="8">
-        <v>49.44</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>48.05</v>
-      </c>
-      <c r="D72" s="8">
-        <v>50.13</v>
-      </c>
-      <c r="E72" s="10">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>62.64</v>
-      </c>
-      <c r="D73" s="8">
-        <v>58.34</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>48.99</v>
-      </c>
-      <c r="D74" s="8">
-        <v>50.76</v>
-      </c>
-      <c r="E74" s="10">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>68.73</v>
-      </c>
-      <c r="D75" s="8">
-        <v>72.22</v>
-      </c>
-      <c r="E75" s="10">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="7" t="s">
+      <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="8">
-        <v>1703.29</v>
-      </c>
-      <c r="D76" s="8">
-        <v>44.64</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-1658.65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="8">
-        <v>-47.71</v>
-      </c>
-      <c r="D77" s="8">
-        <v>-46.64</v>
-      </c>
-      <c r="E77" s="10">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="8">
-        <v>-64.37</v>
-      </c>
-      <c r="D78" s="8">
-        <v>-71.76000000000001</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-7.39</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="8">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="D79" s="8">
-        <v>-59.57</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-68.95999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="8">
-        <v>-32.45</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-12.96</v>
-      </c>
-      <c r="E80" s="10">
-        <v>19.49</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>-11.91</v>
-      </c>
-      <c r="D81" s="8">
-        <v>-16.11</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>165.76</v>
-      </c>
-      <c r="D82" s="8">
-        <v>-27.82</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-193.58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-51.35</v>
-      </c>
-      <c r="D83" s="8">
-        <v>-4.03</v>
-      </c>
-      <c r="E83" s="10">
-        <v>47.32</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>-91.23999999999999</v>
-      </c>
-      <c r="D84" s="8">
+      <c r="C82" s="7">
         <v>-81.23999999999999</v>
       </c>
-      <c r="E84" s="10">
-        <v>10</v>
+      <c r="D82" s="7">
+        <v>-84.15000000000001</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-2.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3600,60 +3503,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>91</v>
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>60.16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>54.6</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="12">
+        <v>54.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F2" s="13">
-        <v>9.9</v>
-      </c>
-      <c r="G2" s="13">
-        <v>11.3</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="12">
+        <v>10.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>12.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3755,61 +3658,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.3626</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3418</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.3129</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.2133</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1904</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1817</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.1223</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.0301</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.0916</v>
+      <c r="A2" s="15">
+        <v>0.3696</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3516</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3096</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2083</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1886</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1839</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1179</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0163</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.08650000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="84">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,43 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.4 → 50.3</t>
+    <t>47.3 → 56.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.4</t>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>56.0</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>49.2 → 51.7</t>
+  </si>
+  <si>
+    <t>49.2</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>50.3 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.3</t>
   </si>
   <si>
-    <t>52.2 → 47.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>47.3</t>
-  </si>
-  <si>
-    <t>50.8 → 49.2</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>47.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -439,8 +445,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -811,8 +817,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -951,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>636.3</v>
+        <v>665.65</v>
       </c>
       <c r="D2">
-        <v>-2.33</v>
+        <v>4.61</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -963,46 +970,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.85</v>
+        <v>-33.94</v>
       </c>
       <c r="H2">
-        <v>73.28</v>
+        <v>81.28</v>
       </c>
       <c r="I2">
-        <v>2.63</v>
+        <v>5.91</v>
       </c>
       <c r="J2">
-        <v>-6.61</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>-7.66</v>
+        <v>-5.05</v>
       </c>
       <c r="L2">
-        <v>21.03</v>
+        <v>28.43</v>
       </c>
       <c r="M2">
-        <v>-8.65</v>
+        <v>-7.39</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>642.47</v>
+        <v>649.9</v>
       </c>
       <c r="Q2">
-        <v>638.29</v>
+        <v>638.26</v>
       </c>
       <c r="R2">
-        <v>656.63</v>
+        <v>656.9299999999999</v>
       </c>
       <c r="S2">
-        <v>616.25</v>
+        <v>616.77</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>7.93</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1017,34 +1024,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.3</v>
+        <v>55.95</v>
       </c>
       <c r="Z2">
-        <v>-4.83</v>
+        <v>-2.35</v>
       </c>
       <c r="AA2">
-        <v>-7.67</v>
+        <v>-6.61</v>
       </c>
       <c r="AB2">
-        <v>2.84</v>
+        <v>4.26</v>
       </c>
       <c r="AC2">
-        <v>70.01000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AD2">
-        <v>83.62</v>
+        <v>75.41</v>
       </c>
       <c r="AE2">
-        <v>24.41</v>
+        <v>26.49</v>
       </c>
       <c r="AF2">
-        <v>-17.1</v>
+        <v>219.3</v>
       </c>
       <c r="AG2">
-        <v>667.51</v>
+        <v>667.36</v>
       </c>
       <c r="AH2">
-        <v>609.0700000000001</v>
+        <v>609.16</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1053,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.13</v>
+        <v>31.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1067,7 +1074,7 @@
         <v>267.1</v>
       </c>
       <c r="D3">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1082,40 +1089,40 @@
         <v>74.31</v>
       </c>
       <c r="I3">
-        <v>-1.58</v>
+        <v>-4.28</v>
       </c>
       <c r="J3">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="K3">
-        <v>22.11</v>
+        <v>20.52</v>
       </c>
       <c r="L3">
-        <v>30.53</v>
+        <v>32.57</v>
       </c>
       <c r="M3">
-        <v>35.16</v>
+        <v>35.63</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>270.73</v>
+        <v>268.34</v>
       </c>
       <c r="Q3">
-        <v>263.3</v>
+        <v>263.36</v>
       </c>
       <c r="R3">
-        <v>258.9</v>
+        <v>259.23</v>
       </c>
       <c r="S3">
-        <v>206.5</v>
+        <v>206.95</v>
       </c>
       <c r="T3">
-        <v>29.34</v>
+        <v>29.07</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1133,28 +1140,28 @@
         <v>53.36</v>
       </c>
       <c r="Z3">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="AB3">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="AC3">
-        <v>40.89</v>
+        <v>34.2</v>
       </c>
       <c r="AD3">
-        <v>56.77</v>
+        <v>42.89</v>
       </c>
       <c r="AE3">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="AF3">
-        <v>-70.31999999999999</v>
+        <v>-64.09</v>
       </c>
       <c r="AG3">
-        <v>277.27</v>
+        <v>277.39</v>
       </c>
       <c r="AH3">
         <v>249.34</v>
@@ -1166,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>20.42</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1180,7 +1187,7 @@
         <v>1091.5</v>
       </c>
       <c r="D4">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1195,43 +1202,43 @@
         <v>15.4</v>
       </c>
       <c r="I4">
-        <v>-1.04</v>
+        <v>-2.98</v>
       </c>
       <c r="J4">
-        <v>6.18</v>
+        <v>6.49</v>
       </c>
       <c r="K4">
-        <v>-11.39</v>
+        <v>-10.99</v>
       </c>
       <c r="L4">
-        <v>12.27</v>
+        <v>10.36</v>
       </c>
       <c r="M4">
-        <v>20.83</v>
+        <v>21.68</v>
       </c>
       <c r="N4">
         <v>23</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P4">
-        <v>1104.68</v>
+        <v>1097.98</v>
       </c>
       <c r="Q4">
-        <v>1083.78</v>
+        <v>1086.68</v>
       </c>
       <c r="R4">
-        <v>1084.58</v>
+        <v>1082.78</v>
       </c>
       <c r="S4">
-        <v>1122.91</v>
+        <v>1123</v>
       </c>
       <c r="T4">
-        <v>-2.8</v>
+        <v>-2.81</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V4" t="s">
         <v>47</v>
@@ -1240,37 +1247,37 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>50.7</v>
       </c>
       <c r="Z4">
-        <v>8.109999999999999</v>
+        <v>7.06</v>
       </c>
       <c r="AA4">
-        <v>5.73</v>
+        <v>5.99</v>
       </c>
       <c r="AB4">
-        <v>2.39</v>
+        <v>1.07</v>
       </c>
       <c r="AC4">
-        <v>41.98</v>
+        <v>19.15</v>
       </c>
       <c r="AD4">
-        <v>54.78</v>
+        <v>37.69</v>
       </c>
       <c r="AE4">
-        <v>24.08</v>
+        <v>23.76</v>
       </c>
       <c r="AF4">
-        <v>-48.21</v>
+        <v>-30.29</v>
       </c>
       <c r="AG4">
-        <v>1145.08</v>
+        <v>1143.24</v>
       </c>
       <c r="AH4">
-        <v>1022.47</v>
+        <v>1030.13</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1279,7 +1286,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>28.62</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,7 +1300,7 @@
         <v>737.85</v>
       </c>
       <c r="D5">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1308,40 +1315,40 @@
         <v>11.47</v>
       </c>
       <c r="I5">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="K5">
-        <v>-1.44</v>
+        <v>-0.18</v>
       </c>
       <c r="L5">
-        <v>8.380000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M5">
-        <v>36.96</v>
+        <v>37.5</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>733.8</v>
+        <v>734.8200000000001</v>
       </c>
       <c r="Q5">
-        <v>732.78</v>
+        <v>733.14</v>
       </c>
       <c r="R5">
-        <v>712.75</v>
+        <v>713.6900000000001</v>
       </c>
       <c r="S5">
-        <v>751.26</v>
+        <v>750.9400000000001</v>
       </c>
       <c r="T5">
-        <v>-1.79</v>
+        <v>-1.74</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1359,31 +1366,31 @@
         <v>55.71</v>
       </c>
       <c r="Z5">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="AA5">
-        <v>5.86</v>
+        <v>5.72</v>
       </c>
       <c r="AB5">
-        <v>-0.63</v>
+        <v>-0.54</v>
       </c>
       <c r="AC5">
-        <v>51.53</v>
+        <v>50.24</v>
       </c>
       <c r="AD5">
-        <v>40.11</v>
+        <v>45.57</v>
       </c>
       <c r="AE5">
-        <v>16.37</v>
+        <v>15.76</v>
       </c>
       <c r="AF5">
-        <v>-36.24</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="AG5">
-        <v>746.49</v>
+        <v>746.99</v>
       </c>
       <c r="AH5">
-        <v>719.08</v>
+        <v>719.29</v>
       </c>
       <c r="AI5">
         <v>690.96</v>
@@ -1392,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>560</v>
+        <v>555.5</v>
       </c>
       <c r="D6">
-        <v>0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1415,46 +1422,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-6.67</v>
+        <v>-7.42</v>
       </c>
       <c r="H6">
-        <v>27.69</v>
+        <v>26.66</v>
       </c>
       <c r="I6">
-        <v>-0.78</v>
+        <v>-3.89</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="K6">
-        <v>6.21</v>
+        <v>4.55</v>
       </c>
       <c r="L6">
-        <v>8.41</v>
+        <v>4.16</v>
       </c>
       <c r="M6">
-        <v>18.39</v>
+        <v>17.91</v>
       </c>
       <c r="N6">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O6">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P6">
-        <v>563.67</v>
+        <v>559.17</v>
       </c>
       <c r="Q6">
-        <v>559.49</v>
+        <v>558.88</v>
       </c>
       <c r="R6">
-        <v>560.95</v>
+        <v>560.38</v>
       </c>
       <c r="S6">
-        <v>519.13</v>
+        <v>519.24</v>
       </c>
       <c r="T6">
-        <v>7.87</v>
+        <v>6.98</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1469,34 +1476,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>50.28</v>
+        <v>47.54</v>
       </c>
       <c r="Z6">
-        <v>1.43</v>
+        <v>0.88</v>
       </c>
       <c r="AA6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB6">
-        <v>0.36</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>36.87</v>
+        <v>33.21</v>
       </c>
       <c r="AD6">
-        <v>45.98</v>
+        <v>36.6</v>
       </c>
       <c r="AE6">
-        <v>12.47</v>
+        <v>12.34</v>
       </c>
       <c r="AF6">
-        <v>-37.68</v>
+        <v>-35.06</v>
       </c>
       <c r="AG6">
-        <v>577.64</v>
+        <v>576.6900000000001</v>
       </c>
       <c r="AH6">
-        <v>541.35</v>
+        <v>541.08</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1505,7 +1512,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>19.27</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1519,7 +1526,7 @@
         <v>11874</v>
       </c>
       <c r="D7">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1534,40 +1541,40 @@
         <v>11.44</v>
       </c>
       <c r="I7">
-        <v>-1.26</v>
+        <v>0.19</v>
       </c>
       <c r="J7">
-        <v>6.05</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K7">
-        <v>-6.3</v>
+        <v>-6.36</v>
       </c>
       <c r="L7">
-        <v>-35.73</v>
+        <v>-33.63</v>
       </c>
       <c r="M7">
-        <v>18.86</v>
+        <v>19.14</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>11781.8</v>
+        <v>11786.2</v>
       </c>
       <c r="Q7">
-        <v>11479.85</v>
+        <v>11521</v>
       </c>
       <c r="R7">
-        <v>11808.48</v>
+        <v>11795.84</v>
       </c>
       <c r="S7">
-        <v>15184.36</v>
+        <v>15159.6</v>
       </c>
       <c r="T7">
-        <v>-21.8</v>
+        <v>-21.67</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1585,31 +1592,31 @@
         <v>54.22</v>
       </c>
       <c r="Z7">
-        <v>63.78</v>
+        <v>69.75</v>
       </c>
       <c r="AA7">
-        <v>7.53</v>
+        <v>19.97</v>
       </c>
       <c r="AB7">
-        <v>56.25</v>
+        <v>49.78</v>
       </c>
       <c r="AC7">
-        <v>48.51</v>
+        <v>49.99</v>
       </c>
       <c r="AD7">
-        <v>55.01</v>
+        <v>50.81</v>
       </c>
       <c r="AE7">
-        <v>374.24</v>
+        <v>379.65</v>
       </c>
       <c r="AF7">
-        <v>67.27</v>
+        <v>-63.97</v>
       </c>
       <c r="AG7">
-        <v>12528.18</v>
+        <v>12563.04</v>
       </c>
       <c r="AH7">
-        <v>10431.52</v>
+        <v>10478.96</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1618,7 +1625,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>27.59</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>339.15</v>
+        <v>335.4</v>
       </c>
       <c r="D8">
-        <v>-0.64</v>
+        <v>-1.11</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1641,46 +1648,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-3.43</v>
+        <v>-4.5</v>
       </c>
       <c r="H8">
-        <v>44.74</v>
+        <v>43.14</v>
       </c>
       <c r="I8">
-        <v>1.01</v>
+        <v>-1.93</v>
       </c>
       <c r="J8">
-        <v>-0.04</v>
+        <v>-1.97</v>
       </c>
       <c r="K8">
-        <v>25.4</v>
+        <v>26.02</v>
       </c>
       <c r="L8">
-        <v>14.12</v>
+        <v>12.97</v>
       </c>
       <c r="M8">
-        <v>30.96</v>
+        <v>30.36</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P8">
-        <v>342.19</v>
+        <v>340.87</v>
       </c>
       <c r="Q8">
-        <v>331.25</v>
+        <v>330.6</v>
       </c>
       <c r="R8">
-        <v>321.05</v>
+        <v>322.2</v>
       </c>
       <c r="S8">
-        <v>281.9</v>
+        <v>282.11</v>
       </c>
       <c r="T8">
-        <v>20.31</v>
+        <v>18.89</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1695,34 +1702,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>56.59</v>
+        <v>53.63</v>
       </c>
       <c r="Z8">
-        <v>5.37</v>
+        <v>4.93</v>
       </c>
       <c r="AA8">
-        <v>4.55</v>
+        <v>4.63</v>
       </c>
       <c r="AB8">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="AC8">
-        <v>82.34</v>
+        <v>66.98</v>
       </c>
       <c r="AD8">
-        <v>91.52</v>
+        <v>80.59</v>
       </c>
       <c r="AE8">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="AF8">
-        <v>-38.77</v>
+        <v>-29.81</v>
       </c>
       <c r="AG8">
-        <v>353.04</v>
+        <v>350.95</v>
       </c>
       <c r="AH8">
-        <v>309.47</v>
+        <v>310.25</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1731,7 +1738,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>32.53</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1270</v>
+        <v>1277.8</v>
       </c>
       <c r="D9">
-        <v>-0.39</v>
+        <v>0.61</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1754,46 +1761,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-4.51</v>
+        <v>-3.92</v>
       </c>
       <c r="H9">
-        <v>23.71</v>
+        <v>24.47</v>
       </c>
       <c r="I9">
-        <v>-2.27</v>
+        <v>-1.86</v>
       </c>
       <c r="J9">
-        <v>4.01</v>
+        <v>3.27</v>
       </c>
       <c r="K9">
-        <v>-1.76</v>
+        <v>-0.58</v>
       </c>
       <c r="L9">
-        <v>21.04</v>
+        <v>21.38</v>
       </c>
       <c r="M9">
-        <v>11.79</v>
+        <v>12.43</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1279.9</v>
+        <v>1275.06</v>
       </c>
       <c r="Q9">
-        <v>1275.85</v>
+        <v>1276.89</v>
       </c>
       <c r="R9">
-        <v>1261.58</v>
+        <v>1261.46</v>
       </c>
       <c r="S9">
-        <v>1216.08</v>
+        <v>1216.55</v>
       </c>
       <c r="T9">
-        <v>4.43</v>
+        <v>5.03</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1808,34 +1815,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>49.2</v>
+        <v>51.69</v>
       </c>
       <c r="Z9">
-        <v>7.86</v>
+        <v>7.05</v>
       </c>
       <c r="AA9">
-        <v>9.699999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AB9">
-        <v>-1.84</v>
+        <v>-2.12</v>
       </c>
       <c r="AC9">
-        <v>5.9</v>
+        <v>7.75</v>
       </c>
       <c r="AD9">
-        <v>16.26</v>
+        <v>9.27</v>
       </c>
       <c r="AE9">
-        <v>24.28</v>
+        <v>25.88</v>
       </c>
       <c r="AF9">
-        <v>-45.97</v>
+        <v>-21.41</v>
       </c>
       <c r="AG9">
-        <v>1323.2</v>
+        <v>1323.4</v>
       </c>
       <c r="AH9">
-        <v>1228.5</v>
+        <v>1230.38</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1844,7 +1851,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.94</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,13 +1862,13 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>91.39</v>
+        <v>91.45</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E10">
-        <v>91.39</v>
+        <v>91.45</v>
       </c>
       <c r="F10">
         <v>36.08</v>
@@ -1870,22 +1877,22 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>153.3</v>
+        <v>153.46</v>
       </c>
       <c r="I10">
-        <v>8.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J10">
-        <v>81.37</v>
+        <v>86.67</v>
       </c>
       <c r="K10">
-        <v>86.31999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="L10">
-        <v>21.63</v>
+        <v>23.58</v>
       </c>
       <c r="M10">
-        <v>-1.63</v>
+        <v>-2.46</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1894,19 +1901,19 @@
         <v>95</v>
       </c>
       <c r="P10">
-        <v>85.91</v>
+        <v>87.33</v>
       </c>
       <c r="Q10">
-        <v>75.90000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="R10">
-        <v>61.39</v>
+        <v>62.2</v>
       </c>
       <c r="S10">
-        <v>59.3</v>
+        <v>59.37</v>
       </c>
       <c r="T10">
-        <v>54.11</v>
+        <v>54.03</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1921,43 +1928,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>75.34</v>
+        <v>75.38</v>
       </c>
       <c r="Z10">
-        <v>8.289999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="AA10">
-        <v>7.44</v>
+        <v>7.64</v>
       </c>
       <c r="AB10">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AC10">
-        <v>60.29</v>
+        <v>73.67</v>
       </c>
       <c r="AD10">
-        <v>53.62</v>
+        <v>61.62</v>
       </c>
       <c r="AE10">
-        <v>5.03</v>
+        <v>5.22</v>
       </c>
       <c r="AF10">
-        <v>-84.15000000000001</v>
+        <v>-34.79</v>
       </c>
       <c r="AG10">
-        <v>95.84999999999999</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="AH10">
-        <v>55.95</v>
+        <v>58.14</v>
       </c>
       <c r="AI10">
-        <v>76.31</v>
+        <v>76.45</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>53.95</v>
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2138,7 +2145,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2157,137 +2164,140 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="F5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="F6" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-3.57</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-6.61</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-3.04</v>
+      <c r="D9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>3.46</v>
+        <v>-6.61</v>
       </c>
       <c r="D10" s="7">
-        <v>-0.35</v>
+        <v>1</v>
       </c>
       <c r="E10" s="8">
-        <v>-3.81</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>5.54</v>
+        <v>-0.35</v>
       </c>
       <c r="D11" s="7">
-        <v>6.18</v>
+        <v>-0.87</v>
       </c>
       <c r="E11" s="9">
-        <v>0.64</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>1.54</v>
+        <v>6.18</v>
       </c>
       <c r="D12" s="7">
-        <v>0.05</v>
+        <v>6.49</v>
       </c>
       <c r="E12" s="8">
-        <v>-1.49</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2298,13 +2308,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="D13" s="7">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="E13" s="9">
-        <v>1.47</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2315,13 +2325,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>4.52</v>
+        <v>6.05</v>
       </c>
       <c r="D14" s="7">
-        <v>6.05</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.53</v>
+        <v>8.130000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2332,13 +2342,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>1.19</v>
+        <v>-0.04</v>
       </c>
       <c r="D15" s="7">
-        <v>-0.04</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.23</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2349,13 +2359,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="D16" s="7">
-        <v>4.01</v>
+        <v>3.27</v>
       </c>
       <c r="E16" s="9">
-        <v>0.09</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2366,13 +2376,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>70.83</v>
+        <v>81.37</v>
       </c>
       <c r="D17" s="7">
-        <v>81.37</v>
-      </c>
-      <c r="E17" s="9">
-        <v>10.54</v>
+        <v>86.67</v>
+      </c>
+      <c r="E17" s="8">
+        <v>5.3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2383,13 +2393,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="D18" s="7">
-        <v>2.63</v>
+        <v>5.91</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.33</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2400,13 +2410,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-0.32</v>
+        <v>-1.58</v>
       </c>
       <c r="D19" s="7">
-        <v>-1.58</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.26</v>
+        <v>-4.28</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2417,13 +2427,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-0.1</v>
+        <v>-1.04</v>
       </c>
       <c r="D20" s="7">
-        <v>-1.04</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.9399999999999999</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2434,13 +2444,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="D21" s="7">
-        <v>0.44</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.04</v>
+        <v>0.7</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2451,13 +2461,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-0.52</v>
+        <v>-0.78</v>
       </c>
       <c r="D22" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.26</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2468,13 +2478,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-3.41</v>
+        <v>-1.26</v>
       </c>
       <c r="D23" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E23" s="9">
-        <v>2.15</v>
+        <v>0.19</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.45</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2485,13 +2495,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>4.23</v>
+        <v>1.01</v>
       </c>
       <c r="D24" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-3.22</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2502,13 +2512,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.52</v>
+        <v>-2.27</v>
       </c>
       <c r="D25" s="7">
-        <v>-2.27</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.25</v>
+        <v>-1.86</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2519,13 +2529,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>-1.28</v>
+        <v>8.19</v>
       </c>
       <c r="D26" s="7">
-        <v>8.19</v>
-      </c>
-      <c r="E26" s="9">
-        <v>9.470000000000001</v>
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2536,13 +2546,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>23.29</v>
+        <v>21.03</v>
       </c>
       <c r="D27" s="7">
-        <v>21.03</v>
+        <v>28.43</v>
       </c>
       <c r="E27" s="8">
-        <v>-2.26</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2553,13 +2563,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>27.16</v>
+        <v>30.53</v>
       </c>
       <c r="D28" s="7">
-        <v>30.53</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.37</v>
+        <v>32.57</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.04</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2570,13 +2580,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>10.26</v>
+        <v>12.27</v>
       </c>
       <c r="D29" s="7">
-        <v>12.27</v>
+        <v>10.36</v>
       </c>
       <c r="E29" s="9">
-        <v>2.01</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2587,13 +2597,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>1.88</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="D30" s="7">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="E30" s="9">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.82</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2604,13 +2614,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>5.18</v>
+        <v>8.41</v>
       </c>
       <c r="D31" s="7">
-        <v>8.41</v>
+        <v>4.16</v>
       </c>
       <c r="E31" s="9">
-        <v>3.23</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2621,13 +2631,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-35.9</v>
+        <v>-35.73</v>
       </c>
       <c r="D32" s="7">
-        <v>-35.73</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.17</v>
+        <v>-33.63</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2638,13 +2648,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>12.81</v>
+        <v>14.12</v>
       </c>
       <c r="D33" s="7">
-        <v>14.12</v>
+        <v>12.97</v>
       </c>
       <c r="E33" s="9">
-        <v>1.31</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2655,13 +2665,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>19.74</v>
+        <v>21.04</v>
       </c>
       <c r="D34" s="7">
-        <v>21.04</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.3</v>
+        <v>21.38</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2672,13 +2682,13 @@
         <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>14.72</v>
+        <v>21.63</v>
       </c>
       <c r="D35" s="7">
-        <v>21.63</v>
-      </c>
-      <c r="E35" s="9">
-        <v>6.91</v>
+        <v>23.58</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2689,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-6.84</v>
+        <v>-7.66</v>
       </c>
       <c r="D36" s="7">
-        <v>-7.66</v>
+        <v>-5.05</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.82</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2706,13 +2716,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>16.48</v>
+        <v>22.11</v>
       </c>
       <c r="D37" s="7">
-        <v>22.11</v>
+        <v>20.52</v>
       </c>
       <c r="E37" s="9">
-        <v>5.63</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2723,13 +2733,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-10.72</v>
+        <v>-11.39</v>
       </c>
       <c r="D38" s="7">
-        <v>-11.39</v>
+        <v>-10.99</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.67</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2740,13 +2750,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-1.88</v>
+        <v>-1.44</v>
       </c>
       <c r="D39" s="7">
-        <v>-1.44</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.44</v>
+        <v>-0.18</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2757,13 +2767,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>8.83</v>
+        <v>6.21</v>
       </c>
       <c r="D40" s="7">
-        <v>6.21</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.62</v>
+        <v>4.55</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2774,13 +2784,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-5.74</v>
+        <v>-6.3</v>
       </c>
       <c r="D41" s="7">
-        <v>-6.3</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-6.36</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2791,13 +2801,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>27.8</v>
+        <v>25.4</v>
       </c>
       <c r="D42" s="7">
-        <v>25.4</v>
+        <v>26.02</v>
       </c>
       <c r="E42" s="8">
-        <v>-2.4</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2808,13 +2818,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>-0.3</v>
+        <v>-1.76</v>
       </c>
       <c r="D43" s="7">
-        <v>-1.76</v>
+        <v>-0.58</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.46</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2825,13 +2835,13 @@
         <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>73.66</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="D44" s="7">
-        <v>86.31999999999999</v>
-      </c>
-      <c r="E44" s="9">
-        <v>12.66</v>
+        <v>86.67</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2842,98 +2852,98 @@
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-35.34</v>
+        <v>-36.85</v>
       </c>
       <c r="D45" s="7">
-        <v>-36.85</v>
+        <v>-33.94</v>
       </c>
       <c r="E45" s="8">
-        <v>-1.51</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-5.25</v>
+        <v>-6.67</v>
       </c>
       <c r="D46" s="7">
-        <v>-4.28</v>
+        <v>-7.42</v>
       </c>
       <c r="E46" s="9">
-        <v>0.97</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-14.66</v>
+        <v>-3.43</v>
       </c>
       <c r="D47" s="7">
-        <v>-15.31</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.65</v>
+        <v>-4.5</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-14.94</v>
+        <v>-4.51</v>
       </c>
       <c r="D48" s="7">
-        <v>-14.66</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.28</v>
+        <v>-3.92</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>-6.9</v>
+        <v>636.3</v>
       </c>
       <c r="D49" s="7">
-        <v>-6.67</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.23</v>
+        <v>665.65</v>
+      </c>
+      <c r="E49" s="8">
+        <v>29.35</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C50" s="7">
-        <v>-47.35</v>
+        <v>560</v>
       </c>
       <c r="D50" s="7">
-        <v>-46.43</v>
+        <v>555.5</v>
       </c>
       <c r="E50" s="9">
-        <v>0.92</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2941,16 +2951,16 @@
         <v>43</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="7">
-        <v>-2.8</v>
+        <v>339.15</v>
       </c>
       <c r="D51" s="7">
-        <v>-3.43</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.63</v>
+        <v>335.4</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2958,16 +2968,16 @@
         <v>44</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>-4.14</v>
+        <v>1270</v>
       </c>
       <c r="D52" s="7">
-        <v>-4.51</v>
+        <v>1277.8</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.37</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2975,16 +2985,16 @@
         <v>45</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>-1.28</v>
+        <v>91.39</v>
       </c>
       <c r="D53" s="7">
-        <v>0</v>
-      </c>
-      <c r="E53" s="9">
-        <v>1.28</v>
+        <v>91.45</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2992,67 +3002,67 @@
         <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C54" s="7">
-        <v>651.5</v>
+        <v>45</v>
       </c>
       <c r="D54" s="7">
-        <v>636.3</v>
+        <v>66</v>
       </c>
       <c r="E54" s="8">
-        <v>-15.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C55" s="7">
-        <v>264.4</v>
+        <v>55</v>
       </c>
       <c r="D55" s="7">
-        <v>267.1</v>
+        <v>45</v>
       </c>
       <c r="E55" s="9">
-        <v>2.7</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C56" s="7">
-        <v>1099.9</v>
+        <v>66</v>
       </c>
       <c r="D56" s="7">
-        <v>1091.5</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-8.4</v>
+        <v>55</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-11</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>735.4</v>
+        <v>47.3</v>
       </c>
       <c r="D57" s="7">
-        <v>737.85</v>
-      </c>
-      <c r="E57" s="9">
-        <v>2.45</v>
+        <v>55.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>8.65</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3060,430 +3070,226 @@
         <v>41</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C58" s="7">
-        <v>558.6</v>
+        <v>50.28</v>
       </c>
       <c r="D58" s="7">
-        <v>560</v>
+        <v>47.54</v>
       </c>
       <c r="E58" s="9">
-        <v>1.4</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C59" s="7">
-        <v>11670</v>
+        <v>56.59</v>
       </c>
       <c r="D59" s="7">
-        <v>11874</v>
+        <v>53.63</v>
       </c>
       <c r="E59" s="9">
-        <v>204</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C60" s="7">
-        <v>341.35</v>
+        <v>49.2</v>
       </c>
       <c r="D60" s="7">
-        <v>339.15</v>
+        <v>51.69</v>
       </c>
       <c r="E60" s="8">
-        <v>-2.2</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="7">
-        <v>1275</v>
+        <v>75.34</v>
       </c>
       <c r="D61" s="7">
-        <v>1270</v>
+        <v>75.38</v>
       </c>
       <c r="E61" s="8">
-        <v>-5</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C62" s="7">
-        <v>87.04000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="D62" s="7">
-        <v>91.39</v>
-      </c>
-      <c r="E62" s="9">
-        <v>4.35</v>
+        <v>219.3</v>
+      </c>
+      <c r="E62" s="8">
+        <v>236.4</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C63" s="7">
-        <v>34</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="D63" s="7">
-        <v>23</v>
+        <v>-64.09</v>
       </c>
       <c r="E63" s="8">
-        <v>-11</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C64" s="7">
-        <v>23</v>
+        <v>-48.21</v>
       </c>
       <c r="D64" s="7">
-        <v>34</v>
-      </c>
-      <c r="E64" s="9">
-        <v>11</v>
+        <v>-30.29</v>
+      </c>
+      <c r="E64" s="8">
+        <v>17.92</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C65" s="7">
-        <v>52.23</v>
+        <v>-36.24</v>
       </c>
       <c r="D65" s="7">
-        <v>47.3</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="E65" s="8">
-        <v>-4.93</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C66" s="7">
-        <v>51.12</v>
+        <v>-37.68</v>
       </c>
       <c r="D66" s="7">
-        <v>53.36</v>
-      </c>
-      <c r="E66" s="9">
-        <v>2.24</v>
+        <v>-35.06</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.62</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C67" s="7">
-        <v>53.09</v>
+        <v>67.27</v>
       </c>
       <c r="D67" s="7">
-        <v>50.7</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.39</v>
+        <v>-63.97</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-131.24</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C68" s="7">
-        <v>54.5</v>
+        <v>-38.77</v>
       </c>
       <c r="D68" s="7">
-        <v>55.71</v>
-      </c>
-      <c r="E68" s="9">
-        <v>1.21</v>
+        <v>-29.81</v>
+      </c>
+      <c r="E68" s="8">
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C69" s="7">
-        <v>49.44</v>
+        <v>-45.97</v>
       </c>
       <c r="D69" s="7">
-        <v>50.28</v>
-      </c>
-      <c r="E69" s="9">
-        <v>0.84</v>
+        <v>-21.41</v>
+      </c>
+      <c r="E69" s="8">
+        <v>24.56</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="7">
-        <v>50.13</v>
+        <v>-84.15000000000001</v>
       </c>
       <c r="D70" s="7">
-        <v>54.22</v>
-      </c>
-      <c r="E70" s="9">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>58.34</v>
-      </c>
-      <c r="D71" s="7">
-        <v>56.59</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>50.76</v>
-      </c>
-      <c r="D72" s="7">
-        <v>49.2</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>72.22</v>
-      </c>
-      <c r="D73" s="7">
-        <v>75.34</v>
-      </c>
-      <c r="E73" s="9">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>44.64</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-17.1</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-61.74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-46.64</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-70.31999999999999</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-23.68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-71.76000000000001</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-48.21</v>
-      </c>
-      <c r="E76" s="9">
-        <v>23.55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-59.57</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-36.24</v>
-      </c>
-      <c r="E77" s="9">
-        <v>23.33</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-12.96</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-37.68</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-24.72</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-16.11</v>
-      </c>
-      <c r="D79" s="7">
-        <v>67.27</v>
-      </c>
-      <c r="E79" s="9">
-        <v>83.38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-27.82</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-38.77</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-10.95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-4.03</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-45.97</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-41.94</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-81.23999999999999</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-84.15000000000001</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-2.91</v>
+        <v>-34.79</v>
+      </c>
+      <c r="E70" s="8">
+        <v>49.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3507,28 +3313,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3542,16 +3348,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>54.7</v>
+        <v>55.4</v>
       </c>
       <c r="E2" s="12">
         <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="G2" s="12">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3688,31 +3494,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3696</v>
+        <v>0.375</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3516</v>
+        <v>0.3563</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3096</v>
+        <v>0.3036</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2083</v>
+        <v>0.2168</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1886</v>
+        <v>0.1914</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1839</v>
+        <v>0.1791</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1179</v>
+        <v>0.1243</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0163</v>
+        <v>-0.0246</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.08650000000000001</v>
+        <v>-0.07389999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="97">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,7 +196,7 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.3 → 56.0</t>
+    <t>47.3 → 50.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
@@ -205,7 +205,7 @@
     <t>47.3</t>
   </si>
   <si>
-    <t>56.0</t>
+    <t>50.2</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
@@ -214,16 +214,37 @@
     <t>No → Yes</t>
   </si>
   <si>
-    <t>49.2 → 51.7</t>
-  </si>
-  <si>
-    <t>49.2</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>50.3 → 47.5</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>75.3 → 66.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>75.3</t>
+  </si>
+  <si>
+    <t>66.3</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -5.0%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-5.0%</t>
+  </si>
+  <si>
+    <t>50.3 → 43.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
@@ -232,7 +253,25 @@
     <t>50.3</t>
   </si>
   <si>
-    <t>47.5</t>
+    <t>43.4</t>
+  </si>
+  <si>
+    <t>54.2 → 46.0</t>
+  </si>
+  <si>
+    <t>54.2</t>
+  </si>
+  <si>
+    <t>46.0</t>
+  </si>
+  <si>
+    <t>56.6 → 48.7</t>
+  </si>
+  <si>
+    <t>56.6</t>
+  </si>
+  <si>
+    <t>48.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -284,7 +323,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,13 +364,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,6 +405,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,14 +495,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -459,7 +512,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -818,8 +871,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -958,10 +1010,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>665.65</v>
+        <v>646.65</v>
       </c>
       <c r="D2">
-        <v>4.61</v>
+        <v>-2.85</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -970,46 +1022,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.94</v>
+        <v>-35.82</v>
       </c>
       <c r="H2">
-        <v>81.28</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I2">
-        <v>5.91</v>
+        <v>2.72</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>-2.94</v>
       </c>
       <c r="K2">
-        <v>-5.05</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L2">
-        <v>28.43</v>
+        <v>22.74</v>
       </c>
       <c r="M2">
-        <v>-7.39</v>
+        <v>-7.69</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>649.9</v>
+        <v>653.33</v>
       </c>
       <c r="Q2">
-        <v>638.26</v>
+        <v>637.1</v>
       </c>
       <c r="R2">
-        <v>656.9299999999999</v>
+        <v>657.1</v>
       </c>
       <c r="S2">
-        <v>616.77</v>
+        <v>617.1799999999999</v>
       </c>
       <c r="T2">
-        <v>7.93</v>
+        <v>4.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1024,34 +1076,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.95</v>
+        <v>50.21</v>
       </c>
       <c r="Z2">
-        <v>-2.35</v>
+        <v>-1.9</v>
       </c>
       <c r="AA2">
-        <v>-6.61</v>
+        <v>-5.67</v>
       </c>
       <c r="AB2">
-        <v>4.26</v>
+        <v>3.77</v>
       </c>
       <c r="AC2">
-        <v>66.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AD2">
-        <v>75.41</v>
+        <v>66.47</v>
       </c>
       <c r="AE2">
-        <v>26.49</v>
+        <v>26.32</v>
       </c>
       <c r="AF2">
-        <v>219.3</v>
+        <v>-39.71</v>
       </c>
       <c r="AG2">
-        <v>667.36</v>
+        <v>662.52</v>
       </c>
       <c r="AH2">
-        <v>609.16</v>
+        <v>611.6900000000001</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1060,7 +1112,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.02</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1071,10 +1123,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>267.1</v>
+        <v>268.65</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1083,25 +1135,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-4.28</v>
+        <v>-3.73</v>
       </c>
       <c r="H3">
-        <v>74.31</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="I3">
-        <v>-4.28</v>
+        <v>-1.79</v>
       </c>
       <c r="J3">
-        <v>-0.87</v>
+        <v>1.02</v>
       </c>
       <c r="K3">
-        <v>20.52</v>
+        <v>23.49</v>
       </c>
       <c r="L3">
-        <v>32.57</v>
+        <v>36.25</v>
       </c>
       <c r="M3">
-        <v>35.63</v>
+        <v>36.4</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1110,19 +1162,19 @@
         <v>82</v>
       </c>
       <c r="P3">
-        <v>268.34</v>
+        <v>267.36</v>
       </c>
       <c r="Q3">
-        <v>263.36</v>
+        <v>263.68</v>
       </c>
       <c r="R3">
-        <v>259.23</v>
+        <v>259.88</v>
       </c>
       <c r="S3">
-        <v>206.95</v>
+        <v>207.41</v>
       </c>
       <c r="T3">
-        <v>29.07</v>
+        <v>29.53</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1137,34 +1189,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>53.36</v>
+        <v>54.74</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="AA3">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="AB3">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>34.2</v>
+        <v>37.03</v>
       </c>
       <c r="AD3">
-        <v>42.89</v>
+        <v>37.37</v>
       </c>
       <c r="AE3">
-        <v>8.17</v>
+        <v>7.94</v>
       </c>
       <c r="AF3">
-        <v>-64.09</v>
+        <v>-50.86</v>
       </c>
       <c r="AG3">
-        <v>277.39</v>
+        <v>277.89</v>
       </c>
       <c r="AH3">
-        <v>249.34</v>
+        <v>249.48</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1173,7 +1225,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>17.82</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1184,10 +1236,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1091.5</v>
+        <v>1101.5</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1196,46 +1248,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-15.31</v>
+        <v>-14.53</v>
       </c>
       <c r="H4">
-        <v>15.4</v>
+        <v>16.46</v>
       </c>
       <c r="I4">
-        <v>-2.98</v>
+        <v>0.59</v>
       </c>
       <c r="J4">
-        <v>6.49</v>
+        <v>6.6</v>
       </c>
       <c r="K4">
-        <v>-10.99</v>
+        <v>-9.94</v>
       </c>
       <c r="L4">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="M4">
-        <v>21.68</v>
+        <v>22.32</v>
       </c>
       <c r="N4">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O4">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P4">
-        <v>1097.98</v>
+        <v>1099.28</v>
       </c>
       <c r="Q4">
-        <v>1086.68</v>
+        <v>1089.53</v>
       </c>
       <c r="R4">
-        <v>1082.78</v>
+        <v>1081.68</v>
       </c>
       <c r="S4">
-        <v>1123</v>
+        <v>1123.16</v>
       </c>
       <c r="T4">
-        <v>-2.81</v>
+        <v>-1.93</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1250,34 +1302,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.7</v>
+        <v>53.58</v>
       </c>
       <c r="Z4">
-        <v>7.06</v>
+        <v>6.96</v>
       </c>
       <c r="AA4">
-        <v>5.99</v>
+        <v>6.19</v>
       </c>
       <c r="AB4">
-        <v>1.07</v>
+        <v>0.77</v>
       </c>
       <c r="AC4">
-        <v>19.15</v>
+        <v>14.27</v>
       </c>
       <c r="AD4">
-        <v>37.69</v>
+        <v>25.13</v>
       </c>
       <c r="AE4">
-        <v>23.76</v>
+        <v>24.08</v>
       </c>
       <c r="AF4">
-        <v>-30.29</v>
+        <v>-39.24</v>
       </c>
       <c r="AG4">
-        <v>1143.24</v>
+        <v>1142.81</v>
       </c>
       <c r="AH4">
-        <v>1030.13</v>
+        <v>1036.24</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1286,7 +1338,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>26.13</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1297,10 +1349,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>737.85</v>
+        <v>732.4</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1309,46 +1361,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.66</v>
+        <v>-15.29</v>
       </c>
       <c r="H5">
-        <v>11.47</v>
+        <v>10.65</v>
       </c>
       <c r="I5">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J5">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="K5">
-        <v>-0.18</v>
+        <v>-0.62</v>
       </c>
       <c r="L5">
-        <v>9.199999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="M5">
-        <v>37.5</v>
+        <v>38.15</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>734.8200000000001</v>
+        <v>736.28</v>
       </c>
       <c r="Q5">
-        <v>733.14</v>
+        <v>732.8099999999999</v>
       </c>
       <c r="R5">
-        <v>713.6900000000001</v>
+        <v>715.03</v>
       </c>
       <c r="S5">
-        <v>750.9400000000001</v>
+        <v>750.59</v>
       </c>
       <c r="T5">
-        <v>-1.74</v>
+        <v>-2.42</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1363,43 +1415,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>55.71</v>
+        <v>52.15</v>
       </c>
       <c r="Z5">
-        <v>5.18</v>
+        <v>4.65</v>
       </c>
       <c r="AA5">
-        <v>5.72</v>
+        <v>5.51</v>
       </c>
       <c r="AB5">
-        <v>-0.54</v>
+        <v>-0.86</v>
       </c>
       <c r="AC5">
-        <v>50.24</v>
+        <v>43.31</v>
       </c>
       <c r="AD5">
-        <v>45.57</v>
+        <v>48.36</v>
       </c>
       <c r="AE5">
-        <v>15.76</v>
+        <v>16.62</v>
       </c>
       <c r="AF5">
-        <v>-9.859999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AG5">
-        <v>746.99</v>
+        <v>746.37</v>
       </c>
       <c r="AH5">
-        <v>719.29</v>
+        <v>719.24</v>
       </c>
       <c r="AI5">
-        <v>690.96</v>
+        <v>692.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>18.17</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1410,10 +1462,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>555.5</v>
+        <v>548.1</v>
       </c>
       <c r="D6">
-        <v>-0.8</v>
+        <v>-1.33</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1422,46 +1474,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-7.42</v>
+        <v>-8.65</v>
       </c>
       <c r="H6">
-        <v>26.66</v>
+        <v>24.98</v>
       </c>
       <c r="I6">
-        <v>-3.89</v>
+        <v>-2.65</v>
       </c>
       <c r="J6">
-        <v>2.64</v>
+        <v>-3.45</v>
       </c>
       <c r="K6">
-        <v>4.55</v>
+        <v>2.4</v>
       </c>
       <c r="L6">
-        <v>4.16</v>
+        <v>3.15</v>
       </c>
       <c r="M6">
-        <v>17.91</v>
+        <v>18.06</v>
       </c>
       <c r="N6">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P6">
-        <v>559.17</v>
+        <v>556.1900000000001</v>
       </c>
       <c r="Q6">
-        <v>558.88</v>
+        <v>557.98</v>
       </c>
       <c r="R6">
-        <v>560.38</v>
+        <v>559.92</v>
       </c>
       <c r="S6">
-        <v>519.24</v>
+        <v>519.3099999999999</v>
       </c>
       <c r="T6">
-        <v>6.98</v>
+        <v>5.54</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1476,34 +1528,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.54</v>
+        <v>43.36</v>
       </c>
       <c r="Z6">
-        <v>0.88</v>
+        <v>-0.15</v>
       </c>
       <c r="AA6">
-        <v>1.03</v>
+        <v>0.8</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC6">
-        <v>33.21</v>
+        <v>21.96</v>
       </c>
       <c r="AD6">
-        <v>36.6</v>
+        <v>30.68</v>
       </c>
       <c r="AE6">
-        <v>12.34</v>
+        <v>12.1</v>
       </c>
       <c r="AF6">
-        <v>-35.06</v>
+        <v>-37.04</v>
       </c>
       <c r="AG6">
-        <v>576.6900000000001</v>
+        <v>576.05</v>
       </c>
       <c r="AH6">
-        <v>541.08</v>
+        <v>539.9</v>
       </c>
       <c r="AI6">
         <v>584.25</v>
@@ -1512,7 +1564,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>17.83</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1575,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11874</v>
+        <v>11489</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-3.24</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1535,46 +1587,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-46.43</v>
+        <v>-48.17</v>
       </c>
       <c r="H7">
-        <v>11.44</v>
+        <v>7.83</v>
       </c>
       <c r="I7">
-        <v>0.19</v>
+        <v>-3.79</v>
       </c>
       <c r="J7">
-        <v>8.130000000000001</v>
+        <v>3.96</v>
       </c>
       <c r="K7">
-        <v>-6.36</v>
+        <v>-8.9</v>
       </c>
       <c r="L7">
-        <v>-33.63</v>
+        <v>-35.79</v>
       </c>
       <c r="M7">
-        <v>19.14</v>
+        <v>18.83</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>11786.2</v>
+        <v>11695.8</v>
       </c>
       <c r="Q7">
-        <v>11521</v>
+        <v>11546.4</v>
       </c>
       <c r="R7">
-        <v>11795.84</v>
+        <v>11779.98</v>
       </c>
       <c r="S7">
-        <v>15159.6</v>
+        <v>15131.67</v>
       </c>
       <c r="T7">
-        <v>-21.67</v>
+        <v>-24.07</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1589,34 +1641,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>54.22</v>
+        <v>45.96</v>
       </c>
       <c r="Z7">
-        <v>69.75</v>
+        <v>42.92</v>
       </c>
       <c r="AA7">
-        <v>19.97</v>
+        <v>24.56</v>
       </c>
       <c r="AB7">
-        <v>49.78</v>
+        <v>18.36</v>
       </c>
       <c r="AC7">
-        <v>49.99</v>
+        <v>38.65</v>
       </c>
       <c r="AD7">
-        <v>50.81</v>
+        <v>45.72</v>
       </c>
       <c r="AE7">
-        <v>379.65</v>
+        <v>386.32</v>
       </c>
       <c r="AF7">
-        <v>-63.97</v>
+        <v>-24.55</v>
       </c>
       <c r="AG7">
-        <v>12563.04</v>
+        <v>12557.32</v>
       </c>
       <c r="AH7">
-        <v>10478.96</v>
+        <v>10535.48</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1625,7 +1677,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.26</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1636,10 +1688,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>335.4</v>
+        <v>328.65</v>
       </c>
       <c r="D8">
-        <v>-1.11</v>
+        <v>-2.01</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1648,46 +1700,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-4.5</v>
+        <v>-6.42</v>
       </c>
       <c r="H8">
-        <v>43.14</v>
+        <v>40.26</v>
       </c>
       <c r="I8">
-        <v>-1.93</v>
+        <v>-3.86</v>
       </c>
       <c r="J8">
-        <v>-1.97</v>
+        <v>-5.68</v>
       </c>
       <c r="K8">
-        <v>26.02</v>
+        <v>25.01</v>
       </c>
       <c r="L8">
-        <v>12.97</v>
+        <v>10.47</v>
       </c>
       <c r="M8">
-        <v>30.36</v>
+        <v>29.41</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>340.87</v>
+        <v>338.23</v>
       </c>
       <c r="Q8">
-        <v>330.6</v>
+        <v>329.8</v>
       </c>
       <c r="R8">
-        <v>322.2</v>
+        <v>323.4</v>
       </c>
       <c r="S8">
-        <v>282.11</v>
+        <v>282.27</v>
       </c>
       <c r="T8">
-        <v>18.89</v>
+        <v>16.43</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1702,34 +1754,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>53.63</v>
+        <v>48.7</v>
       </c>
       <c r="Z8">
-        <v>4.93</v>
+        <v>3.98</v>
       </c>
       <c r="AA8">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="AB8">
-        <v>0.3</v>
+        <v>-0.51</v>
       </c>
       <c r="AC8">
-        <v>66.98</v>
+        <v>50.53</v>
       </c>
       <c r="AD8">
-        <v>80.59</v>
+        <v>66.61</v>
       </c>
       <c r="AE8">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="AF8">
-        <v>-29.81</v>
+        <v>-44.23</v>
       </c>
       <c r="AG8">
-        <v>350.95</v>
+        <v>349.07</v>
       </c>
       <c r="AH8">
-        <v>310.25</v>
+        <v>310.54</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1738,7 +1790,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>30.62</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1749,10 +1801,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1277.8</v>
+        <v>1267.6</v>
       </c>
       <c r="D9">
-        <v>0.61</v>
+        <v>-0.8</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1761,46 +1813,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-3.92</v>
+        <v>-4.69</v>
       </c>
       <c r="H9">
-        <v>24.47</v>
+        <v>23.48</v>
       </c>
       <c r="I9">
-        <v>-1.86</v>
+        <v>-1.23</v>
       </c>
       <c r="J9">
-        <v>3.27</v>
+        <v>0.84</v>
       </c>
       <c r="K9">
-        <v>-0.58</v>
+        <v>-1.22</v>
       </c>
       <c r="L9">
-        <v>21.38</v>
+        <v>20.93</v>
       </c>
       <c r="M9">
-        <v>12.43</v>
+        <v>12.45</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P9">
-        <v>1275.06</v>
+        <v>1271.9</v>
       </c>
       <c r="Q9">
-        <v>1276.89</v>
+        <v>1276.9</v>
       </c>
       <c r="R9">
-        <v>1261.46</v>
+        <v>1261.6</v>
       </c>
       <c r="S9">
-        <v>1216.55</v>
+        <v>1216.85</v>
       </c>
       <c r="T9">
-        <v>5.03</v>
+        <v>4.17</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1815,34 +1867,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>51.69</v>
+        <v>48.36</v>
       </c>
       <c r="Z9">
-        <v>7.05</v>
+        <v>5.51</v>
       </c>
       <c r="AA9">
-        <v>9.17</v>
+        <v>8.44</v>
       </c>
       <c r="AB9">
-        <v>-2.12</v>
+        <v>-2.92</v>
       </c>
       <c r="AC9">
-        <v>7.75</v>
+        <v>4.54</v>
       </c>
       <c r="AD9">
-        <v>9.27</v>
+        <v>6.06</v>
       </c>
       <c r="AE9">
-        <v>25.88</v>
+        <v>25.51</v>
       </c>
       <c r="AF9">
-        <v>-21.41</v>
+        <v>-58.23</v>
       </c>
       <c r="AG9">
         <v>1323.4</v>
       </c>
       <c r="AH9">
-        <v>1230.38</v>
+        <v>1230.4</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1851,7 +1903,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.92</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1914,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>91.45</v>
+        <v>86.88</v>
       </c>
       <c r="D10">
-        <v>0.07000000000000001</v>
+        <v>-5</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1874,46 +1926,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H10">
-        <v>153.46</v>
+        <v>140.8</v>
       </c>
       <c r="I10">
-        <v>8.390000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="J10">
-        <v>86.67</v>
+        <v>47.81</v>
       </c>
       <c r="K10">
-        <v>86.67</v>
+        <v>74.95</v>
       </c>
       <c r="L10">
-        <v>23.58</v>
+        <v>18.43</v>
       </c>
       <c r="M10">
-        <v>-2.46</v>
+        <v>-2.72</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P10">
-        <v>87.33</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="Q10">
-        <v>77.53</v>
+        <v>78.42</v>
       </c>
       <c r="R10">
-        <v>62.2</v>
+        <v>62.97</v>
       </c>
       <c r="S10">
-        <v>59.37</v>
+        <v>59.41</v>
       </c>
       <c r="T10">
-        <v>54.03</v>
+        <v>46.23</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1928,34 +1980,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>75.38</v>
+        <v>66.33</v>
       </c>
       <c r="Z10">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="AA10">
-        <v>7.64</v>
+        <v>7.73</v>
       </c>
       <c r="AB10">
-        <v>0.8</v>
+        <v>0.37</v>
       </c>
       <c r="AC10">
-        <v>73.67</v>
+        <v>61.81</v>
       </c>
       <c r="AD10">
-        <v>61.62</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="AE10">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="AF10">
-        <v>-34.79</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="AG10">
-        <v>96.93000000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="AH10">
-        <v>58.14</v>
+        <v>59.03</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1964,7 +2016,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>56.2</v>
+        <v>56.63</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2157,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2184,1112 +2236,1427 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>70</v>
+      <c r="C7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C13" s="8">
         <v>-6.61</v>
       </c>
-      <c r="D10" s="7">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8">
-        <v>7.61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="D13" s="8">
+        <v>-2.94</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C14" s="8">
         <v>-0.35</v>
       </c>
-      <c r="D11" s="7">
-        <v>-0.87</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="D14" s="8">
+        <v>1.02</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C15" s="8">
         <v>6.18</v>
       </c>
-      <c r="D12" s="7">
-        <v>6.49</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="D15" s="8">
+        <v>6.6</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C17" s="8">
         <v>3.05</v>
       </c>
-      <c r="D13" s="7">
-        <v>2.64</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="D17" s="8">
+        <v>-3.45</v>
+      </c>
+      <c r="E17" s="10">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C18" s="8">
         <v>6.05</v>
       </c>
-      <c r="D14" s="7">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="D18" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="E18" s="10">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C19" s="8">
         <v>-0.04</v>
       </c>
-      <c r="D15" s="7">
-        <v>-1.97</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="D19" s="8">
+        <v>-5.68</v>
+      </c>
+      <c r="E19" s="10">
+        <v>-5.64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C20" s="8">
         <v>4.01</v>
       </c>
-      <c r="D16" s="7">
-        <v>3.27</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="D20" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="E20" s="10">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C21" s="8">
         <v>81.37</v>
       </c>
-      <c r="D17" s="7">
-        <v>86.67</v>
-      </c>
-      <c r="E17" s="8">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="D21" s="8">
+        <v>47.81</v>
+      </c>
+      <c r="E21" s="10">
+        <v>-33.56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C22" s="8">
         <v>2.63</v>
       </c>
-      <c r="D18" s="7">
-        <v>5.91</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="D22" s="8">
+        <v>2.72</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C23" s="8">
         <v>-1.58</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D23" s="8">
+        <v>-1.79</v>
+      </c>
+      <c r="E23" s="10">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>-1.04</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.59</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1.01</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>-0.78</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-2.65</v>
+      </c>
+      <c r="E26" s="10">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-1.26</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-3.79</v>
+      </c>
+      <c r="E27" s="10">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>1.01</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-3.86</v>
+      </c>
+      <c r="E28" s="10">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-2.27</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-1.23</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="8">
+        <v>8.19</v>
+      </c>
+      <c r="D30" s="8">
+        <v>3.59</v>
+      </c>
+      <c r="E30" s="10">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>21.03</v>
+      </c>
+      <c r="D31" s="8">
+        <v>22.74</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>30.53</v>
+      </c>
+      <c r="D32" s="8">
+        <v>36.25</v>
+      </c>
+      <c r="E32" s="9">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>12.27</v>
+      </c>
+      <c r="D33" s="8">
+        <v>10.53</v>
+      </c>
+      <c r="E33" s="10">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="D34" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="E34" s="10">
+        <v>-5.29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>8.41</v>
+      </c>
+      <c r="D35" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="E35" s="10">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.73</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-35.79</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="8">
+        <v>14.12</v>
+      </c>
+      <c r="D37" s="8">
+        <v>10.47</v>
+      </c>
+      <c r="E37" s="10">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="8">
+        <v>21.04</v>
+      </c>
+      <c r="D38" s="8">
+        <v>20.93</v>
+      </c>
+      <c r="E38" s="10">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="8">
+        <v>21.63</v>
+      </c>
+      <c r="D39" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-7.66</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E40" s="10">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>22.11</v>
+      </c>
+      <c r="D41" s="8">
+        <v>23.49</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-11.39</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-9.94</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-1.44</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-0.62</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>6.21</v>
+      </c>
+      <c r="D44" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-6.3</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-8.9</v>
+      </c>
+      <c r="E45" s="10">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8">
+        <v>25.4</v>
+      </c>
+      <c r="D46" s="8">
+        <v>25.01</v>
+      </c>
+      <c r="E46" s="10">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-1.76</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-1.22</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="8">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="D48" s="8">
+        <v>74.95</v>
+      </c>
+      <c r="E48" s="10">
+        <v>-11.37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-36.85</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-35.82</v>
+      </c>
+      <c r="E49" s="9">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
         <v>-4.28</v>
       </c>
-      <c r="E19" s="9">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="D50" s="8">
+        <v>-3.73</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.04</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.98</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-15.31</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-14.53</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.44</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-14.66</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-15.29</v>
+      </c>
+      <c r="E52" s="10">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.89</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>-6.67</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-8.65</v>
+      </c>
+      <c r="E53" s="10">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-46.43</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-48.17</v>
+      </c>
+      <c r="E54" s="10">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.93</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-3.43</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-6.42</v>
+      </c>
+      <c r="E55" s="10">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-2.27</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="8">
+        <v>-4.51</v>
+      </c>
+      <c r="D56" s="8">
+        <v>-4.69</v>
+      </c>
+      <c r="E56" s="10">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>8.19</v>
-      </c>
-      <c r="D26" s="7">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B57" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-5</v>
+      </c>
+      <c r="E57" s="10">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>21.03</v>
-      </c>
-      <c r="D27" s="7">
-        <v>28.43</v>
-      </c>
-      <c r="E27" s="8">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>636.3</v>
+      </c>
+      <c r="D58" s="8">
+        <v>646.65</v>
+      </c>
+      <c r="E58" s="9">
+        <v>10.35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>30.53</v>
-      </c>
-      <c r="D28" s="7">
-        <v>32.57</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="8">
+        <v>267.1</v>
+      </c>
+      <c r="D59" s="8">
+        <v>268.65</v>
+      </c>
+      <c r="E59" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>12.27</v>
-      </c>
-      <c r="D29" s="7">
-        <v>10.36</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B60" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="8">
+        <v>1091.5</v>
+      </c>
+      <c r="D60" s="8">
+        <v>1101.5</v>
+      </c>
+      <c r="E60" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="D30" s="7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>737.85</v>
+      </c>
+      <c r="D61" s="8">
+        <v>732.4</v>
+      </c>
+      <c r="E61" s="10">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>8.41</v>
-      </c>
-      <c r="D31" s="7">
-        <v>4.16</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-4.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>560</v>
+      </c>
+      <c r="D62" s="8">
+        <v>548.1</v>
+      </c>
+      <c r="E62" s="10">
+        <v>-11.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-35.73</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-33.63</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>11874</v>
+      </c>
+      <c r="D63" s="8">
+        <v>11489</v>
+      </c>
+      <c r="E63" s="10">
+        <v>-385</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>14.12</v>
-      </c>
-      <c r="D33" s="7">
-        <v>12.97</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B64" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8">
+        <v>339.15</v>
+      </c>
+      <c r="D64" s="8">
+        <v>328.65</v>
+      </c>
+      <c r="E64" s="10">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>21.04</v>
-      </c>
-      <c r="D34" s="7">
-        <v>21.38</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B65" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1270</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1267.6</v>
+      </c>
+      <c r="E65" s="10">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>21.63</v>
-      </c>
-      <c r="D35" s="7">
-        <v>23.58</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B66" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="8">
+        <v>91.39</v>
+      </c>
+      <c r="D66" s="8">
+        <v>86.88</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-4.51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="8">
+        <v>45</v>
+      </c>
+      <c r="D67" s="8">
+        <v>55</v>
+      </c>
+      <c r="E67" s="9">
         <v>10</v>
       </c>
-      <c r="C36" s="7">
-        <v>-7.66</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-5.05</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="8">
+        <v>23</v>
+      </c>
+      <c r="D68" s="8">
+        <v>45</v>
+      </c>
+      <c r="E68" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="8">
+        <v>34</v>
+      </c>
+      <c r="D69" s="8">
+        <v>23</v>
+      </c>
+      <c r="E69" s="10">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="8">
+        <v>55</v>
+      </c>
+      <c r="D70" s="8">
+        <v>34</v>
+      </c>
+      <c r="E70" s="10">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="8">
+        <v>47.3</v>
+      </c>
+      <c r="D71" s="8">
+        <v>50.21</v>
+      </c>
+      <c r="E71" s="9">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>22.11</v>
-      </c>
-      <c r="D37" s="7">
-        <v>20.52</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="8">
+        <v>53.36</v>
+      </c>
+      <c r="D72" s="8">
+        <v>54.74</v>
+      </c>
+      <c r="E72" s="9">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-11.39</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-10.99</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>50.7</v>
+      </c>
+      <c r="D73" s="8">
+        <v>53.58</v>
+      </c>
+      <c r="E73" s="9">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-1.44</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>55.71</v>
+      </c>
+      <c r="D74" s="8">
+        <v>52.15</v>
+      </c>
+      <c r="E74" s="10">
+        <v>-3.56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>6.21</v>
-      </c>
-      <c r="D40" s="7">
-        <v>4.55</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>50.28</v>
+      </c>
+      <c r="D75" s="8">
+        <v>43.36</v>
+      </c>
+      <c r="E75" s="10">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-6.3</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="8">
+        <v>54.22</v>
+      </c>
+      <c r="D76" s="8">
+        <v>45.96</v>
+      </c>
+      <c r="E76" s="10">
+        <v>-8.26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>25.4</v>
-      </c>
-      <c r="D42" s="7">
-        <v>26.02</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B77" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="8">
+        <v>56.59</v>
+      </c>
+      <c r="D77" s="8">
+        <v>48.7</v>
+      </c>
+      <c r="E77" s="10">
+        <v>-7.89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-1.76</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-0.58</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="8">
+        <v>49.2</v>
+      </c>
+      <c r="D78" s="8">
+        <v>48.36</v>
+      </c>
+      <c r="E78" s="10">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>86.31999999999999</v>
-      </c>
-      <c r="D44" s="7">
-        <v>86.67</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="8">
+        <v>75.34</v>
+      </c>
+      <c r="D79" s="8">
+        <v>66.33</v>
+      </c>
+      <c r="E79" s="10">
+        <v>-9.01</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-36.85</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-33.94</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B80" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="8">
+        <v>-17.1</v>
+      </c>
+      <c r="D80" s="8">
+        <v>-39.71</v>
+      </c>
+      <c r="E80" s="10">
+        <v>-22.61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="8">
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="D81" s="8">
+        <v>-50.86</v>
+      </c>
+      <c r="E81" s="9">
+        <v>19.46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>-48.21</v>
+      </c>
+      <c r="D82" s="8">
+        <v>-39.24</v>
+      </c>
+      <c r="E82" s="9">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-36.24</v>
+      </c>
+      <c r="D83" s="8">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="E83" s="9">
+        <v>100.48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-6.67</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-7.42</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B84" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="8">
+        <v>-37.68</v>
+      </c>
+      <c r="D84" s="8">
+        <v>-37.04</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="8">
+        <v>67.27</v>
+      </c>
+      <c r="D85" s="8">
+        <v>-24.55</v>
+      </c>
+      <c r="E85" s="10">
+        <v>-91.81999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-3.43</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B86" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="8">
+        <v>-38.77</v>
+      </c>
+      <c r="D86" s="8">
+        <v>-44.23</v>
+      </c>
+      <c r="E86" s="10">
+        <v>-5.46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-4.51</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-3.92</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>636.3</v>
-      </c>
-      <c r="D49" s="7">
-        <v>665.65</v>
-      </c>
-      <c r="E49" s="8">
-        <v>29.35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>560</v>
-      </c>
-      <c r="D50" s="7">
-        <v>555.5</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>339.15</v>
-      </c>
-      <c r="D51" s="7">
-        <v>335.4</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>1270</v>
-      </c>
-      <c r="D52" s="7">
-        <v>1277.8</v>
-      </c>
-      <c r="E52" s="8">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
+      <c r="B87" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="8">
+        <v>-45.97</v>
+      </c>
+      <c r="D87" s="8">
+        <v>-58.23</v>
+      </c>
+      <c r="E87" s="10">
+        <v>-12.26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>91.39</v>
-      </c>
-      <c r="D53" s="7">
-        <v>91.45</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="7">
-        <v>45</v>
-      </c>
-      <c r="D54" s="7">
-        <v>66</v>
-      </c>
-      <c r="E54" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="7">
-        <v>55</v>
-      </c>
-      <c r="D55" s="7">
-        <v>45</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="7">
-        <v>66</v>
-      </c>
-      <c r="D56" s="7">
-        <v>55</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>47.3</v>
-      </c>
-      <c r="D57" s="7">
-        <v>55.95</v>
-      </c>
-      <c r="E57" s="8">
-        <v>8.65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>50.28</v>
-      </c>
-      <c r="D58" s="7">
-        <v>47.54</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>56.59</v>
-      </c>
-      <c r="D59" s="7">
-        <v>53.63</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>49.2</v>
-      </c>
-      <c r="D60" s="7">
-        <v>51.69</v>
-      </c>
-      <c r="E60" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>75.34</v>
-      </c>
-      <c r="D61" s="7">
-        <v>75.38</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="B88" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="7">
-        <v>-17.1</v>
-      </c>
-      <c r="D62" s="7">
-        <v>219.3</v>
-      </c>
-      <c r="E62" s="8">
-        <v>236.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-70.31999999999999</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-64.09</v>
-      </c>
-      <c r="E63" s="8">
-        <v>6.23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-48.21</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-30.29</v>
-      </c>
-      <c r="E64" s="8">
-        <v>17.92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-36.24</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E65" s="8">
-        <v>26.38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-37.68</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-35.06</v>
-      </c>
-      <c r="E66" s="8">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>67.27</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-63.97</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-131.24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-38.77</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-29.81</v>
-      </c>
-      <c r="E68" s="8">
-        <v>8.960000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>-45.97</v>
-      </c>
-      <c r="D69" s="7">
-        <v>-21.41</v>
-      </c>
-      <c r="E69" s="8">
-        <v>24.56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
+      <c r="C88" s="8">
         <v>-84.15000000000001</v>
       </c>
-      <c r="D70" s="7">
-        <v>-34.79</v>
-      </c>
-      <c r="E70" s="8">
-        <v>49.36</v>
+      <c r="D88" s="8">
+        <v>-72.73999999999999</v>
+      </c>
+      <c r="E88" s="9">
+        <v>11.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3309,60 +3676,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>83</v>
+      <c r="B1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>60.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="13">
+        <v>51.5</v>
+      </c>
+      <c r="E2" s="13">
+        <v>70</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5.4</v>
+      </c>
+      <c r="G2" s="13">
+        <v>10.8</v>
+      </c>
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>11.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>12.7</v>
-      </c>
-      <c r="H2" s="12">
-        <v>55.4</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -3464,61 +3831,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.375</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3563</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3036</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2168</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1914</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1791</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1243</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0246</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.07389999999999999</v>
+      <c r="A2" s="16">
+        <v>0.3815</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.364</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.2941</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2232</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1883</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1806</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1245</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.0272</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.07690000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,82 +196,37 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.3 → 50.2</t>
+    <t>48.4 → 54.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>47.3</t>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>54.0</t>
+  </si>
+  <si>
+    <t>50.2 → 47.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.2</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>75.3 → 66.3</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>75.3</t>
-  </si>
-  <si>
-    <t>66.3</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -5.0%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-5.0%</t>
-  </si>
-  <si>
-    <t>50.3 → 43.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>43.4</t>
-  </si>
-  <si>
-    <t>54.2 → 46.0</t>
-  </si>
-  <si>
-    <t>54.2</t>
-  </si>
-  <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>56.6 → 48.7</t>
-  </si>
-  <si>
-    <t>56.6</t>
-  </si>
-  <si>
-    <t>48.7</t>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>52.1 → 47.1</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>47.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -323,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,20 +319,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,12 +353,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -495,15 +437,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -512,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -871,7 +812,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -1010,10 +952,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>646.65</v>
+        <v>638.35</v>
       </c>
       <c r="D2">
-        <v>-2.85</v>
+        <v>-1.28</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -1022,46 +964,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.82</v>
+        <v>-36.65</v>
       </c>
       <c r="H2">
-        <v>76.09999999999999</v>
+        <v>73.84</v>
       </c>
       <c r="I2">
-        <v>2.72</v>
+        <v>-4.23</v>
       </c>
       <c r="J2">
-        <v>-2.94</v>
+        <v>-4.7</v>
       </c>
       <c r="K2">
-        <v>-8.199999999999999</v>
+        <v>-7.73</v>
       </c>
       <c r="L2">
-        <v>22.74</v>
+        <v>21.87</v>
       </c>
       <c r="M2">
-        <v>-7.69</v>
+        <v>-7.37</v>
       </c>
       <c r="N2">
         <v>55</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>653.33</v>
+        <v>647.6900000000001</v>
       </c>
       <c r="Q2">
-        <v>637.1</v>
+        <v>636.64</v>
       </c>
       <c r="R2">
-        <v>657.1</v>
+        <v>656.47</v>
       </c>
       <c r="S2">
-        <v>617.1799999999999</v>
+        <v>617.5599999999999</v>
       </c>
       <c r="T2">
-        <v>4.77</v>
+        <v>3.37</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1076,34 +1018,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>50.21</v>
+        <v>47.89</v>
       </c>
       <c r="Z2">
-        <v>-1.9</v>
+        <v>-2.18</v>
       </c>
       <c r="AA2">
-        <v>-5.67</v>
+        <v>-4.97</v>
       </c>
       <c r="AB2">
-        <v>3.77</v>
+        <v>2.79</v>
       </c>
       <c r="AC2">
-        <v>62.8</v>
+        <v>63.91</v>
       </c>
       <c r="AD2">
-        <v>66.47</v>
+        <v>64.44</v>
       </c>
       <c r="AE2">
-        <v>26.32</v>
+        <v>25.58</v>
       </c>
       <c r="AF2">
-        <v>-39.71</v>
+        <v>-61.11</v>
       </c>
       <c r="AG2">
-        <v>662.52</v>
+        <v>661.58</v>
       </c>
       <c r="AH2">
-        <v>611.6900000000001</v>
+        <v>611.7</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1112,7 +1054,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.22</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1123,10 +1065,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>268.65</v>
+        <v>268.7</v>
       </c>
       <c r="D3">
-        <v>0.58</v>
+        <v>0.02</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1135,46 +1077,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-3.73</v>
+        <v>-3.71</v>
       </c>
       <c r="H3">
-        <v>75.31999999999999</v>
+        <v>75.36</v>
       </c>
       <c r="I3">
-        <v>-1.79</v>
+        <v>-0.32</v>
       </c>
       <c r="J3">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="K3">
-        <v>23.49</v>
+        <v>23.78</v>
       </c>
       <c r="L3">
-        <v>36.25</v>
+        <v>33.46</v>
       </c>
       <c r="M3">
-        <v>36.4</v>
+        <v>36.27</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>267.36</v>
+        <v>267.19</v>
       </c>
       <c r="Q3">
-        <v>263.68</v>
+        <v>263.86</v>
       </c>
       <c r="R3">
-        <v>259.88</v>
+        <v>260.46</v>
       </c>
       <c r="S3">
-        <v>207.41</v>
+        <v>207.88</v>
       </c>
       <c r="T3">
-        <v>29.53</v>
+        <v>29.26</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1189,34 +1131,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>54.74</v>
+        <v>54.79</v>
       </c>
       <c r="Z3">
+        <v>2.72</v>
+      </c>
+      <c r="AA3">
         <v>2.79</v>
       </c>
-      <c r="AA3">
-        <v>2.81</v>
-      </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="AC3">
-        <v>37.03</v>
+        <v>36.82</v>
       </c>
       <c r="AD3">
-        <v>37.37</v>
+        <v>36.01</v>
       </c>
       <c r="AE3">
-        <v>7.94</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AF3">
-        <v>-50.86</v>
+        <v>3.47</v>
       </c>
       <c r="AG3">
-        <v>277.89</v>
+        <v>278.23</v>
       </c>
       <c r="AH3">
-        <v>249.48</v>
+        <v>249.49</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1225,7 +1167,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>17.22</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1236,10 +1178,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1101.5</v>
+        <v>1115</v>
       </c>
       <c r="D4">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1248,46 +1190,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-14.53</v>
+        <v>-13.49</v>
       </c>
       <c r="H4">
-        <v>16.46</v>
+        <v>17.89</v>
       </c>
       <c r="I4">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="J4">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="K4">
-        <v>-9.94</v>
+        <v>-6.83</v>
       </c>
       <c r="L4">
-        <v>10.53</v>
+        <v>12.13</v>
       </c>
       <c r="M4">
-        <v>22.32</v>
+        <v>24.6</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P4">
-        <v>1099.28</v>
+        <v>1099.88</v>
       </c>
       <c r="Q4">
-        <v>1089.53</v>
+        <v>1093.03</v>
       </c>
       <c r="R4">
-        <v>1081.68</v>
+        <v>1080.99</v>
       </c>
       <c r="S4">
-        <v>1123.16</v>
+        <v>1123.38</v>
       </c>
       <c r="T4">
-        <v>-1.93</v>
+        <v>-0.75</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1302,34 +1244,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>53.58</v>
+        <v>57.21</v>
       </c>
       <c r="Z4">
-        <v>6.96</v>
+        <v>7.87</v>
       </c>
       <c r="AA4">
-        <v>6.19</v>
+        <v>6.52</v>
       </c>
       <c r="AB4">
-        <v>0.77</v>
+        <v>1.35</v>
       </c>
       <c r="AC4">
-        <v>14.27</v>
+        <v>22.6</v>
       </c>
       <c r="AD4">
-        <v>25.13</v>
+        <v>18.67</v>
       </c>
       <c r="AE4">
-        <v>24.08</v>
+        <v>24.26</v>
       </c>
       <c r="AF4">
-        <v>-39.24</v>
+        <v>27.65</v>
       </c>
       <c r="AG4">
-        <v>1142.81</v>
+        <v>1143.1</v>
       </c>
       <c r="AH4">
-        <v>1036.24</v>
+        <v>1042.95</v>
       </c>
       <c r="AI4">
         <v>1044.51</v>
@@ -1338,7 +1280,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>26.83</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1349,10 +1291,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>732.4</v>
+        <v>724</v>
       </c>
       <c r="D5">
-        <v>-0.74</v>
+        <v>-1.15</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1361,46 +1303,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.29</v>
+        <v>-16.26</v>
       </c>
       <c r="H5">
-        <v>10.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I5">
-        <v>1.01</v>
+        <v>-1.88</v>
       </c>
       <c r="J5">
-        <v>0.23</v>
+        <v>-2.04</v>
       </c>
       <c r="K5">
-        <v>-0.62</v>
+        <v>-1.73</v>
       </c>
       <c r="L5">
-        <v>3.09</v>
+        <v>0.7</v>
       </c>
       <c r="M5">
-        <v>38.15</v>
+        <v>40.05</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>736.28</v>
+        <v>733.5</v>
       </c>
       <c r="Q5">
-        <v>732.8099999999999</v>
+        <v>732.09</v>
       </c>
       <c r="R5">
-        <v>715.03</v>
+        <v>716.1900000000001</v>
       </c>
       <c r="S5">
-        <v>750.59</v>
+        <v>750.3</v>
       </c>
       <c r="T5">
-        <v>-2.42</v>
+        <v>-3.5</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1415,34 +1357,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>52.15</v>
+        <v>47.14</v>
       </c>
       <c r="Z5">
-        <v>4.65</v>
+        <v>3.51</v>
       </c>
       <c r="AA5">
-        <v>5.51</v>
+        <v>5.11</v>
       </c>
       <c r="AB5">
-        <v>-0.86</v>
+        <v>-1.6</v>
       </c>
       <c r="AC5">
-        <v>43.31</v>
+        <v>25.39</v>
       </c>
       <c r="AD5">
-        <v>48.36</v>
+        <v>39.65</v>
       </c>
       <c r="AE5">
-        <v>16.62</v>
+        <v>16.24</v>
       </c>
       <c r="AF5">
-        <v>64.23999999999999</v>
+        <v>-54.73</v>
       </c>
       <c r="AG5">
-        <v>746.37</v>
+        <v>745.9299999999999</v>
       </c>
       <c r="AH5">
-        <v>719.24</v>
+        <v>718.24</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1451,7 +1393,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>19.97</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1462,10 +1404,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>548.1</v>
+        <v>543.95</v>
       </c>
       <c r="D6">
-        <v>-1.33</v>
+        <v>-0.76</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1474,25 +1416,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-8.65</v>
+        <v>-9.34</v>
       </c>
       <c r="H6">
-        <v>24.98</v>
+        <v>24.03</v>
       </c>
       <c r="I6">
         <v>-2.65</v>
       </c>
       <c r="J6">
-        <v>-3.45</v>
+        <v>-3.93</v>
       </c>
       <c r="K6">
-        <v>2.4</v>
+        <v>-0.48</v>
       </c>
       <c r="L6">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="M6">
-        <v>18.06</v>
+        <v>18.71</v>
       </c>
       <c r="N6">
         <v>34</v>
@@ -1501,19 +1443,19 @@
         <v>52</v>
       </c>
       <c r="P6">
-        <v>556.1900000000001</v>
+        <v>553.23</v>
       </c>
       <c r="Q6">
-        <v>557.98</v>
+        <v>557.09</v>
       </c>
       <c r="R6">
-        <v>559.92</v>
+        <v>559.39</v>
       </c>
       <c r="S6">
-        <v>519.3099999999999</v>
+        <v>519.35</v>
       </c>
       <c r="T6">
-        <v>5.54</v>
+        <v>4.74</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1528,43 +1470,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>43.36</v>
+        <v>41.17</v>
       </c>
       <c r="Z6">
-        <v>-0.15</v>
+        <v>-1.28</v>
       </c>
       <c r="AA6">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="AB6">
-        <v>-0.9399999999999999</v>
+        <v>-1.66</v>
       </c>
       <c r="AC6">
-        <v>21.96</v>
+        <v>8.69</v>
       </c>
       <c r="AD6">
-        <v>30.68</v>
+        <v>21.29</v>
       </c>
       <c r="AE6">
-        <v>12.1</v>
+        <v>11.78</v>
       </c>
       <c r="AF6">
-        <v>-37.04</v>
+        <v>-33.35</v>
       </c>
       <c r="AG6">
-        <v>576.05</v>
+        <v>576.11</v>
       </c>
       <c r="AH6">
-        <v>539.9</v>
+        <v>538.0700000000001</v>
       </c>
       <c r="AI6">
-        <v>584.25</v>
+        <v>579.67</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>17.18</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1575,10 +1517,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11489</v>
+        <v>11329</v>
       </c>
       <c r="D7">
-        <v>-3.24</v>
+        <v>-1.39</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1587,25 +1529,25 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.17</v>
+        <v>-48.89</v>
       </c>
       <c r="H7">
-        <v>7.83</v>
+        <v>6.33</v>
       </c>
       <c r="I7">
-        <v>-3.79</v>
+        <v>-2.1</v>
       </c>
       <c r="J7">
-        <v>3.96</v>
+        <v>3.17</v>
       </c>
       <c r="K7">
-        <v>-8.9</v>
+        <v>-10.75</v>
       </c>
       <c r="L7">
-        <v>-35.79</v>
+        <v>-35.92</v>
       </c>
       <c r="M7">
-        <v>18.83</v>
+        <v>19.2</v>
       </c>
       <c r="N7">
         <v>12</v>
@@ -1614,19 +1556,19 @@
         <v>14</v>
       </c>
       <c r="P7">
-        <v>11695.8</v>
+        <v>11647.2</v>
       </c>
       <c r="Q7">
-        <v>11546.4</v>
+        <v>11567.1</v>
       </c>
       <c r="R7">
-        <v>11779.98</v>
+        <v>11758.46</v>
       </c>
       <c r="S7">
-        <v>15131.67</v>
+        <v>15104</v>
       </c>
       <c r="T7">
-        <v>-24.07</v>
+        <v>-24.99</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1641,34 +1583,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>45.96</v>
+        <v>43.03</v>
       </c>
       <c r="Z7">
-        <v>42.92</v>
+        <v>8.65</v>
       </c>
       <c r="AA7">
-        <v>24.56</v>
+        <v>21.38</v>
       </c>
       <c r="AB7">
-        <v>18.36</v>
+        <v>-12.73</v>
       </c>
       <c r="AC7">
-        <v>38.65</v>
+        <v>19.36</v>
       </c>
       <c r="AD7">
-        <v>45.72</v>
+        <v>36</v>
       </c>
       <c r="AE7">
-        <v>386.32</v>
+        <v>384.36</v>
       </c>
       <c r="AF7">
-        <v>-24.55</v>
+        <v>-45.79</v>
       </c>
       <c r="AG7">
-        <v>12557.32</v>
+        <v>12539.82</v>
       </c>
       <c r="AH7">
-        <v>10535.48</v>
+        <v>10594.38</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1677,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>23.07</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1688,10 +1630,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>328.65</v>
+        <v>329.9</v>
       </c>
       <c r="D8">
-        <v>-2.01</v>
+        <v>0.38</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1700,46 +1642,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-6.42</v>
+        <v>-6.06</v>
       </c>
       <c r="H8">
-        <v>40.26</v>
+        <v>40.8</v>
       </c>
       <c r="I8">
-        <v>-3.86</v>
+        <v>-4.82</v>
       </c>
       <c r="J8">
-        <v>-5.68</v>
+        <v>-4.25</v>
       </c>
       <c r="K8">
-        <v>25.01</v>
+        <v>24.28</v>
       </c>
       <c r="L8">
-        <v>10.47</v>
+        <v>10.04</v>
       </c>
       <c r="M8">
-        <v>29.41</v>
+        <v>29.54</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>338.23</v>
+        <v>334.89</v>
       </c>
       <c r="Q8">
         <v>329.8</v>
       </c>
       <c r="R8">
-        <v>323.4</v>
+        <v>324.34</v>
       </c>
       <c r="S8">
-        <v>282.27</v>
+        <v>282.44</v>
       </c>
       <c r="T8">
-        <v>16.43</v>
+        <v>16.8</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1754,34 +1696,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>48.7</v>
+        <v>49.62</v>
       </c>
       <c r="Z8">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="AB8">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="AC8">
-        <v>50.53</v>
+        <v>38.64</v>
       </c>
       <c r="AD8">
-        <v>66.61</v>
+        <v>52.05</v>
       </c>
       <c r="AE8">
-        <v>10.42</v>
+        <v>10.07</v>
       </c>
       <c r="AF8">
-        <v>-44.23</v>
+        <v>-56.02</v>
       </c>
       <c r="AG8">
         <v>349.07</v>
       </c>
       <c r="AH8">
-        <v>310.54</v>
+        <v>310.53</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1790,7 +1732,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.6</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1801,10 +1743,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1267.6</v>
+        <v>1285.8</v>
       </c>
       <c r="D9">
-        <v>-0.8</v>
+        <v>1.44</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1813,46 +1755,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-4.69</v>
+        <v>-3.32</v>
       </c>
       <c r="H9">
-        <v>23.48</v>
+        <v>25.25</v>
       </c>
       <c r="I9">
-        <v>-1.23</v>
+        <v>1.32</v>
       </c>
       <c r="J9">
-        <v>0.84</v>
+        <v>1.45</v>
       </c>
       <c r="K9">
-        <v>-1.22</v>
+        <v>0.35</v>
       </c>
       <c r="L9">
-        <v>20.93</v>
+        <v>22.03</v>
       </c>
       <c r="M9">
-        <v>12.45</v>
+        <v>14.47</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1271.9</v>
+        <v>1275.24</v>
       </c>
       <c r="Q9">
-        <v>1276.9</v>
+        <v>1277.85</v>
       </c>
       <c r="R9">
-        <v>1261.6</v>
+        <v>1262.08</v>
       </c>
       <c r="S9">
-        <v>1216.85</v>
+        <v>1217.23</v>
       </c>
       <c r="T9">
-        <v>4.17</v>
+        <v>5.63</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1867,34 +1809,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>48.36</v>
+        <v>54.04</v>
       </c>
       <c r="Z9">
-        <v>5.51</v>
+        <v>5.7</v>
       </c>
       <c r="AA9">
-        <v>8.44</v>
+        <v>7.89</v>
       </c>
       <c r="AB9">
-        <v>-2.92</v>
+        <v>-2.19</v>
       </c>
       <c r="AC9">
-        <v>4.54</v>
+        <v>12.85</v>
       </c>
       <c r="AD9">
-        <v>6.06</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AE9">
-        <v>25.51</v>
+        <v>25.38</v>
       </c>
       <c r="AF9">
-        <v>-58.23</v>
+        <v>-37.97</v>
       </c>
       <c r="AG9">
-        <v>1323.4</v>
+        <v>1324.26</v>
       </c>
       <c r="AH9">
-        <v>1230.4</v>
+        <v>1231.43</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1903,7 +1845,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.04</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1914,7 +1856,7 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>86.88</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="D10">
         <v>-5</v>
@@ -1926,46 +1868,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-5</v>
+        <v>-9.74</v>
       </c>
       <c r="H10">
-        <v>140.8</v>
+        <v>128.77</v>
       </c>
       <c r="I10">
-        <v>3.59</v>
+        <v>-0.43</v>
       </c>
       <c r="J10">
-        <v>47.81</v>
+        <v>19.54</v>
       </c>
       <c r="K10">
-        <v>74.95</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="L10">
-        <v>18.43</v>
+        <v>15.39</v>
       </c>
       <c r="M10">
-        <v>-2.72</v>
+        <v>-3.33</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>87.93000000000001</v>
+        <v>87.86</v>
       </c>
       <c r="Q10">
-        <v>78.42</v>
+        <v>79.2</v>
       </c>
       <c r="R10">
-        <v>62.97</v>
+        <v>63.63</v>
       </c>
       <c r="S10">
-        <v>59.41</v>
+        <v>59.44</v>
       </c>
       <c r="T10">
-        <v>46.23</v>
+        <v>38.87</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1980,34 +1922,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>66.33</v>
+        <v>59.08</v>
       </c>
       <c r="Z10">
-        <v>8.1</v>
+        <v>7.39</v>
       </c>
       <c r="AA10">
-        <v>7.73</v>
+        <v>7.66</v>
       </c>
       <c r="AB10">
-        <v>0.37</v>
+        <v>-0.27</v>
       </c>
       <c r="AC10">
-        <v>61.81</v>
+        <v>35.19</v>
       </c>
       <c r="AD10">
-        <v>65.26000000000001</v>
+        <v>56.89</v>
       </c>
       <c r="AE10">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="AF10">
-        <v>-72.73999999999999</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="AG10">
-        <v>97.81999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AH10">
-        <v>59.03</v>
+        <v>60.49</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -2016,7 +1958,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>56.63</v>
+        <v>52.87</v>
       </c>
     </row>
   </sheetData>
@@ -2157,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2197,7 +2139,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2216,37 +2158,37 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
@@ -2255,1408 +2197,1243 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-2.94</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-4.7</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1.02</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>6.6</v>
+      </c>
+      <c r="D11" s="7">
+        <v>6.73</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-2.04</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-3.45</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3.96</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-5.68</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-4.25</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>47.81</v>
+      </c>
+      <c r="D17" s="7">
+        <v>19.54</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-28.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-6.61</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-2.94</v>
-      </c>
-      <c r="E13" s="9">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-4.23</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-0.35</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.02</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.79</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.32</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.01</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-1.88</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-3.79</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-2.1</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.86</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.82</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.23</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>3.59</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.43</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-4.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>22.74</v>
+      </c>
+      <c r="D26" s="7">
+        <v>21.87</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>36.25</v>
+      </c>
+      <c r="D27" s="7">
+        <v>33.46</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>10.53</v>
+      </c>
+      <c r="D28" s="7">
+        <v>12.13</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>3.09</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>3.15</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2.02</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-35.79</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-35.92</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>10.47</v>
+      </c>
+      <c r="D32" s="7">
+        <v>10.04</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>20.93</v>
+      </c>
+      <c r="D33" s="7">
+        <v>22.03</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>18.43</v>
+      </c>
+      <c r="D34" s="7">
+        <v>15.39</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-7.73</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>23.49</v>
+      </c>
+      <c r="D36" s="7">
+        <v>23.78</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-9.94</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-6.83</v>
+      </c>
+      <c r="E37" s="9">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-0.62</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-1.73</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-0.48</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-8.9</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-10.75</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>25.01</v>
+      </c>
+      <c r="D41" s="7">
+        <v>24.28</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-1.22</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>74.95</v>
+      </c>
+      <c r="D43" s="7">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-9.800000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-35.82</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-36.65</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-3.73</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-14.53</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-13.49</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-15.29</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-16.26</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-8.65</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-9.34</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-48.17</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-48.89</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-6.42</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-6.06</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-3.32</v>
+      </c>
+      <c r="E51" s="9">
         <v>1.37</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-5</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-9.74</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-4.74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>646.65</v>
+      </c>
+      <c r="D53" s="7">
+        <v>638.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>268.65</v>
+      </c>
+      <c r="D54" s="7">
+        <v>268.7</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>6.18</v>
-      </c>
-      <c r="D15" s="8">
-        <v>6.6</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1101.5</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1115</v>
+      </c>
+      <c r="E55" s="9">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>732.4</v>
+      </c>
+      <c r="D56" s="7">
+        <v>724</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>548.1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>543.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11489</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11329</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>328.65</v>
+      </c>
+      <c r="D59" s="7">
+        <v>329.9</v>
+      </c>
+      <c r="E59" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1267.6</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1285.8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>86.88</v>
+      </c>
+      <c r="D61" s="7">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>50.21</v>
+      </c>
+      <c r="D62" s="7">
+        <v>47.89</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>54.74</v>
+      </c>
+      <c r="D63" s="7">
+        <v>54.79</v>
+      </c>
+      <c r="E63" s="9">
         <v>0.05</v>
       </c>
-      <c r="D16" s="8">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>53.58</v>
+      </c>
+      <c r="D64" s="7">
+        <v>57.21</v>
+      </c>
+      <c r="E64" s="9">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>52.15</v>
+      </c>
+      <c r="D65" s="7">
+        <v>47.14</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>3.05</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-3.45</v>
-      </c>
-      <c r="E17" s="10">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>43.36</v>
+      </c>
+      <c r="D66" s="7">
+        <v>41.17</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>6.05</v>
-      </c>
-      <c r="D18" s="8">
-        <v>3.96</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>45.96</v>
+      </c>
+      <c r="D67" s="7">
+        <v>43.03</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-0.04</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-5.68</v>
-      </c>
-      <c r="E19" s="10">
-        <v>-5.64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>48.7</v>
+      </c>
+      <c r="D68" s="7">
+        <v>49.62</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
-        <v>4.01</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>48.36</v>
+      </c>
+      <c r="D69" s="7">
+        <v>54.04</v>
+      </c>
+      <c r="E69" s="9">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="8">
-        <v>81.37</v>
-      </c>
-      <c r="D21" s="8">
-        <v>47.81</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-33.56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>66.33</v>
+      </c>
+      <c r="D70" s="7">
+        <v>59.08</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-7.25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>2.63</v>
-      </c>
-      <c r="D22" s="8">
-        <v>2.72</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-39.71</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-61.11</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-21.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-1.58</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-1.79</v>
-      </c>
-      <c r="E23" s="10">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-50.86</v>
+      </c>
+      <c r="D72" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="E72" s="9">
+        <v>54.33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>-1.04</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.59</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-39.24</v>
+      </c>
+      <c r="D73" s="7">
+        <v>27.65</v>
+      </c>
+      <c r="E73" s="9">
+        <v>66.89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-54.73</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-118.97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-0.78</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-2.65</v>
-      </c>
-      <c r="E26" s="10">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-37.04</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-33.35</v>
+      </c>
+      <c r="E75" s="9">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-1.26</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-3.79</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-24.55</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-45.79</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-21.24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-3.86</v>
-      </c>
-      <c r="E28" s="10">
-        <v>-4.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-44.23</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-56.02</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-11.79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-2.27</v>
-      </c>
-      <c r="D29" s="8">
-        <v>-1.23</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-58.23</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-37.97</v>
+      </c>
+      <c r="E78" s="9">
+        <v>20.26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="8">
-        <v>8.19</v>
-      </c>
-      <c r="D30" s="8">
-        <v>3.59</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>21.03</v>
-      </c>
-      <c r="D31" s="8">
-        <v>22.74</v>
-      </c>
-      <c r="E31" s="9">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>30.53</v>
-      </c>
-      <c r="D32" s="8">
-        <v>36.25</v>
-      </c>
-      <c r="E32" s="9">
-        <v>5.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>12.27</v>
-      </c>
-      <c r="D33" s="8">
-        <v>10.53</v>
-      </c>
-      <c r="E33" s="10">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="D34" s="8">
-        <v>3.09</v>
-      </c>
-      <c r="E34" s="10">
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>8.41</v>
-      </c>
-      <c r="D35" s="8">
-        <v>3.15</v>
-      </c>
-      <c r="E35" s="10">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-35.73</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-35.79</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="8">
-        <v>14.12</v>
-      </c>
-      <c r="D37" s="8">
-        <v>10.47</v>
-      </c>
-      <c r="E37" s="10">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="8">
-        <v>21.04</v>
-      </c>
-      <c r="D38" s="8">
-        <v>20.93</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="8">
-        <v>21.63</v>
-      </c>
-      <c r="D39" s="8">
-        <v>18.43</v>
-      </c>
-      <c r="E39" s="10">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-7.66</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E40" s="10">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>22.11</v>
-      </c>
-      <c r="D41" s="8">
-        <v>23.49</v>
-      </c>
-      <c r="E41" s="9">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-11.39</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-9.94</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-1.44</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-0.62</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>6.21</v>
-      </c>
-      <c r="D44" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-6.3</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-8.9</v>
-      </c>
-      <c r="E45" s="10">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="8">
-        <v>25.4</v>
-      </c>
-      <c r="D46" s="8">
-        <v>25.01</v>
-      </c>
-      <c r="E46" s="10">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-1.76</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-1.22</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="8">
-        <v>86.31999999999999</v>
-      </c>
-      <c r="D48" s="8">
-        <v>74.95</v>
-      </c>
-      <c r="E48" s="10">
-        <v>-11.37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-36.85</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-35.82</v>
-      </c>
-      <c r="E49" s="9">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-4.28</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-3.73</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-15.31</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-14.53</v>
-      </c>
-      <c r="E51" s="9">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-14.66</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-15.29</v>
-      </c>
-      <c r="E52" s="10">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>-6.67</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-8.65</v>
-      </c>
-      <c r="E53" s="10">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-46.43</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-48.17</v>
-      </c>
-      <c r="E54" s="10">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="8">
-        <v>-3.43</v>
-      </c>
-      <c r="D55" s="8">
-        <v>-6.42</v>
-      </c>
-      <c r="E55" s="10">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="8">
-        <v>-4.51</v>
-      </c>
-      <c r="D56" s="8">
-        <v>-4.69</v>
-      </c>
-      <c r="E56" s="10">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="8">
-        <v>0</v>
-      </c>
-      <c r="D57" s="8">
-        <v>-5</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>636.3</v>
-      </c>
-      <c r="D58" s="8">
-        <v>646.65</v>
-      </c>
-      <c r="E58" s="9">
-        <v>10.35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>267.1</v>
-      </c>
-      <c r="D59" s="8">
-        <v>268.65</v>
-      </c>
-      <c r="E59" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>1091.5</v>
-      </c>
-      <c r="D60" s="8">
-        <v>1101.5</v>
-      </c>
-      <c r="E60" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>737.85</v>
-      </c>
-      <c r="D61" s="8">
-        <v>732.4</v>
-      </c>
-      <c r="E61" s="10">
-        <v>-5.45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>560</v>
-      </c>
-      <c r="D62" s="8">
-        <v>548.1</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>11874</v>
-      </c>
-      <c r="D63" s="8">
-        <v>11489</v>
-      </c>
-      <c r="E63" s="10">
-        <v>-385</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="8">
-        <v>339.15</v>
-      </c>
-      <c r="D64" s="8">
-        <v>328.65</v>
-      </c>
-      <c r="E64" s="10">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="8">
-        <v>1270</v>
-      </c>
-      <c r="D65" s="8">
-        <v>1267.6</v>
-      </c>
-      <c r="E65" s="10">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C66" s="8">
-        <v>91.39</v>
-      </c>
-      <c r="D66" s="8">
-        <v>86.88</v>
-      </c>
-      <c r="E66" s="10">
-        <v>-4.51</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="8">
-        <v>45</v>
-      </c>
-      <c r="D67" s="8">
-        <v>55</v>
-      </c>
-      <c r="E67" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="8">
-        <v>23</v>
-      </c>
-      <c r="D68" s="8">
-        <v>45</v>
-      </c>
-      <c r="E68" s="9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="8">
-        <v>34</v>
-      </c>
-      <c r="D69" s="8">
-        <v>23</v>
-      </c>
-      <c r="E69" s="10">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="8">
-        <v>55</v>
-      </c>
-      <c r="D70" s="8">
-        <v>34</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>47.3</v>
-      </c>
-      <c r="D71" s="8">
-        <v>50.21</v>
-      </c>
-      <c r="E71" s="9">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>53.36</v>
-      </c>
-      <c r="D72" s="8">
-        <v>54.74</v>
-      </c>
-      <c r="E72" s="9">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>50.7</v>
-      </c>
-      <c r="D73" s="8">
-        <v>53.58</v>
-      </c>
-      <c r="E73" s="9">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>55.71</v>
-      </c>
-      <c r="D74" s="8">
-        <v>52.15</v>
-      </c>
-      <c r="E74" s="10">
-        <v>-3.56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>50.28</v>
-      </c>
-      <c r="D75" s="8">
-        <v>43.36</v>
-      </c>
-      <c r="E75" s="10">
-        <v>-6.92</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="8">
-        <v>54.22</v>
-      </c>
-      <c r="D76" s="8">
-        <v>45.96</v>
-      </c>
-      <c r="E76" s="10">
-        <v>-8.26</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="8">
-        <v>56.59</v>
-      </c>
-      <c r="D77" s="8">
-        <v>48.7</v>
-      </c>
-      <c r="E77" s="10">
-        <v>-7.89</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" s="8">
-        <v>49.2</v>
-      </c>
-      <c r="D78" s="8">
-        <v>48.36</v>
-      </c>
-      <c r="E78" s="10">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" s="8">
-        <v>75.34</v>
-      </c>
-      <c r="D79" s="8">
-        <v>66.33</v>
-      </c>
-      <c r="E79" s="10">
-        <v>-9.01</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="7" t="s">
+      <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C80" s="8">
-        <v>-17.1</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-39.71</v>
-      </c>
-      <c r="E80" s="10">
-        <v>-22.61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>-70.31999999999999</v>
-      </c>
-      <c r="D81" s="8">
-        <v>-50.86</v>
-      </c>
-      <c r="E81" s="9">
-        <v>19.46</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>-48.21</v>
-      </c>
-      <c r="D82" s="8">
-        <v>-39.24</v>
-      </c>
-      <c r="E82" s="9">
-        <v>8.970000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-36.24</v>
-      </c>
-      <c r="D83" s="8">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="E83" s="9">
-        <v>100.48</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>-37.68</v>
-      </c>
-      <c r="D84" s="8">
-        <v>-37.04</v>
-      </c>
-      <c r="E84" s="9">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="8">
-        <v>67.27</v>
-      </c>
-      <c r="D85" s="8">
-        <v>-24.55</v>
-      </c>
-      <c r="E85" s="10">
-        <v>-91.81999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="8">
-        <v>-38.77</v>
-      </c>
-      <c r="D86" s="8">
-        <v>-44.23</v>
-      </c>
-      <c r="E86" s="10">
-        <v>-5.46</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C87" s="8">
-        <v>-45.97</v>
-      </c>
-      <c r="D87" s="8">
-        <v>-58.23</v>
-      </c>
-      <c r="E87" s="10">
-        <v>-12.26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88" s="8">
-        <v>-84.15000000000001</v>
-      </c>
-      <c r="D88" s="8">
+      <c r="C79" s="7">
         <v>-72.73999999999999</v>
       </c>
-      <c r="E88" s="9">
-        <v>11.41</v>
+      <c r="D79" s="7">
+        <v>-89.70999999999999</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-16.97</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3676,60 +3453,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>96</v>
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>60.16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>51.5</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="12">
+        <v>50.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F2" s="13">
-        <v>5.4</v>
-      </c>
-      <c r="G2" s="13">
-        <v>10.8</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="12">
+        <v>2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>9.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3831,61 +3608,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.3815</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.364</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.2941</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.2232</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1883</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1806</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.1245</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.0272</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.07690000000000001</v>
+      <c r="A2" s="15">
+        <v>0.4005</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3627</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2954</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.246</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.192</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1871</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1447</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0333</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0737</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,55 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.4 → 54.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>50.2 → 47.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>52.1 → 47.1</t>
-  </si>
-  <si>
-    <t>52.1</t>
-  </si>
-  <si>
-    <t>47.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -428,19 +380,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -812,8 +762,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -952,10 +901,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>638.35</v>
+        <v>637</v>
       </c>
       <c r="D2">
-        <v>-1.28</v>
+        <v>-0.21</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -964,46 +913,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.65</v>
+        <v>-36.78</v>
       </c>
       <c r="H2">
-        <v>73.84</v>
+        <v>73.47</v>
       </c>
       <c r="I2">
-        <v>-4.23</v>
+        <v>-2.23</v>
       </c>
       <c r="J2">
-        <v>-4.7</v>
+        <v>-1.64</v>
       </c>
       <c r="K2">
-        <v>-7.73</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L2">
-        <v>21.87</v>
+        <v>22.82</v>
       </c>
       <c r="M2">
-        <v>-7.37</v>
+        <v>-7.41</v>
       </c>
       <c r="N2">
         <v>55</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>647.6900000000001</v>
+        <v>644.79</v>
       </c>
       <c r="Q2">
-        <v>636.64</v>
+        <v>636.59</v>
       </c>
       <c r="R2">
-        <v>656.47</v>
+        <v>655.2</v>
       </c>
       <c r="S2">
-        <v>617.5599999999999</v>
+        <v>617.9299999999999</v>
       </c>
       <c r="T2">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1018,34 +967,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.89</v>
+        <v>47.51</v>
       </c>
       <c r="Z2">
-        <v>-2.18</v>
+        <v>-2.49</v>
       </c>
       <c r="AA2">
-        <v>-4.97</v>
+        <v>-4.47</v>
       </c>
       <c r="AB2">
-        <v>2.79</v>
+        <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>63.91</v>
+        <v>48.1</v>
       </c>
       <c r="AD2">
-        <v>64.44</v>
+        <v>58.27</v>
       </c>
       <c r="AE2">
-        <v>25.58</v>
+        <v>24.48</v>
       </c>
       <c r="AF2">
-        <v>-61.11</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="AG2">
-        <v>661.58</v>
+        <v>661.52</v>
       </c>
       <c r="AH2">
-        <v>611.7</v>
+        <v>611.66</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1054,7 +1003,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.19</v>
+        <v>30.29</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1065,10 +1014,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>268.7</v>
+        <v>269.75</v>
       </c>
       <c r="D3">
-        <v>0.02</v>
+        <v>0.39</v>
       </c>
       <c r="E3">
         <v>279.05</v>
@@ -1077,46 +1026,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-3.71</v>
+        <v>-3.33</v>
       </c>
       <c r="H3">
-        <v>75.36</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.32</v>
+        <v>2.02</v>
       </c>
       <c r="J3">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="K3">
-        <v>23.78</v>
+        <v>22.61</v>
       </c>
       <c r="L3">
-        <v>33.46</v>
+        <v>36.88</v>
       </c>
       <c r="M3">
-        <v>36.27</v>
+        <v>36.35</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>267.19</v>
+        <v>268.26</v>
       </c>
       <c r="Q3">
-        <v>263.86</v>
+        <v>264.3</v>
       </c>
       <c r="R3">
-        <v>260.46</v>
+        <v>261.35</v>
       </c>
       <c r="S3">
-        <v>207.88</v>
+        <v>208.36</v>
       </c>
       <c r="T3">
-        <v>29.26</v>
+        <v>29.46</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1131,34 +1080,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>54.79</v>
+        <v>55.81</v>
       </c>
       <c r="Z3">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AA3">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AB3">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC3">
-        <v>36.82</v>
+        <v>35.88</v>
       </c>
       <c r="AD3">
-        <v>36.01</v>
+        <v>36.57</v>
       </c>
       <c r="AE3">
-        <v>8.119999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AF3">
-        <v>3.47</v>
+        <v>-34.35</v>
       </c>
       <c r="AG3">
-        <v>278.23</v>
+        <v>278.83</v>
       </c>
       <c r="AH3">
-        <v>249.49</v>
+        <v>249.77</v>
       </c>
       <c r="AI3">
         <v>250.11</v>
@@ -1167,7 +1116,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>19.93</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1178,10 +1127,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1115</v>
+        <v>1118.9</v>
       </c>
       <c r="D4">
-        <v>1.23</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1190,46 +1139,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-13.49</v>
+        <v>-13.18</v>
       </c>
       <c r="H4">
-        <v>17.89</v>
+        <v>18.3</v>
       </c>
       <c r="I4">
-        <v>0.27</v>
+        <v>1.73</v>
       </c>
       <c r="J4">
-        <v>6.73</v>
+        <v>7.07</v>
       </c>
       <c r="K4">
-        <v>-6.83</v>
+        <v>-7.52</v>
       </c>
       <c r="L4">
-        <v>12.13</v>
+        <v>14.94</v>
       </c>
       <c r="M4">
-        <v>24.6</v>
+        <v>24.67</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P4">
-        <v>1099.88</v>
+        <v>1103.68</v>
       </c>
       <c r="Q4">
-        <v>1093.03</v>
+        <v>1096.88</v>
       </c>
       <c r="R4">
-        <v>1080.99</v>
+        <v>1080.94</v>
       </c>
       <c r="S4">
-        <v>1123.38</v>
+        <v>1123.64</v>
       </c>
       <c r="T4">
-        <v>-0.75</v>
+        <v>-0.42</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1244,43 +1193,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>57.21</v>
+        <v>58.23</v>
       </c>
       <c r="Z4">
-        <v>7.87</v>
+        <v>8.81</v>
       </c>
       <c r="AA4">
-        <v>6.52</v>
+        <v>6.98</v>
       </c>
       <c r="AB4">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>22.6</v>
+        <v>40.73</v>
       </c>
       <c r="AD4">
-        <v>18.67</v>
+        <v>25.87</v>
       </c>
       <c r="AE4">
-        <v>24.26</v>
+        <v>24.93</v>
       </c>
       <c r="AF4">
-        <v>27.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>1143.1</v>
+        <v>1141.99</v>
       </c>
       <c r="AH4">
-        <v>1042.95</v>
+        <v>1051.76</v>
       </c>
       <c r="AI4">
-        <v>1044.51</v>
+        <v>1050.42</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>25.94</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1291,10 +1240,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>724</v>
+        <v>718.4</v>
       </c>
       <c r="D5">
-        <v>-1.15</v>
+        <v>-0.77</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1303,46 +1252,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.26</v>
+        <v>-16.91</v>
       </c>
       <c r="H5">
-        <v>9.380000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I5">
-        <v>-1.88</v>
+        <v>-2.31</v>
       </c>
       <c r="J5">
-        <v>-2.04</v>
+        <v>-2.71</v>
       </c>
       <c r="K5">
-        <v>-1.73</v>
+        <v>-2.48</v>
       </c>
       <c r="L5">
-        <v>0.7</v>
+        <v>-1.2</v>
       </c>
       <c r="M5">
-        <v>40.05</v>
+        <v>39.81</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>733.5</v>
+        <v>730.1</v>
       </c>
       <c r="Q5">
-        <v>732.09</v>
+        <v>731.21</v>
       </c>
       <c r="R5">
-        <v>716.1900000000001</v>
+        <v>717.3200000000001</v>
       </c>
       <c r="S5">
-        <v>750.3</v>
+        <v>750.13</v>
       </c>
       <c r="T5">
-        <v>-3.5</v>
+        <v>-4.23</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1357,34 +1306,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.14</v>
+        <v>44.11</v>
       </c>
       <c r="Z5">
-        <v>3.51</v>
+        <v>2.13</v>
       </c>
       <c r="AA5">
-        <v>5.11</v>
+        <v>4.51</v>
       </c>
       <c r="AB5">
-        <v>-1.6</v>
+        <v>-2.38</v>
       </c>
       <c r="AC5">
+        <v>7.46</v>
+      </c>
+      <c r="AD5">
         <v>25.39</v>
       </c>
-      <c r="AD5">
-        <v>39.65</v>
-      </c>
       <c r="AE5">
-        <v>16.24</v>
+        <v>16.17</v>
       </c>
       <c r="AF5">
-        <v>-54.73</v>
+        <v>-36.91</v>
       </c>
       <c r="AG5">
-        <v>745.9299999999999</v>
+        <v>746.21</v>
       </c>
       <c r="AH5">
-        <v>718.24</v>
+        <v>716.22</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1393,7 +1342,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>19.11</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1404,10 +1353,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>543.95</v>
+        <v>542</v>
       </c>
       <c r="D6">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1416,46 +1365,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-9.34</v>
+        <v>-9.67</v>
       </c>
       <c r="H6">
-        <v>24.03</v>
+        <v>23.59</v>
       </c>
       <c r="I6">
-        <v>-2.65</v>
+        <v>-2.97</v>
       </c>
       <c r="J6">
-        <v>-3.93</v>
+        <v>-3.51</v>
       </c>
       <c r="K6">
-        <v>-0.48</v>
+        <v>-1.34</v>
       </c>
       <c r="L6">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="M6">
-        <v>18.71</v>
+        <v>18.61</v>
       </c>
       <c r="N6">
         <v>34</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>553.23</v>
+        <v>549.91</v>
       </c>
       <c r="Q6">
-        <v>557.09</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="R6">
-        <v>559.39</v>
+        <v>559.02</v>
       </c>
       <c r="S6">
-        <v>519.35</v>
+        <v>519.4299999999999</v>
       </c>
       <c r="T6">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1470,43 +1419,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.17</v>
+        <v>40.15</v>
       </c>
       <c r="Z6">
-        <v>-1.28</v>
+        <v>-2.31</v>
       </c>
       <c r="AA6">
-        <v>0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="AB6">
-        <v>-1.66</v>
+        <v>-2.16</v>
       </c>
       <c r="AC6">
-        <v>8.69</v>
+        <v>0.47</v>
       </c>
       <c r="AD6">
-        <v>21.29</v>
+        <v>10.37</v>
       </c>
       <c r="AE6">
-        <v>11.78</v>
+        <v>11.43</v>
       </c>
       <c r="AF6">
-        <v>-33.35</v>
+        <v>-12.28</v>
       </c>
       <c r="AG6">
-        <v>576.11</v>
+        <v>576.5</v>
       </c>
       <c r="AH6">
-        <v>538.0700000000001</v>
+        <v>536.14</v>
       </c>
       <c r="AI6">
-        <v>579.67</v>
+        <v>577.85</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.97</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,10 +1466,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11329</v>
+        <v>11465</v>
       </c>
       <c r="D7">
-        <v>-1.39</v>
+        <v>1.2</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1529,46 +1478,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.89</v>
+        <v>-48.27</v>
       </c>
       <c r="H7">
-        <v>6.33</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
-        <v>-2.1</v>
+        <v>-1.76</v>
       </c>
       <c r="J7">
-        <v>3.17</v>
+        <v>5.04</v>
       </c>
       <c r="K7">
-        <v>-10.75</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L7">
-        <v>-35.92</v>
+        <v>-34.93</v>
       </c>
       <c r="M7">
-        <v>19.2</v>
+        <v>19.47</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P7">
-        <v>11647.2</v>
+        <v>11606.2</v>
       </c>
       <c r="Q7">
-        <v>11567.1</v>
+        <v>11607.6</v>
       </c>
       <c r="R7">
-        <v>11758.46</v>
+        <v>11744.22</v>
       </c>
       <c r="S7">
-        <v>15104</v>
+        <v>15079.42</v>
       </c>
       <c r="T7">
-        <v>-24.99</v>
+        <v>-23.97</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1583,34 +1532,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>43.03</v>
+        <v>46.17</v>
       </c>
       <c r="Z7">
-        <v>8.65</v>
+        <v>-7.45</v>
       </c>
       <c r="AA7">
-        <v>21.38</v>
+        <v>15.61</v>
       </c>
       <c r="AB7">
-        <v>-12.73</v>
+        <v>-23.07</v>
       </c>
       <c r="AC7">
-        <v>19.36</v>
+        <v>7.74</v>
       </c>
       <c r="AD7">
-        <v>36</v>
+        <v>21.92</v>
       </c>
       <c r="AE7">
-        <v>384.36</v>
+        <v>382.12</v>
       </c>
       <c r="AF7">
-        <v>-45.79</v>
+        <v>-44.67</v>
       </c>
       <c r="AG7">
-        <v>12539.82</v>
+        <v>12483</v>
       </c>
       <c r="AH7">
-        <v>10594.38</v>
+        <v>10732.2</v>
       </c>
       <c r="AI7">
         <v>11199.19</v>
@@ -1619,7 +1568,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>22.3</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1630,10 +1579,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>329.9</v>
+        <v>329.85</v>
       </c>
       <c r="D8">
-        <v>0.38</v>
+        <v>-0.02</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1642,46 +1591,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-6.06</v>
+        <v>-6.08</v>
       </c>
       <c r="H8">
-        <v>40.8</v>
+        <v>40.78</v>
       </c>
       <c r="I8">
-        <v>-4.82</v>
+        <v>-3.37</v>
       </c>
       <c r="J8">
-        <v>-4.25</v>
+        <v>-0.05</v>
       </c>
       <c r="K8">
-        <v>24.28</v>
+        <v>20.12</v>
       </c>
       <c r="L8">
-        <v>10.04</v>
+        <v>8.92</v>
       </c>
       <c r="M8">
-        <v>29.54</v>
+        <v>29.51</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P8">
-        <v>334.89</v>
+        <v>332.59</v>
       </c>
       <c r="Q8">
-        <v>329.8</v>
+        <v>330.07</v>
       </c>
       <c r="R8">
-        <v>324.34</v>
+        <v>325.37</v>
       </c>
       <c r="S8">
-        <v>282.44</v>
+        <v>282.64</v>
       </c>
       <c r="T8">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1696,34 +1645,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>49.62</v>
+        <v>49.58</v>
       </c>
       <c r="Z8">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AA8">
-        <v>4.26</v>
+        <v>3.95</v>
       </c>
       <c r="AB8">
-        <v>-0.96</v>
+        <v>-1.23</v>
       </c>
       <c r="AC8">
-        <v>38.64</v>
+        <v>22.79</v>
       </c>
       <c r="AD8">
-        <v>52.05</v>
+        <v>37.32</v>
       </c>
       <c r="AE8">
-        <v>10.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AF8">
-        <v>-56.02</v>
+        <v>-53.55</v>
       </c>
       <c r="AG8">
-        <v>349.07</v>
+        <v>349.17</v>
       </c>
       <c r="AH8">
-        <v>310.53</v>
+        <v>310.96</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1732,7 +1681,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>23.65</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1692,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1285.8</v>
+        <v>1299.7</v>
       </c>
       <c r="D9">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1755,46 +1704,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-3.32</v>
+        <v>-2.28</v>
       </c>
       <c r="H9">
-        <v>25.25</v>
+        <v>26.6</v>
       </c>
       <c r="I9">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="J9">
-        <v>1.45</v>
+        <v>2.59</v>
       </c>
       <c r="K9">
-        <v>0.35</v>
+        <v>1.1</v>
       </c>
       <c r="L9">
-        <v>22.03</v>
+        <v>24.31</v>
       </c>
       <c r="M9">
-        <v>14.47</v>
+        <v>14.71</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1275.24</v>
+        <v>1280.18</v>
       </c>
       <c r="Q9">
-        <v>1277.85</v>
+        <v>1280.49</v>
       </c>
       <c r="R9">
-        <v>1262.08</v>
+        <v>1262.68</v>
       </c>
       <c r="S9">
-        <v>1217.23</v>
+        <v>1217.69</v>
       </c>
       <c r="T9">
-        <v>5.63</v>
+        <v>6.73</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1809,34 +1758,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>54.04</v>
+        <v>57.86</v>
       </c>
       <c r="Z9">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="AA9">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="AB9">
-        <v>-2.19</v>
+        <v>-0.8</v>
       </c>
       <c r="AC9">
-        <v>12.85</v>
+        <v>23.07</v>
       </c>
       <c r="AD9">
-        <v>8.380000000000001</v>
+        <v>13.48</v>
       </c>
       <c r="AE9">
-        <v>25.38</v>
+        <v>25.65</v>
       </c>
       <c r="AF9">
-        <v>-37.97</v>
+        <v>115.79</v>
       </c>
       <c r="AG9">
-        <v>1324.26</v>
+        <v>1325.46</v>
       </c>
       <c r="AH9">
-        <v>1231.43</v>
+        <v>1235.52</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1845,7 +1794,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.56</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1856,10 +1805,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>82.54000000000001</v>
+        <v>82.81</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>0.33</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1868,46 +1817,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-9.74</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="H10">
-        <v>128.77</v>
+        <v>129.52</v>
       </c>
       <c r="I10">
-        <v>-0.43</v>
+        <v>-4.86</v>
       </c>
       <c r="J10">
-        <v>19.54</v>
+        <v>23.49</v>
       </c>
       <c r="K10">
-        <v>65.15000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L10">
-        <v>15.39</v>
+        <v>17.9</v>
       </c>
       <c r="M10">
-        <v>-3.33</v>
+        <v>-3.26</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P10">
-        <v>87.86</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="Q10">
-        <v>79.2</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="R10">
-        <v>63.63</v>
+        <v>64.22</v>
       </c>
       <c r="S10">
-        <v>59.44</v>
+        <v>59.46</v>
       </c>
       <c r="T10">
-        <v>38.87</v>
+        <v>39.27</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1922,34 +1871,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.08</v>
+        <v>59.38</v>
       </c>
       <c r="Z10">
-        <v>7.39</v>
+        <v>6.77</v>
       </c>
       <c r="AA10">
-        <v>7.66</v>
+        <v>7.48</v>
       </c>
       <c r="AB10">
-        <v>-0.27</v>
+        <v>-0.71</v>
       </c>
       <c r="AC10">
-        <v>35.19</v>
+        <v>8.99</v>
       </c>
       <c r="AD10">
-        <v>56.89</v>
+        <v>35.33</v>
       </c>
       <c r="AE10">
-        <v>5.11</v>
+        <v>5.02</v>
       </c>
       <c r="AF10">
-        <v>-89.70999999999999</v>
+        <v>-87.83</v>
       </c>
       <c r="AG10">
-        <v>97.90000000000001</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AH10">
-        <v>60.49</v>
+        <v>63.16</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1958,7 +1907,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>52.87</v>
+        <v>47.28</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2119,1321 +2068,1263 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-4.7</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-1.64</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.06</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.73</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6.73</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.04</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.71</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.93</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3.17</v>
+      </c>
+      <c r="D12" s="5">
+        <v>5.04</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.25</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2.59</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>19.54</v>
+      </c>
+      <c r="D15" s="5">
+        <v>23.49</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-2.94</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-4.7</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-4.23</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.23</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.32</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2.02</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.73</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.88</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.31</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.65</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.97</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2.1</v>
+      </c>
+      <c r="D21" s="5">
         <v>-1.76</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E21" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.37</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.94</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-4.86</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>21.87</v>
+      </c>
+      <c r="D25" s="5">
+        <v>22.82</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>33.46</v>
+      </c>
+      <c r="D26" s="5">
+        <v>36.88</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>12.13</v>
+      </c>
+      <c r="D27" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-1.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2.02</v>
+      </c>
+      <c r="D29" s="5">
+        <v>2.78</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-35.92</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-34.93</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>10.04</v>
+      </c>
+      <c r="D31" s="5">
+        <v>8.92</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>22.03</v>
+      </c>
+      <c r="D32" s="5">
+        <v>24.31</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>15.39</v>
+      </c>
+      <c r="D33" s="5">
+        <v>17.9</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-7.73</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>23.78</v>
+      </c>
+      <c r="D35" s="5">
+        <v>22.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-6.83</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-7.52</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-1.73</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-2.48</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-0.48</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-1.34</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-10.75</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>24.28</v>
+      </c>
+      <c r="D40" s="5">
+        <v>20.12</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="D42" s="5">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-36.65</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-36.78</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-3.71</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-3.33</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-13.49</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-13.18</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-16.26</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-16.91</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-9.34</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-9.67</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-48.89</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-48.27</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-6.06</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-6.08</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-3.32</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-2.28</v>
+      </c>
+      <c r="E50" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-9.74</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>638.35</v>
+      </c>
+      <c r="D52" s="5">
+        <v>637</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>268.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>269.75</v>
+      </c>
+      <c r="E53" s="6">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1115</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1118.9</v>
+      </c>
+      <c r="E54" s="6">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>724</v>
+      </c>
+      <c r="D55" s="5">
+        <v>718.4</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>543.95</v>
+      </c>
+      <c r="D56" s="5">
+        <v>542</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>11329</v>
+      </c>
+      <c r="D57" s="5">
+        <v>11465</v>
+      </c>
+      <c r="E57" s="6">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>329.9</v>
+      </c>
+      <c r="D58" s="5">
+        <v>329.85</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1285.8</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1299.7</v>
+      </c>
+      <c r="E59" s="6">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="D60" s="5">
+        <v>82.81</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>47.89</v>
+      </c>
+      <c r="D61" s="5">
+        <v>47.51</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>54.79</v>
+      </c>
+      <c r="D62" s="5">
+        <v>55.81</v>
+      </c>
+      <c r="E62" s="6">
         <v>1.02</v>
       </c>
-      <c r="D10" s="7">
-        <v>2.46</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>6.6</v>
-      </c>
-      <c r="D11" s="7">
-        <v>6.73</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>57.21</v>
+      </c>
+      <c r="D63" s="5">
+        <v>58.23</v>
+      </c>
+      <c r="E63" s="6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.23</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.04</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>47.14</v>
+      </c>
+      <c r="D64" s="5">
+        <v>44.11</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.45</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>41.17</v>
+      </c>
+      <c r="D65" s="5">
+        <v>40.15</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3.96</v>
-      </c>
-      <c r="D14" s="7">
-        <v>3.17</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>43.03</v>
+      </c>
+      <c r="D66" s="5">
+        <v>46.17</v>
+      </c>
+      <c r="E66" s="6">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-5.68</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-4.25</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>49.62</v>
+      </c>
+      <c r="D67" s="5">
+        <v>49.58</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.45</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>54.04</v>
+      </c>
+      <c r="D68" s="5">
+        <v>57.86</v>
+      </c>
+      <c r="E68" s="6">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>47.81</v>
-      </c>
-      <c r="D17" s="7">
-        <v>19.54</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-28.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>59.08</v>
+      </c>
+      <c r="D69" s="5">
+        <v>59.38</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.72</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-6.95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-61.11</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-71.54000000000001</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-10.43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.79</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>3.47</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-34.35</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-37.82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>27.65</v>
+      </c>
+      <c r="D72" s="5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-19.45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.88</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-54.73</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-36.91</v>
+      </c>
+      <c r="E73" s="6">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-33.35</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-12.28</v>
+      </c>
+      <c r="E74" s="6">
+        <v>21.07</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-3.79</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-45.79</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-44.67</v>
+      </c>
+      <c r="E75" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-3.86</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.82</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-56.02</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-53.55</v>
+      </c>
+      <c r="E76" s="6">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-1.23</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1.32</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-37.97</v>
+      </c>
+      <c r="D77" s="5">
+        <v>115.79</v>
+      </c>
+      <c r="E77" s="6">
+        <v>153.76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3.59</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.43</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-4.02</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>22.74</v>
-      </c>
-      <c r="D26" s="7">
-        <v>21.87</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>36.25</v>
-      </c>
-      <c r="D27" s="7">
-        <v>33.46</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>10.53</v>
-      </c>
-      <c r="D28" s="7">
-        <v>12.13</v>
-      </c>
-      <c r="E28" s="9">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>3.09</v>
-      </c>
-      <c r="D29" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>3.15</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-35.79</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-35.92</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>10.47</v>
-      </c>
-      <c r="D32" s="7">
-        <v>10.04</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>20.93</v>
-      </c>
-      <c r="D33" s="7">
-        <v>22.03</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>18.43</v>
-      </c>
-      <c r="D34" s="7">
-        <v>15.39</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-7.73</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>23.49</v>
-      </c>
-      <c r="D36" s="7">
-        <v>23.78</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-9.94</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-6.83</v>
-      </c>
-      <c r="E37" s="9">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-0.62</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-0.48</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-8.9</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-10.75</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>25.01</v>
-      </c>
-      <c r="D41" s="7">
-        <v>24.28</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-1.22</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>74.95</v>
-      </c>
-      <c r="D43" s="7">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-9.800000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-35.82</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-36.65</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-3.73</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-14.53</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-13.49</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-15.29</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-16.26</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-8.65</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-9.34</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-48.17</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-48.89</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-6.42</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-6.06</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-4.69</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-3.32</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-5</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-9.74</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>646.65</v>
-      </c>
-      <c r="D53" s="7">
-        <v>638.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>268.65</v>
-      </c>
-      <c r="D54" s="7">
-        <v>268.7</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1101.5</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1115</v>
-      </c>
-      <c r="E55" s="9">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>732.4</v>
-      </c>
-      <c r="D56" s="7">
-        <v>724</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-8.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>548.1</v>
-      </c>
-      <c r="D57" s="7">
-        <v>543.95</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-4.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>11489</v>
-      </c>
-      <c r="D58" s="7">
-        <v>11329</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>328.65</v>
-      </c>
-      <c r="D59" s="7">
-        <v>329.9</v>
-      </c>
-      <c r="E59" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1267.6</v>
-      </c>
-      <c r="D60" s="7">
-        <v>1285.8</v>
-      </c>
-      <c r="E60" s="9">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>86.88</v>
-      </c>
-      <c r="D61" s="7">
-        <v>82.54000000000001</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>50.21</v>
-      </c>
-      <c r="D62" s="7">
-        <v>47.89</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>54.74</v>
-      </c>
-      <c r="D63" s="7">
-        <v>54.79</v>
-      </c>
-      <c r="E63" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>53.58</v>
-      </c>
-      <c r="D64" s="7">
-        <v>57.21</v>
-      </c>
-      <c r="E64" s="9">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>52.15</v>
-      </c>
-      <c r="D65" s="7">
-        <v>47.14</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>43.36</v>
-      </c>
-      <c r="D66" s="7">
-        <v>41.17</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>45.96</v>
-      </c>
-      <c r="D67" s="7">
-        <v>43.03</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>48.7</v>
-      </c>
-      <c r="D68" s="7">
-        <v>49.62</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>48.36</v>
-      </c>
-      <c r="D69" s="7">
-        <v>54.04</v>
-      </c>
-      <c r="E69" s="9">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>66.33</v>
-      </c>
-      <c r="D70" s="7">
-        <v>59.08</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-7.25</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="7">
-        <v>-39.71</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-61.11</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-21.4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-50.86</v>
-      </c>
-      <c r="D72" s="7">
-        <v>3.47</v>
-      </c>
-      <c r="E72" s="9">
-        <v>54.33</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-39.24</v>
-      </c>
-      <c r="D73" s="7">
-        <v>27.65</v>
-      </c>
-      <c r="E73" s="9">
-        <v>66.89</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-54.73</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-118.97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-37.04</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-33.35</v>
-      </c>
-      <c r="E75" s="9">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-24.55</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-45.79</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-21.24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-44.23</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-56.02</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-11.79</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-58.23</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-37.97</v>
-      </c>
-      <c r="E78" s="9">
-        <v>20.26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-72.73999999999999</v>
-      </c>
-      <c r="D79" s="7">
+      <c r="C78" s="5">
         <v>-89.70999999999999</v>
       </c>
-      <c r="E79" s="8">
-        <v>-16.97</v>
+      <c r="D78" s="5">
+        <v>-87.83</v>
+      </c>
+      <c r="E78" s="6">
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3453,60 +3344,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>60.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>50.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>51</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
-        <v>2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>9.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3608,61 +3499,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.4005</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3627</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2954</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.246</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.192</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1871</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1447</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0333</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0737</v>
+      <c r="A2" s="13">
+        <v>0.3981</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3635</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2951</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2467</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1947</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1861</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.1471</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0326</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.0741</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.7% → -0.2%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.7%</t>
+  </si>
+  <si>
+    <t>-0.2%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>70.7 → 65.9</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>65.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,13 +313,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +435,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -768,7 +825,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -901,10 +959,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>637</v>
+        <v>636.85</v>
       </c>
       <c r="D2">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -913,46 +971,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.78</v>
+        <v>-36.8</v>
       </c>
       <c r="H2">
-        <v>73.47</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I2">
-        <v>-2.23</v>
+        <v>-4.33</v>
       </c>
       <c r="J2">
-        <v>-1.64</v>
+        <v>-0.08</v>
       </c>
       <c r="K2">
-        <v>-9.630000000000001</v>
+        <v>-7.52</v>
       </c>
       <c r="L2">
-        <v>22.82</v>
+        <v>22.31</v>
       </c>
       <c r="M2">
-        <v>-7.41</v>
+        <v>-6.87</v>
       </c>
       <c r="N2">
         <v>55</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>644.79</v>
+        <v>639.29</v>
       </c>
       <c r="Q2">
-        <v>636.59</v>
+        <v>636.6799999999999</v>
       </c>
       <c r="R2">
-        <v>655.2</v>
+        <v>651.02</v>
       </c>
       <c r="S2">
-        <v>617.9299999999999</v>
+        <v>618.6900000000001</v>
       </c>
       <c r="T2">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -967,34 +1025,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.51</v>
+        <v>47.46</v>
       </c>
       <c r="Z2">
-        <v>-2.49</v>
+        <v>-2.81</v>
       </c>
       <c r="AA2">
-        <v>-4.47</v>
+        <v>-3.85</v>
       </c>
       <c r="AB2">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="AC2">
-        <v>48.1</v>
+        <v>42.63</v>
       </c>
       <c r="AD2">
-        <v>58.27</v>
+        <v>44.72</v>
       </c>
       <c r="AE2">
-        <v>24.48</v>
+        <v>22.78</v>
       </c>
       <c r="AF2">
-        <v>-71.54000000000001</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="AG2">
-        <v>661.52</v>
+        <v>661.61</v>
       </c>
       <c r="AH2">
-        <v>611.66</v>
+        <v>611.75</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1003,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.29</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1014,58 +1072,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>269.75</v>
+        <v>287.25</v>
       </c>
       <c r="D3">
-        <v>0.39</v>
+        <v>-1.51</v>
       </c>
       <c r="E3">
-        <v>279.05</v>
+        <v>291.65</v>
       </c>
       <c r="F3">
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-3.33</v>
+        <v>-1.51</v>
       </c>
       <c r="H3">
-        <v>76.04000000000001</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="I3">
-        <v>2.02</v>
+        <v>7.54</v>
       </c>
       <c r="J3">
-        <v>1.73</v>
+        <v>12.49</v>
       </c>
       <c r="K3">
-        <v>22.61</v>
+        <v>25.51</v>
       </c>
       <c r="L3">
-        <v>36.88</v>
+        <v>40.84</v>
       </c>
       <c r="M3">
-        <v>36.35</v>
+        <v>37.49</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P3">
-        <v>268.26</v>
+        <v>277.2</v>
       </c>
       <c r="Q3">
-        <v>264.3</v>
+        <v>267.93</v>
       </c>
       <c r="R3">
-        <v>261.35</v>
+        <v>263.69</v>
       </c>
       <c r="S3">
-        <v>208.36</v>
+        <v>209.55</v>
       </c>
       <c r="T3">
-        <v>29.46</v>
+        <v>37.08</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1080,43 +1138,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.81</v>
+        <v>65.91</v>
       </c>
       <c r="Z3">
-        <v>2.71</v>
+        <v>5.36</v>
       </c>
       <c r="AA3">
-        <v>2.78</v>
+        <v>3.56</v>
       </c>
       <c r="AB3">
-        <v>-0.07000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>35.88</v>
+        <v>69.08</v>
       </c>
       <c r="AD3">
-        <v>36.57</v>
+        <v>53.41</v>
       </c>
       <c r="AE3">
-        <v>8.029999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="AF3">
-        <v>-34.35</v>
+        <v>1.32</v>
       </c>
       <c r="AG3">
-        <v>278.83</v>
+        <v>287.15</v>
       </c>
       <c r="AH3">
-        <v>249.77</v>
+        <v>248.72</v>
       </c>
       <c r="AI3">
-        <v>250.11</v>
+        <v>262.26</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>22.27</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1127,10 +1185,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1118.9</v>
+        <v>1149</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>1.88</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1139,46 +1197,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-13.18</v>
+        <v>-10.85</v>
       </c>
       <c r="H4">
-        <v>18.3</v>
+        <v>21.48</v>
       </c>
       <c r="I4">
-        <v>1.73</v>
+        <v>5.27</v>
       </c>
       <c r="J4">
-        <v>7.07</v>
+        <v>10.93</v>
       </c>
       <c r="K4">
-        <v>-7.52</v>
+        <v>-6.04</v>
       </c>
       <c r="L4">
-        <v>14.94</v>
+        <v>14.53</v>
       </c>
       <c r="M4">
-        <v>24.67</v>
+        <v>25.61</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>1103.68</v>
+        <v>1122.44</v>
       </c>
       <c r="Q4">
-        <v>1096.88</v>
+        <v>1105.64</v>
       </c>
       <c r="R4">
-        <v>1080.94</v>
+        <v>1081.08</v>
       </c>
       <c r="S4">
-        <v>1123.64</v>
+        <v>1124.24</v>
       </c>
       <c r="T4">
-        <v>-0.42</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1190,46 +1248,46 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>58.23</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="Z4">
-        <v>8.81</v>
+        <v>12.78</v>
       </c>
       <c r="AA4">
-        <v>6.98</v>
+        <v>8.65</v>
       </c>
       <c r="AB4">
-        <v>1.83</v>
+        <v>4.13</v>
       </c>
       <c r="AC4">
-        <v>40.73</v>
+        <v>75.13</v>
       </c>
       <c r="AD4">
-        <v>25.87</v>
+        <v>57.77</v>
       </c>
       <c r="AE4">
-        <v>24.93</v>
+        <v>24.07</v>
       </c>
       <c r="AF4">
-        <v>8.199999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="AG4">
-        <v>1141.99</v>
+        <v>1144.31</v>
       </c>
       <c r="AH4">
-        <v>1051.76</v>
+        <v>1066.97</v>
       </c>
       <c r="AI4">
-        <v>1050.42</v>
+        <v>1067.33</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>28.3</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1240,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>718.4</v>
+        <v>702.4</v>
       </c>
       <c r="D5">
-        <v>-0.77</v>
+        <v>0.15</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1252,46 +1310,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.91</v>
+        <v>-18.76</v>
       </c>
       <c r="H5">
-        <v>8.539999999999999</v>
+        <v>6.12</v>
       </c>
       <c r="I5">
-        <v>-2.31</v>
+        <v>-4.8</v>
       </c>
       <c r="J5">
-        <v>-2.71</v>
+        <v>-1.66</v>
       </c>
       <c r="K5">
-        <v>-2.48</v>
+        <v>-3.48</v>
       </c>
       <c r="L5">
-        <v>-1.2</v>
+        <v>-6.97</v>
       </c>
       <c r="M5">
-        <v>39.81</v>
+        <v>36.49</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>730.1</v>
+        <v>715.71</v>
       </c>
       <c r="Q5">
-        <v>731.21</v>
+        <v>729.49</v>
       </c>
       <c r="R5">
-        <v>717.3200000000001</v>
+        <v>717.92</v>
       </c>
       <c r="S5">
-        <v>750.13</v>
+        <v>749.71</v>
       </c>
       <c r="T5">
-        <v>-4.23</v>
+        <v>-6.31</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1306,34 +1364,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.11</v>
+        <v>37.14</v>
       </c>
       <c r="Z5">
-        <v>2.13</v>
+        <v>-2.18</v>
       </c>
       <c r="AA5">
-        <v>4.51</v>
+        <v>2.4</v>
       </c>
       <c r="AB5">
-        <v>-2.38</v>
+        <v>-4.58</v>
       </c>
       <c r="AC5">
-        <v>7.46</v>
+        <v>0.99</v>
       </c>
       <c r="AD5">
-        <v>25.39</v>
+        <v>2.82</v>
       </c>
       <c r="AE5">
-        <v>16.17</v>
+        <v>16.06</v>
       </c>
       <c r="AF5">
-        <v>-36.91</v>
+        <v>-28.03</v>
       </c>
       <c r="AG5">
-        <v>746.21</v>
+        <v>751.92</v>
       </c>
       <c r="AH5">
-        <v>716.22</v>
+        <v>707.05</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1342,7 +1400,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>17.29</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1353,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>542</v>
+        <v>544.7</v>
       </c>
       <c r="D6">
-        <v>-0.36</v>
+        <v>-0.05</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1365,46 +1423,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-9.67</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="H6">
-        <v>23.59</v>
+        <v>24.2</v>
       </c>
       <c r="I6">
-        <v>-2.97</v>
+        <v>-1.94</v>
       </c>
       <c r="J6">
-        <v>-3.51</v>
+        <v>-1.26</v>
       </c>
       <c r="K6">
-        <v>-1.34</v>
+        <v>-5.11</v>
       </c>
       <c r="L6">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="M6">
-        <v>18.61</v>
+        <v>20.95</v>
       </c>
       <c r="N6">
         <v>34</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>549.91</v>
+        <v>544.74</v>
       </c>
       <c r="Q6">
-        <v>556.3200000000001</v>
+        <v>555.74</v>
       </c>
       <c r="R6">
-        <v>559.02</v>
+        <v>558.58</v>
       </c>
       <c r="S6">
-        <v>519.4299999999999</v>
+        <v>519.59</v>
       </c>
       <c r="T6">
-        <v>4.34</v>
+        <v>4.83</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1419,34 +1477,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.15</v>
+        <v>42.33</v>
       </c>
       <c r="Z6">
-        <v>-2.31</v>
+        <v>-3.28</v>
       </c>
       <c r="AA6">
-        <v>-0.16</v>
+        <v>-1.21</v>
       </c>
       <c r="AB6">
-        <v>-2.16</v>
+        <v>-2.06</v>
       </c>
       <c r="AC6">
-        <v>0.47</v>
+        <v>7.18</v>
       </c>
       <c r="AD6">
-        <v>10.37</v>
+        <v>3.79</v>
       </c>
       <c r="AE6">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="AF6">
-        <v>-12.28</v>
+        <v>-52.13</v>
       </c>
       <c r="AG6">
-        <v>576.5</v>
+        <v>576.9</v>
       </c>
       <c r="AH6">
-        <v>536.14</v>
+        <v>534.58</v>
       </c>
       <c r="AI6">
         <v>577.85</v>
@@ -1455,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.64</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1466,10 +1524,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11465</v>
+        <v>11161</v>
       </c>
       <c r="D7">
-        <v>1.2</v>
+        <v>-1.13</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1478,46 +1536,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.27</v>
+        <v>-49.65</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>4.75</v>
       </c>
       <c r="I7">
-        <v>-1.76</v>
+        <v>-6</v>
       </c>
       <c r="J7">
-        <v>5.04</v>
+        <v>2.72</v>
       </c>
       <c r="K7">
-        <v>-9.210000000000001</v>
+        <v>-10.58</v>
       </c>
       <c r="L7">
-        <v>-34.93</v>
+        <v>-38.91</v>
       </c>
       <c r="M7">
-        <v>19.47</v>
+        <v>18.79</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>11606.2</v>
+        <v>11346.6</v>
       </c>
       <c r="Q7">
-        <v>11607.6</v>
+        <v>11636.9</v>
       </c>
       <c r="R7">
-        <v>11744.22</v>
+        <v>11706.86</v>
       </c>
       <c r="S7">
-        <v>15079.42</v>
+        <v>15022.96</v>
       </c>
       <c r="T7">
-        <v>-23.97</v>
+        <v>-25.71</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1532,43 +1590,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>46.17</v>
+        <v>40.61</v>
       </c>
       <c r="Z7">
-        <v>-7.45</v>
+        <v>-64.66</v>
       </c>
       <c r="AA7">
-        <v>15.61</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AB7">
-        <v>-23.07</v>
+        <v>-56.28</v>
       </c>
       <c r="AC7">
-        <v>7.74</v>
+        <v>4.47</v>
       </c>
       <c r="AD7">
-        <v>21.92</v>
+        <v>5.56</v>
       </c>
       <c r="AE7">
-        <v>382.12</v>
+        <v>383.2</v>
       </c>
       <c r="AF7">
-        <v>-44.67</v>
+        <v>-34.2</v>
       </c>
       <c r="AG7">
-        <v>12483</v>
+        <v>12431.88</v>
       </c>
       <c r="AH7">
-        <v>10732.2</v>
+        <v>10841.92</v>
       </c>
       <c r="AI7">
-        <v>11199.19</v>
+        <v>12426.6</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK7">
-        <v>20.44</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1579,10 +1637,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>329.85</v>
+        <v>340.2</v>
       </c>
       <c r="D8">
-        <v>-0.02</v>
+        <v>1.34</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1591,46 +1649,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-6.08</v>
+        <v>-3.13</v>
       </c>
       <c r="H8">
-        <v>40.78</v>
+        <v>45.19</v>
       </c>
       <c r="I8">
-        <v>-3.37</v>
+        <v>1.43</v>
       </c>
       <c r="J8">
-        <v>-0.05</v>
+        <v>5.42</v>
       </c>
       <c r="K8">
-        <v>20.12</v>
+        <v>21.96</v>
       </c>
       <c r="L8">
-        <v>8.92</v>
+        <v>8.81</v>
       </c>
       <c r="M8">
-        <v>29.51</v>
+        <v>30.77</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="P8">
-        <v>332.59</v>
+        <v>332.86</v>
       </c>
       <c r="Q8">
-        <v>330.07</v>
+        <v>331.64</v>
       </c>
       <c r="R8">
-        <v>325.37</v>
+        <v>327.56</v>
       </c>
       <c r="S8">
-        <v>282.64</v>
+        <v>283.12</v>
       </c>
       <c r="T8">
-        <v>16.7</v>
+        <v>20.16</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1645,34 +1703,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>49.58</v>
+        <v>57.23</v>
       </c>
       <c r="Z8">
-        <v>2.72</v>
+        <v>3.02</v>
       </c>
       <c r="AA8">
-        <v>3.95</v>
+        <v>3.57</v>
       </c>
       <c r="AB8">
-        <v>-1.23</v>
+        <v>-0.54</v>
       </c>
       <c r="AC8">
-        <v>22.79</v>
+        <v>35.35</v>
       </c>
       <c r="AD8">
-        <v>37.32</v>
+        <v>28.08</v>
       </c>
       <c r="AE8">
-        <v>9.779999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="AF8">
-        <v>-53.55</v>
+        <v>-34.33</v>
       </c>
       <c r="AG8">
-        <v>349.17</v>
+        <v>350.54</v>
       </c>
       <c r="AH8">
-        <v>310.96</v>
+        <v>312.74</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1681,7 +1739,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.39</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1692,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1299.7</v>
+        <v>1327</v>
       </c>
       <c r="D9">
-        <v>1.08</v>
+        <v>2.57</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1704,46 +1762,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-2.28</v>
+        <v>-0.23</v>
       </c>
       <c r="H9">
-        <v>26.6</v>
+        <v>29.26</v>
       </c>
       <c r="I9">
-        <v>1.94</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
-        <v>2.59</v>
+        <v>6.95</v>
       </c>
       <c r="K9">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="L9">
-        <v>24.31</v>
+        <v>23.63</v>
       </c>
       <c r="M9">
-        <v>14.71</v>
+        <v>14.95</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P9">
-        <v>1280.18</v>
+        <v>1294.76</v>
       </c>
       <c r="Q9">
-        <v>1280.49</v>
+        <v>1287.26</v>
       </c>
       <c r="R9">
-        <v>1262.68</v>
+        <v>1263.49</v>
       </c>
       <c r="S9">
-        <v>1217.69</v>
+        <v>1218.92</v>
       </c>
       <c r="T9">
-        <v>6.73</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1758,34 +1816,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>57.86</v>
+        <v>63.75</v>
       </c>
       <c r="Z9">
-        <v>6.9</v>
+        <v>10.14</v>
       </c>
       <c r="AA9">
-        <v>7.69</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB9">
-        <v>-0.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC9">
-        <v>23.07</v>
+        <v>48.99</v>
       </c>
       <c r="AD9">
-        <v>13.48</v>
+        <v>35.43</v>
       </c>
       <c r="AE9">
-        <v>25.65</v>
+        <v>25.77</v>
       </c>
       <c r="AF9">
-        <v>115.79</v>
+        <v>139.32</v>
       </c>
       <c r="AG9">
-        <v>1325.46</v>
+        <v>1328.72</v>
       </c>
       <c r="AH9">
-        <v>1235.52</v>
+        <v>1245.79</v>
       </c>
       <c r="AI9">
         <v>1237.29</v>
@@ -1794,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.68</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1805,10 +1863,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>82.81</v>
+        <v>84.75</v>
       </c>
       <c r="D10">
-        <v>0.33</v>
+        <v>4.77</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1817,46 +1875,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-9.449999999999999</v>
+        <v>-7.33</v>
       </c>
       <c r="H10">
-        <v>129.52</v>
+        <v>134.89</v>
       </c>
       <c r="I10">
-        <v>-4.86</v>
+        <v>-7.33</v>
       </c>
       <c r="J10">
-        <v>23.49</v>
+        <v>23</v>
       </c>
       <c r="K10">
-        <v>65.31999999999999</v>
+        <v>63.48</v>
       </c>
       <c r="L10">
-        <v>17.9</v>
+        <v>18.15</v>
       </c>
       <c r="M10">
-        <v>-3.26</v>
+        <v>-2.02</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>87.01000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="Q10">
-        <v>80.20999999999999</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="R10">
-        <v>64.22</v>
+        <v>65.47</v>
       </c>
       <c r="S10">
-        <v>59.46</v>
+        <v>59.51</v>
       </c>
       <c r="T10">
-        <v>39.27</v>
+        <v>42.41</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1871,34 +1929,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.38</v>
+        <v>60.73</v>
       </c>
       <c r="Z10">
-        <v>6.77</v>
+        <v>5.74</v>
       </c>
       <c r="AA10">
-        <v>7.48</v>
+        <v>6.91</v>
       </c>
       <c r="AB10">
-        <v>-0.71</v>
+        <v>-1.17</v>
       </c>
       <c r="AC10">
-        <v>8.99</v>
+        <v>7.17</v>
       </c>
       <c r="AD10">
-        <v>35.33</v>
+        <v>5.56</v>
       </c>
       <c r="AE10">
-        <v>5.02</v>
+        <v>4.81</v>
       </c>
       <c r="AF10">
-        <v>-87.83</v>
+        <v>-80.33</v>
       </c>
       <c r="AG10">
-        <v>97.26000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="AH10">
-        <v>63.16</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1907,7 +1965,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>47.28</v>
+        <v>39.56</v>
       </c>
     </row>
   </sheetData>
@@ -2048,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2068,1263 +2126,1318 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.7</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-1.64</v>
-      </c>
-      <c r="E7" s="6">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-0.08</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>2.46</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="7">
+        <v>11.76</v>
+      </c>
+      <c r="D9" s="7">
+        <v>12.49</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>6.73</v>
-      </c>
-      <c r="D9" s="5">
-        <v>7.07</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="7">
+        <v>8.24</v>
+      </c>
+      <c r="D10" s="7">
+        <v>10.93</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-2.04</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-2.71</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-1.66</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.93</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="7">
+        <v>-2.22</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-1.26</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>3.17</v>
-      </c>
-      <c r="D12" s="5">
-        <v>5.04</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="C13" s="7">
+        <v>5.95</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2.72</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3.45</v>
+      </c>
+      <c r="D14" s="7">
+        <v>5.42</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>3.76</v>
+      </c>
+      <c r="D15" s="7">
+        <v>6.95</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>29.11</v>
+      </c>
+      <c r="D16" s="7">
+        <v>23</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-6.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-4.33</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-4.53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>9.19</v>
+      </c>
+      <c r="D18" s="7">
+        <v>7.54</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3.33</v>
+      </c>
+      <c r="D19" s="7">
+        <v>5.27</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-4.95</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.8</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-2.69</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-1.94</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-4.93</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-6</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.02</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
         <v>1.87</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D24" s="7">
+        <v>3.85</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-11.49</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-7.33</v>
+      </c>
+      <c r="E25" s="9">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>23.75</v>
+      </c>
+      <c r="D26" s="7">
+        <v>22.31</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46.14</v>
+      </c>
+      <c r="D27" s="7">
+        <v>40.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>13.82</v>
+      </c>
+      <c r="D28" s="7">
+        <v>14.53</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-5.8</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>2.47</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2.49</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-36.57</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-38.91</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-4.25</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="E13" s="6">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="D32" s="7">
+        <v>8.81</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.59</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>19.81</v>
+      </c>
+      <c r="D33" s="7">
+        <v>23.63</v>
+      </c>
+      <c r="E33" s="9">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>19.54</v>
-      </c>
-      <c r="D15" s="5">
-        <v>23.49</v>
-      </c>
-      <c r="E15" s="6">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="D34" s="7">
+        <v>18.15</v>
+      </c>
+      <c r="E34" s="9">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-4.23</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.23</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-9.77</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-7.52</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>29.08</v>
+      </c>
+      <c r="D36" s="7">
+        <v>25.51</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-6.04</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-4.17</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-3.48</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.84</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-5.11</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-10.58</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>20.91</v>
+      </c>
+      <c r="D41" s="7">
+        <v>21.96</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.33</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2.58</v>
+      </c>
+      <c r="E42" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>59.2</v>
+      </c>
+      <c r="D43" s="7">
+        <v>63.48</v>
+      </c>
+      <c r="E43" s="9">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-36.72</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-36.8</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-1.51</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-12.49</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-10.85</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-18.88</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-18.76</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-9.18</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-49.07</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-49.65</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-4.41</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-3.13</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-2.73</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-0.23</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-11.55</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-7.33</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="C53" s="7">
+        <v>637.6</v>
+      </c>
+      <c r="D53" s="7">
+        <v>636.85</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.32</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.02</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>291.65</v>
+      </c>
+      <c r="D54" s="7">
+        <v>287.25</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.27</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1127.8</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1149</v>
+      </c>
+      <c r="E55" s="9">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.88</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.31</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>701.35</v>
+      </c>
+      <c r="D56" s="7">
+        <v>702.4</v>
+      </c>
+      <c r="E56" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-2.65</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.97</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>544.95</v>
+      </c>
+      <c r="D57" s="7">
+        <v>544.7</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.76</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11289</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11161</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>335.7</v>
+      </c>
+      <c r="D59" s="7">
+        <v>340.2</v>
+      </c>
+      <c r="E59" s="9">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1293.7</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1327</v>
+      </c>
+      <c r="E60" s="9">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>80.89</v>
+      </c>
+      <c r="D61" s="7">
+        <v>84.75</v>
+      </c>
+      <c r="E61" s="9">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>47.71</v>
+      </c>
+      <c r="D62" s="7">
+        <v>47.46</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>70.73</v>
+      </c>
+      <c r="D63" s="7">
+        <v>65.91</v>
+      </c>
+      <c r="E63" s="8">
         <v>-4.82</v>
       </c>
-      <c r="D22" s="5">
-        <v>-3.37</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>60.53</v>
+      </c>
+      <c r="D64" s="7">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="E64" s="9">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>36.41</v>
+      </c>
+      <c r="D65" s="7">
+        <v>37.14</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>42.48</v>
+      </c>
+      <c r="D66" s="7">
+        <v>42.33</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>42.88</v>
+      </c>
+      <c r="D67" s="7">
+        <v>40.61</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>54.07</v>
+      </c>
+      <c r="D68" s="7">
+        <v>57.23</v>
+      </c>
+      <c r="E68" s="9">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>55.71</v>
+      </c>
+      <c r="D69" s="7">
+        <v>63.75</v>
+      </c>
+      <c r="E69" s="9">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>56.24</v>
+      </c>
+      <c r="D70" s="7">
+        <v>60.73</v>
+      </c>
+      <c r="E70" s="9">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-71.79000000000001</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-75.31999999999999</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>1534.08</v>
+      </c>
+      <c r="D72" s="7">
         <v>1.32</v>
       </c>
-      <c r="D23" s="5">
-        <v>1.94</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="E72" s="8">
+        <v>-1532.76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>8.01</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-1.06</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-9.07</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-11.28</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-28.03</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-16.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-37.81</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-52.13</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-14.32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-22.43</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-34.2</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-11.77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-52.13</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-34.33</v>
+      </c>
+      <c r="E77" s="9">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>29.38</v>
+      </c>
+      <c r="D78" s="7">
+        <v>139.32</v>
+      </c>
+      <c r="E78" s="9">
+        <v>109.94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.43</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-4.86</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>21.87</v>
-      </c>
-      <c r="D25" s="5">
-        <v>22.82</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>33.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>36.88</v>
-      </c>
-      <c r="E26" s="6">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>12.13</v>
-      </c>
-      <c r="D27" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-1.2</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>2.02</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-35.92</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-34.93</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>10.04</v>
-      </c>
-      <c r="D31" s="5">
-        <v>8.92</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>22.03</v>
-      </c>
-      <c r="D32" s="5">
-        <v>24.31</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>15.39</v>
-      </c>
-      <c r="D33" s="5">
-        <v>17.9</v>
-      </c>
-      <c r="E33" s="6">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-7.73</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>23.78</v>
-      </c>
-      <c r="D35" s="5">
-        <v>22.61</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-6.83</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-7.52</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-1.73</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-2.48</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-0.48</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-1.34</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-10.75</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>24.28</v>
-      </c>
-      <c r="D40" s="5">
-        <v>20.12</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-4.16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="D41" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="D42" s="5">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-36.65</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-36.78</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-3.71</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-13.49</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-13.18</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-16.26</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-16.91</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-9.34</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-9.67</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-48.89</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-48.27</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-6.06</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-6.08</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-3.32</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-2.28</v>
-      </c>
-      <c r="E50" s="6">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-9.74</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>638.35</v>
-      </c>
-      <c r="D52" s="5">
-        <v>637</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>268.7</v>
-      </c>
-      <c r="D53" s="5">
-        <v>269.75</v>
-      </c>
-      <c r="E53" s="6">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1115</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1118.9</v>
-      </c>
-      <c r="E54" s="6">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>724</v>
-      </c>
-      <c r="D55" s="5">
-        <v>718.4</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>543.95</v>
-      </c>
-      <c r="D56" s="5">
-        <v>542</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>11329</v>
-      </c>
-      <c r="D57" s="5">
-        <v>11465</v>
-      </c>
-      <c r="E57" s="6">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>329.9</v>
-      </c>
-      <c r="D58" s="5">
-        <v>329.85</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1285.8</v>
-      </c>
-      <c r="D59" s="5">
-        <v>1299.7</v>
-      </c>
-      <c r="E59" s="6">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>82.54000000000001</v>
-      </c>
-      <c r="D60" s="5">
-        <v>82.81</v>
-      </c>
-      <c r="E60" s="6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>47.89</v>
-      </c>
-      <c r="D61" s="5">
-        <v>47.51</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>54.79</v>
-      </c>
-      <c r="D62" s="5">
-        <v>55.81</v>
-      </c>
-      <c r="E62" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>57.21</v>
-      </c>
-      <c r="D63" s="5">
-        <v>58.23</v>
-      </c>
-      <c r="E63" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>47.14</v>
-      </c>
-      <c r="D64" s="5">
-        <v>44.11</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>41.17</v>
-      </c>
-      <c r="D65" s="5">
-        <v>40.15</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>43.03</v>
-      </c>
-      <c r="D66" s="5">
-        <v>46.17</v>
-      </c>
-      <c r="E66" s="6">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>49.62</v>
-      </c>
-      <c r="D67" s="5">
-        <v>49.58</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>54.04</v>
-      </c>
-      <c r="D68" s="5">
-        <v>57.86</v>
-      </c>
-      <c r="E68" s="6">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>59.08</v>
-      </c>
-      <c r="D69" s="5">
-        <v>59.38</v>
-      </c>
-      <c r="E69" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-61.11</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-71.54000000000001</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-10.43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>3.47</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-34.35</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-37.82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>27.65</v>
-      </c>
-      <c r="D72" s="5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-19.45</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-54.73</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-36.91</v>
-      </c>
-      <c r="E73" s="6">
-        <v>17.82</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-33.35</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-12.28</v>
-      </c>
-      <c r="E74" s="6">
-        <v>21.07</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-45.79</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-44.67</v>
-      </c>
-      <c r="E75" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-56.02</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-53.55</v>
-      </c>
-      <c r="E76" s="6">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-37.97</v>
-      </c>
-      <c r="D77" s="5">
-        <v>115.79</v>
-      </c>
-      <c r="E77" s="6">
-        <v>153.76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-89.70999999999999</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-87.83</v>
-      </c>
-      <c r="E78" s="6">
-        <v>1.88</v>
+      <c r="C79" s="7">
+        <v>-92.93000000000001</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-80.33</v>
+      </c>
+      <c r="E79" s="9">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3344,60 +3457,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>64.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>51</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>53.4</v>
+      </c>
+      <c r="E2" s="12">
+        <v>80</v>
+      </c>
+      <c r="F2" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>9</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3499,61 +3612,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3981</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3635</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2951</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2467</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1947</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1861</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.1471</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0326</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0741</v>
+      <c r="A2" s="15">
+        <v>0.3749</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3649</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3077</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2561</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.2095</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1879</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1495</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0202</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0687</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -193,34 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.7% → -0.2%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.7%</t>
-  </si>
-  <si>
-    <t>-0.2%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>70.7 → 65.9</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>70.7</t>
-  </si>
-  <si>
-    <t>65.9</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.5 → 51.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.5% → -3.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.5%</t>
+  </si>
+  <si>
+    <t>-3.4%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -446,8 +446,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,15 +818,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -959,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>636.85</v>
+        <v>646.6</v>
       </c>
       <c r="D2">
-        <v>-0.12</v>
+        <v>1.53</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -971,22 +970,22 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.8</v>
+        <v>-35.83</v>
       </c>
       <c r="H2">
-        <v>73.43000000000001</v>
+        <v>76.09</v>
       </c>
       <c r="I2">
-        <v>-4.33</v>
+        <v>-0.01</v>
       </c>
       <c r="J2">
-        <v>-0.08</v>
+        <v>1.76</v>
       </c>
       <c r="K2">
-        <v>-7.52</v>
+        <v>-8.24</v>
       </c>
       <c r="L2">
-        <v>22.31</v>
+        <v>24.72</v>
       </c>
       <c r="M2">
         <v>-6.87</v>
@@ -995,22 +994,22 @@
         <v>55</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>639.29</v>
+        <v>639.28</v>
       </c>
       <c r="Q2">
-        <v>636.6799999999999</v>
+        <v>637.5</v>
       </c>
       <c r="R2">
-        <v>651.02</v>
+        <v>649.16</v>
       </c>
       <c r="S2">
-        <v>618.6900000000001</v>
+        <v>619.1799999999999</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>4.43</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,34 +1024,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.46</v>
+        <v>50.97</v>
       </c>
       <c r="Z2">
-        <v>-2.81</v>
+        <v>-2.13</v>
       </c>
       <c r="AA2">
-        <v>-3.85</v>
+        <v>-3.51</v>
       </c>
       <c r="AB2">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AC2">
-        <v>42.63</v>
+        <v>49.12</v>
       </c>
       <c r="AD2">
-        <v>44.72</v>
+        <v>45.06</v>
       </c>
       <c r="AE2">
-        <v>22.78</v>
+        <v>22.82</v>
       </c>
       <c r="AF2">
-        <v>-75.31999999999999</v>
+        <v>-47.21</v>
       </c>
       <c r="AG2">
-        <v>661.61</v>
+        <v>662.61</v>
       </c>
       <c r="AH2">
-        <v>611.75</v>
+        <v>612.4</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1061,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.15</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1071,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>287.25</v>
+        <v>281.75</v>
       </c>
       <c r="D3">
-        <v>-1.51</v>
+        <v>-1.91</v>
       </c>
       <c r="E3">
         <v>291.65</v>
@@ -1084,46 +1083,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-1.51</v>
+        <v>-3.39</v>
       </c>
       <c r="H3">
-        <v>87.45999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="I3">
-        <v>7.54</v>
+        <v>4.88</v>
       </c>
       <c r="J3">
-        <v>12.49</v>
+        <v>12.32</v>
       </c>
       <c r="K3">
-        <v>25.51</v>
+        <v>14.5</v>
       </c>
       <c r="L3">
-        <v>40.84</v>
+        <v>38.26</v>
       </c>
       <c r="M3">
-        <v>37.49</v>
+        <v>38.05</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>277.2</v>
+        <v>279.82</v>
       </c>
       <c r="Q3">
-        <v>267.93</v>
+        <v>269.16</v>
       </c>
       <c r="R3">
-        <v>263.69</v>
+        <v>264.4</v>
       </c>
       <c r="S3">
-        <v>209.55</v>
+        <v>210.13</v>
       </c>
       <c r="T3">
-        <v>37.08</v>
+        <v>34.08</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1138,34 +1137,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>65.91</v>
+        <v>60.38</v>
       </c>
       <c r="Z3">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="AA3">
-        <v>3.56</v>
+        <v>3.97</v>
       </c>
       <c r="AB3">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AC3">
-        <v>69.08</v>
+        <v>74.22</v>
       </c>
       <c r="AD3">
-        <v>53.41</v>
+        <v>66.19</v>
       </c>
       <c r="AE3">
-        <v>9.51</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AF3">
-        <v>1.32</v>
+        <v>-49.69</v>
       </c>
       <c r="AG3">
-        <v>287.15</v>
+        <v>288.62</v>
       </c>
       <c r="AH3">
-        <v>248.72</v>
+        <v>249.71</v>
       </c>
       <c r="AI3">
         <v>262.26</v>
@@ -1174,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>34.76</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1184,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1149</v>
+        <v>1154.1</v>
       </c>
       <c r="D4">
-        <v>1.88</v>
+        <v>0.44</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1197,46 +1196,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-10.85</v>
+        <v>-10.45</v>
       </c>
       <c r="H4">
-        <v>21.48</v>
+        <v>22.02</v>
       </c>
       <c r="I4">
-        <v>5.27</v>
+        <v>4.78</v>
       </c>
       <c r="J4">
-        <v>10.93</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K4">
-        <v>-6.04</v>
+        <v>-5.45</v>
       </c>
       <c r="L4">
-        <v>14.53</v>
+        <v>13.79</v>
       </c>
       <c r="M4">
-        <v>25.61</v>
+        <v>25.54</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P4">
-        <v>1122.44</v>
+        <v>1132.96</v>
       </c>
       <c r="Q4">
-        <v>1105.64</v>
+        <v>1110.62</v>
       </c>
       <c r="R4">
-        <v>1081.08</v>
+        <v>1081.17</v>
       </c>
       <c r="S4">
-        <v>1124.24</v>
+        <v>1124.78</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1251,43 +1250,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>65.43000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="Z4">
-        <v>12.78</v>
+        <v>15.11</v>
       </c>
       <c r="AA4">
-        <v>8.65</v>
+        <v>9.94</v>
       </c>
       <c r="AB4">
-        <v>4.13</v>
+        <v>5.16</v>
       </c>
       <c r="AC4">
-        <v>75.13</v>
+        <v>90.34</v>
       </c>
       <c r="AD4">
-        <v>57.77</v>
+        <v>74.31</v>
       </c>
       <c r="AE4">
-        <v>24.07</v>
+        <v>23.56</v>
       </c>
       <c r="AF4">
-        <v>-1.06</v>
+        <v>-28.94</v>
       </c>
       <c r="AG4">
-        <v>1144.31</v>
+        <v>1147.13</v>
       </c>
       <c r="AH4">
-        <v>1066.97</v>
+        <v>1074.12</v>
       </c>
       <c r="AI4">
-        <v>1067.33</v>
+        <v>1077.86</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>33.71</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>702.4</v>
+        <v>701.4</v>
       </c>
       <c r="D5">
-        <v>0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1310,46 +1309,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.76</v>
+        <v>-18.87</v>
       </c>
       <c r="H5">
-        <v>6.12</v>
+        <v>5.97</v>
       </c>
       <c r="I5">
-        <v>-4.8</v>
+        <v>-4.23</v>
       </c>
       <c r="J5">
-        <v>-1.66</v>
+        <v>-3.12</v>
       </c>
       <c r="K5">
-        <v>-3.48</v>
+        <v>-2.88</v>
       </c>
       <c r="L5">
-        <v>-6.97</v>
+        <v>-7.97</v>
       </c>
       <c r="M5">
-        <v>36.49</v>
+        <v>36.67</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>715.71</v>
+        <v>709.51</v>
       </c>
       <c r="Q5">
-        <v>729.49</v>
+        <v>728.34</v>
       </c>
       <c r="R5">
-        <v>717.92</v>
+        <v>717.9299999999999</v>
       </c>
       <c r="S5">
-        <v>749.71</v>
+        <v>749.5700000000001</v>
       </c>
       <c r="T5">
-        <v>-6.31</v>
+        <v>-6.43</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1364,34 +1363,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.14</v>
+        <v>36.71</v>
       </c>
       <c r="Z5">
-        <v>-2.18</v>
+        <v>-3.68</v>
       </c>
       <c r="AA5">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="AB5">
-        <v>-4.58</v>
+        <v>-4.86</v>
       </c>
       <c r="AC5">
-        <v>0.99</v>
+        <v>1.49</v>
       </c>
       <c r="AD5">
-        <v>2.82</v>
+        <v>0.83</v>
       </c>
       <c r="AE5">
-        <v>16.06</v>
+        <v>15.67</v>
       </c>
       <c r="AF5">
-        <v>-28.03</v>
+        <v>-58.48</v>
       </c>
       <c r="AG5">
-        <v>751.92</v>
+        <v>754</v>
       </c>
       <c r="AH5">
-        <v>707.05</v>
+        <v>702.6900000000001</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1400,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>21.73</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>544.7</v>
+        <v>548.4</v>
       </c>
       <c r="D6">
-        <v>-0.05</v>
+        <v>0.68</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1423,46 +1422,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-9.220000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="H6">
-        <v>24.2</v>
+        <v>25.05</v>
       </c>
       <c r="I6">
-        <v>-1.94</v>
+        <v>0.05</v>
       </c>
       <c r="J6">
-        <v>-1.26</v>
+        <v>-0.24</v>
       </c>
       <c r="K6">
-        <v>-5.11</v>
+        <v>-8.6</v>
       </c>
       <c r="L6">
-        <v>2.49</v>
+        <v>3.48</v>
       </c>
       <c r="M6">
-        <v>20.95</v>
+        <v>19.95</v>
       </c>
       <c r="N6">
         <v>34</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>544.74</v>
+        <v>544.8</v>
       </c>
       <c r="Q6">
-        <v>555.74</v>
+        <v>555.95</v>
       </c>
       <c r="R6">
-        <v>558.58</v>
+        <v>558.23</v>
       </c>
       <c r="S6">
-        <v>519.59</v>
+        <v>519.76</v>
       </c>
       <c r="T6">
-        <v>4.83</v>
+        <v>5.51</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1477,43 +1476,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.33</v>
+        <v>45.41</v>
       </c>
       <c r="Z6">
-        <v>-3.28</v>
+        <v>-3.27</v>
       </c>
       <c r="AA6">
-        <v>-1.21</v>
+        <v>-1.63</v>
       </c>
       <c r="AB6">
-        <v>-2.06</v>
+        <v>-1.64</v>
       </c>
       <c r="AC6">
-        <v>7.18</v>
+        <v>15.55</v>
       </c>
       <c r="AD6">
-        <v>3.79</v>
+        <v>8.81</v>
       </c>
       <c r="AE6">
-        <v>11.29</v>
+        <v>11.14</v>
       </c>
       <c r="AF6">
-        <v>-52.13</v>
+        <v>-13.55</v>
       </c>
       <c r="AG6">
-        <v>576.9</v>
+        <v>576.71</v>
       </c>
       <c r="AH6">
-        <v>534.58</v>
+        <v>535.1799999999999</v>
       </c>
       <c r="AI6">
-        <v>577.85</v>
+        <v>577.21</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>17.58</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11161</v>
+        <v>11446</v>
       </c>
       <c r="D7">
-        <v>-1.13</v>
+        <v>2.55</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1536,46 +1535,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.65</v>
+        <v>-48.36</v>
       </c>
       <c r="H7">
-        <v>4.75</v>
+        <v>7.42</v>
       </c>
       <c r="I7">
-        <v>-6</v>
+        <v>-0.37</v>
       </c>
       <c r="J7">
-        <v>2.72</v>
+        <v>4.06</v>
       </c>
       <c r="K7">
-        <v>-10.58</v>
+        <v>-9.17</v>
       </c>
       <c r="L7">
-        <v>-38.91</v>
+        <v>-36.97</v>
       </c>
       <c r="M7">
-        <v>18.79</v>
+        <v>18.01</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P7">
-        <v>11346.6</v>
+        <v>11338</v>
       </c>
       <c r="Q7">
-        <v>11636.9</v>
+        <v>11660.15</v>
       </c>
       <c r="R7">
-        <v>11706.86</v>
+        <v>11687.34</v>
       </c>
       <c r="S7">
-        <v>15022.96</v>
+        <v>14996.93</v>
       </c>
       <c r="T7">
-        <v>-25.71</v>
+        <v>-23.68</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1590,34 +1589,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.61</v>
+        <v>47.3</v>
       </c>
       <c r="Z7">
-        <v>-64.66</v>
+        <v>-65.2</v>
       </c>
       <c r="AA7">
-        <v>-8.380000000000001</v>
+        <v>-19.75</v>
       </c>
       <c r="AB7">
-        <v>-56.28</v>
+        <v>-45.45</v>
       </c>
       <c r="AC7">
-        <v>4.47</v>
+        <v>11.45</v>
       </c>
       <c r="AD7">
-        <v>5.56</v>
+        <v>6.8</v>
       </c>
       <c r="AE7">
-        <v>383.2</v>
+        <v>383.97</v>
       </c>
       <c r="AF7">
-        <v>-34.2</v>
+        <v>-13.87</v>
       </c>
       <c r="AG7">
-        <v>12431.88</v>
+        <v>12399.62</v>
       </c>
       <c r="AH7">
-        <v>10841.92</v>
+        <v>10920.68</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1626,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>23.24</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>340.2</v>
+        <v>343.95</v>
       </c>
       <c r="D8">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1649,46 +1648,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
       <c r="H8">
-        <v>45.19</v>
+        <v>46.79</v>
       </c>
       <c r="I8">
-        <v>1.43</v>
+        <v>4.66</v>
       </c>
       <c r="J8">
-        <v>5.42</v>
+        <v>6.88</v>
       </c>
       <c r="K8">
-        <v>21.96</v>
+        <v>23.04</v>
       </c>
       <c r="L8">
-        <v>8.81</v>
+        <v>11.56</v>
       </c>
       <c r="M8">
-        <v>30.77</v>
+        <v>31.23</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P8">
-        <v>332.86</v>
+        <v>335.92</v>
       </c>
       <c r="Q8">
-        <v>331.64</v>
+        <v>332.92</v>
       </c>
       <c r="R8">
-        <v>327.56</v>
+        <v>328.55</v>
       </c>
       <c r="S8">
-        <v>283.12</v>
+        <v>283.42</v>
       </c>
       <c r="T8">
-        <v>20.16</v>
+        <v>21.36</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1703,34 +1702,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.23</v>
+        <v>59.71</v>
       </c>
       <c r="Z8">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AB8">
-        <v>-0.54</v>
+        <v>-0.03</v>
       </c>
       <c r="AC8">
-        <v>35.35</v>
+        <v>59.55</v>
       </c>
       <c r="AD8">
-        <v>28.08</v>
+        <v>40.33</v>
       </c>
       <c r="AE8">
-        <v>9.57</v>
+        <v>9.43</v>
       </c>
       <c r="AF8">
-        <v>-34.33</v>
+        <v>-19.82</v>
       </c>
       <c r="AG8">
-        <v>350.54</v>
+        <v>351.47</v>
       </c>
       <c r="AH8">
-        <v>312.74</v>
+        <v>314.38</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1739,7 +1738,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>22.52</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1327</v>
+        <v>1320.3</v>
       </c>
       <c r="D9">
-        <v>2.57</v>
+        <v>-0.5</v>
       </c>
       <c r="E9">
         <v>1330</v>
@@ -1762,25 +1761,25 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-0.23</v>
+        <v>-0.73</v>
       </c>
       <c r="H9">
-        <v>29.26</v>
+        <v>28.61</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>4.16</v>
       </c>
       <c r="J9">
-        <v>6.95</v>
+        <v>6.08</v>
       </c>
       <c r="K9">
-        <v>2.58</v>
+        <v>0.84</v>
       </c>
       <c r="L9">
-        <v>23.63</v>
+        <v>21.96</v>
       </c>
       <c r="M9">
-        <v>14.95</v>
+        <v>15.1</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1789,19 +1788,19 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>1294.76</v>
+        <v>1305.3</v>
       </c>
       <c r="Q9">
-        <v>1287.26</v>
+        <v>1290.93</v>
       </c>
       <c r="R9">
-        <v>1263.49</v>
+        <v>1263.97</v>
       </c>
       <c r="S9">
-        <v>1218.92</v>
+        <v>1219.67</v>
       </c>
       <c r="T9">
-        <v>8.869999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1816,43 +1815,43 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>63.75</v>
+        <v>61.34</v>
       </c>
       <c r="Z9">
-        <v>10.14</v>
+        <v>11.74</v>
       </c>
       <c r="AA9">
-        <v>8.119999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="AB9">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="AC9">
-        <v>48.99</v>
+        <v>62.66</v>
       </c>
       <c r="AD9">
-        <v>35.43</v>
+        <v>48.63</v>
       </c>
       <c r="AE9">
-        <v>25.77</v>
+        <v>25.14</v>
       </c>
       <c r="AF9">
-        <v>139.32</v>
+        <v>-26.13</v>
       </c>
       <c r="AG9">
-        <v>1328.72</v>
+        <v>1330.29</v>
       </c>
       <c r="AH9">
-        <v>1245.79</v>
+        <v>1251.56</v>
       </c>
       <c r="AI9">
-        <v>1237.29</v>
+        <v>1242.79</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.13</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>84.75</v>
+        <v>81.87</v>
       </c>
       <c r="D10">
-        <v>4.77</v>
+        <v>-3.4</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1875,46 +1874,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-7.33</v>
+        <v>-10.48</v>
       </c>
       <c r="H10">
-        <v>134.89</v>
+        <v>126.91</v>
       </c>
       <c r="I10">
-        <v>-7.33</v>
+        <v>-5.77</v>
       </c>
       <c r="J10">
-        <v>23</v>
+        <v>17.68</v>
       </c>
       <c r="K10">
-        <v>63.48</v>
+        <v>55.76</v>
       </c>
       <c r="L10">
-        <v>18.15</v>
+        <v>11.74</v>
       </c>
       <c r="M10">
-        <v>-2.02</v>
+        <v>-2.54</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P10">
-        <v>83.56999999999999</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="Q10">
-        <v>81.56999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="R10">
-        <v>65.47</v>
+        <v>66.06</v>
       </c>
       <c r="S10">
-        <v>59.51</v>
+        <v>59.55</v>
       </c>
       <c r="T10">
-        <v>42.41</v>
+        <v>37.49</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1929,34 +1928,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>60.73</v>
+        <v>56.11</v>
       </c>
       <c r="Z10">
-        <v>5.74</v>
+        <v>5.19</v>
       </c>
       <c r="AA10">
-        <v>6.91</v>
+        <v>6.56</v>
       </c>
       <c r="AB10">
-        <v>-1.17</v>
+        <v>-1.37</v>
       </c>
       <c r="AC10">
-        <v>7.17</v>
+        <v>6.67</v>
       </c>
       <c r="AD10">
-        <v>5.56</v>
+        <v>4.78</v>
       </c>
       <c r="AE10">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="AF10">
-        <v>-80.33</v>
+        <v>-92.67</v>
       </c>
       <c r="AG10">
-        <v>96.95</v>
+        <v>96.2</v>
       </c>
       <c r="AH10">
-        <v>66.18000000000001</v>
+        <v>68.34</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1965,7 +1964,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>39.56</v>
+        <v>36.41</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2145,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2218,13 +2217,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="7">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="D8" s="7">
-        <v>-0.08</v>
+        <v>1.76</v>
       </c>
       <c r="E8" s="8">
-        <v>-0.03</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2235,13 +2234,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>11.76</v>
+        <v>12.49</v>
       </c>
       <c r="D9" s="7">
-        <v>12.49</v>
+        <v>12.32</v>
       </c>
       <c r="E9" s="9">
-        <v>0.73</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2252,13 +2251,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>8.24</v>
+        <v>10.93</v>
       </c>
       <c r="D10" s="7">
-        <v>10.93</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E10" s="9">
-        <v>2.69</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2269,13 +2268,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-4.69</v>
+        <v>-1.66</v>
       </c>
       <c r="D11" s="7">
-        <v>-1.66</v>
+        <v>-3.12</v>
       </c>
       <c r="E11" s="9">
-        <v>3.03</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2286,13 +2285,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-2.22</v>
+        <v>-1.26</v>
       </c>
       <c r="D12" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.96</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.02</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2303,13 +2302,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>5.95</v>
+        <v>2.72</v>
       </c>
       <c r="D13" s="7">
-        <v>2.72</v>
+        <v>4.06</v>
       </c>
       <c r="E13" s="8">
-        <v>-3.23</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2320,13 +2319,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>3.45</v>
+        <v>5.42</v>
       </c>
       <c r="D14" s="7">
-        <v>5.42</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.97</v>
+        <v>6.88</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.46</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2337,13 +2336,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>3.76</v>
+        <v>6.95</v>
       </c>
       <c r="D15" s="7">
-        <v>6.95</v>
+        <v>6.08</v>
       </c>
       <c r="E15" s="9">
-        <v>3.19</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2354,13 +2353,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>29.11</v>
+        <v>23</v>
       </c>
       <c r="D16" s="7">
-        <v>23</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-6.11</v>
+        <v>17.68</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-5.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2371,13 +2370,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>0.2</v>
+        <v>-4.33</v>
       </c>
       <c r="D17" s="7">
-        <v>-4.33</v>
+        <v>-0.01</v>
       </c>
       <c r="E17" s="8">
-        <v>-4.53</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2388,13 +2387,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>9.19</v>
+        <v>7.54</v>
       </c>
       <c r="D18" s="7">
-        <v>7.54</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.65</v>
+        <v>4.88</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2405,13 +2404,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>3.33</v>
+        <v>5.27</v>
       </c>
       <c r="D19" s="7">
-        <v>5.27</v>
+        <v>4.78</v>
       </c>
       <c r="E19" s="9">
-        <v>1.94</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2422,13 +2421,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-4.95</v>
+        <v>-4.8</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.8</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.15</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2439,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-2.69</v>
+        <v>-1.94</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.94</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.75</v>
+        <v>0.05</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2456,13 +2455,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-4.93</v>
+        <v>-6</v>
       </c>
       <c r="D22" s="7">
-        <v>-6</v>
+        <v>-0.37</v>
       </c>
       <c r="E22" s="8">
-        <v>-1.07</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2473,13 +2472,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-1.02</v>
+        <v>1.43</v>
       </c>
       <c r="D23" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="E23" s="9">
-        <v>2.45</v>
+        <v>4.66</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.23</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2490,13 +2489,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>1.87</v>
+        <v>3.85</v>
       </c>
       <c r="D24" s="7">
-        <v>3.85</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.98</v>
+        <v>4.16</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2507,13 +2506,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-11.49</v>
+        <v>-7.33</v>
       </c>
       <c r="D25" s="7">
-        <v>-7.33</v>
-      </c>
-      <c r="E25" s="9">
-        <v>4.16</v>
+        <v>-5.77</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2524,13 +2523,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>23.75</v>
+        <v>22.31</v>
       </c>
       <c r="D26" s="7">
-        <v>22.31</v>
+        <v>24.72</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2541,13 +2540,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>46.14</v>
+        <v>40.84</v>
       </c>
       <c r="D27" s="7">
-        <v>40.84</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-5.3</v>
+        <v>38.26</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2558,13 +2557,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>13.82</v>
+        <v>14.53</v>
       </c>
       <c r="D28" s="7">
-        <v>14.53</v>
+        <v>13.79</v>
       </c>
       <c r="E28" s="9">
-        <v>0.71</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2575,13 +2574,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>-5.8</v>
+        <v>-6.97</v>
       </c>
       <c r="D29" s="7">
-        <v>-6.97</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.17</v>
+        <v>-7.97</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2592,13 +2591,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="D30" s="7">
-        <v>2.49</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.02</v>
+        <v>3.48</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.99</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2609,13 +2608,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-36.57</v>
+        <v>-38.91</v>
       </c>
       <c r="D31" s="7">
-        <v>-38.91</v>
+        <v>-36.97</v>
       </c>
       <c r="E31" s="8">
-        <v>-2.34</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2626,13 +2625,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>8.609999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="D32" s="7">
-        <v>8.81</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.2</v>
+        <v>11.56</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2643,13 +2642,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>19.81</v>
+        <v>23.63</v>
       </c>
       <c r="D33" s="7">
-        <v>23.63</v>
+        <v>21.96</v>
       </c>
       <c r="E33" s="9">
-        <v>3.82</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2660,13 +2659,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>10.6</v>
+        <v>18.15</v>
       </c>
       <c r="D34" s="7">
-        <v>18.15</v>
+        <v>11.74</v>
       </c>
       <c r="E34" s="9">
-        <v>7.55</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2677,13 +2676,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>-9.77</v>
+        <v>-7.52</v>
       </c>
       <c r="D35" s="7">
-        <v>-7.52</v>
+        <v>-8.24</v>
       </c>
       <c r="E35" s="9">
-        <v>2.25</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2694,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>29.08</v>
+        <v>25.51</v>
       </c>
       <c r="D36" s="7">
-        <v>25.51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-3.57</v>
+        <v>14.5</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-11.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2711,13 +2710,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-6.97</v>
+        <v>-6.04</v>
       </c>
       <c r="D37" s="7">
-        <v>-6.04</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.93</v>
+        <v>-5.45</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2728,13 +2727,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-4.17</v>
+        <v>-3.48</v>
       </c>
       <c r="D38" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.6899999999999999</v>
+        <v>-2.88</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2745,13 +2744,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-1.84</v>
+        <v>-5.11</v>
       </c>
       <c r="D39" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-3.27</v>
+        <v>-8.6</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-3.49</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2762,13 +2761,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-9.859999999999999</v>
+        <v>-10.58</v>
       </c>
       <c r="D40" s="7">
-        <v>-10.58</v>
+        <v>-9.17</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.72</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2779,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>20.91</v>
+        <v>21.96</v>
       </c>
       <c r="D41" s="7">
-        <v>21.96</v>
-      </c>
-      <c r="E41" s="9">
-        <v>1.05</v>
+        <v>23.04</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2796,13 +2795,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>0.33</v>
+        <v>2.58</v>
       </c>
       <c r="D42" s="7">
-        <v>2.58</v>
+        <v>0.84</v>
       </c>
       <c r="E42" s="9">
-        <v>2.25</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2813,13 +2812,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>59.2</v>
+        <v>63.48</v>
       </c>
       <c r="D43" s="7">
-        <v>63.48</v>
+        <v>55.76</v>
       </c>
       <c r="E43" s="9">
-        <v>4.28</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2830,13 +2829,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-36.72</v>
+        <v>-36.8</v>
       </c>
       <c r="D44" s="7">
-        <v>-36.8</v>
+        <v>-35.83</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.08</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2847,13 +2846,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.51</v>
+        <v>-3.39</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2864,13 +2863,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-12.49</v>
+        <v>-10.85</v>
       </c>
       <c r="D46" s="7">
-        <v>-10.85</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.64</v>
+        <v>-10.45</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2881,13 +2880,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-18.88</v>
+        <v>-18.76</v>
       </c>
       <c r="D47" s="7">
-        <v>-18.76</v>
+        <v>-18.87</v>
       </c>
       <c r="E47" s="9">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2898,13 +2897,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-9.18</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D48" s="7">
-        <v>-9.220000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="E48" s="8">
-        <v>-0.04</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2915,13 +2914,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-49.07</v>
+        <v>-49.65</v>
       </c>
       <c r="D49" s="7">
-        <v>-49.65</v>
+        <v>-48.36</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.58</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2932,13 +2931,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-4.41</v>
+        <v>-3.13</v>
       </c>
       <c r="D50" s="7">
-        <v>-3.13</v>
-      </c>
-      <c r="E50" s="9">
-        <v>1.28</v>
+        <v>-2.06</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2949,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-2.73</v>
+        <v>-0.23</v>
       </c>
       <c r="D51" s="7">
-        <v>-0.23</v>
+        <v>-0.73</v>
       </c>
       <c r="E51" s="9">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2966,13 +2965,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-11.55</v>
+        <v>-7.33</v>
       </c>
       <c r="D52" s="7">
-        <v>-7.33</v>
+        <v>-10.48</v>
       </c>
       <c r="E52" s="9">
-        <v>4.22</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2983,13 +2982,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>637.6</v>
+        <v>636.85</v>
       </c>
       <c r="D53" s="7">
-        <v>636.85</v>
+        <v>646.6</v>
       </c>
       <c r="E53" s="8">
-        <v>-0.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3000,13 +2999,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>291.65</v>
+        <v>287.25</v>
       </c>
       <c r="D54" s="7">
-        <v>287.25</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-4.4</v>
+        <v>281.75</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3017,13 +3016,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>1127.8</v>
+        <v>1149</v>
       </c>
       <c r="D55" s="7">
-        <v>1149</v>
-      </c>
-      <c r="E55" s="9">
-        <v>21.2</v>
+        <v>1154.1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>5.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3034,13 +3033,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>701.35</v>
+        <v>702.4</v>
       </c>
       <c r="D56" s="7">
-        <v>702.4</v>
+        <v>701.4</v>
       </c>
       <c r="E56" s="9">
-        <v>1.05</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3051,13 +3050,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>544.95</v>
+        <v>544.7</v>
       </c>
       <c r="D57" s="7">
-        <v>544.7</v>
+        <v>548.4</v>
       </c>
       <c r="E57" s="8">
-        <v>-0.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3068,13 +3067,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>11289</v>
+        <v>11161</v>
       </c>
       <c r="D58" s="7">
-        <v>11161</v>
+        <v>11446</v>
       </c>
       <c r="E58" s="8">
-        <v>-128</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3085,13 +3084,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>335.7</v>
+        <v>340.2</v>
       </c>
       <c r="D59" s="7">
-        <v>340.2</v>
-      </c>
-      <c r="E59" s="9">
-        <v>4.5</v>
+        <v>343.95</v>
+      </c>
+      <c r="E59" s="8">
+        <v>3.75</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3102,13 +3101,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>1293.7</v>
+        <v>1327</v>
       </c>
       <c r="D60" s="7">
-        <v>1327</v>
+        <v>1320.3</v>
       </c>
       <c r="E60" s="9">
-        <v>33.3</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3119,13 +3118,13 @@
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>80.89</v>
+        <v>84.75</v>
       </c>
       <c r="D61" s="7">
-        <v>84.75</v>
+        <v>81.87</v>
       </c>
       <c r="E61" s="9">
-        <v>3.86</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3136,13 +3135,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="7">
-        <v>47.71</v>
+        <v>47.46</v>
       </c>
       <c r="D62" s="7">
-        <v>47.46</v>
+        <v>50.97</v>
       </c>
       <c r="E62" s="8">
-        <v>-0.25</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3153,13 +3152,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="7">
-        <v>70.73</v>
+        <v>65.91</v>
       </c>
       <c r="D63" s="7">
-        <v>65.91</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-4.82</v>
+        <v>60.38</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-5.53</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3170,13 +3169,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>60.53</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="D64" s="7">
-        <v>65.43000000000001</v>
-      </c>
-      <c r="E64" s="9">
-        <v>4.9</v>
+        <v>66.5</v>
+      </c>
+      <c r="E64" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3187,13 +3186,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>36.41</v>
+        <v>37.14</v>
       </c>
       <c r="D65" s="7">
-        <v>37.14</v>
+        <v>36.71</v>
       </c>
       <c r="E65" s="9">
-        <v>0.73</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3204,13 +3203,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>42.48</v>
+        <v>42.33</v>
       </c>
       <c r="D66" s="7">
-        <v>42.33</v>
+        <v>45.41</v>
       </c>
       <c r="E66" s="8">
-        <v>-0.15</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3221,13 +3220,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>42.88</v>
+        <v>40.61</v>
       </c>
       <c r="D67" s="7">
-        <v>40.61</v>
+        <v>47.3</v>
       </c>
       <c r="E67" s="8">
-        <v>-2.27</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3238,13 +3237,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>54.07</v>
+        <v>57.23</v>
       </c>
       <c r="D68" s="7">
-        <v>57.23</v>
-      </c>
-      <c r="E68" s="9">
-        <v>3.16</v>
+        <v>59.71</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.48</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3255,13 +3254,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>55.71</v>
+        <v>63.75</v>
       </c>
       <c r="D69" s="7">
-        <v>63.75</v>
+        <v>61.34</v>
       </c>
       <c r="E69" s="9">
-        <v>8.039999999999999</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3272,13 +3271,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>56.24</v>
+        <v>60.73</v>
       </c>
       <c r="D70" s="7">
-        <v>60.73</v>
+        <v>56.11</v>
       </c>
       <c r="E70" s="9">
-        <v>4.49</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3289,13 +3288,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="7">
-        <v>-71.79000000000001</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="D71" s="7">
-        <v>-75.31999999999999</v>
+        <v>-47.21</v>
       </c>
       <c r="E71" s="8">
-        <v>-3.53</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3306,13 +3305,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="7">
-        <v>1534.08</v>
+        <v>1.32</v>
       </c>
       <c r="D72" s="7">
-        <v>1.32</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1532.76</v>
+        <v>-49.69</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-51.01</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3323,13 +3322,13 @@
         <v>31</v>
       </c>
       <c r="C73" s="7">
-        <v>8.01</v>
+        <v>-1.06</v>
       </c>
       <c r="D73" s="7">
-        <v>-1.06</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-9.07</v>
+        <v>-28.94</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-27.88</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3340,13 +3339,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>-11.28</v>
+        <v>-28.03</v>
       </c>
       <c r="D74" s="7">
-        <v>-28.03</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-16.75</v>
+        <v>-58.48</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-30.45</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3357,13 +3356,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-37.81</v>
+        <v>-52.13</v>
       </c>
       <c r="D75" s="7">
-        <v>-52.13</v>
+        <v>-13.55</v>
       </c>
       <c r="E75" s="8">
-        <v>-14.32</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3374,13 +3373,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-22.43</v>
+        <v>-34.2</v>
       </c>
       <c r="D76" s="7">
-        <v>-34.2</v>
+        <v>-13.87</v>
       </c>
       <c r="E76" s="8">
-        <v>-11.77</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3391,13 +3390,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-52.13</v>
+        <v>-34.33</v>
       </c>
       <c r="D77" s="7">
-        <v>-34.33</v>
-      </c>
-      <c r="E77" s="9">
-        <v>17.8</v>
+        <v>-19.82</v>
+      </c>
+      <c r="E77" s="8">
+        <v>14.51</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3408,13 +3407,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>29.38</v>
+        <v>139.32</v>
       </c>
       <c r="D78" s="7">
-        <v>139.32</v>
+        <v>-26.13</v>
       </c>
       <c r="E78" s="9">
-        <v>109.94</v>
+        <v>-165.45</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3425,13 +3424,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-92.93000000000001</v>
+        <v>-80.33</v>
       </c>
       <c r="D79" s="7">
-        <v>-80.33</v>
+        <v>-92.67</v>
       </c>
       <c r="E79" s="9">
-        <v>12.6</v>
+        <v>-12.34</v>
       </c>
     </row>
   </sheetData>
@@ -3496,16 +3495,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
       <c r="E2" s="12">
         <v>80</v>
       </c>
       <c r="F2" s="12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="12">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3642,28 +3641,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3749</v>
+        <v>0.3804999999999999</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3649</v>
+        <v>0.3667</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3077</v>
+        <v>0.3123</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2561</v>
+        <v>0.2554</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2095</v>
+        <v>0.1995</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1879</v>
+        <v>0.1801</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1495</v>
+        <v>0.151</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0202</v>
+        <v>-0.0254</v>
       </c>
       <c r="I2" s="15">
         <v>-0.0687</v>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="97">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,85 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-3.4% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-3.4%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-2.1% → -1.8%</t>
+  </si>
+  <si>
+    <t>-2.1%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.5 → 51.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>47.3 → 54.7</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>54.7</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>60.4 → 70.4</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>60.4</t>
+  </si>
+  <si>
+    <t>70.4</t>
+  </si>
+  <si>
+    <t>66.5 → 70.6</t>
+  </si>
+  <si>
+    <t>66.5</t>
+  </si>
+  <si>
+    <t>70.6</t>
+  </si>
+  <si>
+    <t>51.0 → 49.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.0</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.5% → -3.4%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.5%</t>
-  </si>
-  <si>
-    <t>-3.4%</t>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -313,7 +364,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -359,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -444,6 +495,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -818,14 +870,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -958,10 +1011,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>646.6</v>
+        <v>641.4</v>
       </c>
       <c r="D2">
-        <v>1.53</v>
+        <v>-0.8</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -970,46 +1023,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.83</v>
+        <v>-36.34</v>
       </c>
       <c r="H2">
-        <v>76.09</v>
+        <v>74.67</v>
       </c>
       <c r="I2">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="J2">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="K2">
-        <v>-8.24</v>
+        <v>-8.98</v>
       </c>
       <c r="L2">
-        <v>24.72</v>
+        <v>23.71</v>
       </c>
       <c r="M2">
-        <v>-6.87</v>
+        <v>-6.9</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2">
-        <v>639.28</v>
+        <v>639.89</v>
       </c>
       <c r="Q2">
-        <v>637.5</v>
+        <v>637.72</v>
       </c>
       <c r="R2">
-        <v>649.16</v>
+        <v>647.6</v>
       </c>
       <c r="S2">
-        <v>619.1799999999999</v>
+        <v>619.6</v>
       </c>
       <c r="T2">
-        <v>4.43</v>
+        <v>3.52</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1024,34 +1077,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>50.97</v>
+        <v>49.09</v>
       </c>
       <c r="Z2">
-        <v>-2.13</v>
+        <v>-1.98</v>
       </c>
       <c r="AA2">
-        <v>-3.51</v>
+        <v>-3.2</v>
       </c>
       <c r="AB2">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AC2">
-        <v>49.12</v>
+        <v>51.7</v>
       </c>
       <c r="AD2">
-        <v>45.06</v>
+        <v>47.82</v>
       </c>
       <c r="AE2">
-        <v>22.82</v>
+        <v>22.06</v>
       </c>
       <c r="AF2">
-        <v>-47.21</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="AG2">
-        <v>662.61</v>
+        <v>662.89</v>
       </c>
       <c r="AH2">
-        <v>612.4</v>
+        <v>612.5599999999999</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1060,7 +1113,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1071,58 +1124,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>281.75</v>
+        <v>302.45</v>
       </c>
       <c r="D3">
-        <v>-1.91</v>
+        <v>7.35</v>
       </c>
       <c r="E3">
-        <v>291.65</v>
+        <v>302.45</v>
       </c>
       <c r="F3">
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-3.39</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>83.87</v>
+        <v>97.38</v>
       </c>
       <c r="I3">
-        <v>4.88</v>
+        <v>12.56</v>
       </c>
       <c r="J3">
-        <v>12.32</v>
+        <v>17.62</v>
       </c>
       <c r="K3">
-        <v>14.5</v>
+        <v>22.91</v>
       </c>
       <c r="L3">
-        <v>38.26</v>
+        <v>48.79</v>
       </c>
       <c r="M3">
-        <v>38.05</v>
+        <v>40.36</v>
       </c>
       <c r="N3">
+        <v>99</v>
+      </c>
+      <c r="O3">
         <v>88</v>
       </c>
-      <c r="O3">
-        <v>84</v>
-      </c>
       <c r="P3">
-        <v>279.82</v>
+        <v>286.57</v>
       </c>
       <c r="Q3">
-        <v>269.16</v>
+        <v>271.41</v>
       </c>
       <c r="R3">
-        <v>264.4</v>
+        <v>265.49</v>
       </c>
       <c r="S3">
-        <v>210.13</v>
+        <v>210.83</v>
       </c>
       <c r="T3">
-        <v>34.08</v>
+        <v>43.46</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1137,34 +1190,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>60.38</v>
+        <v>70.44</v>
       </c>
       <c r="Z3">
-        <v>5.6</v>
+        <v>7.37</v>
       </c>
       <c r="AA3">
-        <v>3.97</v>
+        <v>4.65</v>
       </c>
       <c r="AB3">
-        <v>1.63</v>
+        <v>2.72</v>
       </c>
       <c r="AC3">
-        <v>74.22</v>
+        <v>73.73</v>
       </c>
       <c r="AD3">
-        <v>66.19</v>
+        <v>72.34</v>
       </c>
       <c r="AE3">
-        <v>9.460000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="AF3">
-        <v>-49.69</v>
+        <v>578.3</v>
       </c>
       <c r="AG3">
-        <v>288.62</v>
+        <v>295.12</v>
       </c>
       <c r="AH3">
-        <v>249.71</v>
+        <v>247.7</v>
       </c>
       <c r="AI3">
         <v>262.26</v>
@@ -1173,7 +1226,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>36.56</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1184,10 +1237,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1154.1</v>
+        <v>1175.4</v>
       </c>
       <c r="D4">
-        <v>0.44</v>
+        <v>1.85</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1196,46 +1249,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-10.45</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H4">
-        <v>22.02</v>
+        <v>24.28</v>
       </c>
       <c r="I4">
-        <v>4.78</v>
+        <v>5.42</v>
       </c>
       <c r="J4">
-        <v>8.300000000000001</v>
+        <v>11.48</v>
       </c>
       <c r="K4">
-        <v>-5.45</v>
+        <v>-3.7</v>
       </c>
       <c r="L4">
-        <v>13.79</v>
+        <v>16.59</v>
       </c>
       <c r="M4">
-        <v>25.54</v>
+        <v>26.28</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1132.96</v>
+        <v>1145.04</v>
       </c>
       <c r="Q4">
-        <v>1110.62</v>
+        <v>1114.96</v>
       </c>
       <c r="R4">
-        <v>1081.17</v>
+        <v>1081.89</v>
       </c>
       <c r="S4">
-        <v>1124.78</v>
+        <v>1125.31</v>
       </c>
       <c r="T4">
-        <v>2.61</v>
+        <v>4.45</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1250,43 +1303,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>66.5</v>
+        <v>70.62</v>
       </c>
       <c r="Z4">
-        <v>15.11</v>
+        <v>18.45</v>
       </c>
       <c r="AA4">
-        <v>9.94</v>
+        <v>11.64</v>
       </c>
       <c r="AB4">
-        <v>5.16</v>
+        <v>6.81</v>
       </c>
       <c r="AC4">
-        <v>90.34</v>
+        <v>100</v>
       </c>
       <c r="AD4">
-        <v>74.31</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="AE4">
-        <v>23.56</v>
+        <v>24.75</v>
       </c>
       <c r="AF4">
-        <v>-28.94</v>
+        <v>5.28</v>
       </c>
       <c r="AG4">
-        <v>1147.13</v>
+        <v>1160.08</v>
       </c>
       <c r="AH4">
-        <v>1074.12</v>
+        <v>1069.84</v>
       </c>
       <c r="AI4">
-        <v>1077.86</v>
+        <v>1088.95</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>37.37</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1297,10 +1350,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>701.4</v>
+        <v>712.95</v>
       </c>
       <c r="D5">
-        <v>-0.14</v>
+        <v>1.65</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1309,46 +1362,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.87</v>
+        <v>-17.54</v>
       </c>
       <c r="H5">
-        <v>5.97</v>
+        <v>7.71</v>
       </c>
       <c r="I5">
-        <v>-4.23</v>
+        <v>-1.53</v>
       </c>
       <c r="J5">
-        <v>-3.12</v>
+        <v>-1.57</v>
       </c>
       <c r="K5">
-        <v>-2.88</v>
+        <v>-1.28</v>
       </c>
       <c r="L5">
-        <v>-7.97</v>
+        <v>-7.57</v>
       </c>
       <c r="M5">
-        <v>36.67</v>
+        <v>38.07</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>709.51</v>
+        <v>707.3</v>
       </c>
       <c r="Q5">
-        <v>728.34</v>
+        <v>727.5700000000001</v>
       </c>
       <c r="R5">
-        <v>717.9299999999999</v>
+        <v>717.99</v>
       </c>
       <c r="S5">
-        <v>749.5700000000001</v>
+        <v>749.48</v>
       </c>
       <c r="T5">
-        <v>-6.43</v>
+        <v>-4.87</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1363,34 +1416,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>36.71</v>
+        <v>44.69</v>
       </c>
       <c r="Z5">
-        <v>-3.68</v>
+        <v>-3.89</v>
       </c>
       <c r="AA5">
-        <v>1.18</v>
+        <v>0.17</v>
       </c>
       <c r="AB5">
-        <v>-4.86</v>
+        <v>-4.06</v>
       </c>
       <c r="AC5">
-        <v>1.49</v>
+        <v>15.61</v>
       </c>
       <c r="AD5">
-        <v>0.83</v>
+        <v>6.03</v>
       </c>
       <c r="AE5">
-        <v>15.67</v>
+        <v>15.79</v>
       </c>
       <c r="AF5">
-        <v>-58.48</v>
+        <v>-14.45</v>
       </c>
       <c r="AG5">
-        <v>754</v>
+        <v>754.13</v>
       </c>
       <c r="AH5">
-        <v>702.6900000000001</v>
+        <v>701</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1399,7 +1452,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.18</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1410,10 +1463,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>548.4</v>
+        <v>543.5</v>
       </c>
       <c r="D6">
-        <v>0.68</v>
+        <v>-0.89</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1422,25 +1475,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-8.6</v>
+        <v>-9.42</v>
       </c>
       <c r="H6">
-        <v>25.05</v>
+        <v>23.93</v>
       </c>
       <c r="I6">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="J6">
-        <v>-0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="K6">
-        <v>-8.6</v>
+        <v>-9.42</v>
       </c>
       <c r="L6">
-        <v>3.48</v>
+        <v>4.61</v>
       </c>
       <c r="M6">
-        <v>19.95</v>
+        <v>18.57</v>
       </c>
       <c r="N6">
         <v>34</v>
@@ -1449,19 +1502,19 @@
         <v>50</v>
       </c>
       <c r="P6">
-        <v>544.8</v>
+        <v>544.71</v>
       </c>
       <c r="Q6">
-        <v>555.95</v>
+        <v>555.84</v>
       </c>
       <c r="R6">
-        <v>558.23</v>
+        <v>557.85</v>
       </c>
       <c r="S6">
-        <v>519.76</v>
+        <v>519.89</v>
       </c>
       <c r="T6">
-        <v>5.51</v>
+        <v>4.54</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1476,34 +1529,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.41</v>
+        <v>42.19</v>
       </c>
       <c r="Z6">
-        <v>-3.27</v>
+        <v>-3.62</v>
       </c>
       <c r="AA6">
-        <v>-1.63</v>
+        <v>-2.02</v>
       </c>
       <c r="AB6">
-        <v>-1.64</v>
+        <v>-1.59</v>
       </c>
       <c r="AC6">
-        <v>15.55</v>
+        <v>15.09</v>
       </c>
       <c r="AD6">
-        <v>8.81</v>
+        <v>12.6</v>
       </c>
       <c r="AE6">
-        <v>11.14</v>
+        <v>11.08</v>
       </c>
       <c r="AF6">
-        <v>-13.55</v>
+        <v>122.11</v>
       </c>
       <c r="AG6">
-        <v>576.71</v>
+        <v>576.85</v>
       </c>
       <c r="AH6">
-        <v>535.1799999999999</v>
+        <v>534.8200000000001</v>
       </c>
       <c r="AI6">
         <v>577.21</v>
@@ -1512,7 +1565,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.13</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1576,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11446</v>
+        <v>11832</v>
       </c>
       <c r="D7">
-        <v>2.55</v>
+        <v>3.37</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1535,49 +1588,49 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.36</v>
+        <v>-46.62</v>
       </c>
       <c r="H7">
-        <v>7.42</v>
+        <v>11.05</v>
       </c>
       <c r="I7">
-        <v>-0.37</v>
+        <v>4.44</v>
       </c>
       <c r="J7">
-        <v>4.06</v>
+        <v>7.75</v>
       </c>
       <c r="K7">
-        <v>-9.17</v>
+        <v>-6.11</v>
       </c>
       <c r="L7">
-        <v>-36.97</v>
+        <v>-35.22</v>
       </c>
       <c r="M7">
-        <v>18.01</v>
+        <v>19.25</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>11338</v>
+        <v>11438.6</v>
       </c>
       <c r="Q7">
-        <v>11660.15</v>
+        <v>11693.6</v>
       </c>
       <c r="R7">
-        <v>11687.34</v>
+        <v>11667.58</v>
       </c>
       <c r="S7">
-        <v>14996.93</v>
+        <v>14970.88</v>
       </c>
       <c r="T7">
-        <v>-23.68</v>
+        <v>-20.97</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
         <v>47</v>
@@ -1586,37 +1639,37 @@
         <v>47</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.3</v>
+        <v>54.74</v>
       </c>
       <c r="Z7">
-        <v>-65.2</v>
+        <v>-34.08</v>
       </c>
       <c r="AA7">
-        <v>-19.75</v>
+        <v>-22.61</v>
       </c>
       <c r="AB7">
-        <v>-45.45</v>
+        <v>-11.47</v>
       </c>
       <c r="AC7">
-        <v>11.45</v>
+        <v>37.53</v>
       </c>
       <c r="AD7">
-        <v>6.8</v>
+        <v>17.82</v>
       </c>
       <c r="AE7">
-        <v>383.97</v>
+        <v>407.83</v>
       </c>
       <c r="AF7">
-        <v>-13.87</v>
+        <v>67.61</v>
       </c>
       <c r="AG7">
-        <v>12399.62</v>
+        <v>12398.08</v>
       </c>
       <c r="AH7">
-        <v>10920.68</v>
+        <v>10989.12</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1625,7 +1678,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>24.83</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1636,10 +1689,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>343.95</v>
+        <v>344.95</v>
       </c>
       <c r="D8">
-        <v>1.1</v>
+        <v>0.29</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1648,46 +1701,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.06</v>
+        <v>-1.78</v>
       </c>
       <c r="H8">
-        <v>46.79</v>
+        <v>47.22</v>
       </c>
       <c r="I8">
-        <v>4.66</v>
+        <v>4.56</v>
       </c>
       <c r="J8">
-        <v>6.88</v>
+        <v>8.41</v>
       </c>
       <c r="K8">
-        <v>23.04</v>
+        <v>23.39</v>
       </c>
       <c r="L8">
-        <v>11.56</v>
+        <v>11.72</v>
       </c>
       <c r="M8">
-        <v>31.23</v>
+        <v>31.33</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P8">
-        <v>335.92</v>
+        <v>338.93</v>
       </c>
       <c r="Q8">
-        <v>332.92</v>
+        <v>334.35</v>
       </c>
       <c r="R8">
-        <v>328.55</v>
+        <v>329.57</v>
       </c>
       <c r="S8">
-        <v>283.42</v>
+        <v>283.75</v>
       </c>
       <c r="T8">
-        <v>21.36</v>
+        <v>21.57</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1702,34 +1755,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>59.71</v>
+        <v>60.37</v>
       </c>
       <c r="Z8">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="AA8">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="AB8">
-        <v>-0.03</v>
+        <v>0.33</v>
       </c>
       <c r="AC8">
-        <v>59.55</v>
+        <v>74.61</v>
       </c>
       <c r="AD8">
-        <v>40.33</v>
+        <v>56.5</v>
       </c>
       <c r="AE8">
-        <v>9.43</v>
+        <v>9.07</v>
       </c>
       <c r="AF8">
-        <v>-19.82</v>
+        <v>-37.67</v>
       </c>
       <c r="AG8">
-        <v>351.47</v>
+        <v>351.94</v>
       </c>
       <c r="AH8">
-        <v>314.38</v>
+        <v>316.75</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1738,7 +1791,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>24.83</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1749,58 +1802,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1320.3</v>
+        <v>1341</v>
       </c>
       <c r="D9">
-        <v>-0.5</v>
+        <v>1.57</v>
       </c>
       <c r="E9">
-        <v>1330</v>
+        <v>1341</v>
       </c>
       <c r="F9">
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>28.61</v>
+        <v>30.63</v>
       </c>
       <c r="I9">
-        <v>4.16</v>
+        <v>4.29</v>
       </c>
       <c r="J9">
-        <v>6.08</v>
+        <v>7.55</v>
       </c>
       <c r="K9">
-        <v>0.84</v>
+        <v>2.42</v>
       </c>
       <c r="L9">
-        <v>21.96</v>
+        <v>25.12</v>
       </c>
       <c r="M9">
-        <v>15.1</v>
+        <v>15.86</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P9">
-        <v>1305.3</v>
+        <v>1316.34</v>
       </c>
       <c r="Q9">
-        <v>1290.93</v>
+        <v>1294.15</v>
       </c>
       <c r="R9">
-        <v>1263.97</v>
+        <v>1265.3</v>
       </c>
       <c r="S9">
-        <v>1219.67</v>
+        <v>1220.52</v>
       </c>
       <c r="T9">
-        <v>8.25</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1815,43 +1868,43 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>61.34</v>
+        <v>65.67</v>
       </c>
       <c r="Z9">
-        <v>11.74</v>
+        <v>14.51</v>
       </c>
       <c r="AA9">
-        <v>8.84</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AB9">
-        <v>2.9</v>
+        <v>4.54</v>
       </c>
       <c r="AC9">
-        <v>62.66</v>
+        <v>84.83</v>
       </c>
       <c r="AD9">
-        <v>48.63</v>
+        <v>65.5</v>
       </c>
       <c r="AE9">
-        <v>25.14</v>
+        <v>25.53</v>
       </c>
       <c r="AF9">
-        <v>-26.13</v>
+        <v>14.78</v>
       </c>
       <c r="AG9">
-        <v>1330.29</v>
+        <v>1338.76</v>
       </c>
       <c r="AH9">
-        <v>1251.56</v>
+        <v>1249.53</v>
       </c>
       <c r="AI9">
-        <v>1242.79</v>
+        <v>1249.12</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>36.49</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1915,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.87</v>
+        <v>81.55</v>
       </c>
       <c r="D10">
-        <v>-3.4</v>
+        <v>-0.39</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1874,46 +1927,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.48</v>
+        <v>-10.83</v>
       </c>
       <c r="H10">
-        <v>126.91</v>
+        <v>126.03</v>
       </c>
       <c r="I10">
-        <v>-5.77</v>
+        <v>-1.2</v>
       </c>
       <c r="J10">
-        <v>17.68</v>
+        <v>20.46</v>
       </c>
       <c r="K10">
-        <v>55.76</v>
+        <v>55.16</v>
       </c>
       <c r="L10">
-        <v>11.74</v>
+        <v>11.18</v>
       </c>
       <c r="M10">
-        <v>-2.54</v>
+        <v>-2.76</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>82.56999999999999</v>
+        <v>82.37</v>
       </c>
       <c r="Q10">
-        <v>82.27</v>
+        <v>82.88</v>
       </c>
       <c r="R10">
-        <v>66.06</v>
+        <v>66.63</v>
       </c>
       <c r="S10">
-        <v>59.55</v>
+        <v>59.58</v>
       </c>
       <c r="T10">
-        <v>37.49</v>
+        <v>36.88</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1928,34 +1981,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>56.11</v>
+        <v>55.6</v>
       </c>
       <c r="Z10">
-        <v>5.19</v>
+        <v>4.68</v>
       </c>
       <c r="AA10">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="AB10">
-        <v>-1.37</v>
+        <v>-1.51</v>
       </c>
       <c r="AC10">
         <v>6.67</v>
       </c>
       <c r="AD10">
-        <v>4.78</v>
+        <v>6.83</v>
       </c>
       <c r="AE10">
-        <v>4.71</v>
+        <v>4.54</v>
       </c>
       <c r="AF10">
-        <v>-92.67</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="AG10">
-        <v>96.2</v>
+        <v>95.44</v>
       </c>
       <c r="AH10">
-        <v>68.34</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1964,7 +2017,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>36.41</v>
+        <v>33.08</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2145,7 +2198,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2164,1279 +2217,1447 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
+      <c r="B7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.84</v>
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.76</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>12.49</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C14" s="8">
         <v>12.32</v>
       </c>
-      <c r="E9" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D14" s="8">
+        <v>17.62</v>
+      </c>
+      <c r="E14" s="9">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>10.93</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C15" s="8">
         <v>8.300000000000001</v>
       </c>
-      <c r="E10" s="9">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="D15" s="8">
+        <v>11.48</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
-        <v>-1.66</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C16" s="8">
         <v>-3.12</v>
       </c>
-      <c r="E11" s="9">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="D16" s="8">
+        <v>-1.57</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C17" s="8">
         <v>-0.24</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="D17" s="8">
+        <v>-0.14</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
-        <v>2.72</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C18" s="8">
         <v>4.06</v>
       </c>
-      <c r="E13" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="D18" s="8">
+        <v>7.75</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C19" s="8">
+        <v>6.88</v>
+      </c>
+      <c r="D19" s="8">
+        <v>8.41</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="8">
+        <v>6.08</v>
+      </c>
+      <c r="D20" s="8">
+        <v>7.55</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="8">
+        <v>17.68</v>
+      </c>
+      <c r="D21" s="8">
+        <v>20.46</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-0.01</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>4.88</v>
+      </c>
+      <c r="D23" s="8">
+        <v>12.56</v>
+      </c>
+      <c r="E23" s="9">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>4.78</v>
+      </c>
+      <c r="D24" s="8">
         <v>5.42</v>
       </c>
-      <c r="D14" s="7">
-        <v>6.88</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="E24" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-4.23</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-1.53</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-0.08</v>
+      </c>
+      <c r="E26" s="10">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-0.37</v>
+      </c>
+      <c r="D27" s="8">
+        <v>4.44</v>
+      </c>
+      <c r="E27" s="9">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>4.66</v>
+      </c>
+      <c r="D28" s="8">
+        <v>4.56</v>
+      </c>
+      <c r="E28" s="10">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>6.95</v>
-      </c>
-      <c r="D15" s="7">
-        <v>6.08</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="D29" s="8">
+        <v>4.29</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>23</v>
-      </c>
-      <c r="D16" s="7">
-        <v>17.68</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-5.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-5.77</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-1.2</v>
+      </c>
+      <c r="E30" s="9">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.33</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.01</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>24.72</v>
+      </c>
+      <c r="D31" s="8">
+        <v>23.71</v>
+      </c>
+      <c r="E31" s="10">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>7.54</v>
-      </c>
-      <c r="D18" s="7">
-        <v>4.88</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>38.26</v>
+      </c>
+      <c r="D32" s="8">
+        <v>48.79</v>
+      </c>
+      <c r="E32" s="9">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>5.27</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4.78</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>13.79</v>
+      </c>
+      <c r="D33" s="8">
+        <v>16.59</v>
+      </c>
+      <c r="E33" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.8</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>-7.97</v>
+      </c>
+      <c r="D34" s="8">
+        <v>-7.57</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.94</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>3.48</v>
+      </c>
+      <c r="D35" s="8">
+        <v>4.61</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-6</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="E22" s="8">
-        <v>5.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-36.97</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-35.22</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="D23" s="7">
-        <v>4.66</v>
-      </c>
-      <c r="E23" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="8">
+        <v>11.56</v>
+      </c>
+      <c r="D37" s="8">
+        <v>11.72</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>3.85</v>
-      </c>
-      <c r="D24" s="7">
-        <v>4.16</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B38" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="8">
+        <v>21.96</v>
+      </c>
+      <c r="D38" s="8">
+        <v>25.12</v>
+      </c>
+      <c r="E38" s="9">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-7.33</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-5.77</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="8">
+        <v>11.74</v>
+      </c>
+      <c r="D39" s="8">
+        <v>11.18</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-8.24</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-8.98</v>
+      </c>
+      <c r="E40" s="10">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="D41" s="8">
+        <v>22.91</v>
+      </c>
+      <c r="E41" s="9">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-5.45</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-3.7</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-2.88</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-1.28</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-8.6</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-9.42</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-9.17</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-6.11</v>
+      </c>
+      <c r="E45" s="9">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8">
+        <v>23.04</v>
+      </c>
+      <c r="D46" s="8">
+        <v>23.39</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="D47" s="8">
+        <v>2.42</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="8">
+        <v>55.76</v>
+      </c>
+      <c r="D48" s="8">
+        <v>55.16</v>
+      </c>
+      <c r="E48" s="10">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-35.83</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-36.34</v>
+      </c>
+      <c r="E49" s="10">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-3.39</v>
+      </c>
+      <c r="D50" s="8">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-10.45</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-18.87</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-17.54</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>-8.6</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-9.42</v>
+      </c>
+      <c r="E53" s="10">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-48.36</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-46.62</v>
+      </c>
+      <c r="E54" s="9">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-2.06</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-1.78</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="8">
+        <v>-0.73</v>
+      </c>
+      <c r="D56" s="8">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="8">
+        <v>-10.48</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-10.83</v>
+      </c>
+      <c r="E57" s="10">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>646.6</v>
+      </c>
+      <c r="D58" s="8">
+        <v>641.4</v>
+      </c>
+      <c r="E58" s="10">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="8">
+        <v>281.75</v>
+      </c>
+      <c r="D59" s="8">
+        <v>302.45</v>
+      </c>
+      <c r="E59" s="9">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="8">
+        <v>1154.1</v>
+      </c>
+      <c r="D60" s="8">
+        <v>1175.4</v>
+      </c>
+      <c r="E60" s="9">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>701.4</v>
+      </c>
+      <c r="D61" s="8">
+        <v>712.95</v>
+      </c>
+      <c r="E61" s="9">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>548.4</v>
+      </c>
+      <c r="D62" s="8">
+        <v>543.5</v>
+      </c>
+      <c r="E62" s="10">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>11446</v>
+      </c>
+      <c r="D63" s="8">
+        <v>11832</v>
+      </c>
+      <c r="E63" s="9">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8">
+        <v>343.95</v>
+      </c>
+      <c r="D64" s="8">
+        <v>344.95</v>
+      </c>
+      <c r="E64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1320.3</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1341</v>
+      </c>
+      <c r="E65" s="9">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="8">
+        <v>81.87</v>
+      </c>
+      <c r="D66" s="8">
+        <v>81.55</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="8">
+        <v>55</v>
+      </c>
+      <c r="D67" s="8">
+        <v>45</v>
+      </c>
+      <c r="E67" s="10">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="8">
+        <v>88</v>
+      </c>
+      <c r="D68" s="8">
+        <v>99</v>
+      </c>
+      <c r="E68" s="9">
         <v>11</v>
       </c>
-      <c r="C26" s="7">
-        <v>22.31</v>
-      </c>
-      <c r="D26" s="7">
-        <v>24.72</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="8">
+        <v>45</v>
+      </c>
+      <c r="D69" s="8">
+        <v>55</v>
+      </c>
+      <c r="E69" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="8">
+        <v>99</v>
+      </c>
+      <c r="D70" s="8">
+        <v>88</v>
+      </c>
+      <c r="E70" s="10">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="8">
+        <v>50.97</v>
+      </c>
+      <c r="D71" s="8">
+        <v>49.09</v>
+      </c>
+      <c r="E71" s="10">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>40.84</v>
-      </c>
-      <c r="D27" s="7">
-        <v>38.26</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="8">
+        <v>60.38</v>
+      </c>
+      <c r="D72" s="8">
+        <v>70.44</v>
+      </c>
+      <c r="E72" s="9">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>14.53</v>
-      </c>
-      <c r="D28" s="7">
-        <v>13.79</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>66.5</v>
+      </c>
+      <c r="D73" s="8">
+        <v>70.62</v>
+      </c>
+      <c r="E73" s="9">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-6.97</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-7.97</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>36.71</v>
+      </c>
+      <c r="D74" s="8">
+        <v>44.69</v>
+      </c>
+      <c r="E74" s="9">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>2.49</v>
-      </c>
-      <c r="D30" s="7">
-        <v>3.48</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>45.41</v>
+      </c>
+      <c r="D75" s="8">
+        <v>42.19</v>
+      </c>
+      <c r="E75" s="10">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-38.91</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-36.97</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="8">
+        <v>47.3</v>
+      </c>
+      <c r="D76" s="8">
+        <v>54.74</v>
+      </c>
+      <c r="E76" s="9">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>8.81</v>
-      </c>
-      <c r="D32" s="7">
-        <v>11.56</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B77" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="8">
+        <v>59.71</v>
+      </c>
+      <c r="D77" s="8">
+        <v>60.37</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>23.63</v>
-      </c>
-      <c r="D33" s="7">
-        <v>21.96</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="8">
+        <v>61.34</v>
+      </c>
+      <c r="D78" s="8">
+        <v>65.67</v>
+      </c>
+      <c r="E78" s="9">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>18.15</v>
-      </c>
-      <c r="D34" s="7">
-        <v>11.74</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-6.41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="8">
+        <v>56.11</v>
+      </c>
+      <c r="D79" s="8">
+        <v>55.6</v>
+      </c>
+      <c r="E79" s="10">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-7.52</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-8.24</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B80" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="8">
+        <v>-47.21</v>
+      </c>
+      <c r="D80" s="8">
+        <v>-77.06999999999999</v>
+      </c>
+      <c r="E80" s="10">
+        <v>-29.86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>25.51</v>
-      </c>
-      <c r="D36" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-11.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="8">
+        <v>-49.69</v>
+      </c>
+      <c r="D81" s="8">
+        <v>578.3</v>
+      </c>
+      <c r="E81" s="9">
+        <v>627.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-6.04</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-5.45</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>-28.94</v>
+      </c>
+      <c r="D82" s="8">
+        <v>5.28</v>
+      </c>
+      <c r="E82" s="9">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-2.88</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-58.48</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-14.45</v>
+      </c>
+      <c r="E83" s="9">
+        <v>44.03</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-8.6</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-3.49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B84" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="8">
+        <v>-13.55</v>
+      </c>
+      <c r="D84" s="8">
+        <v>122.11</v>
+      </c>
+      <c r="E84" s="9">
+        <v>135.66</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-10.58</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-9.17</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B85" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="8">
+        <v>-13.87</v>
+      </c>
+      <c r="D85" s="8">
+        <v>67.61</v>
+      </c>
+      <c r="E85" s="9">
+        <v>81.48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>21.96</v>
-      </c>
-      <c r="D41" s="7">
-        <v>23.04</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B86" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="8">
+        <v>-19.82</v>
+      </c>
+      <c r="D86" s="8">
+        <v>-37.67</v>
+      </c>
+      <c r="E86" s="10">
+        <v>-17.85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>2.58</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B87" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="8">
+        <v>-26.13</v>
+      </c>
+      <c r="D87" s="8">
+        <v>14.78</v>
+      </c>
+      <c r="E87" s="9">
+        <v>40.91</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>63.48</v>
-      </c>
-      <c r="D43" s="7">
-        <v>55.76</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-7.72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-36.8</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-35.83</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-3.39</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-10.85</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-10.45</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-18.76</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-18.87</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-8.6</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-49.65</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-48.36</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-3.13</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-2.06</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-0.23</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-0.73</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-7.33</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-10.48</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>636.85</v>
-      </c>
-      <c r="D53" s="7">
-        <v>646.6</v>
-      </c>
-      <c r="E53" s="8">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>287.25</v>
-      </c>
-      <c r="D54" s="7">
-        <v>281.75</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1149</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1154.1</v>
-      </c>
-      <c r="E55" s="8">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>702.4</v>
-      </c>
-      <c r="D56" s="7">
-        <v>701.4</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>544.7</v>
-      </c>
-      <c r="D57" s="7">
-        <v>548.4</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>11161</v>
-      </c>
-      <c r="D58" s="7">
-        <v>11446</v>
-      </c>
-      <c r="E58" s="8">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>340.2</v>
-      </c>
-      <c r="D59" s="7">
-        <v>343.95</v>
-      </c>
-      <c r="E59" s="8">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1327</v>
-      </c>
-      <c r="D60" s="7">
-        <v>1320.3</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>84.75</v>
-      </c>
-      <c r="D61" s="7">
-        <v>81.87</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>47.46</v>
-      </c>
-      <c r="D62" s="7">
-        <v>50.97</v>
-      </c>
-      <c r="E62" s="8">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>65.91</v>
-      </c>
-      <c r="D63" s="7">
-        <v>60.38</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-5.53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>65.43000000000001</v>
-      </c>
-      <c r="D64" s="7">
-        <v>66.5</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>37.14</v>
-      </c>
-      <c r="D65" s="7">
-        <v>36.71</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>42.33</v>
-      </c>
-      <c r="D66" s="7">
-        <v>45.41</v>
-      </c>
-      <c r="E66" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>40.61</v>
-      </c>
-      <c r="D67" s="7">
-        <v>47.3</v>
-      </c>
-      <c r="E67" s="8">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>57.23</v>
-      </c>
-      <c r="D68" s="7">
-        <v>59.71</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>63.75</v>
-      </c>
-      <c r="D69" s="7">
-        <v>61.34</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>60.73</v>
-      </c>
-      <c r="D70" s="7">
-        <v>56.11</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-4.62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="B88" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="7">
-        <v>-75.31999999999999</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-47.21</v>
-      </c>
-      <c r="E71" s="8">
-        <v>28.11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>1.32</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-49.69</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-51.01</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-1.06</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-28.94</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-27.88</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-28.03</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-58.48</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-30.45</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-52.13</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-13.55</v>
-      </c>
-      <c r="E75" s="8">
-        <v>38.58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-34.2</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-13.87</v>
-      </c>
-      <c r="E76" s="8">
-        <v>20.33</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-34.33</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-19.82</v>
-      </c>
-      <c r="E77" s="8">
-        <v>14.51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>139.32</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-26.13</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-165.45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-80.33</v>
-      </c>
-      <c r="D79" s="7">
+      <c r="C88" s="8">
         <v>-92.67</v>
       </c>
-      <c r="E79" s="9">
-        <v>-12.34</v>
+      <c r="D88" s="8">
+        <v>-91.09999999999999</v>
+      </c>
+      <c r="E88" s="9">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3456,60 +3677,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
+      <c r="B1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>64.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>53.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="13">
+        <v>57</v>
+      </c>
+      <c r="E2" s="13">
         <v>80</v>
       </c>
-      <c r="F2" s="12">
-        <v>6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>6.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="13">
+        <v>8.1</v>
+      </c>
+      <c r="G2" s="13">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -3611,61 +3832,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3804999999999999</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3667</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3123</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2554</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1995</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1801</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.151</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0254</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0687</v>
+      <c r="A2" s="16">
+        <v>0.4036</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3807</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.3133</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2628</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1925</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1857</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1586</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.0276</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.06900000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,85 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.4% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.4%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-2.1% → -1.8%</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>70.6 → 68.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>70.6</t>
+  </si>
+  <si>
+    <t>68.3</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.8% → -3.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.8%</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.3 → 54.7</t>
-  </si>
-  <si>
-    <t>47.3</t>
-  </si>
-  <si>
-    <t>54.7</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>60.4 → 70.4</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>60.4</t>
-  </si>
-  <si>
-    <t>70.4</t>
-  </si>
-  <si>
-    <t>66.5 → 70.6</t>
-  </si>
-  <si>
-    <t>66.5</t>
-  </si>
-  <si>
-    <t>70.6</t>
-  </si>
-  <si>
-    <t>51.0 → 49.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>-3.8%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -357,14 +306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -372,6 +314,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -404,19 +353,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -494,11 +443,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -870,8 +817,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -1011,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>641.4</v>
+        <v>637.55</v>
       </c>
       <c r="D2">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -1023,25 +970,25 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.34</v>
+        <v>-36.73</v>
       </c>
       <c r="H2">
-        <v>74.67</v>
+        <v>73.62</v>
       </c>
       <c r="I2">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="J2">
-        <v>1.79</v>
+        <v>0.09</v>
       </c>
       <c r="K2">
-        <v>-8.98</v>
+        <v>-6.01</v>
       </c>
       <c r="L2">
-        <v>23.71</v>
+        <v>22.95</v>
       </c>
       <c r="M2">
-        <v>-6.9</v>
+        <v>-7.11</v>
       </c>
       <c r="N2">
         <v>45</v>
@@ -1050,19 +997,19 @@
         <v>65</v>
       </c>
       <c r="P2">
-        <v>639.89</v>
+        <v>640</v>
       </c>
       <c r="Q2">
-        <v>637.72</v>
+        <v>638.11</v>
       </c>
       <c r="R2">
-        <v>647.6</v>
+        <v>646.62</v>
       </c>
       <c r="S2">
-        <v>619.6</v>
+        <v>620.04</v>
       </c>
       <c r="T2">
-        <v>3.52</v>
+        <v>2.82</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1077,34 +1024,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.09</v>
+        <v>47.68</v>
       </c>
       <c r="Z2">
-        <v>-1.98</v>
+        <v>-2.15</v>
       </c>
       <c r="AA2">
-        <v>-3.2</v>
+        <v>-2.99</v>
       </c>
       <c r="AB2">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="AC2">
-        <v>51.7</v>
+        <v>46.94</v>
       </c>
       <c r="AD2">
-        <v>47.82</v>
+        <v>49.25</v>
       </c>
       <c r="AE2">
-        <v>22.06</v>
+        <v>21.19</v>
       </c>
       <c r="AF2">
-        <v>-77.06999999999999</v>
+        <v>-67.55</v>
       </c>
       <c r="AG2">
-        <v>662.89</v>
+        <v>663</v>
       </c>
       <c r="AH2">
-        <v>612.5599999999999</v>
+        <v>613.23</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1113,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1124,13 +1071,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>302.45</v>
+        <v>310.25</v>
       </c>
       <c r="D3">
-        <v>7.35</v>
+        <v>2.58</v>
       </c>
       <c r="E3">
-        <v>302.45</v>
+        <v>310.25</v>
       </c>
       <c r="F3">
         <v>153.23</v>
@@ -1139,43 +1086,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>97.38</v>
+        <v>102.47</v>
       </c>
       <c r="I3">
-        <v>12.56</v>
+        <v>15.01</v>
       </c>
       <c r="J3">
-        <v>17.62</v>
+        <v>20.44</v>
       </c>
       <c r="K3">
-        <v>22.91</v>
+        <v>25.56</v>
       </c>
       <c r="L3">
-        <v>48.79</v>
+        <v>54.12</v>
       </c>
       <c r="M3">
-        <v>40.36</v>
+        <v>40.62</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>286.57</v>
+        <v>294.67</v>
       </c>
       <c r="Q3">
-        <v>271.41</v>
+        <v>274.2</v>
       </c>
       <c r="R3">
-        <v>265.49</v>
+        <v>266.52</v>
       </c>
       <c r="S3">
-        <v>210.83</v>
+        <v>211.53</v>
       </c>
       <c r="T3">
-        <v>43.46</v>
+        <v>46.67</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1190,43 +1137,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>70.44</v>
+        <v>73.2</v>
       </c>
       <c r="Z3">
-        <v>7.37</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA3">
-        <v>4.65</v>
+        <v>5.58</v>
       </c>
       <c r="AB3">
-        <v>2.72</v>
+        <v>3.72</v>
       </c>
       <c r="AC3">
-        <v>73.73</v>
+        <v>81.91</v>
       </c>
       <c r="AD3">
-        <v>72.34</v>
+        <v>76.62</v>
       </c>
       <c r="AE3">
-        <v>10.84</v>
+        <v>11.11</v>
       </c>
       <c r="AF3">
-        <v>578.3</v>
+        <v>266.2</v>
       </c>
       <c r="AG3">
-        <v>295.12</v>
+        <v>302.23</v>
       </c>
       <c r="AH3">
-        <v>247.7</v>
+        <v>246.18</v>
       </c>
       <c r="AI3">
-        <v>262.26</v>
+        <v>276.86</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>40.67</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1237,10 +1184,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1175.4</v>
+        <v>1170</v>
       </c>
       <c r="D4">
-        <v>1.85</v>
+        <v>-0.46</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1249,46 +1196,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-8.800000000000001</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="H4">
-        <v>24.28</v>
+        <v>23.7</v>
       </c>
       <c r="I4">
-        <v>5.42</v>
+        <v>4.57</v>
       </c>
       <c r="J4">
-        <v>11.48</v>
+        <v>7.47</v>
       </c>
       <c r="K4">
-        <v>-3.7</v>
+        <v>-3.08</v>
       </c>
       <c r="L4">
-        <v>16.59</v>
+        <v>17.32</v>
       </c>
       <c r="M4">
-        <v>26.28</v>
+        <v>26.15</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1145.04</v>
+        <v>1155.26</v>
       </c>
       <c r="Q4">
-        <v>1114.96</v>
+        <v>1118.78</v>
       </c>
       <c r="R4">
-        <v>1081.89</v>
+        <v>1082.57</v>
       </c>
       <c r="S4">
-        <v>1125.31</v>
+        <v>1125.8</v>
       </c>
       <c r="T4">
-        <v>4.45</v>
+        <v>3.93</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1303,43 +1250,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>70.62</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="Z4">
-        <v>18.45</v>
+        <v>20.43</v>
       </c>
       <c r="AA4">
-        <v>11.64</v>
+        <v>13.4</v>
       </c>
       <c r="AB4">
-        <v>6.81</v>
+        <v>7.03</v>
       </c>
       <c r="AC4">
-        <v>100</v>
+        <v>96.17</v>
       </c>
       <c r="AD4">
-        <v>88.48999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AE4">
-        <v>24.75</v>
+        <v>25.11</v>
       </c>
       <c r="AF4">
-        <v>5.28</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="AG4">
-        <v>1160.08</v>
+        <v>1168.95</v>
       </c>
       <c r="AH4">
-        <v>1069.84</v>
+        <v>1068.6</v>
       </c>
       <c r="AI4">
-        <v>1088.95</v>
+        <v>1106.17</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>42.18</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1350,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>712.95</v>
+        <v>705</v>
       </c>
       <c r="D5">
-        <v>1.65</v>
+        <v>-1.12</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1362,46 +1309,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-17.54</v>
+        <v>-18.46</v>
       </c>
       <c r="H5">
-        <v>7.71</v>
+        <v>6.51</v>
       </c>
       <c r="I5">
-        <v>-1.53</v>
+        <v>-1.87</v>
       </c>
       <c r="J5">
-        <v>-1.57</v>
+        <v>-3.23</v>
       </c>
       <c r="K5">
-        <v>-1.28</v>
+        <v>2.9</v>
       </c>
       <c r="L5">
-        <v>-7.57</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="M5">
-        <v>38.07</v>
+        <v>37.37</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>707.3</v>
+        <v>704.62</v>
       </c>
       <c r="Q5">
-        <v>727.5700000000001</v>
+        <v>725.9299999999999</v>
       </c>
       <c r="R5">
-        <v>717.99</v>
+        <v>717.53</v>
       </c>
       <c r="S5">
-        <v>749.48</v>
+        <v>749.4</v>
       </c>
       <c r="T5">
-        <v>-4.87</v>
+        <v>-5.92</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1416,34 +1363,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.69</v>
+        <v>40.87</v>
       </c>
       <c r="Z5">
-        <v>-3.89</v>
+        <v>-4.64</v>
       </c>
       <c r="AA5">
-        <v>0.17</v>
+        <v>-0.79</v>
       </c>
       <c r="AB5">
-        <v>-4.06</v>
+        <v>-3.85</v>
       </c>
       <c r="AC5">
-        <v>15.61</v>
+        <v>22.23</v>
       </c>
       <c r="AD5">
-        <v>6.03</v>
+        <v>13.11</v>
       </c>
       <c r="AE5">
-        <v>15.79</v>
+        <v>15.52</v>
       </c>
       <c r="AF5">
-        <v>-14.45</v>
+        <v>-24.28</v>
       </c>
       <c r="AG5">
-        <v>754.13</v>
+        <v>753.85</v>
       </c>
       <c r="AH5">
-        <v>701</v>
+        <v>698.01</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1452,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.84</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1463,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>543.5</v>
+        <v>542.1</v>
       </c>
       <c r="D6">
-        <v>-0.89</v>
+        <v>-0.26</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1475,25 +1422,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-9.42</v>
+        <v>-9.65</v>
       </c>
       <c r="H6">
-        <v>23.93</v>
+        <v>23.61</v>
       </c>
       <c r="I6">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="J6">
-        <v>-0.14</v>
+        <v>-0.66</v>
       </c>
       <c r="K6">
-        <v>-9.42</v>
+        <v>-8.59</v>
       </c>
       <c r="L6">
-        <v>4.61</v>
+        <v>5.03</v>
       </c>
       <c r="M6">
-        <v>18.57</v>
+        <v>17.42</v>
       </c>
       <c r="N6">
         <v>34</v>
@@ -1502,19 +1449,19 @@
         <v>50</v>
       </c>
       <c r="P6">
-        <v>544.71</v>
+        <v>544.73</v>
       </c>
       <c r="Q6">
-        <v>555.84</v>
+        <v>555.76</v>
       </c>
       <c r="R6">
-        <v>557.85</v>
+        <v>557.26</v>
       </c>
       <c r="S6">
-        <v>519.89</v>
+        <v>519.99</v>
       </c>
       <c r="T6">
-        <v>4.54</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1529,43 +1476,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.19</v>
+        <v>41.29</v>
       </c>
       <c r="Z6">
-        <v>-3.62</v>
+        <v>-3.96</v>
       </c>
       <c r="AA6">
-        <v>-2.02</v>
+        <v>-2.41</v>
       </c>
       <c r="AB6">
-        <v>-1.59</v>
+        <v>-1.55</v>
       </c>
       <c r="AC6">
-        <v>15.09</v>
+        <v>13.45</v>
       </c>
       <c r="AD6">
-        <v>12.6</v>
+        <v>14.7</v>
       </c>
       <c r="AE6">
-        <v>11.08</v>
+        <v>11.54</v>
       </c>
       <c r="AF6">
-        <v>122.11</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="AG6">
-        <v>576.85</v>
+        <v>576.97</v>
       </c>
       <c r="AH6">
-        <v>534.8200000000001</v>
+        <v>534.54</v>
       </c>
       <c r="AI6">
-        <v>577.21</v>
+        <v>571.73</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>15.87</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1576,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11832</v>
+        <v>11735</v>
       </c>
       <c r="D7">
-        <v>3.37</v>
+        <v>-0.82</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1588,25 +1535,25 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-46.62</v>
+        <v>-47.06</v>
       </c>
       <c r="H7">
-        <v>11.05</v>
+        <v>10.14</v>
       </c>
       <c r="I7">
-        <v>4.44</v>
+        <v>2.35</v>
       </c>
       <c r="J7">
-        <v>7.75</v>
+        <v>5.12</v>
       </c>
       <c r="K7">
-        <v>-6.11</v>
+        <v>-10.94</v>
       </c>
       <c r="L7">
-        <v>-35.22</v>
+        <v>-34.78</v>
       </c>
       <c r="M7">
-        <v>19.25</v>
+        <v>19.05</v>
       </c>
       <c r="N7">
         <v>12</v>
@@ -1615,19 +1562,19 @@
         <v>17</v>
       </c>
       <c r="P7">
-        <v>11438.6</v>
+        <v>11492.6</v>
       </c>
       <c r="Q7">
-        <v>11693.6</v>
+        <v>11720.55</v>
       </c>
       <c r="R7">
-        <v>11667.58</v>
+        <v>11647.34</v>
       </c>
       <c r="S7">
-        <v>14970.88</v>
+        <v>14944.46</v>
       </c>
       <c r="T7">
-        <v>-20.97</v>
+        <v>-21.48</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1642,34 +1589,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>54.74</v>
+        <v>52.72</v>
       </c>
       <c r="Z7">
-        <v>-34.08</v>
+        <v>-17.05</v>
       </c>
       <c r="AA7">
-        <v>-22.61</v>
+        <v>-21.5</v>
       </c>
       <c r="AB7">
-        <v>-11.47</v>
+        <v>4.45</v>
       </c>
       <c r="AC7">
-        <v>37.53</v>
+        <v>63.4</v>
       </c>
       <c r="AD7">
-        <v>17.82</v>
+        <v>37.46</v>
       </c>
       <c r="AE7">
-        <v>407.83</v>
+        <v>402.56</v>
       </c>
       <c r="AF7">
-        <v>67.61</v>
+        <v>23.25</v>
       </c>
       <c r="AG7">
-        <v>12398.08</v>
+        <v>12384.98</v>
       </c>
       <c r="AH7">
-        <v>10989.12</v>
+        <v>11056.12</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1678,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>23.8</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1689,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>344.95</v>
+        <v>337.95</v>
       </c>
       <c r="D8">
-        <v>0.29</v>
+        <v>-2.03</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1701,46 +1648,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.78</v>
+        <v>-3.77</v>
       </c>
       <c r="H8">
-        <v>47.22</v>
+        <v>44.23</v>
       </c>
       <c r="I8">
-        <v>4.56</v>
+        <v>2.46</v>
       </c>
       <c r="J8">
-        <v>8.41</v>
+        <v>6.76</v>
       </c>
       <c r="K8">
-        <v>23.39</v>
+        <v>22.76</v>
       </c>
       <c r="L8">
-        <v>11.72</v>
+        <v>10.73</v>
       </c>
       <c r="M8">
-        <v>31.33</v>
+        <v>30.37</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P8">
-        <v>338.93</v>
+        <v>340.55</v>
       </c>
       <c r="Q8">
-        <v>334.35</v>
+        <v>335.29</v>
       </c>
       <c r="R8">
-        <v>329.57</v>
+        <v>330.34</v>
       </c>
       <c r="S8">
-        <v>283.75</v>
+        <v>284.04</v>
       </c>
       <c r="T8">
-        <v>21.57</v>
+        <v>18.98</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1755,34 +1702,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>60.37</v>
+        <v>53.73</v>
       </c>
       <c r="Z8">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="AA8">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="AB8">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="AC8">
-        <v>74.61</v>
+        <v>66.25</v>
       </c>
       <c r="AD8">
-        <v>56.5</v>
+        <v>66.8</v>
       </c>
       <c r="AE8">
-        <v>9.07</v>
+        <v>9.4</v>
       </c>
       <c r="AF8">
-        <v>-37.67</v>
+        <v>-2.18</v>
       </c>
       <c r="AG8">
-        <v>351.94</v>
+        <v>351.39</v>
       </c>
       <c r="AH8">
-        <v>316.75</v>
+        <v>319.19</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1791,7 +1738,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.97</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1802,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1341</v>
+        <v>1337.5</v>
       </c>
       <c r="D9">
-        <v>1.57</v>
+        <v>-0.26</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1814,46 +1761,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="H9">
-        <v>30.63</v>
+        <v>30.28</v>
       </c>
       <c r="I9">
-        <v>4.29</v>
+        <v>2.91</v>
       </c>
       <c r="J9">
-        <v>7.55</v>
+        <v>4.77</v>
       </c>
       <c r="K9">
-        <v>2.42</v>
+        <v>4.66</v>
       </c>
       <c r="L9">
-        <v>25.12</v>
+        <v>26.83</v>
       </c>
       <c r="M9">
-        <v>15.86</v>
+        <v>15.61</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P9">
-        <v>1316.34</v>
+        <v>1323.9</v>
       </c>
       <c r="Q9">
-        <v>1294.15</v>
+        <v>1297.48</v>
       </c>
       <c r="R9">
-        <v>1265.3</v>
+        <v>1266.31</v>
       </c>
       <c r="S9">
-        <v>1220.52</v>
+        <v>1221.31</v>
       </c>
       <c r="T9">
-        <v>9.869999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1868,43 +1815,43 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>65.67</v>
+        <v>64.36</v>
       </c>
       <c r="Z9">
-        <v>14.51</v>
+        <v>16.23</v>
       </c>
       <c r="AA9">
-        <v>9.970000000000001</v>
+        <v>11.23</v>
       </c>
       <c r="AB9">
-        <v>4.54</v>
+        <v>5.01</v>
       </c>
       <c r="AC9">
-        <v>84.83</v>
+        <v>92.25</v>
       </c>
       <c r="AD9">
-        <v>65.5</v>
+        <v>79.91</v>
       </c>
       <c r="AE9">
-        <v>25.53</v>
+        <v>25.2</v>
       </c>
       <c r="AF9">
-        <v>14.78</v>
+        <v>58.67</v>
       </c>
       <c r="AG9">
-        <v>1338.76</v>
+        <v>1344.65</v>
       </c>
       <c r="AH9">
-        <v>1249.53</v>
+        <v>1250.31</v>
       </c>
       <c r="AI9">
-        <v>1249.12</v>
+        <v>1264.89</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>40.39</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1915,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.55</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.39</v>
+        <v>-1.41</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1927,25 +1874,25 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.83</v>
+        <v>-12.08</v>
       </c>
       <c r="H10">
-        <v>126.03</v>
+        <v>122.84</v>
       </c>
       <c r="I10">
-        <v>-1.2</v>
+        <v>-2.91</v>
       </c>
       <c r="J10">
-        <v>20.46</v>
+        <v>15.82</v>
       </c>
       <c r="K10">
-        <v>55.16</v>
+        <v>57.43</v>
       </c>
       <c r="L10">
-        <v>11.18</v>
+        <v>10.14</v>
       </c>
       <c r="M10">
-        <v>-2.76</v>
+        <v>-3.04</v>
       </c>
       <c r="N10">
         <v>88</v>
@@ -1954,19 +1901,19 @@
         <v>87</v>
       </c>
       <c r="P10">
-        <v>82.37</v>
+        <v>81.89</v>
       </c>
       <c r="Q10">
-        <v>82.88</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="R10">
-        <v>66.63</v>
+        <v>67.2</v>
       </c>
       <c r="S10">
-        <v>59.58</v>
+        <v>59.61</v>
       </c>
       <c r="T10">
-        <v>36.88</v>
+        <v>34.87</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1981,34 +1928,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>55.6</v>
+        <v>53.73</v>
       </c>
       <c r="Z10">
-        <v>4.68</v>
+        <v>4.13</v>
       </c>
       <c r="AA10">
-        <v>6.19</v>
+        <v>5.77</v>
       </c>
       <c r="AB10">
-        <v>-1.51</v>
+        <v>-1.64</v>
       </c>
       <c r="AC10">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>6.83</v>
+        <v>4.44</v>
       </c>
       <c r="AE10">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="AF10">
-        <v>-91.09999999999999</v>
+        <v>-92.63</v>
       </c>
       <c r="AG10">
-        <v>95.44</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AH10">
-        <v>70.31999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -2017,7 +1964,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>33.08</v>
+        <v>28.83</v>
       </c>
     </row>
   </sheetData>
@@ -2158,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2198,7 +2145,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2221,1443 +2168,1258 @@
         <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>17.62</v>
+      </c>
+      <c r="D9" s="6">
+        <v>20.44</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>11.48</v>
+      </c>
+      <c r="D10" s="6">
+        <v>7.47</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>5.12</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>8.41</v>
+      </c>
+      <c r="D14" s="6">
+        <v>6.76</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>7.55</v>
+      </c>
+      <c r="D15" s="6">
+        <v>4.77</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>20.46</v>
+      </c>
+      <c r="D16" s="6">
+        <v>15.82</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-4.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>12.56</v>
+      </c>
+      <c r="D18" s="6">
+        <v>15.01</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>5.42</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4.57</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.53</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.87</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.08</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4.44</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2.35</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.46</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4.29</v>
+      </c>
+      <c r="D24" s="6">
+        <v>2.91</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.2</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>23.71</v>
+      </c>
+      <c r="D26" s="6">
+        <v>22.95</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>48.79</v>
+      </c>
+      <c r="D27" s="6">
+        <v>54.12</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>16.59</v>
+      </c>
+      <c r="D28" s="6">
+        <v>17.32</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-7.57</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>4.61</v>
+      </c>
+      <c r="D30" s="6">
+        <v>5.03</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-35.22</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-34.78</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>11.72</v>
+      </c>
+      <c r="D32" s="6">
+        <v>10.73</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>25.12</v>
+      </c>
+      <c r="D33" s="6">
+        <v>26.83</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>11.18</v>
+      </c>
+      <c r="D34" s="6">
+        <v>10.14</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.98</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-6.01</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>22.91</v>
+      </c>
+      <c r="D36" s="6">
+        <v>25.56</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.7</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-3.08</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="D38" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="E38" s="8">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-9.42</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-8.59</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-6.11</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-10.94</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>23.39</v>
+      </c>
+      <c r="D41" s="6">
+        <v>22.76</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>2.42</v>
+      </c>
+      <c r="D42" s="6">
+        <v>4.66</v>
+      </c>
+      <c r="E42" s="8">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>55.16</v>
+      </c>
+      <c r="D43" s="6">
+        <v>57.43</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-36.34</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-36.73</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-17.54</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-18.46</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9.42</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-46.62</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-47.06</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-1.78</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-3.77</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
         <v>0</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="D50" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-10.83</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-12.08</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>1.76</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.79</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>641.4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>637.55</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>12.32</v>
-      </c>
-      <c r="D14" s="8">
-        <v>17.62</v>
-      </c>
-      <c r="E14" s="9">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>302.45</v>
+      </c>
+      <c r="D53" s="6">
+        <v>310.25</v>
+      </c>
+      <c r="E53" s="8">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="D15" s="8">
-        <v>11.48</v>
-      </c>
-      <c r="E15" s="9">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1175.4</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1170</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-3.12</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-1.57</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>712.95</v>
+      </c>
+      <c r="D55" s="6">
+        <v>705</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-7.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-0.24</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-0.14</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>543.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>542.1</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>4.06</v>
-      </c>
-      <c r="D18" s="8">
-        <v>7.75</v>
-      </c>
-      <c r="E18" s="9">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11832</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11735</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>6.88</v>
-      </c>
-      <c r="D19" s="8">
-        <v>8.41</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>344.95</v>
+      </c>
+      <c r="D58" s="6">
+        <v>337.95</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
-        <v>6.08</v>
-      </c>
-      <c r="D20" s="8">
-        <v>7.55</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1341</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1337.5</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="8">
-        <v>17.68</v>
-      </c>
-      <c r="D21" s="8">
-        <v>20.46</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>81.55</v>
+      </c>
+      <c r="D60" s="6">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-0.01</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>49.09</v>
+      </c>
+      <c r="D61" s="6">
+        <v>47.68</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>4.88</v>
-      </c>
-      <c r="D23" s="8">
-        <v>12.56</v>
-      </c>
-      <c r="E23" s="9">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>70.44</v>
+      </c>
+      <c r="D62" s="6">
+        <v>73.2</v>
+      </c>
+      <c r="E62" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>4.78</v>
-      </c>
-      <c r="D24" s="8">
-        <v>5.42</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>70.62</v>
+      </c>
+      <c r="D63" s="6">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-4.23</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>44.69</v>
+      </c>
+      <c r="D64" s="6">
+        <v>40.87</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>42.19</v>
+      </c>
+      <c r="D65" s="6">
+        <v>41.29</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>54.74</v>
+      </c>
+      <c r="D66" s="6">
+        <v>52.72</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>60.37</v>
+      </c>
+      <c r="D67" s="6">
+        <v>53.73</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-6.64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>65.67</v>
+      </c>
+      <c r="D68" s="6">
+        <v>64.36</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>55.6</v>
+      </c>
+      <c r="D69" s="6">
+        <v>53.73</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-77.06999999999999</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-67.55</v>
+      </c>
+      <c r="E70" s="8">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>578.3</v>
+      </c>
+      <c r="D71" s="6">
+        <v>266.2</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-312.1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>5.28</v>
+      </c>
+      <c r="D72" s="6">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="E72" s="8">
+        <v>75.45999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-14.45</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-24.28</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-9.83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>122.11</v>
+      </c>
+      <c r="D74" s="6">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-32.62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>67.61</v>
+      </c>
+      <c r="D75" s="6">
+        <v>23.25</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-44.36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-37.67</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-2.18</v>
+      </c>
+      <c r="E76" s="8">
+        <v>35.49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>14.78</v>
+      </c>
+      <c r="D77" s="6">
+        <v>58.67</v>
+      </c>
+      <c r="E77" s="8">
+        <v>43.89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-91.09999999999999</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-92.63</v>
+      </c>
+      <c r="E78" s="7">
         <v>-1.53</v>
-      </c>
-      <c r="E25" s="9">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-0.08</v>
-      </c>
-      <c r="E26" s="10">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-0.37</v>
-      </c>
-      <c r="D27" s="8">
-        <v>4.44</v>
-      </c>
-      <c r="E27" s="9">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>4.66</v>
-      </c>
-      <c r="D28" s="8">
-        <v>4.56</v>
-      </c>
-      <c r="E28" s="10">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="8">
-        <v>4.16</v>
-      </c>
-      <c r="D29" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-5.77</v>
-      </c>
-      <c r="D30" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="E30" s="9">
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>24.72</v>
-      </c>
-      <c r="D31" s="8">
-        <v>23.71</v>
-      </c>
-      <c r="E31" s="10">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>38.26</v>
-      </c>
-      <c r="D32" s="8">
-        <v>48.79</v>
-      </c>
-      <c r="E32" s="9">
-        <v>10.53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>13.79</v>
-      </c>
-      <c r="D33" s="8">
-        <v>16.59</v>
-      </c>
-      <c r="E33" s="9">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>-7.97</v>
-      </c>
-      <c r="D34" s="8">
-        <v>-7.57</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>3.48</v>
-      </c>
-      <c r="D35" s="8">
-        <v>4.61</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-36.97</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-35.22</v>
-      </c>
-      <c r="E36" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="8">
-        <v>11.56</v>
-      </c>
-      <c r="D37" s="8">
-        <v>11.72</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="8">
-        <v>21.96</v>
-      </c>
-      <c r="D38" s="8">
-        <v>25.12</v>
-      </c>
-      <c r="E38" s="9">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="8">
-        <v>11.74</v>
-      </c>
-      <c r="D39" s="8">
-        <v>11.18</v>
-      </c>
-      <c r="E39" s="10">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-8.24</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-8.98</v>
-      </c>
-      <c r="E40" s="10">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>14.5</v>
-      </c>
-      <c r="D41" s="8">
-        <v>22.91</v>
-      </c>
-      <c r="E41" s="9">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-5.45</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-3.7</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-2.88</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-1.28</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-8.6</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-9.42</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-9.17</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-6.11</v>
-      </c>
-      <c r="E45" s="9">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="8">
-        <v>23.04</v>
-      </c>
-      <c r="D46" s="8">
-        <v>23.39</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="D47" s="8">
-        <v>2.42</v>
-      </c>
-      <c r="E47" s="9">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="8">
-        <v>55.76</v>
-      </c>
-      <c r="D48" s="8">
-        <v>55.16</v>
-      </c>
-      <c r="E48" s="10">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-35.83</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-36.34</v>
-      </c>
-      <c r="E49" s="10">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-3.39</v>
-      </c>
-      <c r="D50" s="8">
-        <v>0</v>
-      </c>
-      <c r="E50" s="9">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-10.45</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-18.87</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-17.54</v>
-      </c>
-      <c r="E52" s="9">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>-8.6</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-9.42</v>
-      </c>
-      <c r="E53" s="10">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-48.36</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-46.62</v>
-      </c>
-      <c r="E54" s="9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="8">
-        <v>-2.06</v>
-      </c>
-      <c r="D55" s="8">
-        <v>-1.78</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="8">
-        <v>-0.73</v>
-      </c>
-      <c r="D56" s="8">
-        <v>0</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="8">
-        <v>-10.48</v>
-      </c>
-      <c r="D57" s="8">
-        <v>-10.83</v>
-      </c>
-      <c r="E57" s="10">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>646.6</v>
-      </c>
-      <c r="D58" s="8">
-        <v>641.4</v>
-      </c>
-      <c r="E58" s="10">
-        <v>-5.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>281.75</v>
-      </c>
-      <c r="D59" s="8">
-        <v>302.45</v>
-      </c>
-      <c r="E59" s="9">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>1154.1</v>
-      </c>
-      <c r="D60" s="8">
-        <v>1175.4</v>
-      </c>
-      <c r="E60" s="9">
-        <v>21.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>701.4</v>
-      </c>
-      <c r="D61" s="8">
-        <v>712.95</v>
-      </c>
-      <c r="E61" s="9">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>548.4</v>
-      </c>
-      <c r="D62" s="8">
-        <v>543.5</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>11446</v>
-      </c>
-      <c r="D63" s="8">
-        <v>11832</v>
-      </c>
-      <c r="E63" s="9">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="8">
-        <v>343.95</v>
-      </c>
-      <c r="D64" s="8">
-        <v>344.95</v>
-      </c>
-      <c r="E64" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="8">
-        <v>1320.3</v>
-      </c>
-      <c r="D65" s="8">
-        <v>1341</v>
-      </c>
-      <c r="E65" s="9">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C66" s="8">
-        <v>81.87</v>
-      </c>
-      <c r="D66" s="8">
-        <v>81.55</v>
-      </c>
-      <c r="E66" s="10">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="8">
-        <v>55</v>
-      </c>
-      <c r="D67" s="8">
-        <v>45</v>
-      </c>
-      <c r="E67" s="10">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="8">
-        <v>88</v>
-      </c>
-      <c r="D68" s="8">
-        <v>99</v>
-      </c>
-      <c r="E68" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="8">
-        <v>45</v>
-      </c>
-      <c r="D69" s="8">
-        <v>55</v>
-      </c>
-      <c r="E69" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="8">
-        <v>99</v>
-      </c>
-      <c r="D70" s="8">
-        <v>88</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>50.97</v>
-      </c>
-      <c r="D71" s="8">
-        <v>49.09</v>
-      </c>
-      <c r="E71" s="10">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>60.38</v>
-      </c>
-      <c r="D72" s="8">
-        <v>70.44</v>
-      </c>
-      <c r="E72" s="9">
-        <v>10.06</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>66.5</v>
-      </c>
-      <c r="D73" s="8">
-        <v>70.62</v>
-      </c>
-      <c r="E73" s="9">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>36.71</v>
-      </c>
-      <c r="D74" s="8">
-        <v>44.69</v>
-      </c>
-      <c r="E74" s="9">
-        <v>7.98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>45.41</v>
-      </c>
-      <c r="D75" s="8">
-        <v>42.19</v>
-      </c>
-      <c r="E75" s="10">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="8">
-        <v>47.3</v>
-      </c>
-      <c r="D76" s="8">
-        <v>54.74</v>
-      </c>
-      <c r="E76" s="9">
-        <v>7.44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="8">
-        <v>59.71</v>
-      </c>
-      <c r="D77" s="8">
-        <v>60.37</v>
-      </c>
-      <c r="E77" s="9">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" s="8">
-        <v>61.34</v>
-      </c>
-      <c r="D78" s="8">
-        <v>65.67</v>
-      </c>
-      <c r="E78" s="9">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" s="8">
-        <v>56.11</v>
-      </c>
-      <c r="D79" s="8">
-        <v>55.6</v>
-      </c>
-      <c r="E79" s="10">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="8">
-        <v>-47.21</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-77.06999999999999</v>
-      </c>
-      <c r="E80" s="10">
-        <v>-29.86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>-49.69</v>
-      </c>
-      <c r="D81" s="8">
-        <v>578.3</v>
-      </c>
-      <c r="E81" s="9">
-        <v>627.99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>-28.94</v>
-      </c>
-      <c r="D82" s="8">
-        <v>5.28</v>
-      </c>
-      <c r="E82" s="9">
-        <v>34.22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-58.48</v>
-      </c>
-      <c r="D83" s="8">
-        <v>-14.45</v>
-      </c>
-      <c r="E83" s="9">
-        <v>44.03</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>-13.55</v>
-      </c>
-      <c r="D84" s="8">
-        <v>122.11</v>
-      </c>
-      <c r="E84" s="9">
-        <v>135.66</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="8">
-        <v>-13.87</v>
-      </c>
-      <c r="D85" s="8">
-        <v>67.61</v>
-      </c>
-      <c r="E85" s="9">
-        <v>81.48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="8">
-        <v>-19.82</v>
-      </c>
-      <c r="D86" s="8">
-        <v>-37.67</v>
-      </c>
-      <c r="E86" s="10">
-        <v>-17.85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C87" s="8">
-        <v>-26.13</v>
-      </c>
-      <c r="D87" s="8">
-        <v>14.78</v>
-      </c>
-      <c r="E87" s="9">
-        <v>40.91</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88" s="8">
-        <v>-92.67</v>
-      </c>
-      <c r="D88" s="8">
-        <v>-91.09999999999999</v>
-      </c>
-      <c r="E88" s="9">
-        <v>1.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3677,60 +3439,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>96</v>
+      <c r="B1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>64.16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>57</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>55.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>80</v>
       </c>
-      <c r="F2" s="13">
-        <v>8.1</v>
-      </c>
-      <c r="G2" s="13">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>9.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3832,61 +3594,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.4036</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3807</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.3133</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.2628</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1925</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1857</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.1586</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.0276</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.06900000000000001</v>
+      <c r="A2" s="14">
+        <v>0.4061999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3737</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3037</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2615</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1905</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1742</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1561</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0304</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0711</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>70.6 → 68.3</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>70.6</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>68.3 → 70.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>68.3</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.8% → -3.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
+    <t>70.1</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.7 → 49.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.7</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,7 +306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,10 +443,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -817,8 +818,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -958,10 +959,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>637.55</v>
+        <v>635.85</v>
       </c>
       <c r="D2">
-        <v>-0.6</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -970,46 +971,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.73</v>
+        <v>-36.89</v>
       </c>
       <c r="H2">
-        <v>73.62</v>
+        <v>73.16</v>
       </c>
       <c r="I2">
-        <v>0.09</v>
+        <v>-0.27</v>
       </c>
       <c r="J2">
-        <v>0.09</v>
+        <v>0.97</v>
       </c>
       <c r="K2">
-        <v>-6.01</v>
+        <v>-4.66</v>
       </c>
       <c r="L2">
-        <v>22.95</v>
+        <v>22.56</v>
       </c>
       <c r="M2">
-        <v>-7.11</v>
+        <v>-7.76</v>
       </c>
       <c r="N2">
         <v>45</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>640</v>
+        <v>639.65</v>
       </c>
       <c r="Q2">
-        <v>638.11</v>
+        <v>638.24</v>
       </c>
       <c r="R2">
-        <v>646.62</v>
+        <v>645.51</v>
       </c>
       <c r="S2">
-        <v>620.04</v>
+        <v>620.47</v>
       </c>
       <c r="T2">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1024,34 +1025,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.68</v>
+        <v>47.04</v>
       </c>
       <c r="Z2">
-        <v>-2.15</v>
+        <v>-2.39</v>
       </c>
       <c r="AA2">
-        <v>-2.99</v>
+        <v>-2.87</v>
       </c>
       <c r="AB2">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AC2">
-        <v>46.94</v>
+        <v>33.21</v>
       </c>
       <c r="AD2">
-        <v>49.25</v>
+        <v>43.95</v>
       </c>
       <c r="AE2">
-        <v>21.19</v>
+        <v>20.33</v>
       </c>
       <c r="AF2">
-        <v>-67.55</v>
+        <v>-78.33</v>
       </c>
       <c r="AG2">
-        <v>663</v>
+        <v>663.05</v>
       </c>
       <c r="AH2">
-        <v>613.23</v>
+        <v>613.4400000000001</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1060,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.04</v>
+        <v>30.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1071,10 +1072,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>310.25</v>
+        <v>308.6</v>
       </c>
       <c r="D3">
-        <v>2.58</v>
+        <v>-0.53</v>
       </c>
       <c r="E3">
         <v>310.25</v>
@@ -1083,25 +1084,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="H3">
-        <v>102.47</v>
+        <v>101.4</v>
       </c>
       <c r="I3">
-        <v>15.01</v>
+        <v>5.81</v>
       </c>
       <c r="J3">
-        <v>20.44</v>
+        <v>21.35</v>
       </c>
       <c r="K3">
-        <v>25.56</v>
+        <v>28.11</v>
       </c>
       <c r="L3">
-        <v>54.12</v>
+        <v>51.7</v>
       </c>
       <c r="M3">
-        <v>40.62</v>
+        <v>40.75</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1110,19 +1111,19 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>294.67</v>
+        <v>298.06</v>
       </c>
       <c r="Q3">
-        <v>274.2</v>
+        <v>276.79</v>
       </c>
       <c r="R3">
-        <v>266.52</v>
+        <v>267.41</v>
       </c>
       <c r="S3">
-        <v>211.53</v>
+        <v>212.22</v>
       </c>
       <c r="T3">
-        <v>46.67</v>
+        <v>45.42</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1137,34 +1138,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>73.2</v>
+        <v>71.67</v>
       </c>
       <c r="Z3">
-        <v>9.300000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="AA3">
-        <v>5.58</v>
+        <v>6.58</v>
       </c>
       <c r="AB3">
-        <v>3.72</v>
+        <v>3.99</v>
       </c>
       <c r="AC3">
-        <v>81.91</v>
+        <v>97.2</v>
       </c>
       <c r="AD3">
-        <v>76.62</v>
+        <v>84.28</v>
       </c>
       <c r="AE3">
-        <v>11.11</v>
+        <v>10.75</v>
       </c>
       <c r="AF3">
-        <v>266.2</v>
+        <v>-57.7</v>
       </c>
       <c r="AG3">
-        <v>302.23</v>
+        <v>307.51</v>
       </c>
       <c r="AH3">
-        <v>246.18</v>
+        <v>246.07</v>
       </c>
       <c r="AI3">
         <v>276.86</v>
@@ -1173,7 +1174,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>44.99</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1184,10 +1185,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1170</v>
+        <v>1179.2</v>
       </c>
       <c r="D4">
-        <v>-0.46</v>
+        <v>0.79</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1196,46 +1197,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-9.220000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="H4">
-        <v>23.7</v>
+        <v>24.68</v>
       </c>
       <c r="I4">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="J4">
-        <v>7.47</v>
+        <v>7.82</v>
       </c>
       <c r="K4">
-        <v>-3.08</v>
+        <v>-2.53</v>
       </c>
       <c r="L4">
-        <v>17.32</v>
+        <v>18.37</v>
       </c>
       <c r="M4">
-        <v>26.15</v>
+        <v>25.71</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1155.26</v>
+        <v>1165.54</v>
       </c>
       <c r="Q4">
-        <v>1118.78</v>
+        <v>1122.62</v>
       </c>
       <c r="R4">
-        <v>1082.57</v>
+        <v>1083.52</v>
       </c>
       <c r="S4">
-        <v>1125.8</v>
+        <v>1126.3</v>
       </c>
       <c r="T4">
-        <v>3.93</v>
+        <v>4.7</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1250,43 +1251,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>68.31999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Z4">
-        <v>20.43</v>
+        <v>22.48</v>
       </c>
       <c r="AA4">
-        <v>13.4</v>
+        <v>15.22</v>
       </c>
       <c r="AB4">
-        <v>7.03</v>
+        <v>7.27</v>
       </c>
       <c r="AC4">
-        <v>96.17</v>
+        <v>95.31</v>
       </c>
       <c r="AD4">
-        <v>95.5</v>
+        <v>97.16</v>
       </c>
       <c r="AE4">
-        <v>25.11</v>
+        <v>24.88</v>
       </c>
       <c r="AF4">
-        <v>80.73999999999999</v>
+        <v>-21.22</v>
       </c>
       <c r="AG4">
-        <v>1168.95</v>
+        <v>1178.89</v>
       </c>
       <c r="AH4">
-        <v>1068.6</v>
+        <v>1066.34</v>
       </c>
       <c r="AI4">
-        <v>1106.17</v>
+        <v>1106.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>46.91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1297,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>705</v>
+        <v>705.15</v>
       </c>
       <c r="D5">
-        <v>-1.12</v>
+        <v>0.02</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1309,46 +1310,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.46</v>
+        <v>-18.44</v>
       </c>
       <c r="H5">
-        <v>6.51</v>
+        <v>6.53</v>
       </c>
       <c r="I5">
-        <v>-1.87</v>
+        <v>0.54</v>
       </c>
       <c r="J5">
-        <v>-3.23</v>
+        <v>-4.42</v>
       </c>
       <c r="K5">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="L5">
-        <v>-9.220000000000001</v>
+        <v>-11.35</v>
       </c>
       <c r="M5">
-        <v>37.37</v>
+        <v>36.59</v>
       </c>
       <c r="N5">
         <v>23</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>704.62</v>
+        <v>705.38</v>
       </c>
       <c r="Q5">
-        <v>725.9299999999999</v>
+        <v>724.45</v>
       </c>
       <c r="R5">
-        <v>717.53</v>
+        <v>717.49</v>
       </c>
       <c r="S5">
-        <v>749.4</v>
+        <v>749.22</v>
       </c>
       <c r="T5">
-        <v>-5.92</v>
+        <v>-5.88</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1363,34 +1364,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.87</v>
+        <v>40.97</v>
       </c>
       <c r="Z5">
-        <v>-4.64</v>
+        <v>-5.17</v>
       </c>
       <c r="AA5">
-        <v>-0.79</v>
+        <v>-1.67</v>
       </c>
       <c r="AB5">
-        <v>-3.85</v>
+        <v>-3.5</v>
       </c>
       <c r="AC5">
-        <v>22.23</v>
+        <v>29.5</v>
       </c>
       <c r="AD5">
-        <v>13.11</v>
+        <v>22.45</v>
       </c>
       <c r="AE5">
-        <v>15.52</v>
+        <v>15.16</v>
       </c>
       <c r="AF5">
-        <v>-24.28</v>
+        <v>-16.04</v>
       </c>
       <c r="AG5">
-        <v>753.85</v>
+        <v>753.51</v>
       </c>
       <c r="AH5">
-        <v>698.01</v>
+        <v>695.38</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1399,7 +1400,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>21.67</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1410,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>542.1</v>
+        <v>535.3</v>
       </c>
       <c r="D6">
-        <v>-0.26</v>
+        <v>-1.25</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1422,46 +1423,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-9.65</v>
+        <v>-10.78</v>
       </c>
       <c r="H6">
-        <v>23.61</v>
+        <v>22.06</v>
       </c>
       <c r="I6">
-        <v>0.02</v>
+        <v>-1.77</v>
       </c>
       <c r="J6">
-        <v>-0.66</v>
+        <v>-1.54</v>
       </c>
       <c r="K6">
-        <v>-8.59</v>
+        <v>-7.94</v>
       </c>
       <c r="L6">
-        <v>5.03</v>
+        <v>3.01</v>
       </c>
       <c r="M6">
-        <v>17.42</v>
+        <v>16.86</v>
       </c>
       <c r="N6">
         <v>34</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>544.73</v>
+        <v>542.8</v>
       </c>
       <c r="Q6">
-        <v>555.76</v>
+        <v>554.79</v>
       </c>
       <c r="R6">
-        <v>557.26</v>
+        <v>556.45</v>
       </c>
       <c r="S6">
-        <v>519.99</v>
+        <v>520.05</v>
       </c>
       <c r="T6">
-        <v>4.25</v>
+        <v>2.93</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1476,34 +1477,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.29</v>
+        <v>37.15</v>
       </c>
       <c r="Z6">
-        <v>-3.96</v>
+        <v>-4.73</v>
       </c>
       <c r="AA6">
-        <v>-2.41</v>
+        <v>-2.87</v>
       </c>
       <c r="AB6">
-        <v>-1.55</v>
+        <v>-1.85</v>
       </c>
       <c r="AC6">
-        <v>13.45</v>
+        <v>5.08</v>
       </c>
       <c r="AD6">
-        <v>14.7</v>
+        <v>11.21</v>
       </c>
       <c r="AE6">
-        <v>11.54</v>
+        <v>11.2</v>
       </c>
       <c r="AF6">
-        <v>89.48999999999999</v>
+        <v>-38</v>
       </c>
       <c r="AG6">
-        <v>576.97</v>
+        <v>577.9</v>
       </c>
       <c r="AH6">
-        <v>534.54</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="AI6">
         <v>571.73</v>
@@ -1512,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.63</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1524,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11735</v>
+        <v>11578</v>
       </c>
       <c r="D7">
-        <v>-0.82</v>
+        <v>-1.34</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1535,46 +1536,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.06</v>
+        <v>-47.76</v>
       </c>
       <c r="H7">
-        <v>10.14</v>
+        <v>8.66</v>
       </c>
       <c r="I7">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="J7">
-        <v>5.12</v>
+        <v>3.41</v>
       </c>
       <c r="K7">
-        <v>-10.94</v>
+        <v>-10.13</v>
       </c>
       <c r="L7">
-        <v>-34.78</v>
+        <v>-36.05</v>
       </c>
       <c r="M7">
-        <v>19.05</v>
+        <v>18.64</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P7">
-        <v>11492.6</v>
+        <v>11550.4</v>
       </c>
       <c r="Q7">
-        <v>11720.55</v>
+        <v>11736.6</v>
       </c>
       <c r="R7">
-        <v>11647.34</v>
+        <v>11621.64</v>
       </c>
       <c r="S7">
-        <v>14944.46</v>
+        <v>14918.86</v>
       </c>
       <c r="T7">
-        <v>-21.48</v>
+        <v>-22.39</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1589,34 +1590,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>52.72</v>
+        <v>49.55</v>
       </c>
       <c r="Z7">
-        <v>-17.05</v>
+        <v>-16.04</v>
       </c>
       <c r="AA7">
-        <v>-21.5</v>
+        <v>-20.41</v>
       </c>
       <c r="AB7">
-        <v>4.45</v>
+        <v>4.37</v>
       </c>
       <c r="AC7">
-        <v>63.4</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AD7">
-        <v>37.46</v>
+        <v>57.32</v>
       </c>
       <c r="AE7">
-        <v>402.56</v>
+        <v>393.52</v>
       </c>
       <c r="AF7">
-        <v>23.25</v>
+        <v>-68.17</v>
       </c>
       <c r="AG7">
-        <v>12384.98</v>
+        <v>12368.6</v>
       </c>
       <c r="AH7">
-        <v>11056.12</v>
+        <v>11104.6</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1625,7 +1626,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>22.91</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1636,10 +1637,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>337.95</v>
+        <v>342.95</v>
       </c>
       <c r="D8">
-        <v>-2.03</v>
+        <v>1.48</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1648,46 +1649,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-3.77</v>
+        <v>-2.35</v>
       </c>
       <c r="H8">
-        <v>44.23</v>
+        <v>46.37</v>
       </c>
       <c r="I8">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="J8">
-        <v>6.76</v>
+        <v>7.49</v>
       </c>
       <c r="K8">
-        <v>22.76</v>
+        <v>25.21</v>
       </c>
       <c r="L8">
-        <v>10.73</v>
+        <v>13.09</v>
       </c>
       <c r="M8">
-        <v>30.37</v>
+        <v>31</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P8">
-        <v>340.55</v>
+        <v>342</v>
       </c>
       <c r="Q8">
-        <v>335.29</v>
+        <v>336.82</v>
       </c>
       <c r="R8">
-        <v>330.34</v>
+        <v>331.04</v>
       </c>
       <c r="S8">
-        <v>284.04</v>
+        <v>284.34</v>
       </c>
       <c r="T8">
-        <v>18.98</v>
+        <v>20.61</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1702,34 +1703,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>53.73</v>
+        <v>57.34</v>
       </c>
       <c r="Z8">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="AA8">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="AB8">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AC8">
-        <v>66.25</v>
+        <v>60.58</v>
       </c>
       <c r="AD8">
-        <v>66.8</v>
+        <v>67.14</v>
       </c>
       <c r="AE8">
-        <v>9.4</v>
+        <v>9.26</v>
       </c>
       <c r="AF8">
-        <v>-2.18</v>
+        <v>-50.37</v>
       </c>
       <c r="AG8">
-        <v>351.39</v>
+        <v>349.13</v>
       </c>
       <c r="AH8">
-        <v>319.19</v>
+        <v>324.51</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1738,7 +1739,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>23.85</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1749,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1337.5</v>
+        <v>1334.9</v>
       </c>
       <c r="D9">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1761,46 +1762,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-0.26</v>
+        <v>-0.45</v>
       </c>
       <c r="H9">
-        <v>30.28</v>
+        <v>30.03</v>
       </c>
       <c r="I9">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="J9">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
       <c r="K9">
-        <v>4.66</v>
+        <v>2.73</v>
       </c>
       <c r="L9">
-        <v>26.83</v>
+        <v>26.2</v>
       </c>
       <c r="M9">
-        <v>15.61</v>
+        <v>15.28</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P9">
-        <v>1323.9</v>
+        <v>1332.14</v>
       </c>
       <c r="Q9">
-        <v>1297.48</v>
+        <v>1300.73</v>
       </c>
       <c r="R9">
-        <v>1266.31</v>
+        <v>1267.13</v>
       </c>
       <c r="S9">
-        <v>1221.31</v>
+        <v>1222.03</v>
       </c>
       <c r="T9">
-        <v>9.51</v>
+        <v>9.24</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1815,34 +1816,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>64.36</v>
+        <v>63.34</v>
       </c>
       <c r="Z9">
-        <v>16.23</v>
+        <v>17.19</v>
       </c>
       <c r="AA9">
-        <v>11.23</v>
+        <v>12.42</v>
       </c>
       <c r="AB9">
-        <v>5.01</v>
+        <v>4.77</v>
       </c>
       <c r="AC9">
-        <v>92.25</v>
+        <v>93</v>
       </c>
       <c r="AD9">
-        <v>79.91</v>
+        <v>90.03</v>
       </c>
       <c r="AE9">
-        <v>25.2</v>
+        <v>25.09</v>
       </c>
       <c r="AF9">
-        <v>58.67</v>
+        <v>-18.5</v>
       </c>
       <c r="AG9">
-        <v>1344.65</v>
+        <v>1348.85</v>
       </c>
       <c r="AH9">
-        <v>1250.31</v>
+        <v>1252.6</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1851,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>44.34</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1863,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.40000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="D10">
-        <v>-1.41</v>
+        <v>-2.2</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1874,46 +1875,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-12.08</v>
+        <v>-14.02</v>
       </c>
       <c r="H10">
-        <v>122.84</v>
+        <v>117.93</v>
       </c>
       <c r="I10">
-        <v>-2.91</v>
+        <v>-2.79</v>
       </c>
       <c r="J10">
-        <v>15.82</v>
+        <v>16.94</v>
       </c>
       <c r="K10">
-        <v>57.43</v>
+        <v>58.46</v>
       </c>
       <c r="L10">
-        <v>10.14</v>
+        <v>8.41</v>
       </c>
       <c r="M10">
-        <v>-3.04</v>
+        <v>-3.75</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>81.89</v>
+        <v>81.44</v>
       </c>
       <c r="Q10">
-        <v>83.54000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="R10">
-        <v>67.2</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="S10">
-        <v>59.61</v>
+        <v>59.63</v>
       </c>
       <c r="T10">
-        <v>34.87</v>
+        <v>31.86</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1928,34 +1929,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>53.73</v>
+        <v>50.88</v>
       </c>
       <c r="Z10">
-        <v>4.13</v>
+        <v>3.51</v>
       </c>
       <c r="AA10">
-        <v>5.77</v>
+        <v>5.32</v>
       </c>
       <c r="AB10">
-        <v>-1.64</v>
+        <v>-1.81</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.44</v>
+        <v>2.22</v>
       </c>
       <c r="AE10">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="AF10">
-        <v>-92.63</v>
+        <v>-93.20999999999999</v>
       </c>
       <c r="AG10">
-        <v>93.81999999999999</v>
+        <v>91.17</v>
       </c>
       <c r="AH10">
-        <v>73.25</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1964,7 +1965,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>28.83</v>
+        <v>26.07</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2164,22 +2165,22 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2210,1210 +2211,1227 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>1.79</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7">
         <v>0.09</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D8" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>20.44</v>
+      </c>
+      <c r="D9" s="7">
+        <v>21.35</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>7.47</v>
+      </c>
+      <c r="D10" s="7">
+        <v>7.82</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-3.23</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-4.42</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-0.66</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-1.54</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>5.12</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3.41</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>6.76</v>
+      </c>
+      <c r="D14" s="7">
+        <v>7.49</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4.77</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5.04</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>15.82</v>
+      </c>
+      <c r="D16" s="7">
+        <v>16.94</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.27</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>15.01</v>
+      </c>
+      <c r="D18" s="7">
+        <v>5.81</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-9.199999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>4.57</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4.56</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.87</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-1.77</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2.35</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2.56</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.91</v>
+      </c>
+      <c r="D24" s="7">
+        <v>3.18</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-2.91</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.79</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>22.95</v>
+      </c>
+      <c r="D26" s="7">
+        <v>22.56</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>54.12</v>
+      </c>
+      <c r="D27" s="7">
+        <v>51.7</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>17.32</v>
+      </c>
+      <c r="D28" s="7">
+        <v>18.37</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-11.35</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="D30" s="7">
+        <v>3.01</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-34.78</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-36.05</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>10.73</v>
+      </c>
+      <c r="D32" s="7">
+        <v>13.09</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>26.83</v>
+      </c>
+      <c r="D33" s="7">
+        <v>26.2</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.14</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8.41</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-6.01</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-4.66</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>25.56</v>
+      </c>
+      <c r="D36" s="7">
+        <v>28.11</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-3.08</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-2.53</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-8.59</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-7.94</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-10.94</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-10.13</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>22.76</v>
+      </c>
+      <c r="D41" s="7">
+        <v>25.21</v>
+      </c>
+      <c r="E41" s="8">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>4.66</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>57.43</v>
+      </c>
+      <c r="D43" s="7">
+        <v>58.46</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-36.73</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-36.89</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-0.53</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-8.5</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-18.46</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-18.44</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-9.65</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-10.78</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-47.06</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-47.76</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-3.77</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-2.35</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-12.08</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-14.02</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>637.55</v>
+      </c>
+      <c r="D53" s="7">
+        <v>635.85</v>
+      </c>
+      <c r="E53" s="9">
         <v>-1.7</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>17.62</v>
-      </c>
-      <c r="D9" s="6">
-        <v>20.44</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>310.25</v>
+      </c>
+      <c r="D54" s="7">
+        <v>308.6</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>11.48</v>
-      </c>
-      <c r="D10" s="6">
-        <v>7.47</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1170</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1179.2</v>
+      </c>
+      <c r="E55" s="8">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.57</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>705</v>
+      </c>
+      <c r="D56" s="7">
+        <v>705.15</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>542.1</v>
+      </c>
+      <c r="D57" s="7">
+        <v>535.3</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7.75</v>
-      </c>
-      <c r="D13" s="6">
-        <v>5.12</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11735</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11578</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>8.41</v>
-      </c>
-      <c r="D14" s="6">
-        <v>6.76</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>337.95</v>
+      </c>
+      <c r="D59" s="7">
+        <v>342.95</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>7.55</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4.77</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1337.5</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1334.9</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>20.46</v>
-      </c>
-      <c r="D16" s="6">
-        <v>15.82</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-4.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D61" s="7">
+        <v>78.63</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>47.68</v>
+      </c>
+      <c r="D62" s="7">
+        <v>47.04</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>12.56</v>
-      </c>
-      <c r="D18" s="6">
-        <v>15.01</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>73.2</v>
+      </c>
+      <c r="D63" s="7">
+        <v>71.67</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>5.42</v>
-      </c>
-      <c r="D19" s="6">
-        <v>4.57</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="D64" s="7">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E64" s="8">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.53</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.87</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>40.87</v>
+      </c>
+      <c r="D65" s="7">
+        <v>40.97</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.08</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>41.29</v>
+      </c>
+      <c r="D66" s="7">
+        <v>37.15</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.44</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2.35</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>52.72</v>
+      </c>
+      <c r="D67" s="7">
+        <v>49.55</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2.46</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>53.73</v>
+      </c>
+      <c r="D68" s="7">
+        <v>57.34</v>
+      </c>
+      <c r="E68" s="8">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4.29</v>
-      </c>
-      <c r="D24" s="6">
-        <v>2.91</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>64.36</v>
+      </c>
+      <c r="D69" s="7">
+        <v>63.34</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.2</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>53.73</v>
+      </c>
+      <c r="D70" s="7">
+        <v>50.88</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>23.71</v>
-      </c>
-      <c r="D26" s="6">
-        <v>22.95</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-67.55</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-78.33</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-10.78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>48.79</v>
-      </c>
-      <c r="D27" s="6">
-        <v>54.12</v>
-      </c>
-      <c r="E27" s="8">
-        <v>5.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>266.2</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-57.7</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-323.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>16.59</v>
-      </c>
-      <c r="D28" s="6">
-        <v>17.32</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-21.22</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-101.96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-7.57</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-24.28</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-16.04</v>
+      </c>
+      <c r="E74" s="8">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>4.61</v>
-      </c>
-      <c r="D30" s="6">
-        <v>5.03</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-38</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-127.49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-35.22</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-34.78</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>23.25</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-68.17</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-91.42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>11.72</v>
-      </c>
-      <c r="D32" s="6">
-        <v>10.73</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-50.37</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-48.19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>25.12</v>
-      </c>
-      <c r="D33" s="6">
-        <v>26.83</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>58.67</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-18.5</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-77.17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>11.18</v>
-      </c>
-      <c r="D34" s="6">
-        <v>10.14</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-6.01</v>
-      </c>
-      <c r="E35" s="8">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>22.91</v>
-      </c>
-      <c r="D36" s="6">
-        <v>25.56</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.7</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-3.08</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="D38" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="E38" s="8">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-8.59</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-6.11</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-10.94</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-4.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>23.39</v>
-      </c>
-      <c r="D41" s="6">
-        <v>22.76</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>2.42</v>
-      </c>
-      <c r="D42" s="6">
-        <v>4.66</v>
-      </c>
-      <c r="E42" s="8">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>55.16</v>
-      </c>
-      <c r="D43" s="6">
-        <v>57.43</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-36.34</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-36.73</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-17.54</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.46</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-46.62</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-47.06</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-1.78</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>0</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-12.08</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>641.4</v>
-      </c>
-      <c r="D52" s="6">
-        <v>637.55</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>302.45</v>
-      </c>
-      <c r="D53" s="6">
-        <v>310.25</v>
-      </c>
-      <c r="E53" s="8">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1175.4</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1170</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>712.95</v>
-      </c>
-      <c r="D55" s="6">
-        <v>705</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-7.95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>543.5</v>
-      </c>
-      <c r="D56" s="6">
-        <v>542.1</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11832</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11735</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>344.95</v>
-      </c>
-      <c r="D58" s="6">
-        <v>337.95</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1341</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1337.5</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>81.55</v>
-      </c>
-      <c r="D60" s="6">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>49.09</v>
-      </c>
-      <c r="D61" s="6">
-        <v>47.68</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>70.44</v>
-      </c>
-      <c r="D62" s="6">
-        <v>73.2</v>
-      </c>
-      <c r="E62" s="8">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>70.62</v>
-      </c>
-      <c r="D63" s="6">
-        <v>68.31999999999999</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>44.69</v>
-      </c>
-      <c r="D64" s="6">
-        <v>40.87</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-3.82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>42.19</v>
-      </c>
-      <c r="D65" s="6">
-        <v>41.29</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>54.74</v>
-      </c>
-      <c r="D66" s="6">
-        <v>52.72</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>60.37</v>
-      </c>
-      <c r="D67" s="6">
-        <v>53.73</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-6.64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>65.67</v>
-      </c>
-      <c r="D68" s="6">
-        <v>64.36</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>55.6</v>
-      </c>
-      <c r="D69" s="6">
-        <v>53.73</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="6">
-        <v>-77.06999999999999</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-67.55</v>
-      </c>
-      <c r="E70" s="8">
-        <v>9.52</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>578.3</v>
-      </c>
-      <c r="D71" s="6">
-        <v>266.2</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-312.1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>5.28</v>
-      </c>
-      <c r="D72" s="6">
-        <v>80.73999999999999</v>
-      </c>
-      <c r="E72" s="8">
-        <v>75.45999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-14.45</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-24.28</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-9.83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>122.11</v>
-      </c>
-      <c r="D74" s="6">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-32.62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>67.61</v>
-      </c>
-      <c r="D75" s="6">
-        <v>23.25</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-44.36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-37.67</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="E76" s="8">
-        <v>35.49</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="D77" s="6">
-        <v>58.67</v>
-      </c>
-      <c r="E77" s="8">
-        <v>43.89</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-91.09999999999999</v>
-      </c>
-      <c r="D78" s="6">
+      <c r="C79" s="7">
         <v>-92.63</v>
       </c>
-      <c r="E78" s="7">
-        <v>-1.53</v>
+      <c r="D79" s="7">
+        <v>-93.20999999999999</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -3439,60 +3457,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>64.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>55.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>54.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>80</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="12">
         <v>6.3</v>
       </c>
-      <c r="G2" s="11">
-        <v>9.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="12">
+        <v>10.1</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3594,61 +3612,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.4061999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3737</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3037</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2615</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1905</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1742</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1561</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0304</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0711</v>
+      <c r="A2" s="15">
+        <v>0.4075</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3659000000000001</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.31</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2571</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1864</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1686</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1528</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0375</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0776</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.3 → 70.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.3</t>
-  </si>
-  <si>
-    <t>70.1</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.7 → 49.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.7</t>
+    <t>49.5 → 57.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.5</t>
+  </si>
+  <si>
+    <t>57.5</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.5% → -2.5%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-0.5%</t>
+  </si>
+  <si>
+    <t>-2.5%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,7 +306,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -314,13 +321,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,19 +353,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,15 +818,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -959,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>635.85</v>
+        <v>631.35</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-0.71</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -971,46 +970,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.89</v>
+        <v>-37.34</v>
       </c>
       <c r="H2">
-        <v>73.16</v>
+        <v>71.94</v>
       </c>
       <c r="I2">
-        <v>-0.27</v>
+        <v>-0.86</v>
       </c>
       <c r="J2">
-        <v>0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="K2">
-        <v>-4.66</v>
+        <v>-3.63</v>
       </c>
       <c r="L2">
-        <v>22.56</v>
+        <v>24.88</v>
       </c>
       <c r="M2">
-        <v>-7.76</v>
+        <v>-7.79</v>
       </c>
       <c r="N2">
         <v>45</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>639.65</v>
+        <v>638.55</v>
       </c>
       <c r="Q2">
-        <v>638.24</v>
+        <v>638.5599999999999</v>
       </c>
       <c r="R2">
-        <v>645.51</v>
+        <v>644.4</v>
       </c>
       <c r="S2">
-        <v>620.47</v>
+        <v>620.83</v>
       </c>
       <c r="T2">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,34 +1024,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.04</v>
+        <v>45.31</v>
       </c>
       <c r="Z2">
-        <v>-2.39</v>
+        <v>-2.91</v>
       </c>
       <c r="AA2">
-        <v>-2.87</v>
+        <v>-2.88</v>
       </c>
       <c r="AB2">
-        <v>0.48</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>33.21</v>
+        <v>16.14</v>
       </c>
       <c r="AD2">
-        <v>43.95</v>
+        <v>32.1</v>
       </c>
       <c r="AE2">
-        <v>20.33</v>
+        <v>20.06</v>
       </c>
       <c r="AF2">
-        <v>-78.33</v>
+        <v>-63.98</v>
       </c>
       <c r="AG2">
-        <v>663.05</v>
+        <v>662.8099999999999</v>
       </c>
       <c r="AH2">
-        <v>613.4400000000001</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1061,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.98</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1071,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>308.6</v>
+        <v>309.65</v>
       </c>
       <c r="D3">
-        <v>-0.53</v>
+        <v>0.34</v>
       </c>
       <c r="E3">
         <v>310.25</v>
@@ -1084,46 +1083,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-0.53</v>
+        <v>-0.19</v>
       </c>
       <c r="H3">
-        <v>101.4</v>
+        <v>102.08</v>
       </c>
       <c r="I3">
-        <v>5.81</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>21.35</v>
+        <v>20.51</v>
       </c>
       <c r="K3">
-        <v>28.11</v>
+        <v>28.42</v>
       </c>
       <c r="L3">
-        <v>51.7</v>
+        <v>57.7</v>
       </c>
       <c r="M3">
-        <v>40.75</v>
+        <v>41.06</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>298.06</v>
+        <v>302.54</v>
       </c>
       <c r="Q3">
-        <v>276.79</v>
+        <v>279.3</v>
       </c>
       <c r="R3">
-        <v>267.41</v>
+        <v>268.39</v>
       </c>
       <c r="S3">
-        <v>212.22</v>
+        <v>212.91</v>
       </c>
       <c r="T3">
-        <v>45.42</v>
+        <v>45.44</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1138,34 +1137,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>71.67</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="Z3">
-        <v>10.57</v>
+        <v>11.53</v>
       </c>
       <c r="AA3">
-        <v>6.58</v>
+        <v>7.57</v>
       </c>
       <c r="AB3">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="AC3">
-        <v>97.2</v>
+        <v>96</v>
       </c>
       <c r="AD3">
-        <v>84.28</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="AE3">
-        <v>10.75</v>
+        <v>10.95</v>
       </c>
       <c r="AF3">
-        <v>-57.7</v>
+        <v>-14.02</v>
       </c>
       <c r="AG3">
-        <v>307.51</v>
+        <v>312.17</v>
       </c>
       <c r="AH3">
-        <v>246.07</v>
+        <v>246.44</v>
       </c>
       <c r="AI3">
         <v>276.86</v>
@@ -1174,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>48.74</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1184,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1179.2</v>
+        <v>1192.9</v>
       </c>
       <c r="D4">
-        <v>0.79</v>
+        <v>1.16</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1197,46 +1196,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-8.5</v>
+        <v>-7.44</v>
       </c>
       <c r="H4">
-        <v>24.68</v>
+        <v>26.13</v>
       </c>
       <c r="I4">
-        <v>4.56</v>
+        <v>3.82</v>
       </c>
       <c r="J4">
-        <v>7.82</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K4">
-        <v>-2.53</v>
+        <v>-0.87</v>
       </c>
       <c r="L4">
-        <v>18.37</v>
+        <v>22.08</v>
       </c>
       <c r="M4">
-        <v>25.71</v>
+        <v>26.27</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1165.54</v>
+        <v>1174.32</v>
       </c>
       <c r="Q4">
-        <v>1122.62</v>
+        <v>1127.01</v>
       </c>
       <c r="R4">
-        <v>1083.52</v>
+        <v>1084.62</v>
       </c>
       <c r="S4">
-        <v>1126.3</v>
+        <v>1126.86</v>
       </c>
       <c r="T4">
-        <v>4.7</v>
+        <v>5.86</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1251,34 +1250,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>70.09999999999999</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="Z4">
-        <v>22.48</v>
+        <v>24.93</v>
       </c>
       <c r="AA4">
-        <v>15.22</v>
+        <v>17.16</v>
       </c>
       <c r="AB4">
-        <v>7.27</v>
+        <v>7.77</v>
       </c>
       <c r="AC4">
         <v>95.31</v>
       </c>
       <c r="AD4">
-        <v>97.16</v>
+        <v>95.59</v>
       </c>
       <c r="AE4">
-        <v>24.88</v>
+        <v>26.1</v>
       </c>
       <c r="AF4">
-        <v>-21.22</v>
+        <v>-7.57</v>
       </c>
       <c r="AG4">
-        <v>1178.89</v>
+        <v>1190.73</v>
       </c>
       <c r="AH4">
-        <v>1066.34</v>
+        <v>1063.28</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1287,7 +1286,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>51</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>705.15</v>
+        <v>702.15</v>
       </c>
       <c r="D5">
-        <v>0.02</v>
+        <v>-0.43</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1310,46 +1309,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.44</v>
+        <v>-18.79</v>
       </c>
       <c r="H5">
-        <v>6.53</v>
+        <v>6.08</v>
       </c>
       <c r="I5">
-        <v>0.54</v>
+        <v>-0.04</v>
       </c>
       <c r="J5">
-        <v>-4.42</v>
+        <v>-4.44</v>
       </c>
       <c r="K5">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="L5">
-        <v>-11.35</v>
+        <v>-11.6</v>
       </c>
       <c r="M5">
-        <v>36.59</v>
+        <v>36.54</v>
       </c>
       <c r="N5">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O5">
         <v>41</v>
       </c>
       <c r="P5">
-        <v>705.38</v>
+        <v>705.33</v>
       </c>
       <c r="Q5">
-        <v>724.45</v>
+        <v>722.97</v>
       </c>
       <c r="R5">
-        <v>717.49</v>
+        <v>717.6</v>
       </c>
       <c r="S5">
-        <v>749.22</v>
+        <v>749.1</v>
       </c>
       <c r="T5">
-        <v>-5.88</v>
+        <v>-6.27</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1364,34 +1363,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.97</v>
+        <v>39.5</v>
       </c>
       <c r="Z5">
-        <v>-5.17</v>
+        <v>-5.76</v>
       </c>
       <c r="AA5">
-        <v>-1.67</v>
+        <v>-2.49</v>
       </c>
       <c r="AB5">
-        <v>-3.5</v>
+        <v>-3.28</v>
       </c>
       <c r="AC5">
-        <v>29.5</v>
+        <v>20.64</v>
       </c>
       <c r="AD5">
-        <v>22.45</v>
+        <v>24.12</v>
       </c>
       <c r="AE5">
-        <v>15.16</v>
+        <v>15.42</v>
       </c>
       <c r="AF5">
-        <v>-16.04</v>
+        <v>171.01</v>
       </c>
       <c r="AG5">
-        <v>753.51</v>
+        <v>753.45</v>
       </c>
       <c r="AH5">
-        <v>695.38</v>
+        <v>692.49</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1400,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.17</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>535.3</v>
+        <v>520.4</v>
       </c>
       <c r="D6">
-        <v>-1.25</v>
+        <v>-2.78</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1423,46 +1422,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-10.78</v>
+        <v>-13.27</v>
       </c>
       <c r="H6">
-        <v>22.06</v>
+        <v>18.66</v>
       </c>
       <c r="I6">
-        <v>-1.77</v>
+        <v>-4.46</v>
       </c>
       <c r="J6">
-        <v>-1.54</v>
+        <v>-6.18</v>
       </c>
       <c r="K6">
-        <v>-7.94</v>
+        <v>-11.28</v>
       </c>
       <c r="L6">
-        <v>3.01</v>
+        <v>1.77</v>
       </c>
       <c r="M6">
-        <v>16.86</v>
+        <v>15.07</v>
       </c>
       <c r="N6">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>542.8</v>
+        <v>537.9400000000001</v>
       </c>
       <c r="Q6">
-        <v>554.79</v>
+        <v>552.36</v>
       </c>
       <c r="R6">
-        <v>556.45</v>
+        <v>555.46</v>
       </c>
       <c r="S6">
-        <v>520.05</v>
+        <v>520.02</v>
       </c>
       <c r="T6">
-        <v>2.93</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1477,43 +1476,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.15</v>
+        <v>30.03</v>
       </c>
       <c r="Z6">
-        <v>-4.73</v>
+        <v>-6.46</v>
       </c>
       <c r="AA6">
+        <v>-3.59</v>
+      </c>
+      <c r="AB6">
         <v>-2.87</v>
       </c>
-      <c r="AB6">
-        <v>-1.85</v>
-      </c>
       <c r="AC6">
-        <v>5.08</v>
+        <v>1.82</v>
       </c>
       <c r="AD6">
-        <v>11.21</v>
+        <v>6.78</v>
       </c>
       <c r="AE6">
-        <v>11.2</v>
+        <v>11.59</v>
       </c>
       <c r="AF6">
-        <v>-38</v>
+        <v>271.88</v>
       </c>
       <c r="AG6">
-        <v>577.9</v>
+        <v>579.11</v>
       </c>
       <c r="AH6">
-        <v>531.6799999999999</v>
+        <v>525.61</v>
       </c>
       <c r="AI6">
-        <v>571.73</v>
+        <v>563.47</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.02</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11578</v>
+        <v>12027</v>
       </c>
       <c r="D7">
-        <v>-1.34</v>
+        <v>3.88</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1536,46 +1535,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.76</v>
+        <v>-45.74</v>
       </c>
       <c r="H7">
-        <v>8.66</v>
+        <v>12.88</v>
       </c>
       <c r="I7">
-        <v>2.56</v>
+        <v>7.76</v>
       </c>
       <c r="J7">
-        <v>3.41</v>
+        <v>6.84</v>
       </c>
       <c r="K7">
-        <v>-10.13</v>
+        <v>-3.95</v>
       </c>
       <c r="L7">
-        <v>-36.05</v>
+        <v>-32.86</v>
       </c>
       <c r="M7">
-        <v>18.64</v>
+        <v>19.6</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>11550.4</v>
+        <v>11723.6</v>
       </c>
       <c r="Q7">
-        <v>11736.6</v>
+        <v>11737.15</v>
       </c>
       <c r="R7">
-        <v>11621.64</v>
+        <v>11610.62</v>
       </c>
       <c r="S7">
-        <v>14918.86</v>
+        <v>14895.06</v>
       </c>
       <c r="T7">
-        <v>-22.39</v>
+        <v>-19.26</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1590,34 +1589,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>49.55</v>
+        <v>57.45</v>
       </c>
       <c r="Z7">
-        <v>-16.04</v>
+        <v>20.76</v>
       </c>
       <c r="AA7">
-        <v>-20.41</v>
+        <v>-12.17</v>
       </c>
       <c r="AB7">
-        <v>4.37</v>
+        <v>32.93</v>
       </c>
       <c r="AC7">
-        <v>71.04000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="AD7">
-        <v>57.32</v>
+        <v>70.91</v>
       </c>
       <c r="AE7">
-        <v>393.52</v>
+        <v>433.76</v>
       </c>
       <c r="AF7">
-        <v>-68.17</v>
+        <v>186.37</v>
       </c>
       <c r="AG7">
-        <v>12368.6</v>
+        <v>12370.19</v>
       </c>
       <c r="AH7">
-        <v>11104.6</v>
+        <v>11104.11</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1626,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>22.14</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>342.95</v>
+        <v>340</v>
       </c>
       <c r="D8">
-        <v>1.48</v>
+        <v>-0.86</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1649,25 +1648,25 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.35</v>
+        <v>-3.19</v>
       </c>
       <c r="H8">
-        <v>46.37</v>
+        <v>45.11</v>
       </c>
       <c r="I8">
-        <v>2.16</v>
+        <v>-0.06</v>
       </c>
       <c r="J8">
-        <v>7.49</v>
+        <v>8.83</v>
       </c>
       <c r="K8">
-        <v>25.21</v>
+        <v>23.32</v>
       </c>
       <c r="L8">
-        <v>13.09</v>
+        <v>14.63</v>
       </c>
       <c r="M8">
-        <v>31</v>
+        <v>30.51</v>
       </c>
       <c r="N8">
         <v>77</v>
@@ -1676,19 +1675,19 @@
         <v>77</v>
       </c>
       <c r="P8">
-        <v>342</v>
+        <v>341.96</v>
       </c>
       <c r="Q8">
-        <v>336.82</v>
+        <v>337.37</v>
       </c>
       <c r="R8">
-        <v>331.04</v>
+        <v>331.68</v>
       </c>
       <c r="S8">
-        <v>284.34</v>
+        <v>284.62</v>
       </c>
       <c r="T8">
-        <v>20.61</v>
+        <v>19.46</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1703,34 +1702,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.34</v>
+        <v>54.63</v>
       </c>
       <c r="Z8">
-        <v>3.87</v>
+        <v>3.71</v>
       </c>
       <c r="AA8">
         <v>3.7</v>
       </c>
       <c r="AB8">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="AC8">
-        <v>60.58</v>
+        <v>46.86</v>
       </c>
       <c r="AD8">
-        <v>67.14</v>
+        <v>57.89</v>
       </c>
       <c r="AE8">
-        <v>9.26</v>
+        <v>9.02</v>
       </c>
       <c r="AF8">
-        <v>-50.37</v>
+        <v>-71.09</v>
       </c>
       <c r="AG8">
-        <v>349.13</v>
+        <v>349.18</v>
       </c>
       <c r="AH8">
-        <v>324.51</v>
+        <v>325.56</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1739,7 +1738,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.15</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1334.9</v>
+        <v>1307.7</v>
       </c>
       <c r="D9">
-        <v>-0.19</v>
+        <v>-2.04</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1762,46 +1761,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-0.45</v>
+        <v>-2.48</v>
       </c>
       <c r="H9">
-        <v>30.03</v>
+        <v>27.38</v>
       </c>
       <c r="I9">
-        <v>3.18</v>
+        <v>-1.45</v>
       </c>
       <c r="J9">
-        <v>5.04</v>
+        <v>2.97</v>
       </c>
       <c r="K9">
-        <v>2.73</v>
+        <v>-0.24</v>
       </c>
       <c r="L9">
-        <v>26.2</v>
+        <v>24.89</v>
       </c>
       <c r="M9">
-        <v>15.28</v>
+        <v>14.75</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1332.14</v>
+        <v>1328.28</v>
       </c>
       <c r="Q9">
-        <v>1300.73</v>
+        <v>1301.5</v>
       </c>
       <c r="R9">
-        <v>1267.13</v>
+        <v>1267.53</v>
       </c>
       <c r="S9">
-        <v>1222.03</v>
+        <v>1222.66</v>
       </c>
       <c r="T9">
-        <v>9.24</v>
+        <v>6.96</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1816,34 +1815,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>63.34</v>
+        <v>53.81</v>
       </c>
       <c r="Z9">
-        <v>17.19</v>
+        <v>15.58</v>
       </c>
       <c r="AA9">
-        <v>12.42</v>
+        <v>13.05</v>
       </c>
       <c r="AB9">
-        <v>4.77</v>
+        <v>2.53</v>
       </c>
       <c r="AC9">
-        <v>93</v>
+        <v>70.16</v>
       </c>
       <c r="AD9">
-        <v>90.03</v>
+        <v>85.14</v>
       </c>
       <c r="AE9">
-        <v>25.09</v>
+        <v>25.55</v>
       </c>
       <c r="AF9">
-        <v>-18.5</v>
+        <v>13.43</v>
       </c>
       <c r="AG9">
-        <v>1348.85</v>
+        <v>1349.55</v>
       </c>
       <c r="AH9">
-        <v>1252.6</v>
+        <v>1253.44</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1852,7 +1851,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>45.04</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>78.63</v>
+        <v>80.84</v>
       </c>
       <c r="D10">
-        <v>-2.2</v>
+        <v>2.81</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1875,46 +1874,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-14.02</v>
+        <v>-11.6</v>
       </c>
       <c r="H10">
-        <v>117.93</v>
+        <v>124.06</v>
       </c>
       <c r="I10">
-        <v>-2.79</v>
+        <v>-4.61</v>
       </c>
       <c r="J10">
-        <v>16.94</v>
+        <v>21.24</v>
       </c>
       <c r="K10">
-        <v>58.46</v>
+        <v>60.65</v>
       </c>
       <c r="L10">
-        <v>8.41</v>
+        <v>9.1</v>
       </c>
       <c r="M10">
-        <v>-3.75</v>
+        <v>-3.15</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>81.44</v>
+        <v>80.66</v>
       </c>
       <c r="Q10">
-        <v>84.14</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="R10">
-        <v>67.73999999999999</v>
+        <v>68.27</v>
       </c>
       <c r="S10">
-        <v>59.63</v>
+        <v>59.65</v>
       </c>
       <c r="T10">
-        <v>31.86</v>
+        <v>35.52</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1929,34 +1928,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>50.88</v>
+        <v>54.15</v>
       </c>
       <c r="Z10">
-        <v>3.51</v>
+        <v>3.17</v>
       </c>
       <c r="AA10">
-        <v>5.32</v>
+        <v>4.89</v>
       </c>
       <c r="AB10">
-        <v>-1.81</v>
+        <v>-1.72</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AD10">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>4.52</v>
+        <v>4.44</v>
       </c>
       <c r="AF10">
-        <v>-93.20999999999999</v>
+        <v>-95.48</v>
       </c>
       <c r="AG10">
-        <v>91.17</v>
+        <v>91.12</v>
       </c>
       <c r="AH10">
-        <v>77.09999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1965,7 +1964,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>26.07</v>
+        <v>23.69</v>
       </c>
     </row>
   </sheetData>
@@ -2106,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2146,7 +2145,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2166,7 +2165,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>62</v>
@@ -2218,13 +2217,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="7">
-        <v>0.09</v>
+        <v>0.97</v>
       </c>
       <c r="D8" s="7">
-        <v>0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="E8" s="8">
-        <v>0.88</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2235,13 +2234,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>20.44</v>
+        <v>21.35</v>
       </c>
       <c r="D9" s="7">
-        <v>21.35</v>
+        <v>20.51</v>
       </c>
       <c r="E9" s="8">
-        <v>0.91</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2252,13 +2251,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>7.47</v>
+        <v>7.82</v>
       </c>
       <c r="D10" s="7">
-        <v>7.82</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.35</v>
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.39</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2269,13 +2268,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-3.23</v>
+        <v>-4.42</v>
       </c>
       <c r="D11" s="7">
-        <v>-4.42</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.19</v>
+        <v>-4.44</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2286,13 +2285,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-0.66</v>
+        <v>-1.54</v>
       </c>
       <c r="D12" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.88</v>
+        <v>-6.18</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-4.64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2303,13 +2302,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>5.12</v>
+        <v>3.41</v>
       </c>
       <c r="D13" s="7">
-        <v>3.41</v>
+        <v>6.84</v>
       </c>
       <c r="E13" s="9">
-        <v>-1.71</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2320,13 +2319,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>6.76</v>
+        <v>7.49</v>
       </c>
       <c r="D14" s="7">
-        <v>7.49</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.73</v>
+        <v>8.83</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2337,13 +2336,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
       <c r="D15" s="7">
-        <v>5.04</v>
+        <v>2.97</v>
       </c>
       <c r="E15" s="8">
-        <v>0.27</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2354,13 +2353,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>15.82</v>
+        <v>16.94</v>
       </c>
       <c r="D16" s="7">
-        <v>16.94</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.12</v>
+        <v>21.24</v>
+      </c>
+      <c r="E16" s="9">
+        <v>4.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2371,13 +2370,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>0.09</v>
+        <v>-0.27</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.27</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.36</v>
+        <v>-0.86</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2388,13 +2387,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>15.01</v>
+        <v>5.81</v>
       </c>
       <c r="D18" s="7">
-        <v>5.81</v>
+        <v>7.8</v>
       </c>
       <c r="E18" s="9">
-        <v>-9.199999999999999</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2405,13 +2404,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="D19" s="7">
-        <v>4.56</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.01</v>
+        <v>3.82</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2422,13 +2421,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.87</v>
+        <v>0.54</v>
       </c>
       <c r="D20" s="7">
-        <v>0.54</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" s="8">
-        <v>2.41</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2439,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>0.02</v>
+        <v>-1.77</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.77</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.79</v>
+        <v>-4.46</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2456,13 +2455,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="D22" s="7">
-        <v>2.56</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.21</v>
+        <v>7.76</v>
+      </c>
+      <c r="E22" s="9">
+        <v>5.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2473,13 +2472,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="D23" s="7">
-        <v>2.16</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.3</v>
+        <v>-0.06</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2490,13 +2489,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="D24" s="7">
-        <v>3.18</v>
+        <v>-1.45</v>
       </c>
       <c r="E24" s="8">
-        <v>0.27</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2507,13 +2506,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.91</v>
+        <v>-2.79</v>
       </c>
       <c r="D25" s="7">
-        <v>-2.79</v>
+        <v>-4.61</v>
       </c>
       <c r="E25" s="8">
-        <v>0.12</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2524,13 +2523,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>22.95</v>
+        <v>22.56</v>
       </c>
       <c r="D26" s="7">
-        <v>22.56</v>
+        <v>24.88</v>
       </c>
       <c r="E26" s="9">
-        <v>-0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2541,13 +2540,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>54.12</v>
+        <v>51.7</v>
       </c>
       <c r="D27" s="7">
-        <v>51.7</v>
+        <v>57.7</v>
       </c>
       <c r="E27" s="9">
-        <v>-2.42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2558,13 +2557,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>17.32</v>
+        <v>18.37</v>
       </c>
       <c r="D28" s="7">
-        <v>18.37</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.05</v>
+        <v>22.08</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.71</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2575,13 +2574,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>-9.220000000000001</v>
+        <v>-11.35</v>
       </c>
       <c r="D29" s="7">
-        <v>-11.35</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-2.13</v>
+        <v>-11.6</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2592,13 +2591,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>5.03</v>
+        <v>3.01</v>
       </c>
       <c r="D30" s="7">
-        <v>3.01</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-2.02</v>
+        <v>1.77</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2609,13 +2608,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-34.78</v>
+        <v>-36.05</v>
       </c>
       <c r="D31" s="7">
-        <v>-36.05</v>
+        <v>-32.86</v>
       </c>
       <c r="E31" s="9">
-        <v>-1.27</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2626,13 +2625,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>10.73</v>
+        <v>13.09</v>
       </c>
       <c r="D32" s="7">
-        <v>13.09</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.36</v>
+        <v>14.63</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.54</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2643,13 +2642,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>26.83</v>
+        <v>26.2</v>
       </c>
       <c r="D33" s="7">
-        <v>26.2</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.63</v>
+        <v>24.89</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2660,13 +2659,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>10.14</v>
+        <v>8.41</v>
       </c>
       <c r="D34" s="7">
-        <v>8.41</v>
+        <v>9.1</v>
       </c>
       <c r="E34" s="9">
-        <v>-1.73</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2677,13 +2676,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>-6.01</v>
+        <v>-4.66</v>
       </c>
       <c r="D35" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.35</v>
+        <v>-3.63</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.03</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2694,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>25.56</v>
+        <v>28.11</v>
       </c>
       <c r="D36" s="7">
-        <v>28.11</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.55</v>
+        <v>28.42</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.31</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2711,13 +2710,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-3.08</v>
+        <v>-2.53</v>
       </c>
       <c r="D37" s="7">
-        <v>-2.53</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.55</v>
+        <v>-0.87</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1.66</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2728,13 +2727,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="D38" s="7">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="E38" s="9">
-        <v>-1.57</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2745,13 +2744,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-8.59</v>
+        <v>-7.94</v>
       </c>
       <c r="D39" s="7">
-        <v>-7.94</v>
+        <v>-11.28</v>
       </c>
       <c r="E39" s="8">
-        <v>0.65</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2762,13 +2761,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-10.94</v>
+        <v>-10.13</v>
       </c>
       <c r="D40" s="7">
-        <v>-10.13</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.8100000000000001</v>
+        <v>-3.95</v>
+      </c>
+      <c r="E40" s="9">
+        <v>6.18</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2779,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>22.76</v>
+        <v>25.21</v>
       </c>
       <c r="D41" s="7">
-        <v>25.21</v>
+        <v>23.32</v>
       </c>
       <c r="E41" s="8">
-        <v>2.45</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2796,13 +2795,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>4.66</v>
+        <v>2.73</v>
       </c>
       <c r="D42" s="7">
-        <v>2.73</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.93</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2813,13 +2812,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>57.43</v>
+        <v>58.46</v>
       </c>
       <c r="D43" s="7">
-        <v>58.46</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.03</v>
+        <v>60.65</v>
+      </c>
+      <c r="E43" s="9">
+        <v>2.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2830,13 +2829,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-36.73</v>
+        <v>-36.89</v>
       </c>
       <c r="D44" s="7">
-        <v>-36.89</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.16</v>
+        <v>-37.34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2847,13 +2846,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.53</v>
+        <v>-0.19</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.53</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2864,13 +2863,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-9.220000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="D46" s="7">
-        <v>-8.5</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.72</v>
+        <v>-7.44</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.06</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2881,13 +2880,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-18.46</v>
+        <v>-18.44</v>
       </c>
       <c r="D47" s="7">
-        <v>-18.44</v>
+        <v>-18.79</v>
       </c>
       <c r="E47" s="8">
-        <v>0.02</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2898,13 +2897,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-9.65</v>
+        <v>-10.78</v>
       </c>
       <c r="D48" s="7">
-        <v>-10.78</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.13</v>
+        <v>-13.27</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2915,13 +2914,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-47.06</v>
+        <v>-47.76</v>
       </c>
       <c r="D49" s="7">
-        <v>-47.76</v>
+        <v>-45.74</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.7</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2932,13 +2931,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-3.77</v>
+        <v>-2.35</v>
       </c>
       <c r="D50" s="7">
-        <v>-2.35</v>
+        <v>-3.19</v>
       </c>
       <c r="E50" s="8">
-        <v>1.42</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2949,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-0.26</v>
+        <v>-0.45</v>
       </c>
       <c r="D51" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.19</v>
+        <v>-2.48</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2966,13 +2965,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-12.08</v>
+        <v>-14.02</v>
       </c>
       <c r="D52" s="7">
-        <v>-14.02</v>
+        <v>-11.6</v>
       </c>
       <c r="E52" s="9">
-        <v>-1.94</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2983,13 +2982,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>637.55</v>
+        <v>635.85</v>
       </c>
       <c r="D53" s="7">
-        <v>635.85</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.7</v>
+        <v>631.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3000,13 +2999,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>310.25</v>
+        <v>308.6</v>
       </c>
       <c r="D54" s="7">
-        <v>308.6</v>
+        <v>309.65</v>
       </c>
       <c r="E54" s="9">
-        <v>-1.65</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3017,13 +3016,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>1170</v>
+        <v>1179.2</v>
       </c>
       <c r="D55" s="7">
-        <v>1179.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>9.199999999999999</v>
+        <v>1192.9</v>
+      </c>
+      <c r="E55" s="9">
+        <v>13.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3034,13 +3033,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>705</v>
+        <v>705.15</v>
       </c>
       <c r="D56" s="7">
-        <v>705.15</v>
+        <v>702.15</v>
       </c>
       <c r="E56" s="8">
-        <v>0.15</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3051,13 +3050,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>542.1</v>
+        <v>535.3</v>
       </c>
       <c r="D57" s="7">
-        <v>535.3</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-6.8</v>
+        <v>520.4</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-14.9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3068,13 +3067,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>11735</v>
+        <v>11578</v>
       </c>
       <c r="D58" s="7">
-        <v>11578</v>
+        <v>12027</v>
       </c>
       <c r="E58" s="9">
-        <v>-157</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3085,13 +3084,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>337.95</v>
+        <v>342.95</v>
       </c>
       <c r="D59" s="7">
-        <v>342.95</v>
+        <v>340</v>
       </c>
       <c r="E59" s="8">
-        <v>5</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3102,13 +3101,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>1337.5</v>
+        <v>1334.9</v>
       </c>
       <c r="D60" s="7">
-        <v>1334.9</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.6</v>
+        <v>1307.7</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-27.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3119,319 +3118,353 @@
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>80.40000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="D61" s="7">
-        <v>78.63</v>
+        <v>80.84</v>
       </c>
       <c r="E61" s="9">
-        <v>-1.77</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="7">
-        <v>47.68</v>
+        <v>23</v>
       </c>
       <c r="D62" s="7">
-        <v>47.04</v>
+        <v>34</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="7">
-        <v>73.2</v>
+        <v>34</v>
       </c>
       <c r="D63" s="7">
-        <v>71.67</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-1.53</v>
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>68.31999999999999</v>
+        <v>47.04</v>
       </c>
       <c r="D64" s="7">
-        <v>70.09999999999999</v>
+        <v>45.31</v>
       </c>
       <c r="E64" s="8">
-        <v>1.78</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>40.87</v>
+        <v>71.67</v>
       </c>
       <c r="D65" s="7">
-        <v>40.97</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.1</v>
+        <v>72.06999999999999</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>41.29</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D66" s="7">
-        <v>37.15</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="E66" s="9">
-        <v>-4.14</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>52.72</v>
+        <v>40.97</v>
       </c>
       <c r="D67" s="7">
-        <v>49.55</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-3.17</v>
+        <v>39.5</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>53.73</v>
+        <v>37.15</v>
       </c>
       <c r="D68" s="7">
-        <v>57.34</v>
+        <v>30.03</v>
       </c>
       <c r="E68" s="8">
-        <v>3.61</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>64.36</v>
+        <v>49.55</v>
       </c>
       <c r="D69" s="7">
-        <v>63.34</v>
+        <v>57.45</v>
       </c>
       <c r="E69" s="9">
-        <v>-1.02</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>53.73</v>
+        <v>57.34</v>
       </c>
       <c r="D70" s="7">
-        <v>50.88</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-2.85</v>
+        <v>54.63</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>-67.55</v>
+        <v>63.34</v>
       </c>
       <c r="D71" s="7">
-        <v>-78.33</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-10.78</v>
+        <v>53.81</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-9.529999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>266.2</v>
+        <v>50.88</v>
       </c>
       <c r="D72" s="7">
-        <v>-57.7</v>
+        <v>54.15</v>
       </c>
       <c r="E72" s="9">
-        <v>-323.9</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="7">
-        <v>80.73999999999999</v>
+        <v>-78.33</v>
       </c>
       <c r="D73" s="7">
-        <v>-21.22</v>
+        <v>-63.98</v>
       </c>
       <c r="E73" s="9">
-        <v>-101.96</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>-24.28</v>
+        <v>-57.7</v>
       </c>
       <c r="D74" s="7">
-        <v>-16.04</v>
-      </c>
-      <c r="E74" s="8">
-        <v>8.24</v>
+        <v>-14.02</v>
+      </c>
+      <c r="E74" s="9">
+        <v>43.68</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>89.48999999999999</v>
+        <v>-21.22</v>
       </c>
       <c r="D75" s="7">
-        <v>-38</v>
+        <v>-7.57</v>
       </c>
       <c r="E75" s="9">
-        <v>-127.49</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>23.25</v>
+        <v>-16.04</v>
       </c>
       <c r="D76" s="7">
-        <v>-68.17</v>
+        <v>171.01</v>
       </c>
       <c r="E76" s="9">
-        <v>-91.42</v>
+        <v>187.05</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-2.18</v>
+        <v>-38</v>
       </c>
       <c r="D77" s="7">
-        <v>-50.37</v>
+        <v>271.88</v>
       </c>
       <c r="E77" s="9">
-        <v>-48.19</v>
+        <v>309.88</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>58.67</v>
+        <v>-68.17</v>
       </c>
       <c r="D78" s="7">
-        <v>-18.5</v>
+        <v>186.37</v>
       </c>
       <c r="E78" s="9">
-        <v>-77.17</v>
+        <v>254.54</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-92.63</v>
+        <v>-50.37</v>
       </c>
       <c r="D79" s="7">
+        <v>-71.09</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-20.72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-18.5</v>
+      </c>
+      <c r="D80" s="7">
+        <v>13.43</v>
+      </c>
+      <c r="E80" s="9">
+        <v>31.93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
         <v>-93.20999999999999</v>
       </c>
-      <c r="E79" s="9">
-        <v>-0.58</v>
+      <c r="D81" s="7">
+        <v>-95.48</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-2.27</v>
       </c>
     </row>
   </sheetData>
@@ -3496,16 +3529,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>54.2</v>
+        <v>53.3</v>
       </c>
       <c r="E2" s="12">
         <v>80</v>
       </c>
       <c r="F2" s="12">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="G2" s="12">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3642,31 +3675,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4075</v>
+        <v>0.4106</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3659000000000001</v>
+        <v>0.3654</v>
       </c>
       <c r="C2" s="15">
-        <v>0.31</v>
+        <v>0.3051</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2571</v>
+        <v>0.2627</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1864</v>
+        <v>0.196</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1686</v>
+        <v>0.1507</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1528</v>
+        <v>0.1475</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0375</v>
+        <v>-0.0315</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0776</v>
+        <v>-0.0779</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,31 +196,40 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.5 → 57.5</t>
+    <t>45.3 → 64.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>57.5</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.5% → -2.5%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.5%</t>
-  </si>
-  <si>
-    <t>-2.5%</t>
+    <t>45.3</t>
+  </si>
+  <si>
+    <t>64.9</t>
+  </si>
+  <si>
+    <t>39.5 → 57.1</t>
+  </si>
+  <si>
+    <t>39.5</t>
+  </si>
+  <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.6 → 59.8</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>72.6</t>
+  </si>
+  <si>
+    <t>59.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -446,8 +455,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,8 +827,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -958,10 +967,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>631.35</v>
+        <v>694.45</v>
       </c>
       <c r="D2">
-        <v>-0.71</v>
+        <v>9.99</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -970,46 +979,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-37.34</v>
+        <v>-31.08</v>
       </c>
       <c r="H2">
-        <v>71.94</v>
+        <v>89.12</v>
       </c>
       <c r="I2">
-        <v>-0.86</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>-0.31</v>
+        <v>11.11</v>
       </c>
       <c r="K2">
-        <v>-3.63</v>
+        <v>6.61</v>
       </c>
       <c r="L2">
-        <v>24.88</v>
+        <v>34.85</v>
       </c>
       <c r="M2">
-        <v>-7.79</v>
+        <v>-5.78</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>638.55</v>
+        <v>648.12</v>
       </c>
       <c r="Q2">
-        <v>638.5599999999999</v>
+        <v>642.04</v>
       </c>
       <c r="R2">
-        <v>644.4</v>
+        <v>644.9</v>
       </c>
       <c r="S2">
-        <v>620.83</v>
+        <v>621.51</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>11.74</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1024,34 +1033,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.31</v>
+        <v>64.87</v>
       </c>
       <c r="Z2">
-        <v>-2.91</v>
+        <v>1.74</v>
       </c>
       <c r="AA2">
-        <v>-2.88</v>
+        <v>-1.96</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>3.7</v>
       </c>
       <c r="AC2">
-        <v>16.14</v>
+        <v>40.21</v>
       </c>
       <c r="AD2">
-        <v>32.1</v>
+        <v>29.86</v>
       </c>
       <c r="AE2">
-        <v>20.06</v>
+        <v>23.93</v>
       </c>
       <c r="AF2">
-        <v>-63.98</v>
+        <v>475.16</v>
       </c>
       <c r="AG2">
-        <v>662.8099999999999</v>
+        <v>676.02</v>
       </c>
       <c r="AH2">
-        <v>614.3099999999999</v>
+        <v>608.0599999999999</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1060,7 +1069,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.75</v>
+        <v>32.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1071,10 +1080,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>309.65</v>
+        <v>309.75</v>
       </c>
       <c r="D3">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
       <c r="E3">
         <v>310.25</v>
@@ -1083,25 +1092,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="H3">
-        <v>102.08</v>
+        <v>102.15</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>9.94</v>
       </c>
       <c r="J3">
-        <v>20.51</v>
+        <v>19.46</v>
       </c>
       <c r="K3">
-        <v>28.42</v>
+        <v>23.47</v>
       </c>
       <c r="L3">
-        <v>57.7</v>
+        <v>56.55</v>
       </c>
       <c r="M3">
-        <v>41.06</v>
+        <v>40.98</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1110,19 +1119,19 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>302.54</v>
+        <v>308.14</v>
       </c>
       <c r="Q3">
-        <v>279.3</v>
+        <v>281.57</v>
       </c>
       <c r="R3">
-        <v>268.39</v>
+        <v>269.47</v>
       </c>
       <c r="S3">
-        <v>212.91</v>
+        <v>213.61</v>
       </c>
       <c r="T3">
-        <v>45.44</v>
+        <v>45.01</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1137,43 +1146,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>72.06999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="Z3">
-        <v>11.53</v>
+        <v>12.16</v>
       </c>
       <c r="AA3">
-        <v>7.57</v>
+        <v>8.49</v>
       </c>
       <c r="AB3">
-        <v>3.96</v>
+        <v>3.67</v>
       </c>
       <c r="AC3">
-        <v>96</v>
+        <v>94.36</v>
       </c>
       <c r="AD3">
-        <v>91.70999999999999</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="AE3">
-        <v>10.95</v>
+        <v>11.1</v>
       </c>
       <c r="AF3">
-        <v>-14.02</v>
+        <v>44.96</v>
       </c>
       <c r="AG3">
-        <v>312.17</v>
+        <v>316.31</v>
       </c>
       <c r="AH3">
-        <v>246.44</v>
+        <v>246.84</v>
       </c>
       <c r="AI3">
-        <v>276.86</v>
+        <v>279.64</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>49.93</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1184,10 +1193,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1192.9</v>
+        <v>1160</v>
       </c>
       <c r="D4">
-        <v>1.16</v>
+        <v>-2.76</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1196,46 +1205,46 @@
         <v>945.8</v>
       </c>
       <c r="G4">
-        <v>-7.44</v>
+        <v>-9.99</v>
       </c>
       <c r="H4">
-        <v>26.13</v>
+        <v>22.65</v>
       </c>
       <c r="I4">
-        <v>3.82</v>
+        <v>0.51</v>
       </c>
       <c r="J4">
-        <v>8.210000000000001</v>
+        <v>4.97</v>
       </c>
       <c r="K4">
-        <v>-0.87</v>
+        <v>-4.24</v>
       </c>
       <c r="L4">
-        <v>22.08</v>
+        <v>20.24</v>
       </c>
       <c r="M4">
-        <v>26.27</v>
+        <v>25.98</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>1174.32</v>
+        <v>1175.5</v>
       </c>
       <c r="Q4">
-        <v>1127.01</v>
+        <v>1128.81</v>
       </c>
       <c r="R4">
-        <v>1084.62</v>
+        <v>1085.18</v>
       </c>
       <c r="S4">
-        <v>1126.86</v>
+        <v>1127.22</v>
       </c>
       <c r="T4">
-        <v>5.86</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1250,34 +1259,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>72.56999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="Z4">
-        <v>24.93</v>
+        <v>23.93</v>
       </c>
       <c r="AA4">
-        <v>17.16</v>
+        <v>18.51</v>
       </c>
       <c r="AB4">
-        <v>7.77</v>
+        <v>5.42</v>
       </c>
       <c r="AC4">
-        <v>95.31</v>
+        <v>79.67</v>
       </c>
       <c r="AD4">
-        <v>95.59</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AE4">
-        <v>26.1</v>
+        <v>27.52</v>
       </c>
       <c r="AF4">
-        <v>-7.57</v>
+        <v>-37.43</v>
       </c>
       <c r="AG4">
-        <v>1190.73</v>
+        <v>1194.19</v>
       </c>
       <c r="AH4">
-        <v>1063.28</v>
+        <v>1063.42</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1286,7 +1295,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>49.08</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1297,10 +1306,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>702.15</v>
+        <v>734</v>
       </c>
       <c r="D5">
-        <v>-0.43</v>
+        <v>4.54</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1309,46 +1318,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.79</v>
+        <v>-15.1</v>
       </c>
       <c r="H5">
-        <v>6.08</v>
+        <v>10.89</v>
       </c>
       <c r="I5">
-        <v>-0.04</v>
+        <v>4.65</v>
       </c>
       <c r="J5">
-        <v>-4.44</v>
+        <v>0.31</v>
       </c>
       <c r="K5">
-        <v>2.31</v>
+        <v>7.68</v>
       </c>
       <c r="L5">
-        <v>-11.6</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="M5">
-        <v>36.54</v>
+        <v>38.29</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>705.33</v>
+        <v>711.85</v>
       </c>
       <c r="Q5">
-        <v>722.97</v>
+        <v>722.89</v>
       </c>
       <c r="R5">
-        <v>717.6</v>
+        <v>718.11</v>
       </c>
       <c r="S5">
-        <v>749.1</v>
+        <v>749.08</v>
       </c>
       <c r="T5">
-        <v>-6.27</v>
+        <v>-2.01</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1363,34 +1372,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.5</v>
+        <v>57.13</v>
       </c>
       <c r="Z5">
-        <v>-5.76</v>
+        <v>-3.62</v>
       </c>
       <c r="AA5">
-        <v>-2.49</v>
+        <v>-2.71</v>
       </c>
       <c r="AB5">
-        <v>-3.28</v>
+        <v>-0.91</v>
       </c>
       <c r="AC5">
-        <v>20.64</v>
+        <v>46.37</v>
       </c>
       <c r="AD5">
-        <v>24.12</v>
+        <v>32.17</v>
       </c>
       <c r="AE5">
-        <v>15.42</v>
+        <v>17.04</v>
       </c>
       <c r="AF5">
-        <v>171.01</v>
+        <v>169.21</v>
       </c>
       <c r="AG5">
-        <v>753.45</v>
+        <v>753.23</v>
       </c>
       <c r="AH5">
-        <v>692.49</v>
+        <v>692.54</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1399,7 +1408,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>19.61</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1410,10 +1419,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>520.4</v>
+        <v>518</v>
       </c>
       <c r="D6">
-        <v>-2.78</v>
+        <v>-0.46</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1422,46 +1431,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-13.27</v>
+        <v>-13.67</v>
       </c>
       <c r="H6">
-        <v>18.66</v>
+        <v>18.11</v>
       </c>
       <c r="I6">
-        <v>-4.46</v>
+        <v>-5.54</v>
       </c>
       <c r="J6">
-        <v>-6.18</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K6">
-        <v>-11.28</v>
+        <v>-10.42</v>
       </c>
       <c r="L6">
-        <v>1.77</v>
+        <v>4.44</v>
       </c>
       <c r="M6">
-        <v>15.07</v>
+        <v>15.8</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>537.9400000000001</v>
+        <v>531.86</v>
       </c>
       <c r="Q6">
-        <v>552.36</v>
+        <v>549.86</v>
       </c>
       <c r="R6">
-        <v>555.46</v>
+        <v>554.1799999999999</v>
       </c>
       <c r="S6">
-        <v>520.02</v>
+        <v>519.97</v>
       </c>
       <c r="T6">
-        <v>0.07000000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1473,46 +1482,46 @@
         <v>47</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>30.03</v>
+        <v>29.07</v>
       </c>
       <c r="Z6">
-        <v>-6.46</v>
+        <v>-7.94</v>
       </c>
       <c r="AA6">
-        <v>-3.59</v>
+        <v>-4.46</v>
       </c>
       <c r="AB6">
-        <v>-2.87</v>
+        <v>-3.48</v>
       </c>
       <c r="AC6">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>6.78</v>
+        <v>2.3</v>
       </c>
       <c r="AE6">
-        <v>11.59</v>
+        <v>11.63</v>
       </c>
       <c r="AF6">
-        <v>271.88</v>
+        <v>26.85</v>
       </c>
       <c r="AG6">
-        <v>579.11</v>
+        <v>579.63</v>
       </c>
       <c r="AH6">
-        <v>525.61</v>
+        <v>520.09</v>
       </c>
       <c r="AI6">
-        <v>563.47</v>
+        <v>555.41</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>25.79</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1532,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>12027</v>
+        <v>11716</v>
       </c>
       <c r="D7">
-        <v>3.88</v>
+        <v>-2.59</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1535,46 +1544,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-45.74</v>
+        <v>-47.14</v>
       </c>
       <c r="H7">
-        <v>12.88</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I7">
-        <v>7.76</v>
+        <v>2.36</v>
       </c>
       <c r="J7">
-        <v>6.84</v>
+        <v>-2.5</v>
       </c>
       <c r="K7">
-        <v>-3.95</v>
+        <v>-5.69</v>
       </c>
       <c r="L7">
-        <v>-32.86</v>
+        <v>-34.35</v>
       </c>
       <c r="M7">
-        <v>19.6</v>
+        <v>19.14</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>11723.6</v>
+        <v>11777.6</v>
       </c>
       <c r="Q7">
-        <v>11737.15</v>
+        <v>11714.2</v>
       </c>
       <c r="R7">
-        <v>11610.62</v>
+        <v>11592.9</v>
       </c>
       <c r="S7">
-        <v>14895.06</v>
+        <v>14870.04</v>
       </c>
       <c r="T7">
-        <v>-19.26</v>
+        <v>-21.21</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1589,34 +1598,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>57.45</v>
+        <v>51.44</v>
       </c>
       <c r="Z7">
-        <v>20.76</v>
+        <v>24.54</v>
       </c>
       <c r="AA7">
-        <v>-12.17</v>
+        <v>-4.83</v>
       </c>
       <c r="AB7">
-        <v>32.93</v>
+        <v>29.37</v>
       </c>
       <c r="AC7">
-        <v>78.3</v>
+        <v>73.87</v>
       </c>
       <c r="AD7">
-        <v>70.91</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AE7">
-        <v>433.76</v>
+        <v>429</v>
       </c>
       <c r="AF7">
-        <v>186.37</v>
+        <v>-36.08</v>
       </c>
       <c r="AG7">
-        <v>12370.19</v>
+        <v>12312.75</v>
       </c>
       <c r="AH7">
-        <v>11104.11</v>
+        <v>11115.65</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1625,7 +1634,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>25.13</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1636,10 +1645,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>340</v>
+        <v>334.8</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>-1.53</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1648,46 +1657,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-3.19</v>
+        <v>-4.67</v>
       </c>
       <c r="H8">
-        <v>45.11</v>
+        <v>42.89</v>
       </c>
       <c r="I8">
-        <v>-0.06</v>
+        <v>-2.66</v>
       </c>
       <c r="J8">
-        <v>8.83</v>
+        <v>1.76</v>
       </c>
       <c r="K8">
-        <v>23.32</v>
+        <v>23.86</v>
       </c>
       <c r="L8">
-        <v>14.63</v>
+        <v>11.56</v>
       </c>
       <c r="M8">
-        <v>30.51</v>
+        <v>29.79</v>
       </c>
       <c r="N8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P8">
-        <v>341.96</v>
+        <v>340.13</v>
       </c>
       <c r="Q8">
-        <v>337.37</v>
+        <v>337.65</v>
       </c>
       <c r="R8">
-        <v>331.68</v>
+        <v>332.24</v>
       </c>
       <c r="S8">
-        <v>284.62</v>
+        <v>284.88</v>
       </c>
       <c r="T8">
-        <v>19.46</v>
+        <v>17.52</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1702,34 +1711,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>54.63</v>
+        <v>50.13</v>
       </c>
       <c r="Z8">
-        <v>3.71</v>
+        <v>3.13</v>
       </c>
       <c r="AA8">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="AB8">
-        <v>0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="AC8">
-        <v>46.86</v>
+        <v>38.94</v>
       </c>
       <c r="AD8">
-        <v>57.89</v>
+        <v>48.79</v>
       </c>
       <c r="AE8">
-        <v>9.02</v>
+        <v>9.48</v>
       </c>
       <c r="AF8">
-        <v>-71.09</v>
+        <v>-1.1</v>
       </c>
       <c r="AG8">
-        <v>349.18</v>
+        <v>348.9</v>
       </c>
       <c r="AH8">
-        <v>325.56</v>
+        <v>326.39</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1738,7 +1747,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>18.48</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1749,10 +1758,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1307.7</v>
+        <v>1313.5</v>
       </c>
       <c r="D9">
-        <v>-2.04</v>
+        <v>0.44</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1761,46 +1770,46 @@
         <v>1026.6</v>
       </c>
       <c r="G9">
-        <v>-2.48</v>
+        <v>-2.05</v>
       </c>
       <c r="H9">
-        <v>27.38</v>
+        <v>27.95</v>
       </c>
       <c r="I9">
-        <v>-1.45</v>
+        <v>-0.52</v>
       </c>
       <c r="J9">
-        <v>2.97</v>
+        <v>1.64</v>
       </c>
       <c r="K9">
-        <v>-0.24</v>
+        <v>0.05</v>
       </c>
       <c r="L9">
-        <v>24.89</v>
+        <v>26.81</v>
       </c>
       <c r="M9">
-        <v>14.75</v>
+        <v>15.22</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P9">
-        <v>1328.28</v>
+        <v>1326.92</v>
       </c>
       <c r="Q9">
-        <v>1301.5</v>
+        <v>1302.17</v>
       </c>
       <c r="R9">
-        <v>1267.53</v>
+        <v>1268.15</v>
       </c>
       <c r="S9">
-        <v>1222.66</v>
+        <v>1223.3</v>
       </c>
       <c r="T9">
-        <v>6.96</v>
+        <v>7.37</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1815,34 +1824,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>53.81</v>
+        <v>55.35</v>
       </c>
       <c r="Z9">
-        <v>15.58</v>
+        <v>14.6</v>
       </c>
       <c r="AA9">
-        <v>13.05</v>
+        <v>13.36</v>
       </c>
       <c r="AB9">
-        <v>2.53</v>
+        <v>1.24</v>
       </c>
       <c r="AC9">
-        <v>70.16</v>
+        <v>52.82</v>
       </c>
       <c r="AD9">
-        <v>85.14</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AE9">
-        <v>25.55</v>
+        <v>25.22</v>
       </c>
       <c r="AF9">
-        <v>13.43</v>
+        <v>-35.95</v>
       </c>
       <c r="AG9">
-        <v>1349.55</v>
+        <v>1350.51</v>
       </c>
       <c r="AH9">
-        <v>1253.44</v>
+        <v>1253.83</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1851,7 +1860,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>41.72</v>
+        <v>39.01</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1871,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.84</v>
+        <v>79.38</v>
       </c>
       <c r="D10">
-        <v>2.81</v>
+        <v>-1.81</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1874,46 +1883,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.6</v>
+        <v>-13.2</v>
       </c>
       <c r="H10">
-        <v>124.06</v>
+        <v>120.01</v>
       </c>
       <c r="I10">
-        <v>-4.61</v>
+        <v>-3.04</v>
       </c>
       <c r="J10">
-        <v>21.24</v>
+        <v>-0.79</v>
       </c>
       <c r="K10">
-        <v>60.65</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="L10">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="M10">
-        <v>-3.15</v>
+        <v>-3.54</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>80.66</v>
+        <v>80.16</v>
       </c>
       <c r="Q10">
-        <v>84.18000000000001</v>
+        <v>84.02</v>
       </c>
       <c r="R10">
-        <v>68.27</v>
+        <v>68.78</v>
       </c>
       <c r="S10">
-        <v>59.65</v>
+        <v>59.68</v>
       </c>
       <c r="T10">
-        <v>35.52</v>
+        <v>33</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1928,34 +1937,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>54.15</v>
+        <v>51.7</v>
       </c>
       <c r="Z10">
-        <v>3.17</v>
+        <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>4.89</v>
+        <v>4.46</v>
       </c>
       <c r="AB10">
         <v>-1.72</v>
       </c>
       <c r="AC10">
-        <v>4.44</v>
+        <v>5.56</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>3.33</v>
       </c>
       <c r="AE10">
-        <v>4.44</v>
+        <v>4.27</v>
       </c>
       <c r="AF10">
-        <v>-95.48</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="AG10">
-        <v>91.12</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="AH10">
-        <v>77.23</v>
+        <v>76.78</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1964,7 +1973,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>23.69</v>
+        <v>21.62</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2145,7 +2154,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2164,1313 +2173,1367 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-0.31</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.28</v>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>21.35</v>
+        <v>-0.31</v>
       </c>
       <c r="D9" s="7">
-        <v>20.51</v>
+        <v>11.11</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.84</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>7.82</v>
+        <v>20.51</v>
       </c>
       <c r="D10" s="7">
-        <v>8.210000000000001</v>
+        <v>19.46</v>
       </c>
       <c r="E10" s="9">
-        <v>0.39</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-4.42</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D11" s="7">
-        <v>-4.44</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.02</v>
+        <v>4.97</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-1.54</v>
+        <v>-4.44</v>
       </c>
       <c r="D12" s="7">
-        <v>-6.18</v>
+        <v>0.31</v>
       </c>
       <c r="E12" s="8">
-        <v>-4.64</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>3.41</v>
+        <v>-6.18</v>
       </c>
       <c r="D13" s="7">
-        <v>6.84</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="E13" s="9">
-        <v>3.43</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>7.49</v>
+        <v>6.84</v>
       </c>
       <c r="D14" s="7">
-        <v>8.83</v>
+        <v>-2.5</v>
       </c>
       <c r="E14" s="9">
-        <v>1.34</v>
+        <v>-9.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>5.04</v>
+        <v>8.83</v>
       </c>
       <c r="D15" s="7">
-        <v>2.97</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.07</v>
+        <v>1.76</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-7.07</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>16.94</v>
+        <v>2.97</v>
       </c>
       <c r="D16" s="7">
-        <v>21.24</v>
+        <v>1.64</v>
       </c>
       <c r="E16" s="9">
-        <v>4.3</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-0.27</v>
+        <v>21.24</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.86</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.59</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-22.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>5.81</v>
+        <v>-0.86</v>
       </c>
       <c r="D18" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.99</v>
+        <v>7.4</v>
+      </c>
+      <c r="E18" s="8">
+        <v>8.26</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>4.56</v>
+        <v>7.8</v>
       </c>
       <c r="D19" s="7">
-        <v>3.82</v>
+        <v>9.94</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.74</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>0.54</v>
+        <v>3.82</v>
       </c>
       <c r="D20" s="7">
-        <v>-0.04</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.58</v>
+        <v>0.51</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-1.77</v>
+        <v>-0.04</v>
       </c>
       <c r="D21" s="7">
-        <v>-4.46</v>
+        <v>4.65</v>
       </c>
       <c r="E21" s="8">
-        <v>-2.69</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>2.56</v>
+        <v>-4.46</v>
       </c>
       <c r="D22" s="7">
-        <v>7.76</v>
+        <v>-5.54</v>
       </c>
       <c r="E22" s="9">
-        <v>5.2</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>2.16</v>
+        <v>7.76</v>
       </c>
       <c r="D23" s="7">
-        <v>-0.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.22</v>
+        <v>2.36</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-5.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>3.18</v>
+        <v>-0.06</v>
       </c>
       <c r="D24" s="7">
-        <v>-1.45</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-4.63</v>
+        <v>-2.66</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.79</v>
+        <v>-1.45</v>
       </c>
       <c r="D25" s="7">
-        <v>-4.61</v>
+        <v>-0.52</v>
       </c>
       <c r="E25" s="8">
-        <v>-1.82</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>22.56</v>
+        <v>-4.61</v>
       </c>
       <c r="D26" s="7">
-        <v>24.88</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2.32</v>
+        <v>-3.04</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>51.7</v>
+        <v>24.88</v>
       </c>
       <c r="D27" s="7">
-        <v>57.7</v>
-      </c>
-      <c r="E27" s="9">
-        <v>6</v>
+        <v>34.85</v>
+      </c>
+      <c r="E27" s="8">
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>18.37</v>
+        <v>57.7</v>
       </c>
       <c r="D28" s="7">
-        <v>22.08</v>
+        <v>56.55</v>
       </c>
       <c r="E28" s="9">
-        <v>3.71</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>-11.35</v>
+        <v>22.08</v>
       </c>
       <c r="D29" s="7">
-        <v>-11.6</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.25</v>
+        <v>20.24</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>3.01</v>
+        <v>-11.6</v>
       </c>
       <c r="D30" s="7">
-        <v>1.77</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.24</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-36.05</v>
+        <v>1.77</v>
       </c>
       <c r="D31" s="7">
-        <v>-32.86</v>
-      </c>
-      <c r="E31" s="9">
-        <v>3.19</v>
+        <v>4.44</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2.67</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>13.09</v>
+        <v>-32.86</v>
       </c>
       <c r="D32" s="7">
-        <v>14.63</v>
+        <v>-34.35</v>
       </c>
       <c r="E32" s="9">
-        <v>1.54</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>26.2</v>
+        <v>14.63</v>
       </c>
       <c r="D33" s="7">
-        <v>24.89</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.31</v>
+        <v>11.56</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>8.41</v>
+        <v>24.89</v>
       </c>
       <c r="D34" s="7">
-        <v>9.1</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.6899999999999999</v>
+        <v>26.81</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.92</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>-4.66</v>
+        <v>9.1</v>
       </c>
       <c r="D35" s="7">
-        <v>-3.63</v>
+        <v>9.08</v>
       </c>
       <c r="E35" s="9">
-        <v>1.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>28.11</v>
+        <v>-3.63</v>
       </c>
       <c r="D36" s="7">
-        <v>28.42</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.31</v>
+        <v>6.61</v>
+      </c>
+      <c r="E36" s="8">
+        <v>10.24</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-2.53</v>
+        <v>28.42</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.87</v>
+        <v>23.47</v>
       </c>
       <c r="E37" s="9">
-        <v>1.66</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>1.33</v>
+        <v>-0.87</v>
       </c>
       <c r="D38" s="7">
-        <v>2.31</v>
+        <v>-4.24</v>
       </c>
       <c r="E38" s="9">
-        <v>0.98</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-7.94</v>
+        <v>2.31</v>
       </c>
       <c r="D39" s="7">
-        <v>-11.28</v>
+        <v>7.68</v>
       </c>
       <c r="E39" s="8">
-        <v>-3.34</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-10.13</v>
+        <v>-11.28</v>
       </c>
       <c r="D40" s="7">
-        <v>-3.95</v>
-      </c>
-      <c r="E40" s="9">
-        <v>6.18</v>
+        <v>-10.42</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.86</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>25.21</v>
+        <v>-3.95</v>
       </c>
       <c r="D41" s="7">
-        <v>23.32</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.89</v>
+        <v>-5.69</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>2.73</v>
+        <v>23.32</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.24</v>
+        <v>23.86</v>
       </c>
       <c r="E42" s="8">
-        <v>-2.97</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>58.46</v>
+        <v>-0.24</v>
       </c>
       <c r="D43" s="7">
-        <v>60.65</v>
-      </c>
-      <c r="E43" s="9">
-        <v>2.19</v>
+        <v>0.05</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>-36.89</v>
+        <v>60.65</v>
       </c>
       <c r="D44" s="7">
-        <v>-37.34</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.45</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.53</v>
+        <v>-37.34</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.19</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.34</v>
+        <v>-31.08</v>
+      </c>
+      <c r="E45" s="8">
+        <v>6.26</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-8.5</v>
+        <v>-0.19</v>
       </c>
       <c r="D46" s="7">
-        <v>-7.44</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.06</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-18.44</v>
+        <v>-7.44</v>
       </c>
       <c r="D47" s="7">
-        <v>-18.79</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.35</v>
+        <v>-9.99</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-10.78</v>
+        <v>-18.79</v>
       </c>
       <c r="D48" s="7">
-        <v>-13.27</v>
+        <v>-15.1</v>
       </c>
       <c r="E48" s="8">
-        <v>-2.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-47.76</v>
+        <v>-13.27</v>
       </c>
       <c r="D49" s="7">
-        <v>-45.74</v>
+        <v>-13.67</v>
       </c>
       <c r="E49" s="9">
-        <v>2.02</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-2.35</v>
+        <v>-45.74</v>
       </c>
       <c r="D50" s="7">
-        <v>-3.19</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.84</v>
+        <v>-47.14</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-0.45</v>
+        <v>-3.19</v>
       </c>
       <c r="D51" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.03</v>
+        <v>-4.67</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-14.02</v>
+        <v>-2.48</v>
       </c>
       <c r="D52" s="7">
-        <v>-11.6</v>
-      </c>
-      <c r="E52" s="9">
-        <v>2.42</v>
+        <v>-2.05</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>635.85</v>
+        <v>-11.6</v>
       </c>
       <c r="D53" s="7">
-        <v>631.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-4.5</v>
+        <v>-13.2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>308.6</v>
+        <v>631.35</v>
       </c>
       <c r="D54" s="7">
-        <v>309.65</v>
-      </c>
-      <c r="E54" s="9">
-        <v>1.05</v>
+        <v>694.45</v>
+      </c>
+      <c r="E54" s="8">
+        <v>63.1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>1179.2</v>
+        <v>309.65</v>
       </c>
       <c r="D55" s="7">
-        <v>1192.9</v>
-      </c>
-      <c r="E55" s="9">
-        <v>13.7</v>
+        <v>309.75</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>705.15</v>
+        <v>1192.9</v>
       </c>
       <c r="D56" s="7">
-        <v>702.15</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-3</v>
+        <v>1160</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-32.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>535.3</v>
+        <v>702.15</v>
       </c>
       <c r="D57" s="7">
-        <v>520.4</v>
+        <v>734</v>
       </c>
       <c r="E57" s="8">
-        <v>-14.9</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>11578</v>
+        <v>520.4</v>
       </c>
       <c r="D58" s="7">
-        <v>12027</v>
+        <v>518</v>
       </c>
       <c r="E58" s="9">
-        <v>449</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>342.95</v>
+        <v>12027</v>
       </c>
       <c r="D59" s="7">
-        <v>340</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-2.95</v>
+        <v>11716</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-311</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>1334.9</v>
+        <v>340</v>
       </c>
       <c r="D60" s="7">
-        <v>1307.7</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-27.2</v>
+        <v>334.8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-5.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>78.63</v>
+        <v>1307.7</v>
       </c>
       <c r="D61" s="7">
-        <v>80.84</v>
-      </c>
-      <c r="E61" s="9">
-        <v>2.21</v>
+        <v>1313.5</v>
+      </c>
+      <c r="E61" s="8">
+        <v>5.8</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>23</v>
+        <v>80.84</v>
       </c>
       <c r="D62" s="7">
-        <v>34</v>
+        <v>79.38</v>
       </c>
       <c r="E62" s="9">
-        <v>11</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="7">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D63" s="7">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="E63" s="8">
-        <v>-11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>47.04</v>
+        <v>55</v>
       </c>
       <c r="D64" s="7">
-        <v>45.31</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1.73</v>
+        <v>45</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-10</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="7">
-        <v>71.67</v>
+        <v>77</v>
       </c>
       <c r="D65" s="7">
-        <v>72.06999999999999</v>
+        <v>66</v>
       </c>
       <c r="E65" s="9">
-        <v>0.4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="7">
-        <v>70.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="D66" s="7">
-        <v>72.56999999999999</v>
+        <v>55</v>
       </c>
       <c r="E66" s="9">
-        <v>2.47</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>40.97</v>
+        <v>45.31</v>
       </c>
       <c r="D67" s="7">
-        <v>39.5</v>
+        <v>64.87</v>
       </c>
       <c r="E67" s="8">
-        <v>-1.47</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>37.15</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="D68" s="7">
-        <v>30.03</v>
+        <v>72.11</v>
       </c>
       <c r="E68" s="8">
-        <v>-7.12</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>49.55</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D69" s="7">
-        <v>57.45</v>
+        <v>59.8</v>
       </c>
       <c r="E69" s="9">
-        <v>7.9</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>57.34</v>
+        <v>39.5</v>
       </c>
       <c r="D70" s="7">
-        <v>54.63</v>
+        <v>57.13</v>
       </c>
       <c r="E70" s="8">
-        <v>-2.71</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>63.34</v>
+        <v>30.03</v>
       </c>
       <c r="D71" s="7">
-        <v>53.81</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-9.529999999999999</v>
+        <v>29.07</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>50.88</v>
+        <v>57.45</v>
       </c>
       <c r="D72" s="7">
-        <v>54.15</v>
+        <v>51.44</v>
       </c>
       <c r="E72" s="9">
-        <v>3.27</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>-78.33</v>
+        <v>54.63</v>
       </c>
       <c r="D73" s="7">
-        <v>-63.98</v>
+        <v>50.13</v>
       </c>
       <c r="E73" s="9">
-        <v>14.35</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>-57.7</v>
+        <v>53.81</v>
       </c>
       <c r="D74" s="7">
-        <v>-14.02</v>
-      </c>
-      <c r="E74" s="9">
-        <v>43.68</v>
+        <v>55.35</v>
+      </c>
+      <c r="E74" s="8">
+        <v>1.54</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="7">
-        <v>-21.22</v>
+        <v>54.15</v>
       </c>
       <c r="D75" s="7">
-        <v>-7.57</v>
+        <v>51.7</v>
       </c>
       <c r="E75" s="9">
-        <v>13.65</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-16.04</v>
+        <v>-63.98</v>
       </c>
       <c r="D76" s="7">
-        <v>171.01</v>
-      </c>
-      <c r="E76" s="9">
-        <v>187.05</v>
+        <v>475.16</v>
+      </c>
+      <c r="E76" s="8">
+        <v>539.14</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-38</v>
+        <v>-14.02</v>
       </c>
       <c r="D77" s="7">
-        <v>271.88</v>
-      </c>
-      <c r="E77" s="9">
-        <v>309.88</v>
+        <v>44.96</v>
+      </c>
+      <c r="E77" s="8">
+        <v>58.98</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-68.17</v>
+        <v>-7.57</v>
       </c>
       <c r="D78" s="7">
-        <v>186.37</v>
+        <v>-37.43</v>
       </c>
       <c r="E78" s="9">
-        <v>254.54</v>
+        <v>-29.86</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-50.37</v>
+        <v>171.01</v>
       </c>
       <c r="D79" s="7">
-        <v>-71.09</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-20.72</v>
+        <v>169.21</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>-18.5</v>
+        <v>271.88</v>
       </c>
       <c r="D80" s="7">
-        <v>13.43</v>
+        <v>26.85</v>
       </c>
       <c r="E80" s="9">
-        <v>31.93</v>
+        <v>-245.03</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>-93.20999999999999</v>
+        <v>186.37</v>
       </c>
       <c r="D81" s="7">
+        <v>-36.08</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-222.45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-71.09</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-1.1</v>
+      </c>
+      <c r="E82" s="8">
+        <v>69.98999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>13.43</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-35.95</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-49.38</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
         <v>-95.48</v>
       </c>
-      <c r="E81" s="8">
-        <v>-2.27</v>
+      <c r="D84" s="7">
+        <v>-94.34999999999999</v>
+      </c>
+      <c r="E84" s="8">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3494,28 +3557,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3523,22 +3586,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>64.16</v>
+        <v>60.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>53.3</v>
+        <v>54.6</v>
       </c>
       <c r="E2" s="12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="12">
-        <v>10.5</v>
+        <v>11.8</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3675,31 +3738,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4106</v>
+        <v>0.4097999999999999</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3654</v>
+        <v>0.3829</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3051</v>
+        <v>0.2979</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2627</v>
+        <v>0.2598</v>
       </c>
       <c r="E2" s="15">
-        <v>0.196</v>
+        <v>0.1914</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1507</v>
+        <v>0.158</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1475</v>
+        <v>0.1522</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0315</v>
+        <v>-0.0354</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0779</v>
+        <v>-0.0578</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.1 → 46.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>46.0</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.3 → 64.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.3</t>
-  </si>
-  <si>
-    <t>64.9</t>
-  </si>
-  <si>
-    <t>39.5 → 57.1</t>
-  </si>
-  <si>
-    <t>39.5</t>
-  </si>
-  <si>
-    <t>57.1</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.6 → 59.8</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.6</t>
-  </si>
-  <si>
-    <t>59.8</t>
+    <t>51.4 → 46.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>46.8</t>
+  </si>
+  <si>
+    <t>50.1 → 47.9</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>51.7 → 48.9</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -281,7 +290,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,20 +331,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,12 +365,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,12 +451,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -469,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -827,8 +823,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -967,10 +963,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>694.45</v>
+        <v>686.25</v>
       </c>
       <c r="D2">
-        <v>9.99</v>
+        <v>-1.18</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -979,46 +975,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-31.08</v>
+        <v>-31.89</v>
       </c>
       <c r="H2">
-        <v>89.12</v>
+        <v>86.89</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>6.99</v>
       </c>
       <c r="J2">
-        <v>11.11</v>
+        <v>9.84</v>
       </c>
       <c r="K2">
-        <v>6.61</v>
+        <v>4.01</v>
       </c>
       <c r="L2">
-        <v>34.85</v>
+        <v>15.24</v>
       </c>
       <c r="M2">
-        <v>-5.78</v>
+        <v>-6.24</v>
       </c>
       <c r="N2">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>648.12</v>
+        <v>657.09</v>
       </c>
       <c r="Q2">
-        <v>642.04</v>
+        <v>645.03</v>
       </c>
       <c r="R2">
-        <v>644.9</v>
+        <v>645.84</v>
       </c>
       <c r="S2">
-        <v>621.51</v>
+        <v>622.16</v>
       </c>
       <c r="T2">
-        <v>11.74</v>
+        <v>10.3</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1033,34 +1029,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>64.87</v>
+        <v>61.78</v>
       </c>
       <c r="Z2">
-        <v>1.74</v>
+        <v>4.72</v>
       </c>
       <c r="AA2">
-        <v>-1.96</v>
+        <v>-0.62</v>
       </c>
       <c r="AB2">
-        <v>3.7</v>
+        <v>5.34</v>
       </c>
       <c r="AC2">
-        <v>40.21</v>
+        <v>61.4</v>
       </c>
       <c r="AD2">
-        <v>29.86</v>
+        <v>39.25</v>
       </c>
       <c r="AE2">
-        <v>23.93</v>
+        <v>25.36</v>
       </c>
       <c r="AF2">
-        <v>475.16</v>
+        <v>220.66</v>
       </c>
       <c r="AG2">
-        <v>676.02</v>
+        <v>683.47</v>
       </c>
       <c r="AH2">
-        <v>608.0599999999999</v>
+        <v>606.6</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1069,7 +1065,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.97</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1080,10 +1076,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>309.75</v>
+        <v>309.15</v>
       </c>
       <c r="D3">
-        <v>0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="E3">
         <v>310.25</v>
@@ -1092,25 +1088,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-0.16</v>
+        <v>-0.35</v>
       </c>
       <c r="H3">
-        <v>102.15</v>
+        <v>101.76</v>
       </c>
       <c r="I3">
-        <v>9.94</v>
+        <v>2.22</v>
       </c>
       <c r="J3">
-        <v>19.46</v>
+        <v>16.93</v>
       </c>
       <c r="K3">
-        <v>23.47</v>
+        <v>18.9</v>
       </c>
       <c r="L3">
-        <v>56.55</v>
+        <v>58.14</v>
       </c>
       <c r="M3">
-        <v>40.98</v>
+        <v>40.63</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1119,19 +1115,19 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>308.14</v>
+        <v>309.48</v>
       </c>
       <c r="Q3">
-        <v>281.57</v>
+        <v>283.75</v>
       </c>
       <c r="R3">
-        <v>269.47</v>
+        <v>270.5</v>
       </c>
       <c r="S3">
-        <v>213.61</v>
+        <v>214.32</v>
       </c>
       <c r="T3">
-        <v>45.01</v>
+        <v>44.25</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1146,34 +1142,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>72.11</v>
+        <v>71.45</v>
       </c>
       <c r="Z3">
-        <v>12.16</v>
+        <v>12.47</v>
       </c>
       <c r="AA3">
-        <v>8.49</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AB3">
-        <v>3.67</v>
+        <v>3.18</v>
       </c>
       <c r="AC3">
-        <v>94.36</v>
+        <v>93.72</v>
       </c>
       <c r="AD3">
-        <v>95.84999999999999</v>
+        <v>94.69</v>
       </c>
       <c r="AE3">
-        <v>11.1</v>
+        <v>10.97</v>
       </c>
       <c r="AF3">
-        <v>44.96</v>
+        <v>-30.11</v>
       </c>
       <c r="AG3">
-        <v>316.31</v>
+        <v>319.71</v>
       </c>
       <c r="AH3">
-        <v>246.84</v>
+        <v>247.79</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1182,7 +1178,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>51.59</v>
+        <v>51.79</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1193,58 +1189,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1160</v>
+        <v>1159.4</v>
       </c>
       <c r="D4">
-        <v>-2.76</v>
+        <v>-0.05</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
       </c>
       <c r="F4">
-        <v>945.8</v>
+        <v>962.85</v>
       </c>
       <c r="G4">
-        <v>-9.99</v>
+        <v>-10.04</v>
       </c>
       <c r="H4">
-        <v>22.65</v>
+        <v>20.41</v>
       </c>
       <c r="I4">
-        <v>0.51</v>
+        <v>-1.36</v>
       </c>
       <c r="J4">
-        <v>4.97</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>-4.24</v>
+        <v>-3.16</v>
       </c>
       <c r="L4">
-        <v>20.24</v>
+        <v>22.58</v>
       </c>
       <c r="M4">
-        <v>25.98</v>
+        <v>25.5</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1175.5</v>
+        <v>1172.3</v>
       </c>
       <c r="Q4">
-        <v>1128.81</v>
+        <v>1131.11</v>
       </c>
       <c r="R4">
-        <v>1085.18</v>
+        <v>1086.72</v>
       </c>
       <c r="S4">
-        <v>1127.22</v>
+        <v>1127.64</v>
       </c>
       <c r="T4">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1259,34 +1255,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>59.8</v>
+        <v>59.59</v>
       </c>
       <c r="Z4">
-        <v>23.93</v>
+        <v>22.84</v>
       </c>
       <c r="AA4">
-        <v>18.51</v>
+        <v>19.38</v>
       </c>
       <c r="AB4">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="AC4">
-        <v>79.67</v>
+        <v>60.73</v>
       </c>
       <c r="AD4">
-        <v>90.09999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AE4">
-        <v>27.52</v>
+        <v>27.29</v>
       </c>
       <c r="AF4">
-        <v>-37.43</v>
+        <v>-11.29</v>
       </c>
       <c r="AG4">
-        <v>1194.19</v>
+        <v>1197.44</v>
       </c>
       <c r="AH4">
-        <v>1063.42</v>
+        <v>1064.77</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1295,7 +1291,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>46.47</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1306,10 +1302,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>734</v>
+        <v>734.9</v>
       </c>
       <c r="D5">
-        <v>4.54</v>
+        <v>0.12</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1318,46 +1314,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.1</v>
+        <v>-15</v>
       </c>
       <c r="H5">
-        <v>10.89</v>
+        <v>11.03</v>
       </c>
       <c r="I5">
-        <v>4.65</v>
+        <v>3.08</v>
       </c>
       <c r="J5">
-        <v>0.31</v>
+        <v>-0.1</v>
       </c>
       <c r="K5">
-        <v>7.68</v>
+        <v>5.48</v>
       </c>
       <c r="L5">
-        <v>-8.869999999999999</v>
+        <v>-3.56</v>
       </c>
       <c r="M5">
-        <v>38.29</v>
+        <v>38.03</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>711.85</v>
+        <v>716.24</v>
       </c>
       <c r="Q5">
-        <v>722.89</v>
+        <v>722.41</v>
       </c>
       <c r="R5">
-        <v>718.11</v>
+        <v>718.98</v>
       </c>
       <c r="S5">
-        <v>749.08</v>
+        <v>749.0700000000001</v>
       </c>
       <c r="T5">
-        <v>-2.01</v>
+        <v>-1.89</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1372,34 +1368,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>57.13</v>
+        <v>57.51</v>
       </c>
       <c r="Z5">
-        <v>-3.62</v>
+        <v>-1.83</v>
       </c>
       <c r="AA5">
-        <v>-2.71</v>
+        <v>-2.54</v>
       </c>
       <c r="AB5">
-        <v>-0.91</v>
+        <v>0.71</v>
       </c>
       <c r="AC5">
-        <v>46.37</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="AD5">
-        <v>32.17</v>
+        <v>46.31</v>
       </c>
       <c r="AE5">
-        <v>17.04</v>
+        <v>17.65</v>
       </c>
       <c r="AF5">
-        <v>169.21</v>
+        <v>12.64</v>
       </c>
       <c r="AG5">
-        <v>753.23</v>
+        <v>751.59</v>
       </c>
       <c r="AH5">
-        <v>692.54</v>
+        <v>693.22</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1408,7 +1404,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.15</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1419,10 +1415,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>518</v>
+        <v>539.8</v>
       </c>
       <c r="D6">
-        <v>-0.46</v>
+        <v>4.21</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1431,46 +1427,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-13.67</v>
+        <v>-10.03</v>
       </c>
       <c r="H6">
-        <v>18.11</v>
+        <v>23.08</v>
       </c>
       <c r="I6">
-        <v>-5.54</v>
+        <v>-0.68</v>
       </c>
       <c r="J6">
-        <v>-8.960000000000001</v>
+        <v>-4.96</v>
       </c>
       <c r="K6">
-        <v>-10.42</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L6">
-        <v>4.44</v>
+        <v>10.89</v>
       </c>
       <c r="M6">
-        <v>15.8</v>
+        <v>16.86</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="P6">
-        <v>531.86</v>
+        <v>531.12</v>
       </c>
       <c r="Q6">
-        <v>549.86</v>
+        <v>548.55</v>
       </c>
       <c r="R6">
-        <v>554.1799999999999</v>
+        <v>553.59</v>
       </c>
       <c r="S6">
-        <v>519.97</v>
+        <v>520.04</v>
       </c>
       <c r="T6">
-        <v>-0.38</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1482,37 +1478,37 @@
         <v>47</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>29.07</v>
+        <v>46.04</v>
       </c>
       <c r="Z6">
-        <v>-7.94</v>
+        <v>-7.27</v>
       </c>
       <c r="AA6">
-        <v>-4.46</v>
+        <v>-5.02</v>
       </c>
       <c r="AB6">
-        <v>-3.48</v>
+        <v>-2.24</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>26.67</v>
       </c>
       <c r="AD6">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="AE6">
-        <v>11.63</v>
+        <v>12.9</v>
       </c>
       <c r="AF6">
-        <v>26.85</v>
+        <v>104.22</v>
       </c>
       <c r="AG6">
-        <v>579.63</v>
+        <v>577.63</v>
       </c>
       <c r="AH6">
-        <v>520.09</v>
+        <v>519.47</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1521,7 +1517,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>30.65</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1532,10 +1528,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11716</v>
+        <v>11441</v>
       </c>
       <c r="D7">
-        <v>-2.59</v>
+        <v>-2.35</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1544,46 +1540,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.14</v>
+        <v>-48.38</v>
       </c>
       <c r="H7">
-        <v>9.960000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="I7">
-        <v>2.36</v>
+        <v>-3.3</v>
       </c>
       <c r="J7">
-        <v>-2.5</v>
+        <v>-6.03</v>
       </c>
       <c r="K7">
-        <v>-5.69</v>
+        <v>-8.02</v>
       </c>
       <c r="L7">
-        <v>-34.35</v>
+        <v>-34.25</v>
       </c>
       <c r="M7">
-        <v>19.14</v>
+        <v>18.84</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P7">
-        <v>11777.6</v>
+        <v>11699.4</v>
       </c>
       <c r="Q7">
-        <v>11714.2</v>
+        <v>11669.9</v>
       </c>
       <c r="R7">
-        <v>11592.9</v>
+        <v>11575.94</v>
       </c>
       <c r="S7">
-        <v>14870.04</v>
+        <v>14841.28</v>
       </c>
       <c r="T7">
-        <v>-21.21</v>
+        <v>-22.91</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1598,34 +1594,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>51.44</v>
+        <v>46.78</v>
       </c>
       <c r="Z7">
-        <v>24.54</v>
+        <v>5.28</v>
       </c>
       <c r="AA7">
-        <v>-4.83</v>
+        <v>-2.81</v>
       </c>
       <c r="AB7">
-        <v>29.37</v>
+        <v>8.09</v>
       </c>
       <c r="AC7">
-        <v>73.87</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AD7">
-        <v>74.40000000000001</v>
+        <v>73.05</v>
       </c>
       <c r="AE7">
-        <v>429</v>
+        <v>420.64</v>
       </c>
       <c r="AF7">
-        <v>-36.08</v>
+        <v>-63.09</v>
       </c>
       <c r="AG7">
-        <v>12312.75</v>
+        <v>12205.3</v>
       </c>
       <c r="AH7">
-        <v>11115.65</v>
+        <v>11134.5</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1634,7 +1630,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>27.71</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1645,10 +1641,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>334.8</v>
+        <v>332.1</v>
       </c>
       <c r="D8">
-        <v>-1.53</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1657,46 +1653,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-4.67</v>
+        <v>-5.44</v>
       </c>
       <c r="H8">
-        <v>42.89</v>
+        <v>41.74</v>
       </c>
       <c r="I8">
-        <v>-2.66</v>
+        <v>-3.73</v>
       </c>
       <c r="J8">
-        <v>1.76</v>
+        <v>0.87</v>
       </c>
       <c r="K8">
-        <v>23.86</v>
+        <v>21.74</v>
       </c>
       <c r="L8">
-        <v>11.56</v>
+        <v>12.2</v>
       </c>
       <c r="M8">
-        <v>29.79</v>
+        <v>29.4</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O8">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P8">
-        <v>340.13</v>
+        <v>337.56</v>
       </c>
       <c r="Q8">
-        <v>337.65</v>
+        <v>337.53</v>
       </c>
       <c r="R8">
-        <v>332.24</v>
+        <v>332.58</v>
       </c>
       <c r="S8">
-        <v>284.88</v>
+        <v>285.14</v>
       </c>
       <c r="T8">
-        <v>17.52</v>
+        <v>16.47</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1711,34 +1707,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>50.13</v>
+        <v>47.93</v>
       </c>
       <c r="Z8">
-        <v>3.13</v>
+        <v>2.42</v>
       </c>
       <c r="AA8">
-        <v>3.59</v>
+        <v>3.36</v>
       </c>
       <c r="AB8">
-        <v>-0.46</v>
+        <v>-0.93</v>
       </c>
       <c r="AC8">
-        <v>38.94</v>
+        <v>18.28</v>
       </c>
       <c r="AD8">
-        <v>48.79</v>
+        <v>34.69</v>
       </c>
       <c r="AE8">
-        <v>9.48</v>
+        <v>9.24</v>
       </c>
       <c r="AF8">
-        <v>-1.1</v>
+        <v>-30.63</v>
       </c>
       <c r="AG8">
-        <v>348.9</v>
+        <v>348.97</v>
       </c>
       <c r="AH8">
-        <v>326.39</v>
+        <v>326.09</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1747,7 +1743,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>18.94</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1758,58 +1754,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1313.5</v>
+        <v>1306</v>
       </c>
       <c r="D9">
-        <v>0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1026.6</v>
+        <v>1035.5</v>
       </c>
       <c r="G9">
-        <v>-2.05</v>
+        <v>-2.61</v>
       </c>
       <c r="H9">
-        <v>27.95</v>
+        <v>26.12</v>
       </c>
       <c r="I9">
-        <v>-0.52</v>
+        <v>-2.61</v>
       </c>
       <c r="J9">
-        <v>1.64</v>
+        <v>0.46</v>
       </c>
       <c r="K9">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="L9">
-        <v>26.81</v>
+        <v>27.22</v>
       </c>
       <c r="M9">
-        <v>15.22</v>
+        <v>14.81</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O9">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9">
-        <v>1326.92</v>
+        <v>1319.92</v>
       </c>
       <c r="Q9">
-        <v>1302.17</v>
+        <v>1300.97</v>
       </c>
       <c r="R9">
-        <v>1268.15</v>
+        <v>1269.43</v>
       </c>
       <c r="S9">
-        <v>1223.3</v>
+        <v>1224</v>
       </c>
       <c r="T9">
-        <v>7.37</v>
+        <v>6.7</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1824,34 +1820,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>55.35</v>
+        <v>52.89</v>
       </c>
       <c r="Z9">
-        <v>14.6</v>
+        <v>13.07</v>
       </c>
       <c r="AA9">
-        <v>13.36</v>
+        <v>13.3</v>
       </c>
       <c r="AB9">
-        <v>1.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AC9">
-        <v>52.82</v>
+        <v>32.69</v>
       </c>
       <c r="AD9">
-        <v>71.98999999999999</v>
+        <v>51.89</v>
       </c>
       <c r="AE9">
-        <v>25.22</v>
+        <v>24.43</v>
       </c>
       <c r="AF9">
-        <v>-35.95</v>
+        <v>-8.19</v>
       </c>
       <c r="AG9">
-        <v>1350.51</v>
+        <v>1347.56</v>
       </c>
       <c r="AH9">
-        <v>1253.83</v>
+        <v>1254.38</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1860,7 +1856,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>39.01</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1871,10 +1867,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>79.38</v>
+        <v>77.67</v>
       </c>
       <c r="D10">
-        <v>-1.81</v>
+        <v>-2.15</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1883,46 +1879,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-13.2</v>
+        <v>-15.07</v>
       </c>
       <c r="H10">
-        <v>120.01</v>
+        <v>115.27</v>
       </c>
       <c r="I10">
-        <v>-3.04</v>
+        <v>-4.76</v>
       </c>
       <c r="J10">
-        <v>-0.79</v>
+        <v>-5.9</v>
       </c>
       <c r="K10">
-        <v>64.79000000000001</v>
+        <v>55.06</v>
       </c>
       <c r="L10">
-        <v>9.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M10">
-        <v>-3.54</v>
+        <v>-4.31</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P10">
-        <v>80.16</v>
+        <v>79.38</v>
       </c>
       <c r="Q10">
-        <v>84.02</v>
+        <v>83.59</v>
       </c>
       <c r="R10">
-        <v>68.78</v>
+        <v>69.25</v>
       </c>
       <c r="S10">
-        <v>59.68</v>
+        <v>59.72</v>
       </c>
       <c r="T10">
-        <v>33</v>
+        <v>30.07</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1937,34 +1933,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>51.7</v>
+        <v>48.91</v>
       </c>
       <c r="Z10">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="AA10">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="AB10">
-        <v>-1.72</v>
+        <v>-1.77</v>
       </c>
       <c r="AC10">
         <v>5.56</v>
       </c>
       <c r="AD10">
-        <v>3.33</v>
+        <v>5.19</v>
       </c>
       <c r="AE10">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="AF10">
-        <v>-94.34999999999999</v>
+        <v>-91.53</v>
       </c>
       <c r="AG10">
-        <v>91.26000000000001</v>
+        <v>91.28</v>
       </c>
       <c r="AH10">
-        <v>76.78</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1973,7 +1969,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>21.62</v>
+        <v>22.25</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2150,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2173,37 +2169,37 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>68</v>
@@ -2212,982 +2208,985 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-0.31</v>
-      </c>
-      <c r="D9" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="E9" s="8">
-        <v>11.42</v>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>20.51</v>
+        <v>11.11</v>
       </c>
       <c r="D10" s="7">
-        <v>19.46</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-1.05</v>
+        <v>9.84</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>8.210000000000001</v>
+        <v>19.46</v>
       </c>
       <c r="D11" s="7">
-        <v>4.97</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-3.24</v>
+        <v>16.93</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-4.44</v>
+        <v>4.97</v>
       </c>
       <c r="D12" s="7">
-        <v>0.31</v>
+        <v>3.15</v>
       </c>
       <c r="E12" s="8">
-        <v>4.75</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-6.18</v>
+        <v>0.31</v>
       </c>
       <c r="D13" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.78</v>
+        <v>-0.1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>6.84</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D14" s="7">
-        <v>-2.5</v>
+        <v>-4.96</v>
       </c>
       <c r="E14" s="9">
-        <v>-9.34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>8.83</v>
+        <v>-2.5</v>
       </c>
       <c r="D15" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-7.07</v>
+        <v>-6.03</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>2.97</v>
+        <v>1.76</v>
       </c>
       <c r="D16" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-1.33</v>
+        <v>0.87</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>21.24</v>
+        <v>1.64</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-22.03</v>
+        <v>0.46</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-0.86</v>
+        <v>-0.79</v>
       </c>
       <c r="D18" s="7">
-        <v>7.4</v>
+        <v>-5.9</v>
       </c>
       <c r="E18" s="8">
-        <v>8.26</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D19" s="7">
-        <v>9.94</v>
+        <v>6.99</v>
       </c>
       <c r="E19" s="8">
-        <v>2.14</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>3.82</v>
+        <v>9.94</v>
       </c>
       <c r="D20" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-3.31</v>
+        <v>2.22</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-0.04</v>
+        <v>0.51</v>
       </c>
       <c r="D21" s="7">
-        <v>4.65</v>
+        <v>-1.36</v>
       </c>
       <c r="E21" s="8">
-        <v>4.69</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-4.46</v>
+        <v>4.65</v>
       </c>
       <c r="D22" s="7">
-        <v>-5.54</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.08</v>
+        <v>3.08</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>7.76</v>
+        <v>-5.54</v>
       </c>
       <c r="D23" s="7">
-        <v>2.36</v>
+        <v>-0.68</v>
       </c>
       <c r="E23" s="9">
-        <v>-5.4</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-0.06</v>
+        <v>2.36</v>
       </c>
       <c r="D24" s="7">
-        <v>-2.66</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.6</v>
+        <v>-3.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-5.66</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-1.45</v>
+        <v>-2.66</v>
       </c>
       <c r="D25" s="7">
-        <v>-0.52</v>
+        <v>-3.73</v>
       </c>
       <c r="E25" s="8">
-        <v>0.93</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>-4.61</v>
+        <v>-0.52</v>
       </c>
       <c r="D26" s="7">
-        <v>-3.04</v>
+        <v>-2.61</v>
       </c>
       <c r="E26" s="8">
-        <v>1.57</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>24.88</v>
+        <v>-3.04</v>
       </c>
       <c r="D27" s="7">
-        <v>34.85</v>
+        <v>-4.76</v>
       </c>
       <c r="E27" s="8">
-        <v>9.970000000000001</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>57.7</v>
+        <v>34.85</v>
       </c>
       <c r="D28" s="7">
-        <v>56.55</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.15</v>
+        <v>15.24</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-19.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>22.08</v>
+        <v>56.55</v>
       </c>
       <c r="D29" s="7">
-        <v>20.24</v>
+        <v>58.14</v>
       </c>
       <c r="E29" s="9">
-        <v>-1.84</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>-11.6</v>
+        <v>20.24</v>
       </c>
       <c r="D30" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.73</v>
+        <v>22.58</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.34</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>1.77</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="D31" s="7">
-        <v>4.44</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2.67</v>
+        <v>-3.56</v>
+      </c>
+      <c r="E31" s="9">
+        <v>5.31</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-32.86</v>
+        <v>4.44</v>
       </c>
       <c r="D32" s="7">
-        <v>-34.35</v>
+        <v>10.89</v>
       </c>
       <c r="E32" s="9">
-        <v>-1.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>14.63</v>
+        <v>-34.35</v>
       </c>
       <c r="D33" s="7">
-        <v>11.56</v>
+        <v>-34.25</v>
       </c>
       <c r="E33" s="9">
-        <v>-3.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>24.89</v>
+        <v>11.56</v>
       </c>
       <c r="D34" s="7">
-        <v>26.81</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.92</v>
+        <v>12.2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>9.1</v>
+        <v>26.81</v>
       </c>
       <c r="D35" s="7">
-        <v>9.08</v>
+        <v>27.22</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="7">
-        <v>-3.63</v>
+        <v>9.08</v>
       </c>
       <c r="D36" s="7">
-        <v>6.61</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E36" s="8">
-        <v>10.24</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>28.42</v>
+        <v>6.61</v>
       </c>
       <c r="D37" s="7">
-        <v>23.47</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-4.95</v>
+        <v>4.01</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-0.87</v>
+        <v>23.47</v>
       </c>
       <c r="D38" s="7">
-        <v>-4.24</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-3.37</v>
+        <v>18.9</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.57</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>2.31</v>
+        <v>-4.24</v>
       </c>
       <c r="D39" s="7">
-        <v>7.68</v>
-      </c>
-      <c r="E39" s="8">
-        <v>5.37</v>
+        <v>-3.16</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.08</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-11.28</v>
+        <v>7.68</v>
       </c>
       <c r="D40" s="7">
-        <v>-10.42</v>
+        <v>5.48</v>
       </c>
       <c r="E40" s="8">
-        <v>0.86</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-3.95</v>
+        <v>-10.42</v>
       </c>
       <c r="D41" s="7">
-        <v>-5.69</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="E41" s="9">
-        <v>-1.74</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>23.32</v>
+        <v>-5.69</v>
       </c>
       <c r="D42" s="7">
-        <v>23.86</v>
+        <v>-8.02</v>
       </c>
       <c r="E42" s="8">
-        <v>0.54</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>-0.24</v>
+        <v>23.86</v>
       </c>
       <c r="D43" s="7">
-        <v>0.05</v>
+        <v>21.74</v>
       </c>
       <c r="E43" s="8">
-        <v>0.29</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>60.65</v>
+        <v>0.05</v>
       </c>
       <c r="D44" s="7">
-        <v>64.79000000000001</v>
-      </c>
-      <c r="E44" s="8">
-        <v>4.14</v>
+        <v>0.38</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.33</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C45" s="7">
-        <v>-37.34</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D45" s="7">
-        <v>-31.08</v>
+        <v>55.06</v>
       </c>
       <c r="E45" s="8">
-        <v>6.26</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.19</v>
+        <v>-31.08</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.16</v>
+        <v>-31.89</v>
       </c>
       <c r="E46" s="8">
-        <v>0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-7.44</v>
+        <v>-0.16</v>
       </c>
       <c r="D47" s="7">
-        <v>-9.99</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-2.55</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-18.79</v>
+        <v>-9.99</v>
       </c>
       <c r="D48" s="7">
-        <v>-15.1</v>
+        <v>-10.04</v>
       </c>
       <c r="E48" s="8">
-        <v>3.69</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-13.27</v>
+        <v>-15.1</v>
       </c>
       <c r="D49" s="7">
-        <v>-13.67</v>
+        <v>-15</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-45.74</v>
+        <v>-13.67</v>
       </c>
       <c r="D50" s="7">
-        <v>-47.14</v>
+        <v>-10.03</v>
       </c>
       <c r="E50" s="9">
-        <v>-1.4</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-3.19</v>
+        <v>-47.14</v>
       </c>
       <c r="D51" s="7">
-        <v>-4.67</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-1.48</v>
+        <v>-48.38</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-2.48</v>
+        <v>-4.67</v>
       </c>
       <c r="D52" s="7">
-        <v>-2.05</v>
+        <v>-5.44</v>
       </c>
       <c r="E52" s="8">
-        <v>0.43</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>-11.6</v>
+        <v>-2.05</v>
       </c>
       <c r="D53" s="7">
-        <v>-13.2</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.6</v>
+        <v>-2.61</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" s="7">
-        <v>631.35</v>
+        <v>-13.2</v>
       </c>
       <c r="D54" s="7">
-        <v>694.45</v>
+        <v>-15.07</v>
       </c>
       <c r="E54" s="8">
-        <v>63.1</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>309.65</v>
+        <v>694.45</v>
       </c>
       <c r="D55" s="7">
-        <v>309.75</v>
+        <v>686.25</v>
       </c>
       <c r="E55" s="8">
-        <v>0.1</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>1192.9</v>
+        <v>309.75</v>
       </c>
       <c r="D56" s="7">
-        <v>1160</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-32.9</v>
+        <v>309.15</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>702.15</v>
+        <v>1160</v>
       </c>
       <c r="D57" s="7">
-        <v>734</v>
+        <v>1159.4</v>
       </c>
       <c r="E57" s="8">
-        <v>31.85</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>520.4</v>
+        <v>734</v>
       </c>
       <c r="D58" s="7">
-        <v>518</v>
+        <v>734.9</v>
       </c>
       <c r="E58" s="9">
-        <v>-2.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>12027</v>
+        <v>518</v>
       </c>
       <c r="D59" s="7">
-        <v>11716</v>
+        <v>539.8</v>
       </c>
       <c r="E59" s="9">
-        <v>-311</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>340</v>
+        <v>11716</v>
       </c>
       <c r="D60" s="7">
-        <v>334.8</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-5.2</v>
+        <v>11441</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-275</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>1307.7</v>
+        <v>334.8</v>
       </c>
       <c r="D61" s="7">
-        <v>1313.5</v>
+        <v>332.1</v>
       </c>
       <c r="E61" s="8">
-        <v>5.8</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>80.84</v>
+        <v>1313.5</v>
       </c>
       <c r="D62" s="7">
-        <v>79.38</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-1.46</v>
+        <v>1306</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C63" s="7">
-        <v>45</v>
+        <v>79.38</v>
       </c>
       <c r="D63" s="7">
-        <v>77</v>
+        <v>77.67</v>
       </c>
       <c r="E63" s="8">
-        <v>32</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="7">
+        <v>77</v>
+      </c>
+      <c r="D64" s="7">
         <v>55</v>
       </c>
-      <c r="D64" s="7">
-        <v>45</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-10</v>
+      <c r="E64" s="8">
+        <v>-22</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3198,13 +3197,13 @@
         <v>13</v>
       </c>
       <c r="C65" s="7">
+        <v>66</v>
+      </c>
+      <c r="D65" s="7">
         <v>77</v>
       </c>
-      <c r="D65" s="7">
-        <v>66</v>
-      </c>
       <c r="E65" s="9">
-        <v>-11</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3215,13 +3214,13 @@
         <v>13</v>
       </c>
       <c r="C66" s="7">
+        <v>55</v>
+      </c>
+      <c r="D66" s="7">
         <v>66</v>
       </c>
-      <c r="D66" s="7">
-        <v>55</v>
-      </c>
       <c r="E66" s="9">
-        <v>-11</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3232,13 +3231,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>45.31</v>
+        <v>64.87</v>
       </c>
       <c r="D67" s="7">
-        <v>64.87</v>
+        <v>61.78</v>
       </c>
       <c r="E67" s="8">
-        <v>19.56</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3249,13 +3248,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>72.06999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="D68" s="7">
-        <v>72.11</v>
+        <v>71.45</v>
       </c>
       <c r="E68" s="8">
-        <v>0.04</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3266,13 +3265,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>72.56999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="D69" s="7">
-        <v>59.8</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-12.77</v>
+        <v>59.59</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3283,13 +3282,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>39.5</v>
+        <v>57.13</v>
       </c>
       <c r="D70" s="7">
-        <v>57.13</v>
-      </c>
-      <c r="E70" s="8">
-        <v>17.63</v>
+        <v>57.51</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0.38</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3300,13 +3299,13 @@
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>30.03</v>
+        <v>29.07</v>
       </c>
       <c r="D71" s="7">
-        <v>29.07</v>
+        <v>46.04</v>
       </c>
       <c r="E71" s="9">
-        <v>-0.96</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3317,13 +3316,13 @@
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>57.45</v>
+        <v>51.44</v>
       </c>
       <c r="D72" s="7">
-        <v>51.44</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-6.01</v>
+        <v>46.78</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-4.66</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3334,13 +3333,13 @@
         <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>54.63</v>
+        <v>50.13</v>
       </c>
       <c r="D73" s="7">
-        <v>50.13</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-4.5</v>
+        <v>47.93</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3351,13 +3350,13 @@
         <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>53.81</v>
+        <v>55.35</v>
       </c>
       <c r="D74" s="7">
-        <v>55.35</v>
+        <v>52.89</v>
       </c>
       <c r="E74" s="8">
-        <v>1.54</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3368,13 +3367,13 @@
         <v>24</v>
       </c>
       <c r="C75" s="7">
-        <v>54.15</v>
+        <v>51.7</v>
       </c>
       <c r="D75" s="7">
-        <v>51.7</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-2.45</v>
+        <v>48.91</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3385,13 +3384,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-63.98</v>
+        <v>475.16</v>
       </c>
       <c r="D76" s="7">
-        <v>475.16</v>
+        <v>220.66</v>
       </c>
       <c r="E76" s="8">
-        <v>539.14</v>
+        <v>-254.5</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3402,13 +3401,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-14.02</v>
+        <v>44.96</v>
       </c>
       <c r="D77" s="7">
-        <v>44.96</v>
+        <v>-30.11</v>
       </c>
       <c r="E77" s="8">
-        <v>58.98</v>
+        <v>-75.06999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3419,13 +3418,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-7.57</v>
+        <v>-37.43</v>
       </c>
       <c r="D78" s="7">
-        <v>-37.43</v>
+        <v>-11.29</v>
       </c>
       <c r="E78" s="9">
-        <v>-29.86</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3436,13 +3435,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>171.01</v>
+        <v>169.21</v>
       </c>
       <c r="D79" s="7">
-        <v>169.21</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-1.8</v>
+        <v>12.64</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-156.57</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3453,13 +3452,13 @@
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>271.88</v>
+        <v>26.85</v>
       </c>
       <c r="D80" s="7">
-        <v>26.85</v>
+        <v>104.22</v>
       </c>
       <c r="E80" s="9">
-        <v>-245.03</v>
+        <v>77.37</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3470,13 +3469,13 @@
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>186.37</v>
+        <v>-36.08</v>
       </c>
       <c r="D81" s="7">
-        <v>-36.08</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-222.45</v>
+        <v>-63.09</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-27.01</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3487,13 +3486,13 @@
         <v>31</v>
       </c>
       <c r="C82" s="7">
-        <v>-71.09</v>
+        <v>-1.1</v>
       </c>
       <c r="D82" s="7">
-        <v>-1.1</v>
+        <v>-30.63</v>
       </c>
       <c r="E82" s="8">
-        <v>69.98999999999999</v>
+        <v>-29.53</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3504,13 +3503,13 @@
         <v>31</v>
       </c>
       <c r="C83" s="7">
-        <v>13.43</v>
+        <v>-35.95</v>
       </c>
       <c r="D83" s="7">
-        <v>-35.95</v>
+        <v>-8.19</v>
       </c>
       <c r="E83" s="9">
-        <v>-49.38</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3521,19 +3520,19 @@
         <v>31</v>
       </c>
       <c r="C84" s="7">
-        <v>-95.48</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="D84" s="7">
-        <v>-94.34999999999999</v>
-      </c>
-      <c r="E84" s="8">
-        <v>1.13</v>
+        <v>-91.53</v>
+      </c>
+      <c r="E84" s="9">
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3557,28 +3556,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3586,22 +3585,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>60.16</v>
+        <v>64.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
       <c r="E2" s="12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F2" s="12">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="G2" s="12">
-        <v>11.8</v>
+        <v>9.6</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3738,31 +3737,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4097999999999999</v>
+        <v>0.4063000000000001</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3829</v>
+        <v>0.3803</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2979</v>
+        <v>0.294</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2598</v>
+        <v>0.255</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1914</v>
+        <v>0.1884</v>
       </c>
       <c r="F2" s="15">
-        <v>0.158</v>
+        <v>0.1686</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1522</v>
+        <v>0.1481</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0354</v>
+        <v>-0.0431</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0578</v>
+        <v>-0.0624</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -193,52 +193,25 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.1 → 46.0</t>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.1</t>
-  </si>
-  <si>
-    <t>46.0</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.4 → 46.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>50.1 → 47.9</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>51.7 → 48.9</t>
-  </si>
-  <si>
-    <t>51.7</t>
+    <t>48.9 → 54.9</t>
   </si>
   <si>
     <t>48.9</t>
+  </si>
+  <si>
+    <t>54.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -440,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -448,7 +421,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -823,8 +795,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -963,10 +935,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>686.25</v>
+        <v>683.7</v>
       </c>
       <c r="D2">
-        <v>-1.18</v>
+        <v>-0.37</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -975,88 +947,88 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-31.89</v>
+        <v>-32.15</v>
       </c>
       <c r="H2">
-        <v>86.89</v>
+        <v>86.19</v>
       </c>
       <c r="I2">
-        <v>6.99</v>
+        <v>7.24</v>
       </c>
       <c r="J2">
-        <v>9.84</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K2">
-        <v>4.01</v>
+        <v>5.04</v>
       </c>
       <c r="L2">
-        <v>15.24</v>
+        <v>12.83</v>
       </c>
       <c r="M2">
-        <v>-6.24</v>
+        <v>-6.05</v>
       </c>
       <c r="N2">
         <v>55</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>657.09</v>
+        <v>666.3200000000001</v>
       </c>
       <c r="Q2">
-        <v>645.03</v>
+        <v>647.58</v>
       </c>
       <c r="R2">
-        <v>645.84</v>
+        <v>646.35</v>
       </c>
       <c r="S2">
-        <v>622.16</v>
+        <v>622.84</v>
       </c>
       <c r="T2">
-        <v>10.3</v>
+        <v>9.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
         <v>47</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>61.78</v>
+        <v>60.81</v>
       </c>
       <c r="Z2">
-        <v>4.72</v>
+        <v>6.79</v>
       </c>
       <c r="AA2">
-        <v>-0.62</v>
+        <v>0.86</v>
       </c>
       <c r="AB2">
-        <v>5.34</v>
+        <v>5.93</v>
       </c>
       <c r="AC2">
-        <v>61.4</v>
+        <v>87.81</v>
       </c>
       <c r="AD2">
-        <v>39.25</v>
+        <v>63.14</v>
       </c>
       <c r="AE2">
-        <v>25.36</v>
+        <v>24.79</v>
       </c>
       <c r="AF2">
-        <v>220.66</v>
+        <v>-57.21</v>
       </c>
       <c r="AG2">
-        <v>683.47</v>
+        <v>689.21</v>
       </c>
       <c r="AH2">
-        <v>606.6</v>
+        <v>605.95</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1065,7 +1037,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.71</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1076,37 +1048,37 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>309.15</v>
+        <v>310.85</v>
       </c>
       <c r="D3">
-        <v>-0.19</v>
+        <v>0.55</v>
       </c>
       <c r="E3">
-        <v>310.25</v>
+        <v>310.85</v>
       </c>
       <c r="F3">
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>101.76</v>
+        <v>102.86</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>0.19</v>
       </c>
       <c r="J3">
-        <v>16.93</v>
+        <v>17.04</v>
       </c>
       <c r="K3">
-        <v>18.9</v>
+        <v>24.06</v>
       </c>
       <c r="L3">
-        <v>58.14</v>
+        <v>57.03</v>
       </c>
       <c r="M3">
-        <v>40.63</v>
+        <v>40.11</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1115,61 +1087,61 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>309.48</v>
+        <v>309.6</v>
       </c>
       <c r="Q3">
-        <v>283.75</v>
+        <v>286.03</v>
       </c>
       <c r="R3">
-        <v>270.5</v>
+        <v>271.55</v>
       </c>
       <c r="S3">
-        <v>214.32</v>
+        <v>215.04</v>
       </c>
       <c r="T3">
-        <v>44.25</v>
+        <v>44.56</v>
       </c>
       <c r="U3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>71.45</v>
+        <v>72.23</v>
       </c>
       <c r="Z3">
-        <v>12.47</v>
+        <v>12.7</v>
       </c>
       <c r="AA3">
-        <v>9.279999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AB3">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="AC3">
-        <v>93.72</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AD3">
-        <v>94.69</v>
+        <v>93.95</v>
       </c>
       <c r="AE3">
-        <v>10.97</v>
+        <v>10.78</v>
       </c>
       <c r="AF3">
-        <v>-30.11</v>
+        <v>-33.87</v>
       </c>
       <c r="AG3">
-        <v>319.71</v>
+        <v>322.82</v>
       </c>
       <c r="AH3">
-        <v>247.79</v>
+        <v>249.24</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1178,7 +1150,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>51.79</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1189,100 +1161,100 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1159.4</v>
+        <v>1145</v>
       </c>
       <c r="D4">
-        <v>-0.05</v>
+        <v>-1.24</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
       </c>
       <c r="F4">
-        <v>962.85</v>
+        <v>975.15</v>
       </c>
       <c r="G4">
-        <v>-10.04</v>
+        <v>-11.16</v>
       </c>
       <c r="H4">
-        <v>20.41</v>
+        <v>17.42</v>
       </c>
       <c r="I4">
-        <v>-1.36</v>
+        <v>-2.14</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="K4">
-        <v>-3.16</v>
+        <v>-3.07</v>
       </c>
       <c r="L4">
-        <v>22.58</v>
+        <v>18.92</v>
       </c>
       <c r="M4">
-        <v>25.5</v>
+        <v>24.22</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1172.3</v>
+        <v>1167.3</v>
       </c>
       <c r="Q4">
-        <v>1131.11</v>
+        <v>1133.31</v>
       </c>
       <c r="R4">
-        <v>1086.72</v>
+        <v>1087.82</v>
       </c>
       <c r="S4">
-        <v>1127.64</v>
+        <v>1127.96</v>
       </c>
       <c r="T4">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
       <c r="U4" t="s">
+        <v>47</v>
+      </c>
+      <c r="V4" t="s">
         <v>48</v>
       </c>
-      <c r="V4" t="s">
-        <v>47</v>
-      </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X4">
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>59.59</v>
+        <v>54.72</v>
       </c>
       <c r="Z4">
-        <v>22.84</v>
+        <v>20.57</v>
       </c>
       <c r="AA4">
-        <v>19.38</v>
+        <v>19.62</v>
       </c>
       <c r="AB4">
-        <v>3.46</v>
+        <v>0.95</v>
       </c>
       <c r="AC4">
-        <v>60.73</v>
+        <v>33.51</v>
       </c>
       <c r="AD4">
-        <v>78.56999999999999</v>
+        <v>57.97</v>
       </c>
       <c r="AE4">
-        <v>27.29</v>
+        <v>27.79</v>
       </c>
       <c r="AF4">
-        <v>-11.29</v>
+        <v>20.2</v>
       </c>
       <c r="AG4">
-        <v>1197.44</v>
+        <v>1198.34</v>
       </c>
       <c r="AH4">
-        <v>1064.77</v>
+        <v>1068.27</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1291,7 +1263,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>42.76</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1302,10 +1274,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>734.9</v>
+        <v>738.4</v>
       </c>
       <c r="D5">
-        <v>0.12</v>
+        <v>0.48</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1314,88 +1286,88 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15</v>
+        <v>-14.59</v>
       </c>
       <c r="H5">
-        <v>11.03</v>
+        <v>11.56</v>
       </c>
       <c r="I5">
-        <v>3.08</v>
+        <v>4.74</v>
       </c>
       <c r="J5">
-        <v>-0.1</v>
+        <v>-0.82</v>
       </c>
       <c r="K5">
-        <v>5.48</v>
+        <v>6.91</v>
       </c>
       <c r="L5">
-        <v>-3.56</v>
+        <v>-2.12</v>
       </c>
       <c r="M5">
-        <v>38.03</v>
+        <v>37.73</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>716.24</v>
+        <v>722.92</v>
       </c>
       <c r="Q5">
-        <v>722.41</v>
+        <v>722.7</v>
       </c>
       <c r="R5">
-        <v>718.98</v>
+        <v>719.84</v>
       </c>
       <c r="S5">
-        <v>749.0700000000001</v>
+        <v>749.02</v>
       </c>
       <c r="T5">
-        <v>-1.89</v>
+        <v>-1.42</v>
       </c>
       <c r="U5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" t="s">
         <v>48</v>
       </c>
-      <c r="V5" t="s">
-        <v>47</v>
-      </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>57.51</v>
+        <v>59.02</v>
       </c>
       <c r="Z5">
-        <v>-1.83</v>
+        <v>-0.13</v>
       </c>
       <c r="AA5">
-        <v>-2.54</v>
+        <v>-2.06</v>
       </c>
       <c r="AB5">
-        <v>0.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>71.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="AD5">
-        <v>46.31</v>
+        <v>72.77</v>
       </c>
       <c r="AE5">
-        <v>17.65</v>
+        <v>17.46</v>
       </c>
       <c r="AF5">
-        <v>12.64</v>
+        <v>175.21</v>
       </c>
       <c r="AG5">
-        <v>751.59</v>
+        <v>752.4299999999999</v>
       </c>
       <c r="AH5">
-        <v>693.22</v>
+        <v>692.97</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1404,7 +1376,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.77</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1415,10 +1387,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>539.8</v>
+        <v>539.5</v>
       </c>
       <c r="D6">
-        <v>4.21</v>
+        <v>-0.06</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1427,88 +1399,88 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-10.03</v>
+        <v>-10.08</v>
       </c>
       <c r="H6">
-        <v>23.08</v>
+        <v>23.02</v>
       </c>
       <c r="I6">
-        <v>-0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="J6">
-        <v>-4.96</v>
+        <v>-4.68</v>
       </c>
       <c r="K6">
-        <v>-8.210000000000001</v>
+        <v>-7.65</v>
       </c>
       <c r="L6">
-        <v>10.89</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M6">
-        <v>16.86</v>
+        <v>16.77</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>531.12</v>
+        <v>530.6</v>
       </c>
       <c r="Q6">
-        <v>548.55</v>
+        <v>547.45</v>
       </c>
       <c r="R6">
-        <v>553.59</v>
+        <v>552.9</v>
       </c>
       <c r="S6">
-        <v>520.04</v>
+        <v>520.11</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="U6" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6" t="s">
         <v>47</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>48</v>
-      </c>
-      <c r="W6" t="s">
-        <v>47</v>
       </c>
       <c r="X6">
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.04</v>
+        <v>45.88</v>
       </c>
       <c r="Z6">
-        <v>-7.27</v>
+        <v>-6.68</v>
       </c>
       <c r="AA6">
-        <v>-5.02</v>
+        <v>-5.35</v>
       </c>
       <c r="AB6">
-        <v>-2.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AC6">
-        <v>26.67</v>
+        <v>57.01</v>
       </c>
       <c r="AD6">
-        <v>9.5</v>
+        <v>27.89</v>
       </c>
       <c r="AE6">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="AF6">
-        <v>104.22</v>
+        <v>-2.64</v>
       </c>
       <c r="AG6">
-        <v>577.63</v>
+        <v>576.12</v>
       </c>
       <c r="AH6">
-        <v>519.47</v>
+        <v>518.77</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1517,7 +1489,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>29.25</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1528,10 +1500,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11441</v>
+        <v>11590</v>
       </c>
       <c r="D7">
-        <v>-2.35</v>
+        <v>1.3</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1540,88 +1512,88 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.38</v>
+        <v>-47.71</v>
       </c>
       <c r="H7">
-        <v>7.38</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I7">
-        <v>-3.3</v>
+        <v>-1.24</v>
       </c>
       <c r="J7">
-        <v>-6.03</v>
+        <v>-5.98</v>
       </c>
       <c r="K7">
-        <v>-8.02</v>
+        <v>-7.32</v>
       </c>
       <c r="L7">
-        <v>-34.25</v>
+        <v>-35.32</v>
       </c>
       <c r="M7">
-        <v>18.84</v>
+        <v>19.26</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P7">
-        <v>11699.4</v>
+        <v>11670.4</v>
       </c>
       <c r="Q7">
-        <v>11669.9</v>
+        <v>11645.3</v>
       </c>
       <c r="R7">
-        <v>11575.94</v>
+        <v>11563.6</v>
       </c>
       <c r="S7">
-        <v>14841.28</v>
+        <v>14809.52</v>
       </c>
       <c r="T7">
-        <v>-22.91</v>
+        <v>-21.74</v>
       </c>
       <c r="U7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V7" t="s">
         <v>48</v>
       </c>
-      <c r="V7" t="s">
-        <v>47</v>
-      </c>
       <c r="W7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>46.78</v>
+        <v>49.45</v>
       </c>
       <c r="Z7">
-        <v>5.28</v>
+        <v>2.02</v>
       </c>
       <c r="AA7">
-        <v>-2.81</v>
+        <v>-1.84</v>
       </c>
       <c r="AB7">
-        <v>8.09</v>
+        <v>3.87</v>
       </c>
       <c r="AC7">
-        <v>66.98999999999999</v>
+        <v>51.17</v>
       </c>
       <c r="AD7">
-        <v>73.05</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AE7">
-        <v>420.64</v>
+        <v>432.38</v>
       </c>
       <c r="AF7">
-        <v>-63.09</v>
+        <v>880.59</v>
       </c>
       <c r="AG7">
-        <v>12205.3</v>
+        <v>12144.99</v>
       </c>
       <c r="AH7">
-        <v>11134.5</v>
+        <v>11145.61</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1630,7 +1602,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>25.81</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1641,10 +1613,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>332.1</v>
+        <v>334.1</v>
       </c>
       <c r="D8">
-        <v>-0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1653,88 +1625,88 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-5.44</v>
+        <v>-4.87</v>
       </c>
       <c r="H8">
-        <v>41.74</v>
+        <v>42.59</v>
       </c>
       <c r="I8">
-        <v>-3.73</v>
+        <v>-1.14</v>
       </c>
       <c r="J8">
-        <v>0.87</v>
+        <v>-0.09</v>
       </c>
       <c r="K8">
-        <v>21.74</v>
+        <v>20.14</v>
       </c>
       <c r="L8">
-        <v>12.2</v>
+        <v>11.95</v>
       </c>
       <c r="M8">
-        <v>29.4</v>
+        <v>29.63</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P8">
-        <v>337.56</v>
+        <v>336.79</v>
       </c>
       <c r="Q8">
-        <v>337.53</v>
+        <v>337.86</v>
       </c>
       <c r="R8">
-        <v>332.58</v>
+        <v>332.49</v>
       </c>
       <c r="S8">
-        <v>285.14</v>
+        <v>285.4</v>
       </c>
       <c r="T8">
-        <v>16.47</v>
+        <v>17.06</v>
       </c>
       <c r="U8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>47.93</v>
+        <v>49.69</v>
       </c>
       <c r="Z8">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AA8">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AB8">
-        <v>-0.93</v>
+        <v>-1.08</v>
       </c>
       <c r="AC8">
-        <v>18.28</v>
+        <v>8.83</v>
       </c>
       <c r="AD8">
-        <v>34.69</v>
+        <v>22.02</v>
       </c>
       <c r="AE8">
-        <v>9.24</v>
+        <v>9.02</v>
       </c>
       <c r="AF8">
-        <v>-30.63</v>
+        <v>11.34</v>
       </c>
       <c r="AG8">
-        <v>348.97</v>
+        <v>348.43</v>
       </c>
       <c r="AH8">
-        <v>326.09</v>
+        <v>327.29</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1743,7 +1715,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>19.8</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1754,37 +1726,37 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D9">
-        <v>-0.57</v>
+        <v>0.15</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1035.5</v>
+        <v>1044</v>
       </c>
       <c r="G9">
-        <v>-2.61</v>
+        <v>-2.46</v>
       </c>
       <c r="H9">
-        <v>26.12</v>
+        <v>25.29</v>
       </c>
       <c r="I9">
-        <v>-2.61</v>
+        <v>-2.21</v>
       </c>
       <c r="J9">
-        <v>0.46</v>
+        <v>-1.65</v>
       </c>
       <c r="K9">
-        <v>0.38</v>
+        <v>1.87</v>
       </c>
       <c r="L9">
-        <v>27.22</v>
+        <v>26.32</v>
       </c>
       <c r="M9">
-        <v>14.81</v>
+        <v>14.65</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1793,58 +1765,58 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>1319.92</v>
+        <v>1314.02</v>
       </c>
       <c r="Q9">
         <v>1300.97</v>
       </c>
       <c r="R9">
-        <v>1269.43</v>
+        <v>1270.96</v>
       </c>
       <c r="S9">
-        <v>1224</v>
+        <v>1224.66</v>
       </c>
       <c r="T9">
-        <v>6.7</v>
+        <v>6.81</v>
       </c>
       <c r="U9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X9">
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>52.89</v>
+        <v>53.49</v>
       </c>
       <c r="Z9">
-        <v>13.07</v>
+        <v>11.88</v>
       </c>
       <c r="AA9">
-        <v>13.3</v>
+        <v>13.02</v>
       </c>
       <c r="AB9">
-        <v>-0.23</v>
+        <v>-1.14</v>
       </c>
       <c r="AC9">
-        <v>32.69</v>
+        <v>32.07</v>
       </c>
       <c r="AD9">
-        <v>51.89</v>
+        <v>39.2</v>
       </c>
       <c r="AE9">
-        <v>24.43</v>
+        <v>24.82</v>
       </c>
       <c r="AF9">
-        <v>-8.19</v>
+        <v>-24.32</v>
       </c>
       <c r="AG9">
-        <v>1347.56</v>
+        <v>1347.57</v>
       </c>
       <c r="AH9">
         <v>1254.38</v>
@@ -1856,7 +1828,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>34.98</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1867,10 +1839,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>77.67</v>
+        <v>81.55</v>
       </c>
       <c r="D10">
-        <v>-2.15</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1879,88 +1851,88 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-15.07</v>
+        <v>-10.83</v>
       </c>
       <c r="H10">
-        <v>115.27</v>
+        <v>126.03</v>
       </c>
       <c r="I10">
-        <v>-4.76</v>
+        <v>1.43</v>
       </c>
       <c r="J10">
-        <v>-5.9</v>
+        <v>-5.38</v>
       </c>
       <c r="K10">
-        <v>55.06</v>
+        <v>60.66</v>
       </c>
       <c r="L10">
-        <v>8.279999999999999</v>
+        <v>14.52</v>
       </c>
       <c r="M10">
-        <v>-4.31</v>
+        <v>-3.74</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>79.38</v>
+        <v>79.61</v>
       </c>
       <c r="Q10">
-        <v>83.59</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="R10">
-        <v>69.25</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="S10">
-        <v>59.72</v>
+        <v>59.77</v>
       </c>
       <c r="T10">
-        <v>30.07</v>
+        <v>36.43</v>
       </c>
       <c r="U10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X10">
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>48.91</v>
+        <v>54.86</v>
       </c>
       <c r="Z10">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AA10">
-        <v>4.02</v>
+        <v>3.64</v>
       </c>
       <c r="AB10">
-        <v>-1.77</v>
+        <v>-1.51</v>
       </c>
       <c r="AC10">
-        <v>5.56</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>5.19</v>
+        <v>6.57</v>
       </c>
       <c r="AE10">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="AF10">
-        <v>-91.53</v>
+        <v>-71.77</v>
       </c>
       <c r="AG10">
-        <v>91.28</v>
+        <v>90.69</v>
       </c>
       <c r="AH10">
-        <v>75.90000000000001</v>
+        <v>75.84</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1969,7 +1941,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>22.25</v>
+        <v>20.19</v>
       </c>
     </row>
   </sheetData>
@@ -2110,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2150,1389 +2122,1318 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>9.84</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>16.93</v>
+      </c>
+      <c r="D10" s="6">
+        <v>17.04</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2.84</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.82</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-4.96</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.03</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-5.98</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.09</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.65</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.9</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-5.38</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6.99</v>
+      </c>
+      <c r="D18" s="6">
+        <v>7.24</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2.22</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.36</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.14</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3.08</v>
+      </c>
+      <c r="D21" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-0.68</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-0.48</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-1.24</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-2.61</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-4.76</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="E26" s="8">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>15.24</v>
+      </c>
+      <c r="D27" s="6">
+        <v>12.83</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>58.14</v>
+      </c>
+      <c r="D28" s="6">
+        <v>57.03</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>22.58</v>
+      </c>
+      <c r="D29" s="6">
+        <v>18.92</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-3.56</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-2.12</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>10.89</v>
+      </c>
+      <c r="D31" s="6">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-34.25</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-35.32</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="D33" s="6">
+        <v>11.95</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>27.22</v>
+      </c>
+      <c r="D34" s="6">
+        <v>26.32</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D35" s="6">
+        <v>14.52</v>
+      </c>
+      <c r="E35" s="8">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4.01</v>
+      </c>
+      <c r="D36" s="6">
+        <v>5.04</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>18.9</v>
+      </c>
+      <c r="D37" s="6">
+        <v>24.06</v>
+      </c>
+      <c r="E37" s="8">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-3.16</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5.48</v>
+      </c>
+      <c r="D39" s="6">
+        <v>6.91</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-7.65</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.02</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-7.32</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>21.74</v>
+      </c>
+      <c r="D42" s="6">
+        <v>20.14</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1.87</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>55.06</v>
+      </c>
+      <c r="D44" s="6">
+        <v>60.66</v>
+      </c>
+      <c r="E44" s="8">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-31.89</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-32.15</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="D46" s="6">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E46" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-10.04</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-11.16</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-15</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-14.59</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-10.03</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-48.38</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-47.71</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-5.44</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-2.61</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-15.07</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-10.83</v>
+      </c>
+      <c r="E53" s="8">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="D10" s="7">
-        <v>9.84</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>686.25</v>
+      </c>
+      <c r="D54" s="6">
+        <v>683.7</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>19.46</v>
-      </c>
-      <c r="D11" s="7">
-        <v>16.93</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>309.15</v>
+      </c>
+      <c r="D55" s="6">
+        <v>310.85</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>4.97</v>
-      </c>
-      <c r="D12" s="7">
-        <v>3.15</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1159.4</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1145</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-14.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.31</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>734.9</v>
+      </c>
+      <c r="D57" s="6">
+        <v>738.4</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-4.96</v>
-      </c>
-      <c r="E14" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>539.8</v>
+      </c>
+      <c r="D58" s="6">
+        <v>539.5</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.5</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-6.03</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-3.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>11441</v>
+      </c>
+      <c r="D59" s="6">
+        <v>11590</v>
+      </c>
+      <c r="E59" s="8">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>332.1</v>
+      </c>
+      <c r="D60" s="6">
+        <v>334.1</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1306</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1308</v>
+      </c>
+      <c r="E61" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>77.67</v>
+      </c>
+      <c r="D62" s="6">
+        <v>81.55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>61.78</v>
+      </c>
+      <c r="D63" s="6">
+        <v>60.81</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>71.45</v>
+      </c>
+      <c r="D64" s="6">
+        <v>72.23</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>59.59</v>
+      </c>
+      <c r="D65" s="6">
+        <v>54.72</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>57.51</v>
+      </c>
+      <c r="D66" s="6">
+        <v>59.02</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>46.04</v>
+      </c>
+      <c r="D67" s="6">
+        <v>45.88</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>46.78</v>
+      </c>
+      <c r="D68" s="6">
+        <v>49.45</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>47.93</v>
+      </c>
+      <c r="D69" s="6">
+        <v>49.69</v>
+      </c>
+      <c r="E69" s="8">
         <v>1.76</v>
       </c>
-      <c r="D16" s="7">
-        <v>0.87</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.46</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>52.89</v>
+      </c>
+      <c r="D70" s="6">
+        <v>53.49</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-5.9</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>48.91</v>
+      </c>
+      <c r="D71" s="6">
+        <v>54.86</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="D19" s="7">
-        <v>6.99</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>220.66</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-57.21</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-277.87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>9.94</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2.22</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-7.72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-30.11</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-33.87</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-3.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.36</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-11.29</v>
+      </c>
+      <c r="D74" s="6">
+        <v>20.2</v>
+      </c>
+      <c r="E74" s="8">
+        <v>31.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>4.65</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>12.64</v>
+      </c>
+      <c r="D75" s="6">
+        <v>175.21</v>
+      </c>
+      <c r="E75" s="8">
+        <v>162.57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-5.54</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-0.68</v>
-      </c>
-      <c r="E23" s="9">
-        <v>4.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>104.22</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-106.86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.36</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-3.3</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-5.66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-63.09</v>
+      </c>
+      <c r="D77" s="6">
+        <v>880.59</v>
+      </c>
+      <c r="E77" s="8">
+        <v>943.6799999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-2.66</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.73</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-30.63</v>
+      </c>
+      <c r="D78" s="6">
+        <v>11.34</v>
+      </c>
+      <c r="E78" s="8">
+        <v>41.97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.52</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-8.19</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-24.32</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-16.13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-3.04</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-4.76</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>34.85</v>
-      </c>
-      <c r="D28" s="7">
-        <v>15.24</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-19.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>56.55</v>
-      </c>
-      <c r="D29" s="7">
-        <v>58.14</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>20.24</v>
-      </c>
-      <c r="D30" s="7">
-        <v>22.58</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-3.56</v>
-      </c>
-      <c r="E31" s="9">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>4.44</v>
-      </c>
-      <c r="D32" s="7">
-        <v>10.89</v>
-      </c>
-      <c r="E32" s="9">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-34.35</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-34.25</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>11.56</v>
-      </c>
-      <c r="D34" s="7">
-        <v>12.2</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>26.81</v>
-      </c>
-      <c r="D35" s="7">
-        <v>27.22</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>9.08</v>
-      </c>
-      <c r="D36" s="7">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>6.61</v>
-      </c>
-      <c r="D37" s="7">
-        <v>4.01</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>23.47</v>
-      </c>
-      <c r="D38" s="7">
-        <v>18.9</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-4.57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-4.24</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-3.16</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>7.68</v>
-      </c>
-      <c r="D40" s="7">
-        <v>5.48</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-10.42</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E41" s="9">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-5.69</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.02</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>23.86</v>
-      </c>
-      <c r="D43" s="7">
-        <v>21.74</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="D44" s="7">
-        <v>0.38</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>64.79000000000001</v>
-      </c>
-      <c r="D45" s="7">
-        <v>55.06</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-9.73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-31.08</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-31.89</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-0.35</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-9.99</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-10.04</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-15</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-13.67</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-10.03</v>
-      </c>
-      <c r="E50" s="9">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-47.14</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-48.38</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-4.67</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-5.44</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-13.2</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-15.07</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>694.45</v>
-      </c>
-      <c r="D55" s="7">
-        <v>686.25</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-8.199999999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>309.75</v>
-      </c>
-      <c r="D56" s="7">
-        <v>309.15</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1160</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1159.4</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>734</v>
-      </c>
-      <c r="D58" s="7">
-        <v>734.9</v>
-      </c>
-      <c r="E58" s="9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>518</v>
-      </c>
-      <c r="D59" s="7">
-        <v>539.8</v>
-      </c>
-      <c r="E59" s="9">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>11716</v>
-      </c>
-      <c r="D60" s="7">
-        <v>11441</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-275</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>334.8</v>
-      </c>
-      <c r="D61" s="7">
-        <v>332.1</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1313.5</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1306</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-7.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>79.38</v>
-      </c>
-      <c r="D63" s="7">
-        <v>77.67</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>77</v>
-      </c>
-      <c r="D64" s="7">
-        <v>55</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>66</v>
-      </c>
-      <c r="D65" s="7">
-        <v>77</v>
-      </c>
-      <c r="E65" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>55</v>
-      </c>
-      <c r="D66" s="7">
-        <v>66</v>
-      </c>
-      <c r="E66" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>64.87</v>
-      </c>
-      <c r="D67" s="7">
-        <v>61.78</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>72.11</v>
-      </c>
-      <c r="D68" s="7">
-        <v>71.45</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>59.8</v>
-      </c>
-      <c r="D69" s="7">
-        <v>59.59</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>57.13</v>
-      </c>
-      <c r="D70" s="7">
-        <v>57.51</v>
-      </c>
-      <c r="E70" s="9">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>29.07</v>
-      </c>
-      <c r="D71" s="7">
-        <v>46.04</v>
-      </c>
-      <c r="E71" s="9">
-        <v>16.97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>51.44</v>
-      </c>
-      <c r="D72" s="7">
-        <v>46.78</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-4.66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>50.13</v>
-      </c>
-      <c r="D73" s="7">
-        <v>47.93</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>55.35</v>
-      </c>
-      <c r="D74" s="7">
-        <v>52.89</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>51.7</v>
-      </c>
-      <c r="D75" s="7">
-        <v>48.91</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="7">
-        <v>475.16</v>
-      </c>
-      <c r="D76" s="7">
-        <v>220.66</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-254.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>44.96</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-30.11</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-75.06999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-37.43</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-11.29</v>
-      </c>
-      <c r="E78" s="9">
-        <v>26.14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>169.21</v>
-      </c>
-      <c r="D79" s="7">
-        <v>12.64</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-156.57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>26.85</v>
-      </c>
-      <c r="D80" s="7">
-        <v>104.22</v>
-      </c>
-      <c r="E80" s="9">
-        <v>77.37</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-36.08</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-63.09</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-27.01</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-30.63</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-29.53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-35.95</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-8.19</v>
-      </c>
-      <c r="E83" s="9">
-        <v>27.76</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-94.34999999999999</v>
-      </c>
-      <c r="D84" s="7">
+      <c r="C80" s="6">
         <v>-91.53</v>
       </c>
-      <c r="E84" s="9">
-        <v>2.82</v>
+      <c r="D80" s="6">
+        <v>-71.77</v>
+      </c>
+      <c r="E80" s="8">
+        <v>19.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3552,61 +3453,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>64.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>55.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>80</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="12">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="13">
-        <v>9</v>
-      </c>
-      <c r="D2" s="12">
-        <v>54.8</v>
-      </c>
-      <c r="E2" s="12">
-        <v>80</v>
-      </c>
-      <c r="F2" s="12">
-        <v>1.6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>9.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>11.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
-        <v>40</v>
+      <c r="I2" s="11">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3707,61 +3608,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.4063000000000001</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3803</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.294</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.255</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1884</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1686</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1481</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0431</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0624</v>
+      <c r="A2" s="14">
+        <v>0.4011</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3773</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2963</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2422</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1926</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1677</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1465</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0374</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0605</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,25 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.9 → 54.9</t>
-  </si>
-  <si>
-    <t>48.9</t>
-  </si>
-  <si>
-    <t>54.9</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.5% → -1.2%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.5%</t>
+  </si>
+  <si>
+    <t>-1.2%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.2 → 65.9</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>72.2</t>
+  </si>
+  <si>
+    <t>65.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -263,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,13 +313,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,14 +443,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -437,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -795,8 +818,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -935,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>683.7</v>
+        <v>672.35</v>
       </c>
       <c r="D2">
-        <v>-0.37</v>
+        <v>-1.66</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -947,46 +970,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.15</v>
+        <v>-33.27</v>
       </c>
       <c r="H2">
-        <v>86.19</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I2">
-        <v>7.24</v>
+        <v>5.74</v>
       </c>
       <c r="J2">
-        <v>9.140000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="K2">
-        <v>5.04</v>
+        <v>5.38</v>
       </c>
       <c r="L2">
-        <v>12.83</v>
+        <v>15.02</v>
       </c>
       <c r="M2">
-        <v>-6.05</v>
+        <v>-6.45</v>
       </c>
       <c r="N2">
         <v>55</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>666.3200000000001</v>
+        <v>673.62</v>
       </c>
       <c r="Q2">
-        <v>647.58</v>
+        <v>650.2</v>
       </c>
       <c r="R2">
-        <v>646.35</v>
+        <v>646.9299999999999</v>
       </c>
       <c r="S2">
-        <v>622.84</v>
+        <v>623.45</v>
       </c>
       <c r="T2">
-        <v>9.77</v>
+        <v>7.84</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1001,34 +1024,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>60.81</v>
+        <v>56.55</v>
       </c>
       <c r="Z2">
-        <v>6.79</v>
+        <v>7.43</v>
       </c>
       <c r="AA2">
-        <v>0.86</v>
+        <v>2.18</v>
       </c>
       <c r="AB2">
-        <v>5.93</v>
+        <v>5.26</v>
       </c>
       <c r="AC2">
-        <v>87.81</v>
+        <v>73.62</v>
       </c>
       <c r="AD2">
-        <v>63.14</v>
+        <v>74.28</v>
       </c>
       <c r="AE2">
-        <v>24.79</v>
+        <v>24.3</v>
       </c>
       <c r="AF2">
-        <v>-57.21</v>
+        <v>-65.88</v>
       </c>
       <c r="AG2">
-        <v>689.21</v>
+        <v>691.1</v>
       </c>
       <c r="AH2">
-        <v>605.95</v>
+        <v>609.3</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1037,7 +1060,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>41.83</v>
+        <v>44.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1048,10 +1071,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>310.85</v>
+        <v>305.3</v>
       </c>
       <c r="D3">
-        <v>0.55</v>
+        <v>-1.79</v>
       </c>
       <c r="E3">
         <v>310.85</v>
@@ -1060,46 +1083,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="H3">
-        <v>102.86</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="I3">
-        <v>0.19</v>
+        <v>-1.07</v>
       </c>
       <c r="J3">
-        <v>17.04</v>
+        <v>15.1</v>
       </c>
       <c r="K3">
-        <v>24.06</v>
+        <v>29.31</v>
       </c>
       <c r="L3">
-        <v>57.03</v>
+        <v>50.11</v>
       </c>
       <c r="M3">
-        <v>40.11</v>
+        <v>39.94</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>309.6</v>
+        <v>308.94</v>
       </c>
       <c r="Q3">
-        <v>286.03</v>
+        <v>287.72</v>
       </c>
       <c r="R3">
-        <v>271.55</v>
+        <v>272.44</v>
       </c>
       <c r="S3">
-        <v>215.04</v>
+        <v>215.74</v>
       </c>
       <c r="T3">
-        <v>44.56</v>
+        <v>41.51</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1114,34 +1137,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>72.23</v>
+        <v>65.89</v>
       </c>
       <c r="Z3">
-        <v>12.7</v>
+        <v>12.29</v>
       </c>
       <c r="AA3">
-        <v>9.960000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="AB3">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="AC3">
-        <v>93.79000000000001</v>
+        <v>82.22</v>
       </c>
       <c r="AD3">
-        <v>93.95</v>
+        <v>89.91</v>
       </c>
       <c r="AE3">
-        <v>10.78</v>
+        <v>10.56</v>
       </c>
       <c r="AF3">
-        <v>-33.87</v>
+        <v>-71.45999999999999</v>
       </c>
       <c r="AG3">
-        <v>322.82</v>
+        <v>324.8</v>
       </c>
       <c r="AH3">
-        <v>249.24</v>
+        <v>250.65</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1150,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>52.31</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1161,58 +1184,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1145</v>
+        <v>1165</v>
       </c>
       <c r="D4">
-        <v>-1.24</v>
+        <v>1.75</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
       </c>
       <c r="F4">
-        <v>975.15</v>
+        <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.16</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="H4">
-        <v>17.42</v>
+        <v>18.15</v>
       </c>
       <c r="I4">
-        <v>-2.14</v>
+        <v>-1.2</v>
       </c>
       <c r="J4">
-        <v>2.84</v>
+        <v>5.81</v>
       </c>
       <c r="K4">
-        <v>-3.07</v>
+        <v>0.75</v>
       </c>
       <c r="L4">
-        <v>18.92</v>
+        <v>19.47</v>
       </c>
       <c r="M4">
-        <v>24.22</v>
+        <v>24.83</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>1167.3</v>
+        <v>1164.46</v>
       </c>
       <c r="Q4">
-        <v>1133.31</v>
+        <v>1136.41</v>
       </c>
       <c r="R4">
-        <v>1087.82</v>
+        <v>1089.93</v>
       </c>
       <c r="S4">
-        <v>1127.96</v>
+        <v>1128.46</v>
       </c>
       <c r="T4">
-        <v>1.51</v>
+        <v>3.24</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1227,34 +1250,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>54.72</v>
+        <v>59.65</v>
       </c>
       <c r="Z4">
-        <v>20.57</v>
+        <v>20.15</v>
       </c>
       <c r="AA4">
-        <v>19.62</v>
+        <v>19.72</v>
       </c>
       <c r="AB4">
-        <v>0.95</v>
+        <v>0.43</v>
       </c>
       <c r="AC4">
-        <v>33.51</v>
+        <v>30.31</v>
       </c>
       <c r="AD4">
-        <v>57.97</v>
+        <v>41.52</v>
       </c>
       <c r="AE4">
-        <v>27.79</v>
+        <v>28.1</v>
       </c>
       <c r="AF4">
-        <v>20.2</v>
+        <v>10.77</v>
       </c>
       <c r="AG4">
-        <v>1198.34</v>
+        <v>1201.27</v>
       </c>
       <c r="AH4">
-        <v>1068.27</v>
+        <v>1071.54</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1263,7 +1286,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>38.08</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1274,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>738.4</v>
+        <v>737.85</v>
       </c>
       <c r="D5">
-        <v>0.48</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1286,46 +1309,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.59</v>
+        <v>-14.66</v>
       </c>
       <c r="H5">
-        <v>11.56</v>
+        <v>11.47</v>
       </c>
       <c r="I5">
-        <v>4.74</v>
+        <v>4.64</v>
       </c>
       <c r="J5">
-        <v>-0.82</v>
+        <v>0.73</v>
       </c>
       <c r="K5">
-        <v>6.91</v>
+        <v>10.84</v>
       </c>
       <c r="L5">
-        <v>-2.12</v>
+        <v>-2.95</v>
       </c>
       <c r="M5">
-        <v>37.73</v>
+        <v>36.27</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>722.92</v>
+        <v>729.46</v>
       </c>
       <c r="Q5">
-        <v>722.7</v>
+        <v>722.86</v>
       </c>
       <c r="R5">
-        <v>719.84</v>
+        <v>720.7</v>
       </c>
       <c r="S5">
-        <v>749.02</v>
+        <v>748.96</v>
       </c>
       <c r="T5">
-        <v>-1.42</v>
+        <v>-1.48</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1340,34 +1363,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>59.02</v>
+        <v>58.67</v>
       </c>
       <c r="Z5">
-        <v>-0.13</v>
+        <v>1.16</v>
       </c>
       <c r="AA5">
-        <v>-2.06</v>
+        <v>-1.41</v>
       </c>
       <c r="AB5">
-        <v>1.93</v>
+        <v>2.58</v>
       </c>
       <c r="AC5">
-        <v>100</v>
+        <v>99.48</v>
       </c>
       <c r="AD5">
-        <v>72.77</v>
+        <v>90.47</v>
       </c>
       <c r="AE5">
-        <v>17.46</v>
+        <v>16.88</v>
       </c>
       <c r="AF5">
-        <v>175.21</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="AG5">
-        <v>752.4299999999999</v>
+        <v>752.89</v>
       </c>
       <c r="AH5">
-        <v>692.97</v>
+        <v>692.83</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1376,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>27.05</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1387,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>539.5</v>
+        <v>539.85</v>
       </c>
       <c r="D6">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1399,46 +1422,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-10.08</v>
+        <v>-10.03</v>
       </c>
       <c r="H6">
-        <v>23.02</v>
+        <v>23.1</v>
       </c>
       <c r="I6">
-        <v>-0.48</v>
+        <v>0.85</v>
       </c>
       <c r="J6">
-        <v>-4.68</v>
+        <v>-3.86</v>
       </c>
       <c r="K6">
-        <v>-7.65</v>
+        <v>-5.45</v>
       </c>
       <c r="L6">
-        <v>8.029999999999999</v>
+        <v>5.94</v>
       </c>
       <c r="M6">
-        <v>16.77</v>
+        <v>16.65</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>530.6</v>
+        <v>531.51</v>
       </c>
       <c r="Q6">
-        <v>547.45</v>
+        <v>546.22</v>
       </c>
       <c r="R6">
-        <v>552.9</v>
+        <v>552.22</v>
       </c>
       <c r="S6">
-        <v>520.11</v>
+        <v>520.1799999999999</v>
       </c>
       <c r="T6">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1453,34 +1476,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.88</v>
+        <v>46.12</v>
       </c>
       <c r="Z6">
-        <v>-6.68</v>
+        <v>-6.12</v>
       </c>
       <c r="AA6">
-        <v>-5.35</v>
+        <v>-5.51</v>
       </c>
       <c r="AB6">
-        <v>-1.33</v>
+        <v>-0.61</v>
       </c>
       <c r="AC6">
-        <v>57.01</v>
+        <v>90.34</v>
       </c>
       <c r="AD6">
-        <v>27.89</v>
+        <v>58.01</v>
       </c>
       <c r="AE6">
-        <v>12.8</v>
+        <v>12.31</v>
       </c>
       <c r="AF6">
-        <v>-2.64</v>
+        <v>36.66</v>
       </c>
       <c r="AG6">
-        <v>576.12</v>
+        <v>573.9299999999999</v>
       </c>
       <c r="AH6">
-        <v>518.77</v>
+        <v>518.51</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1489,7 +1512,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>26.48</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1500,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11590</v>
+        <v>11472</v>
       </c>
       <c r="D7">
-        <v>1.3</v>
+        <v>-1.02</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1512,46 +1535,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-47.71</v>
+        <v>-48.24</v>
       </c>
       <c r="H7">
-        <v>8.779999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="I7">
-        <v>-1.24</v>
+        <v>-0.92</v>
       </c>
       <c r="J7">
-        <v>-5.98</v>
+        <v>-5.05</v>
       </c>
       <c r="K7">
-        <v>-7.32</v>
+        <v>-6.6</v>
       </c>
       <c r="L7">
-        <v>-35.32</v>
+        <v>-35.9</v>
       </c>
       <c r="M7">
-        <v>19.26</v>
+        <v>19.01</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P7">
-        <v>11670.4</v>
+        <v>11649.2</v>
       </c>
       <c r="Q7">
-        <v>11645.3</v>
+        <v>11617.65</v>
       </c>
       <c r="R7">
-        <v>11563.6</v>
+        <v>11550.04</v>
       </c>
       <c r="S7">
-        <v>14809.52</v>
+        <v>14778.91</v>
       </c>
       <c r="T7">
-        <v>-21.74</v>
+        <v>-22.38</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1566,34 +1589,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>49.45</v>
+        <v>47.42</v>
       </c>
       <c r="Z7">
-        <v>2.02</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AA7">
-        <v>-1.84</v>
+        <v>-3.47</v>
       </c>
       <c r="AB7">
-        <v>3.87</v>
+        <v>-6.5</v>
       </c>
       <c r="AC7">
-        <v>51.17</v>
+        <v>43.22</v>
       </c>
       <c r="AD7">
-        <v>64.01000000000001</v>
+        <v>53.79</v>
       </c>
       <c r="AE7">
-        <v>432.38</v>
+        <v>433.71</v>
       </c>
       <c r="AF7">
-        <v>880.59</v>
+        <v>-40.4</v>
       </c>
       <c r="AG7">
-        <v>12144.99</v>
+        <v>12089.29</v>
       </c>
       <c r="AH7">
-        <v>11145.61</v>
+        <v>11146.01</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1602,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>26.65</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1613,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>334.1</v>
+        <v>333</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>-0.33</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1625,46 +1648,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-4.87</v>
+        <v>-5.18</v>
       </c>
       <c r="H8">
-        <v>42.59</v>
+        <v>42.12</v>
       </c>
       <c r="I8">
-        <v>-1.14</v>
+        <v>-2.9</v>
       </c>
       <c r="J8">
-        <v>-0.09</v>
+        <v>1.68</v>
       </c>
       <c r="K8">
-        <v>20.14</v>
+        <v>24.05</v>
       </c>
       <c r="L8">
-        <v>11.95</v>
+        <v>10.01</v>
       </c>
       <c r="M8">
-        <v>29.63</v>
+        <v>29.46</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P8">
-        <v>336.79</v>
+        <v>334.8</v>
       </c>
       <c r="Q8">
-        <v>337.86</v>
+        <v>337.72</v>
       </c>
       <c r="R8">
-        <v>332.49</v>
+        <v>332.55</v>
       </c>
       <c r="S8">
-        <v>285.4</v>
+        <v>285.69</v>
       </c>
       <c r="T8">
-        <v>17.06</v>
+        <v>16.56</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1679,34 +1702,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>49.69</v>
+        <v>48.72</v>
       </c>
       <c r="Z8">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AA8">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AB8">
-        <v>-1.08</v>
+        <v>-1.22</v>
       </c>
       <c r="AC8">
-        <v>8.83</v>
+        <v>6.84</v>
       </c>
       <c r="AD8">
-        <v>22.02</v>
+        <v>11.32</v>
       </c>
       <c r="AE8">
-        <v>9.02</v>
+        <v>8.75</v>
       </c>
       <c r="AF8">
-        <v>11.34</v>
+        <v>-15.55</v>
       </c>
       <c r="AG8">
-        <v>348.43</v>
+        <v>348.48</v>
       </c>
       <c r="AH8">
-        <v>327.29</v>
+        <v>326.97</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1715,7 +1738,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>20.02</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1726,37 +1749,37 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1308</v>
+        <v>1325</v>
       </c>
       <c r="D9">
-        <v>0.15</v>
+        <v>1.3</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1044</v>
+        <v>1072.2</v>
       </c>
       <c r="G9">
-        <v>-2.46</v>
+        <v>-1.19</v>
       </c>
       <c r="H9">
-        <v>25.29</v>
+        <v>23.58</v>
       </c>
       <c r="I9">
-        <v>-2.21</v>
+        <v>-0.74</v>
       </c>
       <c r="J9">
-        <v>-1.65</v>
+        <v>1.31</v>
       </c>
       <c r="K9">
-        <v>1.87</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
-        <v>26.32</v>
+        <v>26.92</v>
       </c>
       <c r="M9">
-        <v>14.65</v>
+        <v>15.1</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1765,19 +1788,19 @@
         <v>70</v>
       </c>
       <c r="P9">
-        <v>1314.02</v>
+        <v>1312.04</v>
       </c>
       <c r="Q9">
-        <v>1300.97</v>
+        <v>1302.25</v>
       </c>
       <c r="R9">
-        <v>1270.96</v>
+        <v>1272.84</v>
       </c>
       <c r="S9">
-        <v>1224.66</v>
+        <v>1225.47</v>
       </c>
       <c r="T9">
-        <v>6.81</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1792,34 +1815,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>53.49</v>
+        <v>58.3</v>
       </c>
       <c r="Z9">
-        <v>11.88</v>
+        <v>12.17</v>
       </c>
       <c r="AA9">
-        <v>13.02</v>
+        <v>12.85</v>
       </c>
       <c r="AB9">
-        <v>-1.14</v>
+        <v>-0.68</v>
       </c>
       <c r="AC9">
-        <v>32.07</v>
+        <v>37.74</v>
       </c>
       <c r="AD9">
-        <v>39.2</v>
+        <v>34.17</v>
       </c>
       <c r="AE9">
-        <v>24.82</v>
+        <v>25.31</v>
       </c>
       <c r="AF9">
-        <v>-24.32</v>
+        <v>-34.22</v>
       </c>
       <c r="AG9">
-        <v>1347.57</v>
+        <v>1350.05</v>
       </c>
       <c r="AH9">
-        <v>1254.38</v>
+        <v>1254.45</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1828,7 +1851,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.81</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1839,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.55</v>
+        <v>85.47</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1851,46 +1874,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.83</v>
+        <v>-6.54</v>
       </c>
       <c r="H10">
-        <v>126.03</v>
+        <v>136.89</v>
       </c>
       <c r="I10">
-        <v>1.43</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>-5.38</v>
+        <v>-3.06</v>
       </c>
       <c r="K10">
-        <v>60.66</v>
+        <v>75.97</v>
       </c>
       <c r="L10">
-        <v>14.52</v>
+        <v>15.1</v>
       </c>
       <c r="M10">
-        <v>-3.74</v>
+        <v>-2.81</v>
       </c>
       <c r="N10">
+        <v>99</v>
+      </c>
+      <c r="O10">
         <v>88</v>
       </c>
-      <c r="O10">
-        <v>85</v>
-      </c>
       <c r="P10">
-        <v>79.61</v>
+        <v>80.98</v>
       </c>
       <c r="Q10">
-        <v>83.26000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="R10">
-        <v>69.84999999999999</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="S10">
-        <v>59.77</v>
+        <v>59.85</v>
       </c>
       <c r="T10">
-        <v>36.43</v>
+        <v>42.8</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1905,31 +1928,31 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>54.86</v>
+        <v>59.93</v>
       </c>
       <c r="Z10">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="AA10">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="AB10">
-        <v>-1.51</v>
+        <v>-1.04</v>
       </c>
       <c r="AC10">
-        <v>8.6</v>
+        <v>28.58</v>
       </c>
       <c r="AD10">
-        <v>6.57</v>
+        <v>14.25</v>
       </c>
       <c r="AE10">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="AF10">
-        <v>-71.77</v>
+        <v>-32.22</v>
       </c>
       <c r="AG10">
-        <v>90.69</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="AH10">
         <v>75.84</v>
@@ -1941,7 +1964,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.19</v>
+        <v>20.68</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2122,1318 +2145,1332 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D8" s="7">
+        <v>6.26</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>17.04</v>
+      </c>
+      <c r="D9" s="7">
+        <v>15.1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2.84</v>
+      </c>
+      <c r="D10" s="7">
+        <v>5.81</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.82</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-4.68</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-3.86</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-5.98</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-5.05</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-0.09</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-1.65</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-5.38</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-3.06</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>7.24</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5.74</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-1.07</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-2.14</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.2</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>4.74</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4.64</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.48</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-1.24</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.92</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-2.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.21</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-0.74</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="D25" s="7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E25" s="9">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>12.83</v>
+      </c>
+      <c r="D26" s="7">
+        <v>15.02</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>57.03</v>
+      </c>
+      <c r="D27" s="7">
+        <v>50.11</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>18.92</v>
+      </c>
+      <c r="D28" s="7">
+        <v>19.47</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-2.12</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-2.95</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="D30" s="7">
+        <v>5.94</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-35.32</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-35.9</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>11.95</v>
+      </c>
+      <c r="D32" s="7">
+        <v>10.01</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>26.32</v>
+      </c>
+      <c r="D33" s="7">
+        <v>26.92</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>14.52</v>
+      </c>
+      <c r="D34" s="7">
+        <v>15.1</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>5.04</v>
+      </c>
+      <c r="D35" s="7">
+        <v>5.38</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>24.06</v>
+      </c>
+      <c r="D36" s="7">
+        <v>29.31</v>
+      </c>
+      <c r="E36" s="9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-3.07</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="E37" s="9">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>6.91</v>
+      </c>
+      <c r="D38" s="7">
+        <v>10.84</v>
+      </c>
+      <c r="E38" s="9">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-7.65</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-5.45</v>
+      </c>
+      <c r="E39" s="9">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-7.32</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-6.6</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>20.14</v>
+      </c>
+      <c r="D41" s="7">
+        <v>24.05</v>
+      </c>
+      <c r="E41" s="9">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="D42" s="7">
+        <v>5.1</v>
+      </c>
+      <c r="E42" s="9">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>60.66</v>
+      </c>
+      <c r="D43" s="7">
+        <v>75.97</v>
+      </c>
+      <c r="E43" s="9">
+        <v>15.31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-32.15</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-33.27</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D45" s="7">
+        <v>-1.79</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-11.16</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-14.59</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-14.66</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-10.08</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-10.03</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-47.71</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-48.24</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-4.87</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-5.18</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-2.46</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-1.19</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-10.83</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-6.54</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>9.84</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>683.7</v>
+      </c>
+      <c r="D53" s="7">
+        <v>672.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-11.35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>16.93</v>
-      </c>
-      <c r="D10" s="6">
-        <v>17.04</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>310.85</v>
+      </c>
+      <c r="D54" s="7">
+        <v>305.3</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-5.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2.84</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1145</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1165</v>
+      </c>
+      <c r="E55" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.82</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>738.4</v>
+      </c>
+      <c r="D56" s="7">
+        <v>737.85</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-4.96</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-4.68</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>539.5</v>
+      </c>
+      <c r="D57" s="7">
+        <v>539.85</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-6.03</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-5.98</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11590</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11472</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>334.1</v>
+      </c>
+      <c r="D59" s="7">
+        <v>333</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.65</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1308</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1325</v>
+      </c>
+      <c r="E60" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.38</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>81.55</v>
+      </c>
+      <c r="D61" s="7">
+        <v>85.47</v>
+      </c>
+      <c r="E61" s="9">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>99</v>
+      </c>
+      <c r="D62" s="7">
+        <v>88</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>88</v>
+      </c>
+      <c r="D63" s="7">
+        <v>99</v>
+      </c>
+      <c r="E63" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>6.99</v>
-      </c>
-      <c r="D18" s="6">
-        <v>7.24</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>60.81</v>
+      </c>
+      <c r="D64" s="7">
+        <v>56.55</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-4.26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2.22</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="E19" s="7">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>72.23</v>
+      </c>
+      <c r="D65" s="7">
+        <v>65.89</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-6.34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>54.72</v>
+      </c>
+      <c r="D66" s="7">
+        <v>59.65</v>
+      </c>
+      <c r="E66" s="9">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>59.02</v>
+      </c>
+      <c r="D67" s="7">
+        <v>58.67</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>45.88</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46.12</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>49.45</v>
+      </c>
+      <c r="D69" s="7">
+        <v>47.42</v>
+      </c>
+      <c r="E69" s="8">
         <v>-2.03</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>49.69</v>
+      </c>
+      <c r="D70" s="7">
+        <v>48.72</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>53.49</v>
+      </c>
+      <c r="D71" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="E71" s="9">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>54.86</v>
+      </c>
+      <c r="D72" s="7">
+        <v>59.93</v>
+      </c>
+      <c r="E72" s="9">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-57.21</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-65.88</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-8.67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-33.87</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-71.45999999999999</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-37.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="D75" s="7">
+        <v>10.77</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-9.43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="D21" s="6">
-        <v>4.74</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>175.21</v>
+      </c>
+      <c r="D76" s="7">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-88.56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.68</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.48</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-2.64</v>
+      </c>
+      <c r="D77" s="7">
+        <v>36.66</v>
+      </c>
+      <c r="E77" s="9">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.24</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>880.59</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-40.4</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-920.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>11.34</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-15.55</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-26.89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-24.32</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-34.22</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-9.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-4.76</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1.43</v>
-      </c>
-      <c r="E26" s="8">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>15.24</v>
-      </c>
-      <c r="D27" s="6">
-        <v>12.83</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>58.14</v>
-      </c>
-      <c r="D28" s="6">
-        <v>57.03</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>22.58</v>
-      </c>
-      <c r="D29" s="6">
-        <v>18.92</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>10.89</v>
-      </c>
-      <c r="D31" s="6">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-34.25</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-35.32</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>12.2</v>
-      </c>
-      <c r="D33" s="6">
-        <v>11.95</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>27.22</v>
-      </c>
-      <c r="D34" s="6">
-        <v>26.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="D35" s="6">
-        <v>14.52</v>
-      </c>
-      <c r="E35" s="8">
-        <v>6.24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4.01</v>
-      </c>
-      <c r="D36" s="6">
-        <v>5.04</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>18.9</v>
-      </c>
-      <c r="D37" s="6">
-        <v>24.06</v>
-      </c>
-      <c r="E37" s="8">
-        <v>5.16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5.48</v>
-      </c>
-      <c r="D39" s="6">
-        <v>6.91</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-7.32</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>21.74</v>
-      </c>
-      <c r="D42" s="6">
-        <v>20.14</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1.87</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>55.06</v>
-      </c>
-      <c r="D44" s="6">
-        <v>60.66</v>
-      </c>
-      <c r="E44" s="8">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-31.89</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-32.15</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="D46" s="6">
-        <v>0</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-10.04</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-11.16</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-15</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-14.59</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-48.38</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-47.71</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-15.07</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="E53" s="8">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>686.25</v>
-      </c>
-      <c r="D54" s="6">
-        <v>683.7</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>309.15</v>
-      </c>
-      <c r="D55" s="6">
-        <v>310.85</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1159.4</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1145</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-14.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>734.9</v>
-      </c>
-      <c r="D57" s="6">
-        <v>738.4</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>539.8</v>
-      </c>
-      <c r="D58" s="6">
-        <v>539.5</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>11441</v>
-      </c>
-      <c r="D59" s="6">
-        <v>11590</v>
-      </c>
-      <c r="E59" s="8">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>332.1</v>
-      </c>
-      <c r="D60" s="6">
-        <v>334.1</v>
-      </c>
-      <c r="E60" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1306</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1308</v>
-      </c>
-      <c r="E61" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>77.67</v>
-      </c>
-      <c r="D62" s="6">
-        <v>81.55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>61.78</v>
-      </c>
-      <c r="D63" s="6">
-        <v>60.81</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>71.45</v>
-      </c>
-      <c r="D64" s="6">
-        <v>72.23</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>59.59</v>
-      </c>
-      <c r="D65" s="6">
-        <v>54.72</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-4.87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>57.51</v>
-      </c>
-      <c r="D66" s="6">
-        <v>59.02</v>
-      </c>
-      <c r="E66" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>46.04</v>
-      </c>
-      <c r="D67" s="6">
-        <v>45.88</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>46.78</v>
-      </c>
-      <c r="D68" s="6">
-        <v>49.45</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>47.93</v>
-      </c>
-      <c r="D69" s="6">
-        <v>49.69</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>52.89</v>
-      </c>
-      <c r="D70" s="6">
-        <v>53.49</v>
-      </c>
-      <c r="E70" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>48.91</v>
-      </c>
-      <c r="D71" s="6">
-        <v>54.86</v>
-      </c>
-      <c r="E71" s="8">
-        <v>5.95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>220.66</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-57.21</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-277.87</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-30.11</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-33.87</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-3.76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-11.29</v>
-      </c>
-      <c r="D74" s="6">
-        <v>20.2</v>
-      </c>
-      <c r="E74" s="8">
-        <v>31.49</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>12.64</v>
-      </c>
-      <c r="D75" s="6">
-        <v>175.21</v>
-      </c>
-      <c r="E75" s="8">
-        <v>162.57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>104.22</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-106.86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-63.09</v>
-      </c>
-      <c r="D77" s="6">
-        <v>880.59</v>
-      </c>
-      <c r="E77" s="8">
-        <v>943.6799999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-30.63</v>
-      </c>
-      <c r="D78" s="6">
-        <v>11.34</v>
-      </c>
-      <c r="E78" s="8">
-        <v>41.97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-8.19</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-24.32</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-16.13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-91.53</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C81" s="7">
         <v>-71.77</v>
       </c>
-      <c r="E80" s="8">
-        <v>19.76</v>
+      <c r="D81" s="7">
+        <v>-32.22</v>
+      </c>
+      <c r="E81" s="9">
+        <v>39.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3453,60 +3490,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>64.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>55.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>55.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>80</v>
       </c>
-      <c r="F2" s="11">
-        <v>1.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>11.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>2.1</v>
+      </c>
+      <c r="G2" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3608,61 +3645,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.4011</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3773</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2963</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2422</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1926</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1677</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1465</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0374</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0605</v>
+      <c r="A2" s="15">
+        <v>0.3994</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3627</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2946</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2483</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1901</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1665</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.151</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0281</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0645</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.5% → -1.2%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.5%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.2% → -2.9%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.2%</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.2 → 65.9</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.2</t>
-  </si>
-  <si>
-    <t>65.9</t>
+    <t>-2.9%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,13 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,11 +428,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -825,7 +809,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -958,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>672.35</v>
+        <v>699.1</v>
       </c>
       <c r="D2">
-        <v>-1.66</v>
+        <v>3.98</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -970,46 +955,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.27</v>
+        <v>-30.62</v>
       </c>
       <c r="H2">
-        <v>83.09999999999999</v>
+        <v>90.39</v>
       </c>
       <c r="I2">
-        <v>5.74</v>
+        <v>10.73</v>
       </c>
       <c r="J2">
-        <v>6.26</v>
+        <v>12.76</v>
       </c>
       <c r="K2">
-        <v>5.38</v>
+        <v>4.36</v>
       </c>
       <c r="L2">
-        <v>15.02</v>
+        <v>17.58</v>
       </c>
       <c r="M2">
-        <v>-6.45</v>
+        <v>-5.7</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>673.62</v>
+        <v>687.17</v>
       </c>
       <c r="Q2">
-        <v>650.2</v>
+        <v>653.73</v>
       </c>
       <c r="R2">
-        <v>646.9299999999999</v>
+        <v>648.15</v>
       </c>
       <c r="S2">
-        <v>623.45</v>
+        <v>624.21</v>
       </c>
       <c r="T2">
-        <v>7.84</v>
+        <v>12</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1024,34 +1009,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>56.55</v>
+        <v>63.11</v>
       </c>
       <c r="Z2">
-        <v>7.43</v>
+        <v>9.98</v>
       </c>
       <c r="AA2">
-        <v>2.18</v>
+        <v>3.74</v>
       </c>
       <c r="AB2">
-        <v>5.26</v>
+        <v>6.25</v>
       </c>
       <c r="AC2">
-        <v>73.62</v>
+        <v>75.89</v>
       </c>
       <c r="AD2">
-        <v>74.28</v>
+        <v>79.11</v>
       </c>
       <c r="AE2">
-        <v>24.3</v>
+        <v>25.93</v>
       </c>
       <c r="AF2">
-        <v>-65.88</v>
+        <v>11.64</v>
       </c>
       <c r="AG2">
-        <v>691.1</v>
+        <v>698.73</v>
       </c>
       <c r="AH2">
-        <v>609.3</v>
+        <v>608.73</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1060,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>44.23</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1071,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>305.3</v>
+        <v>309.55</v>
       </c>
       <c r="D3">
-        <v>-1.79</v>
+        <v>1.39</v>
       </c>
       <c r="E3">
         <v>310.85</v>
@@ -1083,46 +1068,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-1.79</v>
+        <v>-0.42</v>
       </c>
       <c r="H3">
-        <v>99.23999999999999</v>
+        <v>102.02</v>
       </c>
       <c r="I3">
-        <v>-1.07</v>
+        <v>-0.03</v>
       </c>
       <c r="J3">
-        <v>15.1</v>
+        <v>14.06</v>
       </c>
       <c r="K3">
-        <v>29.31</v>
+        <v>29.08</v>
       </c>
       <c r="L3">
-        <v>50.11</v>
+        <v>49.05</v>
       </c>
       <c r="M3">
-        <v>39.94</v>
+        <v>40.5</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>308.94</v>
+        <v>308.92</v>
       </c>
       <c r="Q3">
-        <v>287.72</v>
+        <v>289.25</v>
       </c>
       <c r="R3">
-        <v>272.44</v>
+        <v>273.43</v>
       </c>
       <c r="S3">
-        <v>215.74</v>
+        <v>216.47</v>
       </c>
       <c r="T3">
-        <v>41.51</v>
+        <v>43</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1137,34 +1122,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>65.89</v>
+        <v>68.19</v>
       </c>
       <c r="Z3">
-        <v>12.29</v>
+        <v>12.18</v>
       </c>
       <c r="AA3">
-        <v>10.43</v>
+        <v>10.78</v>
       </c>
       <c r="AB3">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>82.22</v>
+        <v>76.09</v>
       </c>
       <c r="AD3">
-        <v>89.91</v>
+        <v>84.03</v>
       </c>
       <c r="AE3">
-        <v>10.56</v>
+        <v>10.33</v>
       </c>
       <c r="AF3">
-        <v>-71.45999999999999</v>
+        <v>-26.39</v>
       </c>
       <c r="AG3">
-        <v>324.8</v>
+        <v>327.32</v>
       </c>
       <c r="AH3">
-        <v>250.65</v>
+        <v>251.18</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1173,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>51.12</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1184,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1165</v>
+        <v>1147.9</v>
       </c>
       <c r="D4">
-        <v>1.75</v>
+        <v>-1.47</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1196,46 +1181,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-9.609999999999999</v>
+        <v>-10.93</v>
       </c>
       <c r="H4">
-        <v>18.15</v>
+        <v>16.42</v>
       </c>
       <c r="I4">
-        <v>-1.2</v>
+        <v>-3.77</v>
       </c>
       <c r="J4">
-        <v>5.81</v>
+        <v>4.07</v>
       </c>
       <c r="K4">
-        <v>0.75</v>
+        <v>-0.17</v>
       </c>
       <c r="L4">
-        <v>19.47</v>
+        <v>11.63</v>
       </c>
       <c r="M4">
-        <v>24.83</v>
+        <v>23.83</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P4">
-        <v>1164.46</v>
+        <v>1155.46</v>
       </c>
       <c r="Q4">
-        <v>1136.41</v>
+        <v>1137.55</v>
       </c>
       <c r="R4">
-        <v>1089.93</v>
+        <v>1091.53</v>
       </c>
       <c r="S4">
-        <v>1128.46</v>
+        <v>1128.84</v>
       </c>
       <c r="T4">
-        <v>3.24</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1250,34 +1235,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>59.65</v>
+        <v>54.21</v>
       </c>
       <c r="Z4">
-        <v>20.15</v>
+        <v>18.23</v>
       </c>
       <c r="AA4">
-        <v>19.72</v>
+        <v>19.42</v>
       </c>
       <c r="AB4">
-        <v>0.43</v>
+        <v>-1.2</v>
       </c>
       <c r="AC4">
-        <v>30.31</v>
+        <v>16.77</v>
       </c>
       <c r="AD4">
-        <v>41.52</v>
+        <v>26.86</v>
       </c>
       <c r="AE4">
-        <v>28.1</v>
+        <v>28.81</v>
       </c>
       <c r="AF4">
-        <v>10.77</v>
+        <v>-1.85</v>
       </c>
       <c r="AG4">
-        <v>1201.27</v>
+        <v>1202.37</v>
       </c>
       <c r="AH4">
-        <v>1071.54</v>
+        <v>1072.73</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1286,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>34.41</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1297,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>737.85</v>
+        <v>736.8</v>
       </c>
       <c r="D5">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1309,46 +1294,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.66</v>
+        <v>-14.78</v>
       </c>
       <c r="H5">
-        <v>11.47</v>
+        <v>11.32</v>
       </c>
       <c r="I5">
-        <v>4.64</v>
+        <v>4.93</v>
       </c>
       <c r="J5">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="K5">
-        <v>10.84</v>
+        <v>10.71</v>
       </c>
       <c r="L5">
-        <v>-2.95</v>
+        <v>-3.02</v>
       </c>
       <c r="M5">
-        <v>36.27</v>
+        <v>36.35</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>729.46</v>
+        <v>736.39</v>
       </c>
       <c r="Q5">
-        <v>722.86</v>
+        <v>723.0599999999999</v>
       </c>
       <c r="R5">
-        <v>720.7</v>
+        <v>721.77</v>
       </c>
       <c r="S5">
-        <v>748.96</v>
+        <v>748.79</v>
       </c>
       <c r="T5">
-        <v>-1.48</v>
+        <v>-1.6</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1363,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>58.67</v>
+        <v>57.95</v>
       </c>
       <c r="Z5">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="AA5">
-        <v>-1.41</v>
+        <v>-0.71</v>
       </c>
       <c r="AB5">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="AC5">
-        <v>99.48</v>
+        <v>97.91</v>
       </c>
       <c r="AD5">
-        <v>90.47</v>
+        <v>99.13</v>
       </c>
       <c r="AE5">
-        <v>16.88</v>
+        <v>16.6</v>
       </c>
       <c r="AF5">
-        <v>86.65000000000001</v>
+        <v>22.32</v>
       </c>
       <c r="AG5">
-        <v>752.89</v>
+        <v>753.4299999999999</v>
       </c>
       <c r="AH5">
-        <v>692.83</v>
+        <v>692.6900000000001</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1399,7 +1384,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>29.07</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1410,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>539.85</v>
+        <v>530</v>
       </c>
       <c r="D6">
-        <v>0.06</v>
+        <v>-1.82</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1422,46 +1407,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-10.03</v>
+        <v>-11.67</v>
       </c>
       <c r="H6">
-        <v>23.1</v>
+        <v>20.85</v>
       </c>
       <c r="I6">
-        <v>0.85</v>
+        <v>1.84</v>
       </c>
       <c r="J6">
-        <v>-3.86</v>
+        <v>-6.09</v>
       </c>
       <c r="K6">
-        <v>-5.45</v>
+        <v>-7.08</v>
       </c>
       <c r="L6">
-        <v>5.94</v>
+        <v>4.47</v>
       </c>
       <c r="M6">
-        <v>16.65</v>
+        <v>16.39</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>531.51</v>
+        <v>533.4299999999999</v>
       </c>
       <c r="Q6">
-        <v>546.22</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="R6">
-        <v>552.22</v>
+        <v>551.1</v>
       </c>
       <c r="S6">
-        <v>520.1799999999999</v>
+        <v>520.27</v>
       </c>
       <c r="T6">
-        <v>3.78</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1476,34 +1461,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.12</v>
+        <v>40.67</v>
       </c>
       <c r="Z6">
-        <v>-6.12</v>
+        <v>-6.39</v>
       </c>
       <c r="AA6">
-        <v>-5.51</v>
+        <v>-5.68</v>
       </c>
       <c r="AB6">
-        <v>-0.61</v>
+        <v>-0.71</v>
       </c>
       <c r="AC6">
-        <v>90.34</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="AD6">
-        <v>58.01</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AE6">
-        <v>12.31</v>
+        <v>12.38</v>
       </c>
       <c r="AF6">
-        <v>36.66</v>
+        <v>38.41</v>
       </c>
       <c r="AG6">
-        <v>573.9299999999999</v>
+        <v>568.03</v>
       </c>
       <c r="AH6">
-        <v>518.51</v>
+        <v>519.61</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1512,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.1</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11472</v>
+        <v>11372</v>
       </c>
       <c r="D7">
-        <v>-1.02</v>
+        <v>-0.87</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1535,46 +1520,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.24</v>
+        <v>-48.69</v>
       </c>
       <c r="H7">
-        <v>7.67</v>
+        <v>6.73</v>
       </c>
       <c r="I7">
-        <v>-0.92</v>
+        <v>-5.45</v>
       </c>
       <c r="J7">
-        <v>-5.05</v>
+        <v>-5.43</v>
       </c>
       <c r="K7">
-        <v>-6.6</v>
+        <v>-8.33</v>
       </c>
       <c r="L7">
-        <v>-35.9</v>
+        <v>-38.99</v>
       </c>
       <c r="M7">
-        <v>19.01</v>
+        <v>18.72</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>11649.2</v>
+        <v>11518.2</v>
       </c>
       <c r="Q7">
-        <v>11617.65</v>
+        <v>11593.65</v>
       </c>
       <c r="R7">
-        <v>11550.04</v>
+        <v>11537.08</v>
       </c>
       <c r="S7">
-        <v>14778.91</v>
+        <v>14749.58</v>
       </c>
       <c r="T7">
-        <v>-22.38</v>
+        <v>-22.9</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1589,34 +1574,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.42</v>
+        <v>45.71</v>
       </c>
       <c r="Z7">
-        <v>-9.970000000000001</v>
+        <v>-27.22</v>
       </c>
       <c r="AA7">
-        <v>-3.47</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="AB7">
-        <v>-6.5</v>
+        <v>-19.01</v>
       </c>
       <c r="AC7">
-        <v>43.22</v>
+        <v>41.1</v>
       </c>
       <c r="AD7">
-        <v>53.79</v>
+        <v>45.16</v>
       </c>
       <c r="AE7">
-        <v>433.71</v>
+        <v>419.66</v>
       </c>
       <c r="AF7">
-        <v>-40.4</v>
+        <v>-73.84999999999999</v>
       </c>
       <c r="AG7">
-        <v>12089.29</v>
+        <v>12063.93</v>
       </c>
       <c r="AH7">
-        <v>11146.01</v>
+        <v>11123.37</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1625,7 +1610,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>26.57</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1636,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>333</v>
+        <v>330.85</v>
       </c>
       <c r="D8">
-        <v>-0.33</v>
+        <v>-0.65</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1648,46 +1633,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-5.18</v>
+        <v>-5.79</v>
       </c>
       <c r="H8">
-        <v>42.12</v>
+        <v>41.2</v>
       </c>
       <c r="I8">
-        <v>-2.9</v>
+        <v>-2.69</v>
       </c>
       <c r="J8">
-        <v>1.68</v>
+        <v>-1.46</v>
       </c>
       <c r="K8">
-        <v>24.05</v>
+        <v>16.99</v>
       </c>
       <c r="L8">
-        <v>10.01</v>
+        <v>7.93</v>
       </c>
       <c r="M8">
-        <v>29.46</v>
+        <v>29.08</v>
       </c>
       <c r="N8">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>334.8</v>
+        <v>332.97</v>
       </c>
       <c r="Q8">
-        <v>337.72</v>
+        <v>337.17</v>
       </c>
       <c r="R8">
-        <v>332.55</v>
+        <v>332.75</v>
       </c>
       <c r="S8">
-        <v>285.69</v>
+        <v>285.96</v>
       </c>
       <c r="T8">
-        <v>16.56</v>
+        <v>15.7</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1702,34 +1687,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>48.72</v>
+        <v>46.78</v>
       </c>
       <c r="Z8">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AA8">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="AB8">
-        <v>-1.22</v>
+        <v>-1.4</v>
       </c>
       <c r="AC8">
         <v>6.84</v>
       </c>
       <c r="AD8">
-        <v>11.32</v>
+        <v>7.5</v>
       </c>
       <c r="AE8">
         <v>8.75</v>
       </c>
       <c r="AF8">
-        <v>-15.55</v>
+        <v>3.04</v>
       </c>
       <c r="AG8">
-        <v>348.48</v>
+        <v>348.14</v>
       </c>
       <c r="AH8">
-        <v>326.97</v>
+        <v>326.19</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1738,7 +1723,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>19.79</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1749,58 +1734,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="D9">
-        <v>1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1072.2</v>
+        <v>1072.4</v>
       </c>
       <c r="G9">
-        <v>-1.19</v>
+        <v>-2.91</v>
       </c>
       <c r="H9">
-        <v>23.58</v>
+        <v>21.41</v>
       </c>
       <c r="I9">
-        <v>-0.74</v>
+        <v>-0.44</v>
       </c>
       <c r="J9">
-        <v>1.31</v>
+        <v>0.19</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>3.19</v>
       </c>
       <c r="L9">
-        <v>26.92</v>
+        <v>21.43</v>
       </c>
       <c r="M9">
-        <v>15.1</v>
+        <v>14.78</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1312.04</v>
+        <v>1310.9</v>
       </c>
       <c r="Q9">
         <v>1302.25</v>
       </c>
       <c r="R9">
-        <v>1272.84</v>
+        <v>1274.23</v>
       </c>
       <c r="S9">
-        <v>1225.47</v>
+        <v>1226.15</v>
       </c>
       <c r="T9">
-        <v>8.119999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1815,28 +1800,28 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>58.3</v>
+        <v>50.66</v>
       </c>
       <c r="Z9">
-        <v>12.17</v>
+        <v>10.42</v>
       </c>
       <c r="AA9">
-        <v>12.85</v>
+        <v>12.36</v>
       </c>
       <c r="AB9">
-        <v>-0.68</v>
+        <v>-1.94</v>
       </c>
       <c r="AC9">
-        <v>37.74</v>
+        <v>29.01</v>
       </c>
       <c r="AD9">
-        <v>34.17</v>
+        <v>32.94</v>
       </c>
       <c r="AE9">
-        <v>25.31</v>
+        <v>25.93</v>
       </c>
       <c r="AF9">
-        <v>-34.22</v>
+        <v>-20.54</v>
       </c>
       <c r="AG9">
         <v>1350.05</v>
@@ -1851,7 +1836,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.68</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>85.47</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D10">
-        <v>4.81</v>
+        <v>-1.84</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1874,46 +1859,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-6.54</v>
+        <v>-8.26</v>
       </c>
       <c r="H10">
-        <v>136.89</v>
+        <v>132.54</v>
       </c>
       <c r="I10">
-        <v>8.699999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="J10">
-        <v>-3.06</v>
+        <v>-0.67</v>
       </c>
       <c r="K10">
-        <v>75.97</v>
+        <v>69.36</v>
       </c>
       <c r="L10">
-        <v>15.1</v>
+        <v>13.41</v>
       </c>
       <c r="M10">
-        <v>-2.81</v>
+        <v>-3.47</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>80.98</v>
+        <v>81.59</v>
       </c>
       <c r="Q10">
-        <v>83.31</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="R10">
-        <v>70.51000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="S10">
-        <v>59.85</v>
+        <v>59.92</v>
       </c>
       <c r="T10">
-        <v>42.8</v>
+        <v>40.02</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1928,34 +1913,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.93</v>
+        <v>57.16</v>
       </c>
       <c r="Z10">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA10">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AB10">
-        <v>-1.04</v>
+        <v>-0.83</v>
       </c>
       <c r="AC10">
-        <v>28.58</v>
+        <v>51.84</v>
       </c>
       <c r="AD10">
-        <v>14.25</v>
+        <v>29.67</v>
       </c>
       <c r="AE10">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="AF10">
-        <v>-32.22</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="AG10">
-        <v>90.79000000000001</v>
+        <v>90.75</v>
       </c>
       <c r="AH10">
-        <v>75.84</v>
+        <v>75.83</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1964,7 +1949,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.68</v>
+        <v>17.98</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2163,1314 +2148,1328 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6.26</v>
+      </c>
+      <c r="D7" s="6">
+        <v>12.76</v>
+      </c>
+      <c r="E7" s="7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>15.1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>14.06</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>5.81</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.29</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.09</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-5.05</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.43</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.68</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.31</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="D8" s="7">
-        <v>6.26</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>5.74</v>
+      </c>
+      <c r="D16" s="6">
+        <v>10.73</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>17.04</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.07</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.03</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.2</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.77</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.64</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4.93</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-5.45</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-4.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-2.9</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.74</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.44</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3.79</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-4.91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>15.02</v>
+      </c>
+      <c r="D25" s="6">
+        <v>17.58</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>50.11</v>
+      </c>
+      <c r="D26" s="6">
+        <v>49.05</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>19.47</v>
+      </c>
+      <c r="D27" s="6">
+        <v>11.63</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-7.84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-3.02</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>5.94</v>
+      </c>
+      <c r="D29" s="6">
+        <v>4.47</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-35.9</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-38.99</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>10.01</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>26.92</v>
+      </c>
+      <c r="D32" s="6">
+        <v>21.43</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
         <v>15.1</v>
       </c>
-      <c r="E9" s="8">
+      <c r="D33" s="6">
+        <v>13.41</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>5.38</v>
+      </c>
+      <c r="D34" s="6">
+        <v>4.36</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>29.31</v>
+      </c>
+      <c r="D35" s="6">
+        <v>29.08</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.17</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>10.84</v>
+      </c>
+      <c r="D37" s="6">
+        <v>10.71</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-5.45</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.08</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.6</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-8.33</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>24.05</v>
+      </c>
+      <c r="D40" s="6">
+        <v>16.99</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-7.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>5.1</v>
+      </c>
+      <c r="D41" s="6">
+        <v>3.19</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>75.97</v>
+      </c>
+      <c r="D42" s="6">
+        <v>69.36</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-6.61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-33.27</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-30.62</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-1.79</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-0.42</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-10.93</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-14.66</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-14.78</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-10.03</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-11.67</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-48.24</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-48.69</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-5.18</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-5.79</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-6.54</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-8.26</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>672.35</v>
+      </c>
+      <c r="D52" s="6">
+        <v>699.1</v>
+      </c>
+      <c r="E52" s="7">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>305.3</v>
+      </c>
+      <c r="D53" s="6">
+        <v>309.55</v>
+      </c>
+      <c r="E53" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1165</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1147.9</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-17.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>737.85</v>
+      </c>
+      <c r="D55" s="6">
+        <v>736.8</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>539.85</v>
+      </c>
+      <c r="D56" s="6">
+        <v>530</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-9.85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11472</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11372</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>333</v>
+      </c>
+      <c r="D58" s="6">
+        <v>330.85</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1325</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1302</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>85.47</v>
+      </c>
+      <c r="D60" s="6">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>55</v>
+      </c>
+      <c r="D61" s="6">
+        <v>77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>88</v>
+      </c>
+      <c r="D62" s="6">
+        <v>99</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>77</v>
+      </c>
+      <c r="D63" s="6">
+        <v>55</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>99</v>
+      </c>
+      <c r="D64" s="6">
+        <v>88</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>56.55</v>
+      </c>
+      <c r="D65" s="6">
+        <v>63.11</v>
+      </c>
+      <c r="E65" s="7">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>65.89</v>
+      </c>
+      <c r="D66" s="6">
+        <v>68.19</v>
+      </c>
+      <c r="E66" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>59.65</v>
+      </c>
+      <c r="D67" s="6">
+        <v>54.21</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-5.44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>58.67</v>
+      </c>
+      <c r="D68" s="6">
+        <v>57.95</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>46.12</v>
+      </c>
+      <c r="D69" s="6">
+        <v>40.67</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>47.42</v>
+      </c>
+      <c r="D70" s="6">
+        <v>45.71</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>48.72</v>
+      </c>
+      <c r="D71" s="6">
+        <v>46.78</v>
+      </c>
+      <c r="E71" s="8">
         <v>-1.94</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>58.3</v>
+      </c>
+      <c r="D72" s="6">
+        <v>50.66</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-7.64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>59.93</v>
+      </c>
+      <c r="D73" s="6">
+        <v>57.16</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-65.88</v>
+      </c>
+      <c r="D74" s="6">
+        <v>11.64</v>
+      </c>
+      <c r="E74" s="7">
+        <v>77.52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-71.45999999999999</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-26.39</v>
+      </c>
+      <c r="E75" s="7">
+        <v>45.07</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2.84</v>
-      </c>
-      <c r="D10" s="7">
-        <v>5.81</v>
-      </c>
-      <c r="E10" s="9">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>10.77</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-12.62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.82</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="D77" s="6">
+        <v>22.32</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-64.33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-3.86</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>36.66</v>
+      </c>
+      <c r="D78" s="6">
+        <v>38.41</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-5.98</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-5.05</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-40.4</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-73.84999999999999</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-33.45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-0.09</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.68</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-15.55</v>
+      </c>
+      <c r="D80" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="E80" s="7">
+        <v>18.59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.65</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.31</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-34.22</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-20.54</v>
+      </c>
+      <c r="E81" s="7">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-5.38</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3.06</v>
-      </c>
-      <c r="E16" s="9">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>7.24</v>
-      </c>
-      <c r="D17" s="7">
-        <v>5.74</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-1.07</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-2.14</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>4.74</v>
-      </c>
-      <c r="D20" s="7">
-        <v>4.64</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.48</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.92</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-2.9</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.21</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.74</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="D25" s="7">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E25" s="9">
-        <v>7.27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>12.83</v>
-      </c>
-      <c r="D26" s="7">
-        <v>15.02</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>57.03</v>
-      </c>
-      <c r="D27" s="7">
-        <v>50.11</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-6.92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>18.92</v>
-      </c>
-      <c r="D28" s="7">
-        <v>19.47</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-2.12</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-2.95</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="D30" s="7">
-        <v>5.94</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-35.32</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-35.9</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>11.95</v>
-      </c>
-      <c r="D32" s="7">
-        <v>10.01</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>26.32</v>
-      </c>
-      <c r="D33" s="7">
-        <v>26.92</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>14.52</v>
-      </c>
-      <c r="D34" s="7">
-        <v>15.1</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>5.04</v>
-      </c>
-      <c r="D35" s="7">
-        <v>5.38</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>24.06</v>
-      </c>
-      <c r="D36" s="7">
-        <v>29.31</v>
-      </c>
-      <c r="E36" s="9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-3.07</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="E37" s="9">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>6.91</v>
-      </c>
-      <c r="D38" s="7">
-        <v>10.84</v>
-      </c>
-      <c r="E38" s="9">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-7.65</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-5.45</v>
-      </c>
-      <c r="E39" s="9">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-7.32</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-6.6</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>20.14</v>
-      </c>
-      <c r="D41" s="7">
-        <v>24.05</v>
-      </c>
-      <c r="E41" s="9">
-        <v>3.91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="D42" s="7">
-        <v>5.1</v>
-      </c>
-      <c r="E42" s="9">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>60.66</v>
-      </c>
-      <c r="D43" s="7">
-        <v>75.97</v>
-      </c>
-      <c r="E43" s="9">
-        <v>15.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-32.15</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-33.27</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-1.79</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-11.16</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-14.59</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-14.66</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-10.08</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-10.03</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-47.71</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-48.24</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-4.87</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-5.18</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-2.46</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-10.83</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-6.54</v>
-      </c>
-      <c r="E52" s="9">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>683.7</v>
-      </c>
-      <c r="D53" s="7">
-        <v>672.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-11.35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>310.85</v>
-      </c>
-      <c r="D54" s="7">
-        <v>305.3</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1145</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1165</v>
-      </c>
-      <c r="E55" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>738.4</v>
-      </c>
-      <c r="D56" s="7">
-        <v>737.85</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>539.5</v>
-      </c>
-      <c r="D57" s="7">
-        <v>539.85</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>11590</v>
-      </c>
-      <c r="D58" s="7">
-        <v>11472</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>334.1</v>
-      </c>
-      <c r="D59" s="7">
-        <v>333</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1308</v>
-      </c>
-      <c r="D60" s="7">
-        <v>1325</v>
-      </c>
-      <c r="E60" s="9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>81.55</v>
-      </c>
-      <c r="D61" s="7">
-        <v>85.47</v>
-      </c>
-      <c r="E61" s="9">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>99</v>
-      </c>
-      <c r="D62" s="7">
-        <v>88</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>88</v>
-      </c>
-      <c r="D63" s="7">
-        <v>99</v>
-      </c>
-      <c r="E63" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>60.81</v>
-      </c>
-      <c r="D64" s="7">
-        <v>56.55</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>72.23</v>
-      </c>
-      <c r="D65" s="7">
-        <v>65.89</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-6.34</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>54.72</v>
-      </c>
-      <c r="D66" s="7">
-        <v>59.65</v>
-      </c>
-      <c r="E66" s="9">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>59.02</v>
-      </c>
-      <c r="D67" s="7">
-        <v>58.67</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>45.88</v>
-      </c>
-      <c r="D68" s="7">
-        <v>46.12</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>49.45</v>
-      </c>
-      <c r="D69" s="7">
-        <v>47.42</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>49.69</v>
-      </c>
-      <c r="D70" s="7">
-        <v>48.72</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>53.49</v>
-      </c>
-      <c r="D71" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="E71" s="9">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>54.86</v>
-      </c>
-      <c r="D72" s="7">
-        <v>59.93</v>
-      </c>
-      <c r="E72" s="9">
-        <v>5.07</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="7">
-        <v>-57.21</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-65.88</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-8.67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-33.87</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-71.45999999999999</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-37.59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>20.2</v>
-      </c>
-      <c r="D75" s="7">
-        <v>10.77</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-9.43</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>175.21</v>
-      </c>
-      <c r="D76" s="7">
-        <v>86.65000000000001</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-88.56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-2.64</v>
-      </c>
-      <c r="D77" s="7">
-        <v>36.66</v>
-      </c>
-      <c r="E77" s="9">
-        <v>39.3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>880.59</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-40.4</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-920.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>11.34</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-15.55</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-26.89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-24.32</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-34.22</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-9.9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-71.77</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C82" s="6">
         <v>-32.22</v>
       </c>
-      <c r="E81" s="9">
-        <v>39.55</v>
+      <c r="D82" s="6">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="E82" s="7">
+        <v>119.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3490,60 +3489,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>64.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>55.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>53.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>80</v>
       </c>
-      <c r="F2" s="12">
-        <v>2.1</v>
-      </c>
-      <c r="G2" s="12">
-        <v>15.5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3645,61 +3644,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3994</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3627</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2946</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2483</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1901</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1665</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.151</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0281</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0645</v>
+      <c r="A2" s="14">
+        <v>0.405</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3635</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2908</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2383</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1872</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1639</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1478</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0347</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.057</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.2% → -2.9%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.2%</t>
-  </si>
-  <si>
-    <t>-2.9%</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.7 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,7 +291,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -303,15 +303,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,19 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,12 +417,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -444,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -802,8 +789,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -943,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>699.1</v>
+        <v>683.8</v>
       </c>
       <c r="D2">
-        <v>3.98</v>
+        <v>-2.19</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -955,46 +942,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-30.62</v>
+        <v>-32.14</v>
       </c>
       <c r="H2">
-        <v>90.39</v>
+        <v>86.22</v>
       </c>
       <c r="I2">
-        <v>10.73</v>
+        <v>-1.53</v>
       </c>
       <c r="J2">
-        <v>12.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K2">
-        <v>4.36</v>
+        <v>-2.37</v>
       </c>
       <c r="L2">
-        <v>17.58</v>
+        <v>16.24</v>
       </c>
       <c r="M2">
-        <v>-5.7</v>
+        <v>-6.39</v>
       </c>
       <c r="N2">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>687.17</v>
+        <v>685.04</v>
       </c>
       <c r="Q2">
-        <v>653.73</v>
+        <v>656.4400000000001</v>
       </c>
       <c r="R2">
-        <v>648.15</v>
+        <v>649.39</v>
       </c>
       <c r="S2">
-        <v>624.21</v>
+        <v>624.9400000000001</v>
       </c>
       <c r="T2">
-        <v>12</v>
+        <v>9.42</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>63.11</v>
+        <v>57.74</v>
       </c>
       <c r="Z2">
-        <v>9.98</v>
+        <v>10.65</v>
       </c>
       <c r="AA2">
-        <v>3.74</v>
+        <v>5.12</v>
       </c>
       <c r="AB2">
-        <v>6.25</v>
+        <v>5.53</v>
       </c>
       <c r="AC2">
-        <v>75.89</v>
+        <v>70.66</v>
       </c>
       <c r="AD2">
-        <v>79.11</v>
+        <v>73.39</v>
       </c>
       <c r="AE2">
-        <v>25.93</v>
+        <v>25.94</v>
       </c>
       <c r="AF2">
-        <v>11.64</v>
+        <v>-69.13</v>
       </c>
       <c r="AG2">
-        <v>698.73</v>
+        <v>701.84</v>
       </c>
       <c r="AH2">
-        <v>608.73</v>
+        <v>611.05</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1045,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>48.01</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>309.55</v>
+        <v>307.6</v>
       </c>
       <c r="D3">
-        <v>1.39</v>
+        <v>-0.63</v>
       </c>
       <c r="E3">
         <v>310.85</v>
@@ -1068,46 +1055,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-0.42</v>
+        <v>-1.05</v>
       </c>
       <c r="H3">
-        <v>102.02</v>
+        <v>100.74</v>
       </c>
       <c r="I3">
-        <v>-0.03</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J3">
-        <v>14.06</v>
+        <v>10.23</v>
       </c>
       <c r="K3">
-        <v>29.08</v>
+        <v>36.61</v>
       </c>
       <c r="L3">
-        <v>49.05</v>
+        <v>51.09</v>
       </c>
       <c r="M3">
-        <v>40.5</v>
+        <v>40.78</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>308.92</v>
+        <v>308.49</v>
       </c>
       <c r="Q3">
-        <v>289.25</v>
+        <v>290.95</v>
       </c>
       <c r="R3">
-        <v>273.43</v>
+        <v>274.35</v>
       </c>
       <c r="S3">
-        <v>216.47</v>
+        <v>217.18</v>
       </c>
       <c r="T3">
-        <v>43</v>
+        <v>41.63</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1122,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>68.19</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="Z3">
-        <v>12.18</v>
+        <v>11.79</v>
       </c>
       <c r="AA3">
-        <v>10.78</v>
+        <v>10.98</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC3">
-        <v>76.09</v>
+        <v>63.9</v>
       </c>
       <c r="AD3">
-        <v>84.03</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="AE3">
-        <v>10.33</v>
+        <v>10.56</v>
       </c>
       <c r="AF3">
-        <v>-26.39</v>
+        <v>-29.79</v>
       </c>
       <c r="AG3">
-        <v>327.32</v>
+        <v>329.11</v>
       </c>
       <c r="AH3">
-        <v>251.18</v>
+        <v>252.79</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1158,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>50.25</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1147.9</v>
+        <v>1136.3</v>
       </c>
       <c r="D4">
-        <v>-1.47</v>
+        <v>-1.01</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1181,22 +1168,22 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-10.93</v>
+        <v>-11.83</v>
       </c>
       <c r="H4">
-        <v>16.42</v>
+        <v>15.24</v>
       </c>
       <c r="I4">
-        <v>-3.77</v>
+        <v>-2.04</v>
       </c>
       <c r="J4">
-        <v>4.07</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>-0.17</v>
+        <v>1.36</v>
       </c>
       <c r="L4">
-        <v>11.63</v>
+        <v>10.12</v>
       </c>
       <c r="M4">
         <v>23.83</v>
@@ -1205,22 +1192,22 @@
         <v>45</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P4">
-        <v>1155.46</v>
+        <v>1150.72</v>
       </c>
       <c r="Q4">
-        <v>1137.55</v>
+        <v>1139.62</v>
       </c>
       <c r="R4">
-        <v>1091.53</v>
+        <v>1093.05</v>
       </c>
       <c r="S4">
-        <v>1128.84</v>
+        <v>1129.18</v>
       </c>
       <c r="T4">
-        <v>1.69</v>
+        <v>0.63</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>54.21</v>
+        <v>50.83</v>
       </c>
       <c r="Z4">
-        <v>18.23</v>
+        <v>15.59</v>
       </c>
       <c r="AA4">
-        <v>19.42</v>
+        <v>18.66</v>
       </c>
       <c r="AB4">
-        <v>-1.2</v>
+        <v>-3.07</v>
       </c>
       <c r="AC4">
-        <v>16.77</v>
+        <v>10.65</v>
       </c>
       <c r="AD4">
-        <v>26.86</v>
+        <v>19.24</v>
       </c>
       <c r="AE4">
-        <v>28.81</v>
+        <v>27.9</v>
       </c>
       <c r="AF4">
-        <v>-1.85</v>
+        <v>-43.46</v>
       </c>
       <c r="AG4">
-        <v>1202.37</v>
+        <v>1201.29</v>
       </c>
       <c r="AH4">
-        <v>1072.73</v>
+        <v>1077.94</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1271,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>30.5</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>736.8</v>
+        <v>738.75</v>
       </c>
       <c r="D5">
-        <v>-0.14</v>
+        <v>0.26</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1294,46 +1281,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.78</v>
+        <v>-14.55</v>
       </c>
       <c r="H5">
-        <v>11.32</v>
+        <v>11.61</v>
       </c>
       <c r="I5">
-        <v>4.93</v>
+        <v>0.65</v>
       </c>
       <c r="J5">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="K5">
-        <v>10.71</v>
+        <v>11.61</v>
       </c>
       <c r="L5">
-        <v>-3.02</v>
+        <v>-0.97</v>
       </c>
       <c r="M5">
-        <v>36.35</v>
+        <v>36.36</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>736.39</v>
+        <v>737.34</v>
       </c>
       <c r="Q5">
-        <v>723.0599999999999</v>
+        <v>723.75</v>
       </c>
       <c r="R5">
-        <v>721.77</v>
+        <v>722.7</v>
       </c>
       <c r="S5">
-        <v>748.79</v>
+        <v>748.64</v>
       </c>
       <c r="T5">
-        <v>-1.6</v>
+        <v>-1.32</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>57.95</v>
+        <v>58.95</v>
       </c>
       <c r="Z5">
-        <v>2.08</v>
+        <v>2.93</v>
       </c>
       <c r="AA5">
-        <v>-0.71</v>
+        <v>0.01</v>
       </c>
       <c r="AB5">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="AC5">
-        <v>97.91</v>
+        <v>97.81</v>
       </c>
       <c r="AD5">
-        <v>99.13</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE5">
-        <v>16.6</v>
+        <v>16.34</v>
       </c>
       <c r="AF5">
-        <v>22.32</v>
+        <v>-9.59</v>
       </c>
       <c r="AG5">
-        <v>753.4299999999999</v>
+        <v>754.91</v>
       </c>
       <c r="AH5">
-        <v>692.6900000000001</v>
+        <v>692.58</v>
       </c>
       <c r="AI5">
         <v>692.25</v>
@@ -1384,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>28.9</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>530</v>
+        <v>526.5</v>
       </c>
       <c r="D6">
-        <v>-1.82</v>
+        <v>-0.66</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1407,46 +1394,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-11.67</v>
+        <v>-12.25</v>
       </c>
       <c r="H6">
-        <v>20.85</v>
+        <v>20.05</v>
       </c>
       <c r="I6">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="J6">
+        <v>-8.91</v>
+      </c>
+      <c r="K6">
         <v>-6.09</v>
       </c>
-      <c r="K6">
-        <v>-7.08</v>
-      </c>
       <c r="L6">
-        <v>4.47</v>
+        <v>5.13</v>
       </c>
       <c r="M6">
-        <v>16.39</v>
+        <v>15.23</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>533.4299999999999</v>
+        <v>535.13</v>
       </c>
       <c r="Q6">
-        <v>543.8200000000001</v>
+        <v>541.99</v>
       </c>
       <c r="R6">
-        <v>551.1</v>
+        <v>549.97</v>
       </c>
       <c r="S6">
-        <v>520.27</v>
+        <v>520.39</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1461,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.67</v>
+        <v>38.91</v>
       </c>
       <c r="Z6">
-        <v>-6.39</v>
+        <v>-6.82</v>
       </c>
       <c r="AA6">
-        <v>-5.68</v>
+        <v>-5.91</v>
       </c>
       <c r="AB6">
-        <v>-0.71</v>
+        <v>-0.9</v>
       </c>
       <c r="AC6">
-        <v>86.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="AD6">
-        <v>77.90000000000001</v>
+        <v>83.98</v>
       </c>
       <c r="AE6">
-        <v>12.38</v>
+        <v>12.04</v>
       </c>
       <c r="AF6">
-        <v>38.41</v>
+        <v>-6.02</v>
       </c>
       <c r="AG6">
-        <v>568.03</v>
+        <v>565.61</v>
       </c>
       <c r="AH6">
-        <v>519.61</v>
+        <v>518.38</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1497,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.71</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11372</v>
+        <v>11466</v>
       </c>
       <c r="D7">
-        <v>-0.87</v>
+        <v>0.83</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1520,46 +1507,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.69</v>
+        <v>-48.27</v>
       </c>
       <c r="H7">
-        <v>6.73</v>
+        <v>7.61</v>
       </c>
       <c r="I7">
-        <v>-5.45</v>
+        <v>-2.13</v>
       </c>
       <c r="J7">
-        <v>-5.43</v>
+        <v>-3.26</v>
       </c>
       <c r="K7">
-        <v>-8.33</v>
+        <v>-5.84</v>
       </c>
       <c r="L7">
-        <v>-38.99</v>
+        <v>-38.73</v>
       </c>
       <c r="M7">
-        <v>18.72</v>
+        <v>19.16</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>11518.2</v>
+        <v>11468.2</v>
       </c>
       <c r="Q7">
-        <v>11593.65</v>
+        <v>11569.9</v>
       </c>
       <c r="R7">
-        <v>11537.08</v>
+        <v>11524.98</v>
       </c>
       <c r="S7">
-        <v>14749.58</v>
+        <v>14718.26</v>
       </c>
       <c r="T7">
-        <v>-22.9</v>
+        <v>-22.1</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1574,34 +1561,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>45.71</v>
+        <v>47.62</v>
       </c>
       <c r="Z7">
-        <v>-27.22</v>
+        <v>-32.94</v>
       </c>
       <c r="AA7">
-        <v>-8.220000000000001</v>
+        <v>-13.16</v>
       </c>
       <c r="AB7">
-        <v>-19.01</v>
+        <v>-19.77</v>
       </c>
       <c r="AC7">
-        <v>41.1</v>
+        <v>37.48</v>
       </c>
       <c r="AD7">
-        <v>45.16</v>
+        <v>40.6</v>
       </c>
       <c r="AE7">
-        <v>419.66</v>
+        <v>413.04</v>
       </c>
       <c r="AF7">
-        <v>-73.84999999999999</v>
+        <v>-64.08</v>
       </c>
       <c r="AG7">
-        <v>12063.93</v>
+        <v>12013.54</v>
       </c>
       <c r="AH7">
-        <v>11123.37</v>
+        <v>11126.26</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1610,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>25.75</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>330.85</v>
+        <v>332</v>
       </c>
       <c r="D8">
-        <v>-0.65</v>
+        <v>0.35</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1633,46 +1620,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-5.79</v>
+        <v>-5.47</v>
       </c>
       <c r="H8">
-        <v>41.2</v>
+        <v>41.69</v>
       </c>
       <c r="I8">
-        <v>-2.69</v>
+        <v>-0.84</v>
       </c>
       <c r="J8">
-        <v>-1.46</v>
+        <v>-2.92</v>
       </c>
       <c r="K8">
-        <v>16.99</v>
+        <v>19.17</v>
       </c>
       <c r="L8">
-        <v>7.93</v>
+        <v>9.48</v>
       </c>
       <c r="M8">
-        <v>29.08</v>
+        <v>29.2</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="O8">
         <v>70</v>
       </c>
       <c r="P8">
-        <v>332.97</v>
+        <v>332.41</v>
       </c>
       <c r="Q8">
-        <v>337.17</v>
+        <v>336.67</v>
       </c>
       <c r="R8">
-        <v>332.75</v>
+        <v>332.95</v>
       </c>
       <c r="S8">
-        <v>285.96</v>
+        <v>286.23</v>
       </c>
       <c r="T8">
-        <v>15.7</v>
+        <v>15.99</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>46.78</v>
+        <v>47.97</v>
       </c>
       <c r="Z8">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA8">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="AB8">
-        <v>-1.4</v>
+        <v>-1.39</v>
       </c>
       <c r="AC8">
-        <v>6.84</v>
+        <v>5.03</v>
       </c>
       <c r="AD8">
-        <v>7.5</v>
+        <v>6.24</v>
       </c>
       <c r="AE8">
-        <v>8.75</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AF8">
-        <v>3.04</v>
+        <v>-32.45</v>
       </c>
       <c r="AG8">
-        <v>348.14</v>
+        <v>347.65</v>
       </c>
       <c r="AH8">
-        <v>326.19</v>
+        <v>325.7</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1723,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.16</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,58 +1721,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1302</v>
+        <v>1297.3</v>
       </c>
       <c r="D9">
-        <v>-1.74</v>
+        <v>-0.36</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1072.4</v>
+        <v>1073.1</v>
       </c>
       <c r="G9">
-        <v>-2.91</v>
+        <v>-3.26</v>
       </c>
       <c r="H9">
-        <v>21.41</v>
+        <v>20.89</v>
       </c>
       <c r="I9">
-        <v>-0.44</v>
+        <v>-1.23</v>
       </c>
       <c r="J9">
-        <v>0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="K9">
-        <v>3.19</v>
+        <v>2.17</v>
       </c>
       <c r="L9">
-        <v>21.43</v>
+        <v>20.97</v>
       </c>
       <c r="M9">
-        <v>14.78</v>
+        <v>14.59</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P9">
-        <v>1310.9</v>
+        <v>1307.66</v>
       </c>
       <c r="Q9">
-        <v>1302.25</v>
+        <v>1302.95</v>
       </c>
       <c r="R9">
-        <v>1274.23</v>
+        <v>1275.65</v>
       </c>
       <c r="S9">
-        <v>1226.15</v>
+        <v>1226.79</v>
       </c>
       <c r="T9">
-        <v>6.19</v>
+        <v>5.75</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,34 +1787,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>50.66</v>
+        <v>49.24</v>
       </c>
       <c r="Z9">
-        <v>10.42</v>
+        <v>8.56</v>
       </c>
       <c r="AA9">
-        <v>12.36</v>
+        <v>11.6</v>
       </c>
       <c r="AB9">
-        <v>-1.94</v>
+        <v>-3.04</v>
       </c>
       <c r="AC9">
-        <v>29.01</v>
+        <v>19.14</v>
       </c>
       <c r="AD9">
-        <v>32.94</v>
+        <v>28.63</v>
       </c>
       <c r="AE9">
-        <v>25.93</v>
+        <v>25.46</v>
       </c>
       <c r="AF9">
-        <v>-20.54</v>
+        <v>-17.63</v>
       </c>
       <c r="AG9">
-        <v>1350.05</v>
+        <v>1349.99</v>
       </c>
       <c r="AH9">
-        <v>1254.45</v>
+        <v>1255.9</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1836,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.99</v>
+        <v>32.78</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>83.90000000000001</v>
+        <v>84.12</v>
       </c>
       <c r="D10">
-        <v>-1.84</v>
+        <v>0.26</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1859,46 +1846,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-8.26</v>
+        <v>-8.02</v>
       </c>
       <c r="H10">
-        <v>132.54</v>
+        <v>133.15</v>
       </c>
       <c r="I10">
-        <v>3.79</v>
+        <v>5.97</v>
       </c>
       <c r="J10">
-        <v>-0.67</v>
+        <v>-0.3</v>
       </c>
       <c r="K10">
-        <v>69.36</v>
+        <v>57.88</v>
       </c>
       <c r="L10">
-        <v>13.41</v>
+        <v>14.95</v>
       </c>
       <c r="M10">
-        <v>-3.47</v>
+        <v>-3.22</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>81.59</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="Q10">
-        <v>83.29000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="R10">
-        <v>71.17</v>
+        <v>71.84</v>
       </c>
       <c r="S10">
-        <v>59.92</v>
+        <v>59.99</v>
       </c>
       <c r="T10">
-        <v>40.02</v>
+        <v>40.21</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1913,31 +1900,31 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>57.16</v>
+        <v>57.46</v>
       </c>
       <c r="Z10">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AA10">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="AB10">
-        <v>-0.83</v>
+        <v>-0.66</v>
       </c>
       <c r="AC10">
-        <v>51.84</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="AD10">
-        <v>29.67</v>
+        <v>49.63</v>
       </c>
       <c r="AE10">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="AF10">
-        <v>87.01000000000001</v>
+        <v>33.62</v>
       </c>
       <c r="AG10">
-        <v>90.75</v>
+        <v>90.77</v>
       </c>
       <c r="AH10">
         <v>75.83</v>
@@ -1949,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>17.98</v>
+        <v>16.34</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2182,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>6.26</v>
+        <v>12.76</v>
       </c>
       <c r="D7" s="6">
-        <v>12.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E7" s="7">
-        <v>6.5</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2199,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>15.1</v>
+        <v>14.06</v>
       </c>
       <c r="D8" s="6">
-        <v>14.06</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.04</v>
+        <v>10.23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2216,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>5.81</v>
+        <v>4.07</v>
       </c>
       <c r="D9" s="6">
-        <v>4.07</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.74</v>
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2233,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="D10" s="6">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.44</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2250,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.86</v>
+        <v>-6.09</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.23</v>
+        <v>-8.91</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.82</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2267,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.05</v>
+        <v>-5.43</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.43</v>
+        <v>-3.26</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.38</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2284,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.68</v>
+        <v>-1.46</v>
       </c>
       <c r="D13" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="E13" s="7">
         <v>-1.46</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-3.14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2301,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>1.31</v>
+        <v>0.19</v>
       </c>
       <c r="D14" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.12</v>
+        <v>-0.36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2318,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.06</v>
+        <v>-0.67</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.39</v>
+        <v>-0.3</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2335,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>5.74</v>
+        <v>10.73</v>
       </c>
       <c r="D16" s="6">
-        <v>10.73</v>
+        <v>-1.53</v>
       </c>
       <c r="E16" s="7">
-        <v>4.99</v>
+        <v>-12.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2352,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.07</v>
+        <v>-0.03</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.03</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E17" s="7">
-        <v>1.04</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2369,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.2</v>
+        <v>-3.77</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.77</v>
+        <v>-2.04</v>
       </c>
       <c r="E18" s="8">
-        <v>-2.57</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2386,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>4.64</v>
+        <v>4.93</v>
       </c>
       <c r="D19" s="6">
-        <v>4.93</v>
+        <v>0.65</v>
       </c>
       <c r="E19" s="7">
-        <v>0.29</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2403,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.85</v>
+        <v>1.84</v>
       </c>
       <c r="D20" s="6">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="E20" s="7">
-        <v>0.99</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2420,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.92</v>
+        <v>-5.45</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.45</v>
+        <v>-2.13</v>
       </c>
       <c r="E21" s="8">
-        <v>-4.53</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2437,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.9</v>
+        <v>-2.69</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.21</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.85</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2454,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.74</v>
+        <v>-0.44</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.44</v>
+        <v>-1.23</v>
       </c>
       <c r="E23" s="7">
-        <v>0.3</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2471,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>8.699999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="D24" s="6">
-        <v>3.79</v>
+        <v>5.97</v>
       </c>
       <c r="E24" s="8">
-        <v>-4.91</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2488,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>15.02</v>
+        <v>17.58</v>
       </c>
       <c r="D25" s="6">
-        <v>17.58</v>
+        <v>16.24</v>
       </c>
       <c r="E25" s="7">
-        <v>2.56</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2505,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>50.11</v>
+        <v>49.05</v>
       </c>
       <c r="D26" s="6">
-        <v>49.05</v>
+        <v>51.09</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.06</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2522,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>19.47</v>
+        <v>11.63</v>
       </c>
       <c r="D27" s="6">
-        <v>11.63</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-7.84</v>
+        <v>10.12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2539,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.95</v>
+        <v>-3.02</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.02</v>
+        <v>-0.97</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.07000000000000001</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2556,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>5.94</v>
+        <v>4.47</v>
       </c>
       <c r="D29" s="6">
-        <v>4.47</v>
+        <v>5.13</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.47</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2573,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-35.9</v>
+        <v>-38.99</v>
       </c>
       <c r="D30" s="6">
-        <v>-38.99</v>
+        <v>-38.73</v>
       </c>
       <c r="E30" s="8">
-        <v>-3.09</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2590,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>10.01</v>
+        <v>7.93</v>
       </c>
       <c r="D31" s="6">
-        <v>7.93</v>
+        <v>9.48</v>
       </c>
       <c r="E31" s="8">
-        <v>-2.08</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2607,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>26.92</v>
+        <v>21.43</v>
       </c>
       <c r="D32" s="6">
-        <v>21.43</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-5.49</v>
+        <v>20.97</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2624,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>15.1</v>
+        <v>13.41</v>
       </c>
       <c r="D33" s="6">
-        <v>13.41</v>
+        <v>14.95</v>
       </c>
       <c r="E33" s="8">
-        <v>-1.69</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2641,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>5.38</v>
+        <v>4.36</v>
       </c>
       <c r="D34" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.02</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2658,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>29.31</v>
+        <v>29.08</v>
       </c>
       <c r="D35" s="6">
-        <v>29.08</v>
+        <v>36.61</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.23</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2675,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>0.75</v>
+        <v>-0.17</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.17</v>
+        <v>1.36</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.92</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2692,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>10.84</v>
+        <v>10.71</v>
       </c>
       <c r="D37" s="6">
-        <v>10.71</v>
+        <v>11.61</v>
       </c>
       <c r="E37" s="8">
-        <v>-0.13</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2709,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.45</v>
+        <v>-7.08</v>
       </c>
       <c r="D38" s="6">
-        <v>-7.08</v>
+        <v>-6.09</v>
       </c>
       <c r="E38" s="8">
-        <v>-1.63</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2726,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.6</v>
+        <v>-8.33</v>
       </c>
       <c r="D39" s="6">
-        <v>-8.33</v>
+        <v>-5.84</v>
       </c>
       <c r="E39" s="8">
-        <v>-1.73</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2743,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>24.05</v>
+        <v>16.99</v>
       </c>
       <c r="D40" s="6">
-        <v>16.99</v>
+        <v>19.17</v>
       </c>
       <c r="E40" s="8">
-        <v>-7.06</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2760,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>5.1</v>
+        <v>3.19</v>
       </c>
       <c r="D41" s="6">
-        <v>3.19</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.91</v>
+        <v>2.17</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2777,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>75.97</v>
+        <v>69.36</v>
       </c>
       <c r="D42" s="6">
-        <v>69.36</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-6.61</v>
+        <v>57.88</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-11.48</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2794,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-33.27</v>
+        <v>-30.62</v>
       </c>
       <c r="D43" s="6">
-        <v>-30.62</v>
+        <v>-32.14</v>
       </c>
       <c r="E43" s="7">
-        <v>2.65</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2811,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-1.79</v>
+        <v>-0.42</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.42</v>
+        <v>-1.05</v>
       </c>
       <c r="E44" s="7">
-        <v>1.37</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2828,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-9.609999999999999</v>
+        <v>-10.93</v>
       </c>
       <c r="D45" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.32</v>
+        <v>-11.83</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2845,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-14.66</v>
+        <v>-14.78</v>
       </c>
       <c r="D46" s="6">
-        <v>-14.78</v>
+        <v>-14.55</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.12</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2862,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-10.03</v>
+        <v>-11.67</v>
       </c>
       <c r="D47" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.64</v>
+        <v>-12.25</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2879,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-48.24</v>
+        <v>-48.69</v>
       </c>
       <c r="D48" s="6">
-        <v>-48.69</v>
+        <v>-48.27</v>
       </c>
       <c r="E48" s="8">
-        <v>-0.45</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2896,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-5.18</v>
+        <v>-5.79</v>
       </c>
       <c r="D49" s="6">
-        <v>-5.79</v>
+        <v>-5.47</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.61</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2913,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-1.19</v>
+        <v>-2.91</v>
       </c>
       <c r="D50" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.72</v>
+        <v>-3.26</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2930,13 +2917,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-6.54</v>
+        <v>-8.26</v>
       </c>
       <c r="D51" s="6">
-        <v>-8.26</v>
+        <v>-8.02</v>
       </c>
       <c r="E51" s="8">
-        <v>-1.72</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2947,13 +2934,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>672.35</v>
+        <v>699.1</v>
       </c>
       <c r="D52" s="6">
-        <v>699.1</v>
+        <v>683.8</v>
       </c>
       <c r="E52" s="7">
-        <v>26.75</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2964,13 +2951,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>305.3</v>
+        <v>309.55</v>
       </c>
       <c r="D53" s="6">
-        <v>309.55</v>
+        <v>307.6</v>
       </c>
       <c r="E53" s="7">
-        <v>4.25</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2981,13 +2968,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1165</v>
+        <v>1147.9</v>
       </c>
       <c r="D54" s="6">
-        <v>1147.9</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-17.1</v>
+        <v>1136.3</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-11.6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2998,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>737.85</v>
+        <v>736.8</v>
       </c>
       <c r="D55" s="6">
-        <v>736.8</v>
+        <v>738.75</v>
       </c>
       <c r="E55" s="8">
-        <v>-1.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3015,13 +3002,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>539.85</v>
+        <v>530</v>
       </c>
       <c r="D56" s="6">
-        <v>530</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-9.85</v>
+        <v>526.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3032,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>11472</v>
+        <v>11372</v>
       </c>
       <c r="D57" s="6">
-        <v>11372</v>
+        <v>11466</v>
       </c>
       <c r="E57" s="8">
-        <v>-100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3049,13 +3036,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>333</v>
+        <v>330.85</v>
       </c>
       <c r="D58" s="6">
-        <v>330.85</v>
+        <v>332</v>
       </c>
       <c r="E58" s="8">
-        <v>-2.15</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3066,13 +3053,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="D59" s="6">
-        <v>1302</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-23</v>
+        <v>1297.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3083,13 +3070,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>85.47</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D60" s="6">
-        <v>83.90000000000001</v>
+        <v>84.12</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.57</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3100,370 +3087,336 @@
         <v>13</v>
       </c>
       <c r="C61" s="6">
+        <v>77</v>
+      </c>
+      <c r="D61" s="6">
         <v>55</v>
       </c>
-      <c r="D61" s="6">
-        <v>77</v>
-      </c>
       <c r="E61" s="7">
-        <v>22</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="D62" s="6">
-        <v>99</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="E62" s="8">
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>77</v>
+        <v>63.11</v>
       </c>
       <c r="D63" s="6">
-        <v>55</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-22</v>
+        <v>57.74</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-5.37</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>99</v>
+        <v>68.19</v>
       </c>
       <c r="D64" s="6">
-        <v>88</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11</v>
+        <v>65.98999999999999</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>56.55</v>
+        <v>54.21</v>
       </c>
       <c r="D65" s="6">
-        <v>63.11</v>
+        <v>50.83</v>
       </c>
       <c r="E65" s="7">
-        <v>6.56</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>65.89</v>
+        <v>57.95</v>
       </c>
       <c r="D66" s="6">
-        <v>68.19</v>
-      </c>
-      <c r="E66" s="7">
-        <v>2.3</v>
+        <v>58.95</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>59.65</v>
+        <v>40.67</v>
       </c>
       <c r="D67" s="6">
-        <v>54.21</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-5.44</v>
+        <v>38.91</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>58.67</v>
+        <v>45.71</v>
       </c>
       <c r="D68" s="6">
-        <v>57.95</v>
+        <v>47.62</v>
       </c>
       <c r="E68" s="8">
-        <v>-0.72</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>46.12</v>
+        <v>46.78</v>
       </c>
       <c r="D69" s="6">
-        <v>40.67</v>
+        <v>47.97</v>
       </c>
       <c r="E69" s="8">
-        <v>-5.45</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>47.42</v>
+        <v>50.66</v>
       </c>
       <c r="D70" s="6">
-        <v>45.71</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.71</v>
+        <v>49.24</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>48.72</v>
+        <v>57.16</v>
       </c>
       <c r="D71" s="6">
-        <v>46.78</v>
+        <v>57.46</v>
       </c>
       <c r="E71" s="8">
-        <v>-1.94</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>58.3</v>
+        <v>11.64</v>
       </c>
       <c r="D72" s="6">
-        <v>50.66</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-7.64</v>
+        <v>-69.13</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-80.77</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>59.93</v>
+        <v>-26.39</v>
       </c>
       <c r="D73" s="6">
-        <v>57.16</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-2.77</v>
+        <v>-29.79</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-65.88</v>
+        <v>-1.85</v>
       </c>
       <c r="D74" s="6">
-        <v>11.64</v>
+        <v>-43.46</v>
       </c>
       <c r="E74" s="7">
-        <v>77.52</v>
+        <v>-41.61</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-71.45999999999999</v>
+        <v>22.32</v>
       </c>
       <c r="D75" s="6">
-        <v>-26.39</v>
+        <v>-9.59</v>
       </c>
       <c r="E75" s="7">
-        <v>45.07</v>
+        <v>-31.91</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>10.77</v>
+        <v>38.41</v>
       </c>
       <c r="D76" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-12.62</v>
+        <v>-6.02</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-44.43</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>86.65000000000001</v>
+        <v>-73.84999999999999</v>
       </c>
       <c r="D77" s="6">
-        <v>22.32</v>
+        <v>-64.08</v>
       </c>
       <c r="E77" s="8">
-        <v>-64.33</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>36.66</v>
+        <v>3.04</v>
       </c>
       <c r="D78" s="6">
-        <v>38.41</v>
+        <v>-32.45</v>
       </c>
       <c r="E78" s="7">
-        <v>1.75</v>
+        <v>-35.49</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-40.4</v>
+        <v>-20.54</v>
       </c>
       <c r="D79" s="6">
-        <v>-73.84999999999999</v>
+        <v>-17.63</v>
       </c>
       <c r="E79" s="8">
-        <v>-33.45</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-15.55</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D80" s="6">
-        <v>3.04</v>
+        <v>33.62</v>
       </c>
       <c r="E80" s="7">
-        <v>18.59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-34.22</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-20.54</v>
-      </c>
-      <c r="E81" s="7">
-        <v>13.68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-32.22</v>
-      </c>
-      <c r="D82" s="6">
-        <v>87.01000000000001</v>
-      </c>
-      <c r="E82" s="7">
-        <v>119.23</v>
+        <v>-53.39</v>
       </c>
     </row>
   </sheetData>
@@ -3528,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>53.8</v>
+        <v>52.7</v>
       </c>
       <c r="E2" s="11">
         <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="G2" s="11">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3674,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.405</v>
+        <v>0.4078</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3635</v>
+        <v>0.3636</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2908</v>
+        <v>0.292</v>
       </c>
       <c r="D2" s="14">
         <v>0.2383</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1872</v>
+        <v>0.1916</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1639</v>
+        <v>0.1523</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1478</v>
+        <v>0.1459</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0347</v>
+        <v>-0.0322</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.057</v>
+        <v>-0.0639</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,40 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.7 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.7</t>
+    <t>48.0 → 56.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>56.5</t>
+  </si>
+  <si>
+    <t>49.2 → 53.1</t>
   </si>
   <si>
     <t>49.2</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>59.0 → 74.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>74.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,20 +315,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +452,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +968,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>683.8</v>
+        <v>675.7</v>
       </c>
       <c r="D2">
-        <v>-2.19</v>
+        <v>-1.18</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -942,46 +980,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.14</v>
+        <v>-32.94</v>
       </c>
       <c r="H2">
-        <v>86.22</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="I2">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="J2">
-        <v>8.800000000000001</v>
+        <v>7.34</v>
       </c>
       <c r="K2">
-        <v>-2.37</v>
+        <v>-7.66</v>
       </c>
       <c r="L2">
-        <v>16.24</v>
+        <v>17.17</v>
       </c>
       <c r="M2">
-        <v>-6.39</v>
+        <v>-6.83</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>685.04</v>
+        <v>682.9299999999999</v>
       </c>
       <c r="Q2">
-        <v>656.4400000000001</v>
+        <v>656.9</v>
       </c>
       <c r="R2">
-        <v>649.39</v>
+        <v>650.65</v>
       </c>
       <c r="S2">
-        <v>624.9400000000001</v>
+        <v>625.65</v>
       </c>
       <c r="T2">
-        <v>9.42</v>
+        <v>8</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1034,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>57.74</v>
+        <v>55.07</v>
       </c>
       <c r="Z2">
-        <v>10.65</v>
+        <v>10.4</v>
       </c>
       <c r="AA2">
-        <v>5.12</v>
+        <v>6.18</v>
       </c>
       <c r="AB2">
-        <v>5.53</v>
+        <v>4.23</v>
       </c>
       <c r="AC2">
-        <v>70.66</v>
+        <v>68.14</v>
       </c>
       <c r="AD2">
-        <v>73.39</v>
+        <v>71.56</v>
       </c>
       <c r="AE2">
-        <v>25.94</v>
+        <v>26.15</v>
       </c>
       <c r="AF2">
-        <v>-69.13</v>
+        <v>-72.45</v>
       </c>
       <c r="AG2">
-        <v>701.84</v>
+        <v>702.9</v>
       </c>
       <c r="AH2">
-        <v>611.05</v>
+        <v>610.9</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1032,7 +1070,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>51.29</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,37 +1081,37 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>307.6</v>
+        <v>311.7</v>
       </c>
       <c r="D3">
-        <v>-0.63</v>
+        <v>1.33</v>
       </c>
       <c r="E3">
-        <v>310.85</v>
+        <v>311.7</v>
       </c>
       <c r="F3">
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>100.74</v>
+        <v>103.42</v>
       </c>
       <c r="I3">
-        <v>-0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="J3">
-        <v>10.23</v>
+        <v>13.95</v>
       </c>
       <c r="K3">
-        <v>36.61</v>
+        <v>39.47</v>
       </c>
       <c r="L3">
-        <v>51.09</v>
+        <v>56.56</v>
       </c>
       <c r="M3">
-        <v>40.78</v>
+        <v>40.88</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1082,19 +1120,19 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>308.49</v>
+        <v>309</v>
       </c>
       <c r="Q3">
-        <v>290.95</v>
+        <v>293.06</v>
       </c>
       <c r="R3">
-        <v>274.35</v>
+        <v>275.38</v>
       </c>
       <c r="S3">
-        <v>217.18</v>
+        <v>217.93</v>
       </c>
       <c r="T3">
-        <v>41.63</v>
+        <v>43.03</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1147,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>65.98999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="Z3">
-        <v>11.79</v>
+        <v>11.68</v>
       </c>
       <c r="AA3">
-        <v>10.98</v>
+        <v>11.12</v>
       </c>
       <c r="AB3">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC3">
-        <v>63.9</v>
+        <v>64.38</v>
       </c>
       <c r="AD3">
-        <v>74.06999999999999</v>
+        <v>68.12</v>
       </c>
       <c r="AE3">
-        <v>10.56</v>
+        <v>10.53</v>
       </c>
       <c r="AF3">
-        <v>-29.79</v>
+        <v>-33.94</v>
       </c>
       <c r="AG3">
-        <v>329.11</v>
+        <v>330.9</v>
       </c>
       <c r="AH3">
-        <v>252.79</v>
+        <v>255.22</v>
       </c>
       <c r="AI3">
         <v>279.64</v>
@@ -1145,7 +1183,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>44.78</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1194,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1136.3</v>
+        <v>1146.5</v>
       </c>
       <c r="D4">
-        <v>-1.01</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1168,46 +1206,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.83</v>
+        <v>-11.04</v>
       </c>
       <c r="H4">
-        <v>15.24</v>
+        <v>16.28</v>
       </c>
       <c r="I4">
-        <v>-2.04</v>
+        <v>-1.11</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="L4">
-        <v>10.12</v>
+        <v>10.79</v>
       </c>
       <c r="M4">
-        <v>23.83</v>
+        <v>23.77</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>1150.72</v>
+        <v>1148.14</v>
       </c>
       <c r="Q4">
-        <v>1139.62</v>
+        <v>1141.34</v>
       </c>
       <c r="R4">
-        <v>1093.05</v>
+        <v>1095.41</v>
       </c>
       <c r="S4">
-        <v>1129.18</v>
+        <v>1129.72</v>
       </c>
       <c r="T4">
-        <v>0.63</v>
+        <v>1.49</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1260,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>50.83</v>
+        <v>53.57</v>
       </c>
       <c r="Z4">
-        <v>15.59</v>
+        <v>14.16</v>
       </c>
       <c r="AA4">
-        <v>18.66</v>
+        <v>17.76</v>
       </c>
       <c r="AB4">
-        <v>-3.07</v>
+        <v>-3.6</v>
       </c>
       <c r="AC4">
-        <v>10.65</v>
+        <v>4.21</v>
       </c>
       <c r="AD4">
-        <v>19.24</v>
+        <v>10.54</v>
       </c>
       <c r="AE4">
-        <v>27.9</v>
+        <v>27.86</v>
       </c>
       <c r="AF4">
-        <v>-43.46</v>
+        <v>-22.54</v>
       </c>
       <c r="AG4">
-        <v>1201.29</v>
+        <v>1201.67</v>
       </c>
       <c r="AH4">
-        <v>1077.94</v>
+        <v>1081.01</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1258,7 +1296,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>27.11</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>738.75</v>
+        <v>783.3</v>
       </c>
       <c r="D5">
-        <v>0.26</v>
+        <v>6.03</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1281,46 +1319,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.55</v>
+        <v>-9.4</v>
       </c>
       <c r="H5">
-        <v>11.61</v>
+        <v>18.34</v>
       </c>
       <c r="I5">
-        <v>0.65</v>
+        <v>6.59</v>
       </c>
       <c r="J5">
-        <v>0.82</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="K5">
-        <v>11.61</v>
+        <v>15.3</v>
       </c>
       <c r="L5">
-        <v>-0.97</v>
+        <v>3.78</v>
       </c>
       <c r="M5">
-        <v>36.36</v>
+        <v>37.17</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>737.34</v>
+        <v>747.02</v>
       </c>
       <c r="Q5">
-        <v>723.75</v>
+        <v>726.02</v>
       </c>
       <c r="R5">
-        <v>722.7</v>
+        <v>724.72</v>
       </c>
       <c r="S5">
-        <v>748.64</v>
+        <v>748.8</v>
       </c>
       <c r="T5">
-        <v>-1.32</v>
+        <v>4.61</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,46 +1370,46 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>58.95</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="Z5">
-        <v>2.93</v>
+        <v>7.11</v>
       </c>
       <c r="AA5">
-        <v>0.01</v>
+        <v>1.43</v>
       </c>
       <c r="AB5">
-        <v>2.91</v>
+        <v>5.68</v>
       </c>
       <c r="AC5">
-        <v>97.81</v>
+        <v>98.33</v>
       </c>
       <c r="AD5">
-        <v>98.40000000000001</v>
+        <v>98.02</v>
       </c>
       <c r="AE5">
-        <v>16.34</v>
+        <v>19.68</v>
       </c>
       <c r="AF5">
-        <v>-9.59</v>
+        <v>1261.35</v>
       </c>
       <c r="AG5">
-        <v>754.91</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AH5">
-        <v>692.58</v>
+        <v>685.35</v>
       </c>
       <c r="AI5">
-        <v>692.25</v>
+        <v>703.47</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>28.26</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>526.5</v>
+        <v>534.8</v>
       </c>
       <c r="D6">
-        <v>-0.66</v>
+        <v>1.58</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1394,46 +1432,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-12.25</v>
+        <v>-10.87</v>
       </c>
       <c r="H6">
-        <v>20.05</v>
+        <v>21.94</v>
       </c>
       <c r="I6">
-        <v>1.64</v>
+        <v>-0.93</v>
       </c>
       <c r="J6">
-        <v>-8.91</v>
+        <v>-5.01</v>
       </c>
       <c r="K6">
-        <v>-6.09</v>
+        <v>-3.16</v>
       </c>
       <c r="L6">
-        <v>5.13</v>
+        <v>6.45</v>
       </c>
       <c r="M6">
-        <v>15.23</v>
+        <v>14.47</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>535.13</v>
+        <v>534.13</v>
       </c>
       <c r="Q6">
-        <v>541.99</v>
+        <v>540.8</v>
       </c>
       <c r="R6">
-        <v>549.97</v>
+        <v>549.27</v>
       </c>
       <c r="S6">
-        <v>520.39</v>
+        <v>520.65</v>
       </c>
       <c r="T6">
-        <v>1.17</v>
+        <v>2.72</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1486,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.91</v>
+        <v>44.99</v>
       </c>
       <c r="Z6">
-        <v>-6.82</v>
+        <v>-6.41</v>
       </c>
       <c r="AA6">
-        <v>-5.91</v>
+        <v>-6.01</v>
       </c>
       <c r="AB6">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AC6">
-        <v>75.26000000000001</v>
+        <v>73.05</v>
       </c>
       <c r="AD6">
-        <v>83.98</v>
+        <v>78.22</v>
       </c>
       <c r="AE6">
-        <v>12.04</v>
+        <v>12.63</v>
       </c>
       <c r="AF6">
-        <v>-6.02</v>
+        <v>6.61</v>
       </c>
       <c r="AG6">
-        <v>565.61</v>
+        <v>563.24</v>
       </c>
       <c r="AH6">
-        <v>518.38</v>
+        <v>518.36</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1484,7 +1522,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.7</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11466</v>
+        <v>11344</v>
       </c>
       <c r="D7">
-        <v>0.83</v>
+        <v>-1.06</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1507,46 +1545,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.27</v>
+        <v>-48.82</v>
       </c>
       <c r="H7">
-        <v>7.61</v>
+        <v>6.47</v>
       </c>
       <c r="I7">
-        <v>-2.13</v>
+        <v>-0.85</v>
       </c>
       <c r="J7">
-        <v>-3.26</v>
+        <v>-5</v>
       </c>
       <c r="K7">
-        <v>-5.84</v>
+        <v>-5.95</v>
       </c>
       <c r="L7">
-        <v>-38.73</v>
+        <v>-39.9</v>
       </c>
       <c r="M7">
-        <v>19.16</v>
+        <v>19.05</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P7">
-        <v>11468.2</v>
+        <v>11448.8</v>
       </c>
       <c r="Q7">
-        <v>11569.9</v>
+        <v>11558.5</v>
       </c>
       <c r="R7">
-        <v>11524.98</v>
+        <v>11510.52</v>
       </c>
       <c r="S7">
-        <v>14718.26</v>
+        <v>14688.36</v>
       </c>
       <c r="T7">
-        <v>-22.1</v>
+        <v>-22.77</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1599,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.62</v>
+        <v>45.39</v>
       </c>
       <c r="Z7">
-        <v>-32.94</v>
+        <v>-46.77</v>
       </c>
       <c r="AA7">
-        <v>-13.16</v>
+        <v>-19.88</v>
       </c>
       <c r="AB7">
-        <v>-19.77</v>
+        <v>-26.88</v>
       </c>
       <c r="AC7">
-        <v>37.48</v>
+        <v>33.45</v>
       </c>
       <c r="AD7">
-        <v>40.6</v>
+        <v>37.34</v>
       </c>
       <c r="AE7">
-        <v>413.04</v>
+        <v>395.39</v>
       </c>
       <c r="AF7">
-        <v>-64.08</v>
+        <v>-81.06</v>
       </c>
       <c r="AG7">
-        <v>12013.54</v>
+        <v>12013.49</v>
       </c>
       <c r="AH7">
-        <v>11126.26</v>
+        <v>11103.51</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1597,7 +1635,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>23.64</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1646,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>332</v>
+        <v>341.4</v>
       </c>
       <c r="D8">
-        <v>0.35</v>
+        <v>2.83</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1620,46 +1658,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-5.47</v>
+        <v>-2.79</v>
       </c>
       <c r="H8">
-        <v>41.69</v>
+        <v>45.7</v>
       </c>
       <c r="I8">
-        <v>-0.84</v>
+        <v>2.8</v>
       </c>
       <c r="J8">
-        <v>-2.92</v>
+        <v>-0.13</v>
       </c>
       <c r="K8">
-        <v>19.17</v>
+        <v>23.94</v>
       </c>
       <c r="L8">
-        <v>9.48</v>
+        <v>13.76</v>
       </c>
       <c r="M8">
-        <v>29.2</v>
+        <v>30.4</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>332.41</v>
+        <v>334.27</v>
       </c>
       <c r="Q8">
-        <v>336.67</v>
+        <v>336.41</v>
       </c>
       <c r="R8">
-        <v>332.95</v>
+        <v>333.17</v>
       </c>
       <c r="S8">
-        <v>286.23</v>
+        <v>286.59</v>
       </c>
       <c r="T8">
-        <v>15.99</v>
+        <v>19.12</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1712,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>47.97</v>
+        <v>56.54</v>
       </c>
       <c r="Z8">
-        <v>0.6899999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="AA8">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB8">
-        <v>-1.39</v>
+        <v>-0.73</v>
       </c>
       <c r="AC8">
-        <v>5.03</v>
+        <v>26.87</v>
       </c>
       <c r="AD8">
-        <v>6.24</v>
+        <v>12.91</v>
       </c>
       <c r="AE8">
-        <v>8.630000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AF8">
-        <v>-32.45</v>
+        <v>134.4</v>
       </c>
       <c r="AG8">
-        <v>347.65</v>
+        <v>346.62</v>
       </c>
       <c r="AH8">
-        <v>325.7</v>
+        <v>326.21</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1710,7 +1748,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>23.04</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,37 +1759,37 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1297.3</v>
+        <v>1310</v>
       </c>
       <c r="D9">
-        <v>-0.36</v>
+        <v>0.98</v>
       </c>
       <c r="E9">
         <v>1341</v>
       </c>
       <c r="F9">
-        <v>1073.1</v>
+        <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-3.26</v>
+        <v>-2.31</v>
       </c>
       <c r="H9">
-        <v>20.89</v>
+        <v>21.37</v>
       </c>
       <c r="I9">
-        <v>-1.23</v>
+        <v>0.31</v>
       </c>
       <c r="J9">
-        <v>-0.36</v>
+        <v>2.07</v>
       </c>
       <c r="K9">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="L9">
-        <v>20.97</v>
+        <v>22.08</v>
       </c>
       <c r="M9">
-        <v>14.59</v>
+        <v>14.75</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1760,19 +1798,19 @@
         <v>66</v>
       </c>
       <c r="P9">
-        <v>1307.66</v>
+        <v>1308.46</v>
       </c>
       <c r="Q9">
-        <v>1302.95</v>
+        <v>1304.99</v>
       </c>
       <c r="R9">
-        <v>1275.65</v>
+        <v>1277.53</v>
       </c>
       <c r="S9">
-        <v>1226.79</v>
+        <v>1227.64</v>
       </c>
       <c r="T9">
-        <v>5.75</v>
+        <v>6.71</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1825,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>49.24</v>
+        <v>53.07</v>
       </c>
       <c r="Z9">
-        <v>8.56</v>
+        <v>8.01</v>
       </c>
       <c r="AA9">
-        <v>11.6</v>
+        <v>10.88</v>
       </c>
       <c r="AB9">
-        <v>-3.04</v>
+        <v>-2.87</v>
       </c>
       <c r="AC9">
-        <v>19.14</v>
+        <v>7.77</v>
       </c>
       <c r="AD9">
-        <v>28.63</v>
+        <v>18.64</v>
       </c>
       <c r="AE9">
-        <v>25.46</v>
+        <v>25.27</v>
       </c>
       <c r="AF9">
-        <v>-17.63</v>
+        <v>-8.58</v>
       </c>
       <c r="AG9">
-        <v>1349.99</v>
+        <v>1349.32</v>
       </c>
       <c r="AH9">
-        <v>1255.9</v>
+        <v>1260.66</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1823,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.78</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1872,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>84.12</v>
+        <v>83.86</v>
       </c>
       <c r="D10">
-        <v>0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1846,46 +1884,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-8.02</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H10">
-        <v>133.15</v>
+        <v>132.43</v>
       </c>
       <c r="I10">
-        <v>5.97</v>
+        <v>7.97</v>
       </c>
       <c r="J10">
-        <v>-0.3</v>
+        <v>-0.01</v>
       </c>
       <c r="K10">
-        <v>57.88</v>
+        <v>63.69</v>
       </c>
       <c r="L10">
-        <v>14.95</v>
+        <v>15.54</v>
       </c>
       <c r="M10">
-        <v>-3.22</v>
+        <v>-3.01</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>82.54000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="Q10">
-        <v>83.3</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="R10">
-        <v>71.84</v>
+        <v>72.47</v>
       </c>
       <c r="S10">
-        <v>59.99</v>
+        <v>60.07</v>
       </c>
       <c r="T10">
-        <v>40.21</v>
+        <v>39.6</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1938,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>57.46</v>
+        <v>56.96</v>
       </c>
       <c r="Z10">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AA10">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="AB10">
-        <v>-0.66</v>
+        <v>-0.57</v>
       </c>
       <c r="AC10">
-        <v>68.45999999999999</v>
+        <v>70.06</v>
       </c>
       <c r="AD10">
-        <v>49.63</v>
+        <v>63.46</v>
       </c>
       <c r="AE10">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="AF10">
-        <v>33.62</v>
+        <v>-41.4</v>
       </c>
       <c r="AG10">
-        <v>90.77</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="AH10">
-        <v>75.83</v>
+        <v>75.88</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1936,7 +1974,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>16.34</v>
+        <v>14.47</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2155,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1294 +2173,1334 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>12.76</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C9" s="7">
         <v>8.800000000000001</v>
       </c>
-      <c r="E7" s="7">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D9" s="7">
+        <v>7.34</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>14.06</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>10.23</v>
       </c>
-      <c r="E8" s="7">
-        <v>-3.83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="7">
+        <v>13.95</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>4.07</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C12" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="D12" s="7">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E12" s="9">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.91</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-5.01</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-3.26</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-5</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-2.92</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.13</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2.07</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.01</v>
+      </c>
+      <c r="E17" s="9">
         <v>0.29</v>
       </c>
-      <c r="D10" s="6">
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1.53</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-1.54</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D19" s="7">
         <v>0.82</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="E19" s="9">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-2.04</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.11</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="D21" s="7">
+        <v>6.59</v>
+      </c>
+      <c r="E21" s="9">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1.64</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.93</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-2.13</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-0.85</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.84</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-1.23</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>5.97</v>
+      </c>
+      <c r="D26" s="7">
+        <v>7.97</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>16.24</v>
+      </c>
+      <c r="D27" s="7">
+        <v>17.17</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>51.09</v>
+      </c>
+      <c r="D28" s="7">
+        <v>56.56</v>
+      </c>
+      <c r="E28" s="9">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>10.12</v>
+      </c>
+      <c r="D29" s="7">
+        <v>10.79</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-0.97</v>
+      </c>
+      <c r="D30" s="7">
+        <v>3.78</v>
+      </c>
+      <c r="E30" s="9">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>5.13</v>
+      </c>
+      <c r="D31" s="7">
+        <v>6.45</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-38.73</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-39.9</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>9.48</v>
+      </c>
+      <c r="D33" s="7">
+        <v>13.76</v>
+      </c>
+      <c r="E33" s="9">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>20.97</v>
+      </c>
+      <c r="D34" s="7">
+        <v>22.08</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>14.95</v>
+      </c>
+      <c r="D35" s="7">
+        <v>15.54</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-2.37</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-7.66</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-5.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>36.61</v>
+      </c>
+      <c r="D37" s="7">
+        <v>39.47</v>
+      </c>
+      <c r="E37" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="D38" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>11.61</v>
+      </c>
+      <c r="D39" s="7">
+        <v>15.3</v>
+      </c>
+      <c r="E39" s="9">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
         <v>-6.09</v>
       </c>
-      <c r="D11" s="6">
-        <v>-8.91</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D40" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="E40" s="9">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-5.84</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-5.95</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>19.17</v>
+      </c>
+      <c r="D42" s="7">
+        <v>23.94</v>
+      </c>
+      <c r="E42" s="9">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2.17</v>
+      </c>
+      <c r="D43" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>57.88</v>
+      </c>
+      <c r="D44" s="7">
+        <v>63.69</v>
+      </c>
+      <c r="E44" s="9">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-32.14</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-32.94</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-1.05</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-11.83</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-11.04</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-14.55</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-9.4</v>
+      </c>
+      <c r="E48" s="9">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-12.25</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-10.87</v>
+      </c>
+      <c r="E49" s="9">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-48.27</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-48.82</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-5.47</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-2.79</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
         <v>-3.26</v>
       </c>
-      <c r="E12" s="8">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D52" s="7">
+        <v>-2.31</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-8.02</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>683.8</v>
+      </c>
+      <c r="D54" s="7">
+        <v>675.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>307.6</v>
+      </c>
+      <c r="D55" s="7">
+        <v>311.7</v>
+      </c>
+      <c r="E55" s="9">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1136.3</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1146.5</v>
+      </c>
+      <c r="E56" s="9">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>738.75</v>
+      </c>
+      <c r="D57" s="7">
+        <v>783.3</v>
+      </c>
+      <c r="E57" s="9">
+        <v>44.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>526.5</v>
+      </c>
+      <c r="D58" s="7">
+        <v>534.8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>11466</v>
+      </c>
+      <c r="D59" s="7">
+        <v>11344</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.92</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>332</v>
+      </c>
+      <c r="D60" s="7">
+        <v>341.4</v>
+      </c>
+      <c r="E60" s="9">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1297.3</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1310</v>
+      </c>
+      <c r="E61" s="9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>84.12</v>
+      </c>
+      <c r="D62" s="7">
+        <v>83.86</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>10.73</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.53</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-12.26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>55</v>
+      </c>
+      <c r="D63" s="7">
+        <v>34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>34</v>
+      </c>
+      <c r="D64" s="7">
+        <v>55</v>
+      </c>
+      <c r="E64" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>57.74</v>
+      </c>
+      <c r="D65" s="7">
+        <v>55.07</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.03</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="D66" s="7">
+        <v>68.31</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.04</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>50.83</v>
+      </c>
+      <c r="D67" s="7">
+        <v>53.57</v>
+      </c>
+      <c r="E67" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>4.93</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>58.95</v>
+      </c>
+      <c r="D68" s="7">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="E68" s="9">
+        <v>15.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.84</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.64</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>38.91</v>
+      </c>
+      <c r="D69" s="7">
+        <v>44.99</v>
+      </c>
+      <c r="E69" s="9">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.45</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-2.13</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>47.62</v>
+      </c>
+      <c r="D70" s="7">
+        <v>45.39</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>47.97</v>
+      </c>
+      <c r="D71" s="7">
+        <v>56.54</v>
+      </c>
+      <c r="E71" s="9">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.44</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>49.24</v>
+      </c>
+      <c r="D72" s="7">
+        <v>53.07</v>
+      </c>
+      <c r="E72" s="9">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="D24" s="6">
-        <v>5.97</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>57.46</v>
+      </c>
+      <c r="D73" s="7">
+        <v>56.96</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>17.58</v>
-      </c>
-      <c r="D25" s="6">
-        <v>16.24</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-69.13</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-72.45</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>49.05</v>
-      </c>
-      <c r="D26" s="6">
-        <v>51.09</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-29.79</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-33.94</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>11.63</v>
-      </c>
-      <c r="D27" s="6">
-        <v>10.12</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-43.46</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-22.54</v>
+      </c>
+      <c r="E76" s="9">
+        <v>20.92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-3.02</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-9.59</v>
+      </c>
+      <c r="D77" s="7">
+        <v>1261.35</v>
+      </c>
+      <c r="E77" s="9">
+        <v>1270.94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="D29" s="6">
-        <v>5.13</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-6.02</v>
+      </c>
+      <c r="D78" s="7">
+        <v>6.61</v>
+      </c>
+      <c r="E78" s="9">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-38.99</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-38.73</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-64.08</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-81.06</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-16.98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>7.93</v>
-      </c>
-      <c r="D31" s="6">
-        <v>9.48</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-32.45</v>
+      </c>
+      <c r="D80" s="7">
+        <v>134.4</v>
+      </c>
+      <c r="E80" s="9">
+        <v>166.85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>21.43</v>
-      </c>
-      <c r="D32" s="6">
-        <v>20.97</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-17.63</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-8.58</v>
+      </c>
+      <c r="E81" s="9">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>13.41</v>
-      </c>
-      <c r="D33" s="6">
-        <v>14.95</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>29.08</v>
-      </c>
-      <c r="D35" s="6">
-        <v>36.61</v>
-      </c>
-      <c r="E35" s="8">
-        <v>7.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>10.71</v>
-      </c>
-      <c r="D37" s="6">
-        <v>11.61</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-7.08</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-8.33</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.84</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>16.99</v>
-      </c>
-      <c r="D40" s="6">
-        <v>19.17</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3.19</v>
-      </c>
-      <c r="D41" s="6">
-        <v>2.17</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>69.36</v>
-      </c>
-      <c r="D42" s="6">
-        <v>57.88</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-11.48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-30.62</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-32.14</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-0.42</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-11.83</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-14.78</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.55</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-12.25</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-48.69</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-48.27</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-5.79</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-3.26</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-8.26</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>699.1</v>
-      </c>
-      <c r="D52" s="6">
-        <v>683.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>309.55</v>
-      </c>
-      <c r="D53" s="6">
-        <v>307.6</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1147.9</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1136.3</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-11.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>736.8</v>
-      </c>
-      <c r="D55" s="6">
-        <v>738.75</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>530</v>
-      </c>
-      <c r="D56" s="6">
-        <v>526.5</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11372</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11466</v>
-      </c>
-      <c r="E57" s="8">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>330.85</v>
-      </c>
-      <c r="D58" s="6">
-        <v>332</v>
-      </c>
-      <c r="E58" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1302</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1297.3</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="D60" s="6">
-        <v>84.12</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>77</v>
-      </c>
-      <c r="D61" s="6">
-        <v>55</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>55</v>
-      </c>
-      <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>63.11</v>
-      </c>
-      <c r="D63" s="6">
-        <v>57.74</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-5.37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>68.19</v>
-      </c>
-      <c r="D64" s="6">
-        <v>65.98999999999999</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>54.21</v>
-      </c>
-      <c r="D65" s="6">
-        <v>50.83</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-3.38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>57.95</v>
-      </c>
-      <c r="D66" s="6">
-        <v>58.95</v>
-      </c>
-      <c r="E66" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>40.67</v>
-      </c>
-      <c r="D67" s="6">
-        <v>38.91</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>45.71</v>
-      </c>
-      <c r="D68" s="6">
-        <v>47.62</v>
-      </c>
-      <c r="E68" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>46.78</v>
-      </c>
-      <c r="D69" s="6">
-        <v>47.97</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>50.66</v>
-      </c>
-      <c r="D70" s="6">
-        <v>49.24</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>57.16</v>
-      </c>
-      <c r="D71" s="6">
-        <v>57.46</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>11.64</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-69.13</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-80.77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-26.39</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-29.79</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-43.46</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-41.61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>22.32</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-9.59</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-31.91</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>38.41</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-44.43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-73.84999999999999</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-64.08</v>
-      </c>
-      <c r="E77" s="8">
-        <v>9.77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-32.45</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-35.49</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-20.54</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="E79" s="8">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>87.01000000000001</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C82" s="7">
         <v>33.62</v>
       </c>
-      <c r="E80" s="7">
-        <v>-53.39</v>
+      <c r="D82" s="7">
+        <v>-41.4</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-75.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3442,60 +3520,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>68.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>52.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>80</v>
-      </c>
-      <c r="F2" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>12.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>56.4</v>
+      </c>
+      <c r="E2" s="12">
+        <v>90</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>14.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3597,61 +3675,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.4078</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3636</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.292</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2383</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1916</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1523</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1459</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0322</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0639</v>
+      <c r="A2" s="15">
+        <v>0.4088000000000001</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3717</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.304</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2377</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1905</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1475</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1447</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0301</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0683</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.0 → 56.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>56.5</t>
-  </si>
-  <si>
-    <t>49.2 → 53.1</t>
-  </si>
-  <si>
-    <t>49.2</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>74.1 → 62.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>74.1</t>
+  </si>
+  <si>
+    <t>62.3</t>
   </si>
   <si>
     <t>RSI Overbought Entry</t>
   </si>
   <si>
-    <t>59.0 → 74.1</t>
+    <t>68.3 → 71.3</t>
   </si>
   <si>
     <t>⚠️ CAUTION</t>
   </si>
   <si>
-    <t>59.0</t>
-  </si>
-  <si>
-    <t>74.1</t>
+    <t>68.3</t>
+  </si>
+  <si>
+    <t>71.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -281,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,7 +306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,8 +325,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,7 +360,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,6 +373,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,11 +460,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -469,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -968,10 +972,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>675.7</v>
+        <v>677.3</v>
       </c>
       <c r="D2">
-        <v>-1.18</v>
+        <v>0.24</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -980,46 +984,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.94</v>
+        <v>-32.78</v>
       </c>
       <c r="H2">
-        <v>84.01000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I2">
-        <v>-1.54</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J2">
-        <v>7.34</v>
+        <v>1.61</v>
       </c>
       <c r="K2">
-        <v>-7.66</v>
+        <v>-9.93</v>
       </c>
       <c r="L2">
-        <v>17.17</v>
+        <v>16.44</v>
       </c>
       <c r="M2">
-        <v>-6.83</v>
+        <v>-7.01</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>682.9299999999999</v>
+        <v>681.65</v>
       </c>
       <c r="Q2">
-        <v>656.9</v>
+        <v>658.1900000000001</v>
       </c>
       <c r="R2">
-        <v>650.65</v>
+        <v>651.85</v>
       </c>
       <c r="S2">
-        <v>625.65</v>
+        <v>626.4299999999999</v>
       </c>
       <c r="T2">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1034,34 +1038,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>55.07</v>
+        <v>55.51</v>
       </c>
       <c r="Z2">
-        <v>10.4</v>
+        <v>10.22</v>
       </c>
       <c r="AA2">
-        <v>6.18</v>
+        <v>6.99</v>
       </c>
       <c r="AB2">
-        <v>4.23</v>
+        <v>3.23</v>
       </c>
       <c r="AC2">
-        <v>68.14</v>
+        <v>55.18</v>
       </c>
       <c r="AD2">
-        <v>71.56</v>
+        <v>64.66</v>
       </c>
       <c r="AE2">
-        <v>26.15</v>
+        <v>25.33</v>
       </c>
       <c r="AF2">
-        <v>-72.45</v>
+        <v>-81.14</v>
       </c>
       <c r="AG2">
-        <v>702.9</v>
+        <v>705</v>
       </c>
       <c r="AH2">
-        <v>610.9</v>
+        <v>611.38</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1070,7 +1074,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>51.44</v>
+        <v>51.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1081,13 +1085,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>311.7</v>
+        <v>317.5</v>
       </c>
       <c r="D3">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="E3">
-        <v>311.7</v>
+        <v>317.5</v>
       </c>
       <c r="F3">
         <v>153.23</v>
@@ -1096,43 +1100,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>103.42</v>
+        <v>107.2</v>
       </c>
       <c r="I3">
-        <v>0.82</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
-        <v>13.95</v>
+        <v>17.79</v>
       </c>
       <c r="K3">
-        <v>39.47</v>
+        <v>33.12</v>
       </c>
       <c r="L3">
-        <v>56.56</v>
+        <v>58.2</v>
       </c>
       <c r="M3">
-        <v>40.88</v>
+        <v>41.33</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>309</v>
+        <v>310.33</v>
       </c>
       <c r="Q3">
-        <v>293.06</v>
+        <v>295.72</v>
       </c>
       <c r="R3">
-        <v>275.38</v>
+        <v>276.48</v>
       </c>
       <c r="S3">
-        <v>217.93</v>
+        <v>218.71</v>
       </c>
       <c r="T3">
-        <v>43.03</v>
+        <v>45.17</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1147,43 +1151,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>68.31</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="Z3">
-        <v>11.68</v>
+        <v>11.92</v>
       </c>
       <c r="AA3">
-        <v>11.12</v>
+        <v>11.28</v>
       </c>
       <c r="AB3">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="AC3">
-        <v>64.38</v>
+        <v>68.47</v>
       </c>
       <c r="AD3">
-        <v>68.12</v>
+        <v>65.58</v>
       </c>
       <c r="AE3">
-        <v>10.53</v>
+        <v>10.59</v>
       </c>
       <c r="AF3">
-        <v>-33.94</v>
+        <v>10.01</v>
       </c>
       <c r="AG3">
-        <v>330.9</v>
+        <v>332.52</v>
       </c>
       <c r="AH3">
-        <v>255.22</v>
+        <v>258.91</v>
       </c>
       <c r="AI3">
-        <v>279.64</v>
+        <v>282.53</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>41.61</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1194,10 +1198,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1146.5</v>
+        <v>1137</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1206,25 +1210,25 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.04</v>
+        <v>-11.78</v>
       </c>
       <c r="H4">
-        <v>16.28</v>
+        <v>15.31</v>
       </c>
       <c r="I4">
-        <v>-1.11</v>
+        <v>-0.7</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="K4">
-        <v>2.25</v>
+        <v>-1</v>
       </c>
       <c r="L4">
-        <v>10.79</v>
+        <v>9.16</v>
       </c>
       <c r="M4">
-        <v>23.77</v>
+        <v>23.41</v>
       </c>
       <c r="N4">
         <v>45</v>
@@ -1233,19 +1237,19 @@
         <v>61</v>
       </c>
       <c r="P4">
-        <v>1148.14</v>
+        <v>1146.54</v>
       </c>
       <c r="Q4">
-        <v>1141.34</v>
+        <v>1143.2</v>
       </c>
       <c r="R4">
-        <v>1095.41</v>
+        <v>1097.27</v>
       </c>
       <c r="S4">
-        <v>1129.72</v>
+        <v>1130.3</v>
       </c>
       <c r="T4">
-        <v>1.49</v>
+        <v>0.59</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1260,34 +1264,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>53.57</v>
+        <v>50.73</v>
       </c>
       <c r="Z4">
-        <v>14.16</v>
+        <v>12.12</v>
       </c>
       <c r="AA4">
-        <v>17.76</v>
+        <v>16.63</v>
       </c>
       <c r="AB4">
-        <v>-3.6</v>
+        <v>-4.51</v>
       </c>
       <c r="AC4">
         <v>4.21</v>
       </c>
       <c r="AD4">
-        <v>10.54</v>
+        <v>6.36</v>
       </c>
       <c r="AE4">
-        <v>27.86</v>
+        <v>27.35</v>
       </c>
       <c r="AF4">
-        <v>-22.54</v>
+        <v>-26.32</v>
       </c>
       <c r="AG4">
-        <v>1201.67</v>
+        <v>1200.36</v>
       </c>
       <c r="AH4">
-        <v>1081.01</v>
+        <v>1086.03</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1296,7 +1300,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.66</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1307,10 +1311,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>783.3</v>
+        <v>762.15</v>
       </c>
       <c r="D5">
-        <v>6.03</v>
+        <v>-2.7</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1319,46 +1323,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-9.4</v>
+        <v>-11.85</v>
       </c>
       <c r="H5">
-        <v>18.34</v>
+        <v>15.15</v>
       </c>
       <c r="I5">
-        <v>6.59</v>
+        <v>3.22</v>
       </c>
       <c r="J5">
-        <v>8.029999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="K5">
-        <v>15.3</v>
+        <v>9.73</v>
       </c>
       <c r="L5">
-        <v>3.78</v>
+        <v>1.92</v>
       </c>
       <c r="M5">
-        <v>37.17</v>
+        <v>36.59</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>747.02</v>
+        <v>751.77</v>
       </c>
       <c r="Q5">
-        <v>726.02</v>
+        <v>727.35</v>
       </c>
       <c r="R5">
-        <v>724.72</v>
+        <v>726.14</v>
       </c>
       <c r="S5">
-        <v>748.8</v>
+        <v>748.85</v>
       </c>
       <c r="T5">
-        <v>4.61</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1373,43 +1377,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>74.06999999999999</v>
+        <v>62.33</v>
       </c>
       <c r="Z5">
-        <v>7.11</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>2.87</v>
       </c>
       <c r="AB5">
-        <v>5.68</v>
+        <v>5.75</v>
       </c>
       <c r="AC5">
-        <v>98.33</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AD5">
-        <v>98.02</v>
+        <v>95.19</v>
       </c>
       <c r="AE5">
-        <v>19.68</v>
+        <v>20.44</v>
       </c>
       <c r="AF5">
-        <v>1261.35</v>
+        <v>27.16</v>
       </c>
       <c r="AG5">
-        <v>766.6799999999999</v>
+        <v>770.97</v>
       </c>
       <c r="AH5">
-        <v>685.35</v>
+        <v>683.73</v>
       </c>
       <c r="AI5">
-        <v>703.47</v>
+        <v>713.98</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>34.18</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1420,10 +1424,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>534.8</v>
+        <v>530.45</v>
       </c>
       <c r="D6">
-        <v>1.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1432,25 +1436,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-10.87</v>
+        <v>-11.59</v>
       </c>
       <c r="H6">
-        <v>21.94</v>
+        <v>20.95</v>
       </c>
       <c r="I6">
-        <v>-0.93</v>
+        <v>-1.68</v>
       </c>
       <c r="J6">
-        <v>-5.01</v>
+        <v>-5.06</v>
       </c>
       <c r="K6">
-        <v>-3.16</v>
+        <v>-5.17</v>
       </c>
       <c r="L6">
-        <v>6.45</v>
+        <v>4.32</v>
       </c>
       <c r="M6">
-        <v>14.47</v>
+        <v>13.2</v>
       </c>
       <c r="N6">
         <v>23</v>
@@ -1459,19 +1463,19 @@
         <v>51</v>
       </c>
       <c r="P6">
-        <v>534.13</v>
+        <v>532.3200000000001</v>
       </c>
       <c r="Q6">
-        <v>540.8</v>
+        <v>539.39</v>
       </c>
       <c r="R6">
-        <v>549.27</v>
+        <v>548.5700000000001</v>
       </c>
       <c r="S6">
-        <v>520.65</v>
+        <v>520.9</v>
       </c>
       <c r="T6">
-        <v>2.72</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1486,34 +1490,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.99</v>
+        <v>42.6</v>
       </c>
       <c r="Z6">
-        <v>-6.41</v>
+        <v>-6.36</v>
       </c>
       <c r="AA6">
-        <v>-6.01</v>
+        <v>-6.08</v>
       </c>
       <c r="AB6">
-        <v>-0.4</v>
+        <v>-0.28</v>
       </c>
       <c r="AC6">
-        <v>73.05</v>
+        <v>76.81</v>
       </c>
       <c r="AD6">
-        <v>78.22</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AE6">
-        <v>12.63</v>
+        <v>12.25</v>
       </c>
       <c r="AF6">
-        <v>6.61</v>
+        <v>-51.97</v>
       </c>
       <c r="AG6">
-        <v>563.24</v>
+        <v>560.63</v>
       </c>
       <c r="AH6">
-        <v>518.36</v>
+        <v>518.15</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1522,7 +1526,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.57</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,10 +1537,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11344</v>
+        <v>11444</v>
       </c>
       <c r="D7">
-        <v>-1.06</v>
+        <v>0.88</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1545,46 +1549,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.82</v>
+        <v>-48.37</v>
       </c>
       <c r="H7">
-        <v>6.47</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
-        <v>-0.85</v>
+        <v>-1.26</v>
       </c>
       <c r="J7">
-        <v>-5</v>
+        <v>-1.11</v>
       </c>
       <c r="K7">
-        <v>-5.95</v>
+        <v>-6.63</v>
       </c>
       <c r="L7">
-        <v>-39.9</v>
+        <v>-39.75</v>
       </c>
       <c r="M7">
-        <v>19.05</v>
+        <v>19.11</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>11448.8</v>
+        <v>11419.6</v>
       </c>
       <c r="Q7">
-        <v>11558.5</v>
+        <v>11547.2</v>
       </c>
       <c r="R7">
-        <v>11510.52</v>
+        <v>11491.86</v>
       </c>
       <c r="S7">
-        <v>14688.36</v>
+        <v>14654.84</v>
       </c>
       <c r="T7">
-        <v>-22.77</v>
+        <v>-21.91</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1599,34 +1603,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>45.39</v>
+        <v>47.56</v>
       </c>
       <c r="Z7">
-        <v>-46.77</v>
+        <v>-49.09</v>
       </c>
       <c r="AA7">
-        <v>-19.88</v>
+        <v>-25.72</v>
       </c>
       <c r="AB7">
-        <v>-26.88</v>
+        <v>-23.37</v>
       </c>
       <c r="AC7">
-        <v>33.45</v>
+        <v>37.12</v>
       </c>
       <c r="AD7">
-        <v>37.34</v>
+        <v>36.01</v>
       </c>
       <c r="AE7">
-        <v>395.39</v>
+        <v>385.44</v>
       </c>
       <c r="AF7">
-        <v>-81.06</v>
+        <v>-1.96</v>
       </c>
       <c r="AG7">
-        <v>12013.49</v>
+        <v>12001.75</v>
       </c>
       <c r="AH7">
-        <v>11103.51</v>
+        <v>11092.65</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1635,7 +1639,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>21.81</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1646,10 +1650,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>341.4</v>
+        <v>342.45</v>
       </c>
       <c r="D8">
-        <v>2.83</v>
+        <v>0.31</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1658,46 +1662,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.79</v>
+        <v>-2.49</v>
       </c>
       <c r="H8">
-        <v>45.7</v>
+        <v>46.15</v>
       </c>
       <c r="I8">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J8">
-        <v>-0.13</v>
+        <v>-1.2</v>
       </c>
       <c r="K8">
-        <v>23.94</v>
+        <v>17.68</v>
       </c>
       <c r="L8">
-        <v>13.76</v>
+        <v>13.68</v>
       </c>
       <c r="M8">
-        <v>30.4</v>
+        <v>30.51</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P8">
-        <v>334.27</v>
+        <v>335.94</v>
       </c>
       <c r="Q8">
-        <v>336.41</v>
+        <v>336.47</v>
       </c>
       <c r="R8">
-        <v>333.17</v>
+        <v>333.46</v>
       </c>
       <c r="S8">
-        <v>286.59</v>
+        <v>286.96</v>
       </c>
       <c r="T8">
-        <v>19.12</v>
+        <v>19.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1712,34 +1716,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>56.54</v>
+        <v>57.39</v>
       </c>
       <c r="Z8">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="AA8">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>-0.73</v>
+        <v>-0.23</v>
       </c>
       <c r="AC8">
-        <v>26.87</v>
+        <v>52.88</v>
       </c>
       <c r="AD8">
-        <v>12.91</v>
+        <v>28.26</v>
       </c>
       <c r="AE8">
-        <v>9.039999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AF8">
-        <v>134.4</v>
+        <v>17.23</v>
       </c>
       <c r="AG8">
-        <v>346.62</v>
+        <v>346.8</v>
       </c>
       <c r="AH8">
-        <v>326.21</v>
+        <v>326.14</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1748,7 +1752,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.57</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1759,10 +1763,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="D9">
-        <v>0.98</v>
+        <v>-0.46</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1771,46 +1775,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-2.31</v>
+        <v>-2.76</v>
       </c>
       <c r="H9">
-        <v>21.37</v>
+        <v>20.82</v>
       </c>
       <c r="I9">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
       <c r="J9">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="K9">
-        <v>2.16</v>
+        <v>0.49</v>
       </c>
       <c r="L9">
-        <v>22.08</v>
+        <v>18.39</v>
       </c>
       <c r="M9">
-        <v>14.75</v>
+        <v>14.49</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1308.46</v>
+        <v>1307.66</v>
       </c>
       <c r="Q9">
-        <v>1304.99</v>
+        <v>1306.44</v>
       </c>
       <c r="R9">
-        <v>1277.53</v>
+        <v>1279.13</v>
       </c>
       <c r="S9">
-        <v>1227.64</v>
+        <v>1228.63</v>
       </c>
       <c r="T9">
-        <v>6.71</v>
+        <v>6.13</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1825,34 +1829,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>53.07</v>
+        <v>51.11</v>
       </c>
       <c r="Z9">
-        <v>8.01</v>
+        <v>7.02</v>
       </c>
       <c r="AA9">
-        <v>10.88</v>
+        <v>10.11</v>
       </c>
       <c r="AB9">
-        <v>-2.87</v>
+        <v>-3.09</v>
       </c>
       <c r="AC9">
-        <v>7.77</v>
+        <v>11.55</v>
       </c>
       <c r="AD9">
-        <v>18.64</v>
+        <v>12.82</v>
       </c>
       <c r="AE9">
-        <v>25.27</v>
+        <v>24.8</v>
       </c>
       <c r="AF9">
-        <v>-8.58</v>
+        <v>-32.04</v>
       </c>
       <c r="AG9">
-        <v>1349.32</v>
+        <v>1348.48</v>
       </c>
       <c r="AH9">
-        <v>1260.66</v>
+        <v>1264.4</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1861,7 +1865,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>30.22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1872,10 +1876,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>83.86</v>
+        <v>85.44</v>
       </c>
       <c r="D10">
-        <v>-0.31</v>
+        <v>1.88</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1884,46 +1888,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-8.300000000000001</v>
+        <v>-6.57</v>
       </c>
       <c r="H10">
-        <v>132.43</v>
+        <v>136.81</v>
       </c>
       <c r="I10">
-        <v>7.97</v>
+        <v>4.77</v>
       </c>
       <c r="J10">
-        <v>-0.01</v>
+        <v>3.06</v>
       </c>
       <c r="K10">
-        <v>63.69</v>
+        <v>64.81</v>
       </c>
       <c r="L10">
-        <v>15.54</v>
+        <v>17.36</v>
       </c>
       <c r="M10">
-        <v>-3.01</v>
+        <v>-2.46</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P10">
-        <v>83.78</v>
+        <v>84.56</v>
       </c>
       <c r="Q10">
-        <v>83.34999999999999</v>
+        <v>83.27</v>
       </c>
       <c r="R10">
-        <v>72.47</v>
+        <v>73.14</v>
       </c>
       <c r="S10">
-        <v>60.07</v>
+        <v>60.16</v>
       </c>
       <c r="T10">
-        <v>39.6</v>
+        <v>42.01</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1938,34 +1942,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>56.96</v>
+        <v>59.28</v>
       </c>
       <c r="Z10">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA10">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="AB10">
-        <v>-0.57</v>
+        <v>-0.41</v>
       </c>
       <c r="AC10">
-        <v>70.06</v>
+        <v>76.05</v>
       </c>
       <c r="AD10">
-        <v>63.46</v>
+        <v>71.53</v>
       </c>
       <c r="AE10">
         <v>4.12</v>
       </c>
       <c r="AF10">
-        <v>-41.4</v>
+        <v>122.35</v>
       </c>
       <c r="AG10">
-        <v>90.81999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AH10">
-        <v>75.88</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1974,7 +1978,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>14.47</v>
+        <v>13.94</v>
       </c>
     </row>
   </sheetData>
@@ -2115,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2155,7 +2159,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2174,1004 +2178,1001 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>7.34</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-5.73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>8.800000000000001</v>
+        <v>13.95</v>
       </c>
       <c r="D9" s="7">
-        <v>7.34</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.46</v>
+        <v>17.79</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3.84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>10.23</v>
+        <v>4.7</v>
       </c>
       <c r="D10" s="7">
-        <v>13.95</v>
-      </c>
-      <c r="E10" s="9">
-        <v>3.72</v>
+        <v>2.25</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D11" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="E11" s="9">
-        <v>3.7</v>
+        <v>3.29</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-4.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>0.82</v>
+        <v>-5.01</v>
       </c>
       <c r="D12" s="7">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="E12" s="9">
-        <v>7.21</v>
+        <v>-5.06</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-8.91</v>
+        <v>-5</v>
       </c>
       <c r="D13" s="7">
-        <v>-5.01</v>
+        <v>-1.11</v>
       </c>
       <c r="E13" s="9">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-3.26</v>
+        <v>-0.13</v>
       </c>
       <c r="D14" s="7">
-        <v>-5</v>
+        <v>-1.2</v>
       </c>
       <c r="E14" s="8">
-        <v>-1.74</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-2.92</v>
+        <v>2.07</v>
       </c>
       <c r="D15" s="7">
-        <v>-0.13</v>
+        <v>2.75</v>
       </c>
       <c r="E15" s="9">
-        <v>2.79</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-0.36</v>
+        <v>-0.01</v>
       </c>
       <c r="D16" s="7">
-        <v>2.07</v>
+        <v>3.06</v>
       </c>
       <c r="E16" s="9">
-        <v>2.43</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-0.3</v>
+        <v>-1.54</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E17" s="9">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-1.53</v>
+        <v>0.82</v>
       </c>
       <c r="D18" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.01</v>
+        <v>2.14</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="D19" s="7">
-        <v>0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="E19" s="9">
-        <v>1.51</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-2.04</v>
+        <v>6.59</v>
       </c>
       <c r="D20" s="7">
-        <v>-1.11</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.93</v>
+        <v>3.22</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>0.65</v>
+        <v>-0.93</v>
       </c>
       <c r="D21" s="7">
-        <v>6.59</v>
-      </c>
-      <c r="E21" s="9">
-        <v>5.94</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>1.64</v>
+        <v>-0.85</v>
       </c>
       <c r="D22" s="7">
-        <v>-0.93</v>
+        <v>-1.26</v>
       </c>
       <c r="E22" s="8">
-        <v>-2.57</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-2.13</v>
+        <v>2.8</v>
       </c>
       <c r="D23" s="7">
-        <v>-0.85</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.28</v>
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-0.84</v>
+        <v>0.31</v>
       </c>
       <c r="D24" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="E24" s="9">
-        <v>3.64</v>
+        <v>-0.31</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-1.23</v>
+        <v>7.97</v>
       </c>
       <c r="D25" s="7">
-        <v>0.31</v>
-      </c>
-      <c r="E25" s="9">
-        <v>1.54</v>
+        <v>4.77</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>5.97</v>
+        <v>17.17</v>
       </c>
       <c r="D26" s="7">
-        <v>7.97</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2</v>
+        <v>16.44</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>16.24</v>
+        <v>56.56</v>
       </c>
       <c r="D27" s="7">
-        <v>17.17</v>
+        <v>58.2</v>
       </c>
       <c r="E27" s="9">
-        <v>0.93</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>51.09</v>
+        <v>10.79</v>
       </c>
       <c r="D28" s="7">
-        <v>56.56</v>
-      </c>
-      <c r="E28" s="9">
-        <v>5.47</v>
+        <v>9.16</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>10.12</v>
+        <v>3.78</v>
       </c>
       <c r="D29" s="7">
-        <v>10.79</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.67</v>
+        <v>1.92</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>-0.97</v>
+        <v>6.45</v>
       </c>
       <c r="D30" s="7">
-        <v>3.78</v>
-      </c>
-      <c r="E30" s="9">
-        <v>4.75</v>
+        <v>4.32</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>5.13</v>
+        <v>-39.9</v>
       </c>
       <c r="D31" s="7">
-        <v>6.45</v>
+        <v>-39.75</v>
       </c>
       <c r="E31" s="9">
-        <v>1.32</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-38.73</v>
+        <v>13.76</v>
       </c>
       <c r="D32" s="7">
-        <v>-39.9</v>
+        <v>13.68</v>
       </c>
       <c r="E32" s="8">
-        <v>-1.17</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>9.48</v>
+        <v>22.08</v>
       </c>
       <c r="D33" s="7">
-        <v>13.76</v>
-      </c>
-      <c r="E33" s="9">
-        <v>4.28</v>
+        <v>18.39</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>20.97</v>
+        <v>15.54</v>
       </c>
       <c r="D34" s="7">
-        <v>22.08</v>
+        <v>17.36</v>
       </c>
       <c r="E34" s="9">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>14.95</v>
+        <v>-7.66</v>
       </c>
       <c r="D35" s="7">
-        <v>15.54</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.59</v>
+        <v>-9.93</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-2.37</v>
+        <v>39.47</v>
       </c>
       <c r="D36" s="7">
-        <v>-7.66</v>
+        <v>33.12</v>
       </c>
       <c r="E36" s="8">
-        <v>-5.29</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>36.61</v>
+        <v>2.25</v>
       </c>
       <c r="D37" s="7">
-        <v>39.47</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.86</v>
+        <v>-1</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>1.36</v>
+        <v>15.3</v>
       </c>
       <c r="D38" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.89</v>
+        <v>9.73</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>11.61</v>
+        <v>-3.16</v>
       </c>
       <c r="D39" s="7">
-        <v>15.3</v>
-      </c>
-      <c r="E39" s="9">
-        <v>3.69</v>
+        <v>-5.17</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-6.09</v>
+        <v>-5.95</v>
       </c>
       <c r="D40" s="7">
-        <v>-3.16</v>
-      </c>
-      <c r="E40" s="9">
-        <v>2.93</v>
+        <v>-6.63</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-5.84</v>
+        <v>23.94</v>
       </c>
       <c r="D41" s="7">
-        <v>-5.95</v>
+        <v>17.68</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.11</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>19.17</v>
+        <v>2.16</v>
       </c>
       <c r="D42" s="7">
-        <v>23.94</v>
-      </c>
-      <c r="E42" s="9">
-        <v>4.77</v>
+        <v>0.49</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>2.17</v>
+        <v>63.69</v>
       </c>
       <c r="D43" s="7">
-        <v>2.16</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.01</v>
+        <v>64.81</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.12</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>57.88</v>
+        <v>-32.94</v>
       </c>
       <c r="D44" s="7">
-        <v>63.69</v>
+        <v>-32.78</v>
       </c>
       <c r="E44" s="9">
-        <v>5.81</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-32.14</v>
+        <v>-11.04</v>
       </c>
       <c r="D45" s="7">
-        <v>-32.94</v>
+        <v>-11.78</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.8</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-1.05</v>
+        <v>-9.4</v>
       </c>
       <c r="D46" s="7">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.05</v>
+        <v>-11.85</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-11.83</v>
+        <v>-10.87</v>
       </c>
       <c r="D47" s="7">
-        <v>-11.04</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.79</v>
+        <v>-11.59</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-14.55</v>
+        <v>-48.82</v>
       </c>
       <c r="D48" s="7">
-        <v>-9.4</v>
+        <v>-48.37</v>
       </c>
       <c r="E48" s="9">
-        <v>5.15</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-12.25</v>
+        <v>-2.79</v>
       </c>
       <c r="D49" s="7">
-        <v>-10.87</v>
+        <v>-2.49</v>
       </c>
       <c r="E49" s="9">
-        <v>1.38</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-48.27</v>
+        <v>-2.31</v>
       </c>
       <c r="D50" s="7">
-        <v>-48.82</v>
+        <v>-2.76</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.55</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-5.47</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="D51" s="7">
-        <v>-2.79</v>
+        <v>-6.57</v>
       </c>
       <c r="E51" s="9">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>-3.26</v>
+        <v>675.7</v>
       </c>
       <c r="D52" s="7">
-        <v>-2.31</v>
+        <v>677.3</v>
       </c>
       <c r="E52" s="9">
-        <v>0.95</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>-8.02</v>
+        <v>311.7</v>
       </c>
       <c r="D53" s="7">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.28</v>
+        <v>317.5</v>
+      </c>
+      <c r="E53" s="9">
+        <v>5.8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>683.8</v>
+        <v>1146.5</v>
       </c>
       <c r="D54" s="7">
-        <v>675.7</v>
+        <v>1137</v>
       </c>
       <c r="E54" s="8">
-        <v>-8.1</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>307.6</v>
+        <v>783.3</v>
       </c>
       <c r="D55" s="7">
-        <v>311.7</v>
-      </c>
-      <c r="E55" s="9">
-        <v>4.1</v>
+        <v>762.15</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-21.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>1136.3</v>
+        <v>534.8</v>
       </c>
       <c r="D56" s="7">
-        <v>1146.5</v>
-      </c>
-      <c r="E56" s="9">
-        <v>10.2</v>
+        <v>530.45</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-4.35</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>738.75</v>
+        <v>11344</v>
       </c>
       <c r="D57" s="7">
-        <v>783.3</v>
+        <v>11444</v>
       </c>
       <c r="E57" s="9">
-        <v>44.55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>526.5</v>
+        <v>341.4</v>
       </c>
       <c r="D58" s="7">
-        <v>534.8</v>
+        <v>342.45</v>
       </c>
       <c r="E58" s="9">
-        <v>8.300000000000001</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>11466</v>
+        <v>1310</v>
       </c>
       <c r="D59" s="7">
-        <v>11344</v>
+        <v>1304</v>
       </c>
       <c r="E59" s="8">
-        <v>-122</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>332</v>
+        <v>83.86</v>
       </c>
       <c r="D60" s="7">
-        <v>341.4</v>
+        <v>85.44</v>
       </c>
       <c r="E60" s="9">
-        <v>9.4</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="7">
-        <v>1297.3</v>
+        <v>55.07</v>
       </c>
       <c r="D61" s="7">
-        <v>1310</v>
+        <v>55.51</v>
       </c>
       <c r="E61" s="9">
-        <v>12.7</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C62" s="7">
-        <v>84.12</v>
+        <v>68.31</v>
       </c>
       <c r="D62" s="7">
-        <v>83.86</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.26</v>
+        <v>71.29000000000001</v>
+      </c>
+      <c r="E62" s="9">
+        <v>2.98</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="7">
-        <v>55</v>
+        <v>53.57</v>
       </c>
       <c r="D63" s="7">
-        <v>34</v>
+        <v>50.73</v>
       </c>
       <c r="E63" s="8">
-        <v>-21</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3179,328 +3180,260 @@
         <v>40</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>34</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="D64" s="7">
-        <v>55</v>
-      </c>
-      <c r="E64" s="9">
-        <v>21</v>
+        <v>62.33</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-11.74</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>57.74</v>
+        <v>44.99</v>
       </c>
       <c r="D65" s="7">
-        <v>55.07</v>
+        <v>42.6</v>
       </c>
       <c r="E65" s="8">
-        <v>-2.67</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>65.98999999999999</v>
+        <v>45.39</v>
       </c>
       <c r="D66" s="7">
-        <v>68.31</v>
+        <v>47.56</v>
       </c>
       <c r="E66" s="9">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>50.83</v>
+        <v>56.54</v>
       </c>
       <c r="D67" s="7">
-        <v>53.57</v>
+        <v>57.39</v>
       </c>
       <c r="E67" s="9">
-        <v>2.74</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>58.95</v>
+        <v>53.07</v>
       </c>
       <c r="D68" s="7">
-        <v>74.06999999999999</v>
-      </c>
-      <c r="E68" s="9">
-        <v>15.12</v>
+        <v>51.11</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>38.91</v>
+        <v>56.96</v>
       </c>
       <c r="D69" s="7">
-        <v>44.99</v>
+        <v>59.28</v>
       </c>
       <c r="E69" s="9">
-        <v>6.08</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="7">
-        <v>47.62</v>
+        <v>-72.45</v>
       </c>
       <c r="D70" s="7">
-        <v>45.39</v>
+        <v>-81.14</v>
       </c>
       <c r="E70" s="8">
-        <v>-2.23</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="7">
-        <v>47.97</v>
+        <v>-33.94</v>
       </c>
       <c r="D71" s="7">
-        <v>56.54</v>
+        <v>10.01</v>
       </c>
       <c r="E71" s="9">
-        <v>8.57</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="7">
-        <v>49.24</v>
+        <v>-22.54</v>
       </c>
       <c r="D72" s="7">
-        <v>53.07</v>
-      </c>
-      <c r="E72" s="9">
-        <v>3.83</v>
+        <v>-26.32</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="7">
-        <v>57.46</v>
+        <v>1261.35</v>
       </c>
       <c r="D73" s="7">
-        <v>56.96</v>
+        <v>27.16</v>
       </c>
       <c r="E73" s="8">
-        <v>-0.5</v>
+        <v>-1234.19</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>-69.13</v>
+        <v>6.61</v>
       </c>
       <c r="D74" s="7">
-        <v>-72.45</v>
+        <v>-51.97</v>
       </c>
       <c r="E74" s="8">
-        <v>-3.32</v>
+        <v>-58.58</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-29.79</v>
+        <v>-81.06</v>
       </c>
       <c r="D75" s="7">
-        <v>-33.94</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-4.15</v>
+        <v>-1.96</v>
+      </c>
+      <c r="E75" s="9">
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-43.46</v>
+        <v>134.4</v>
       </c>
       <c r="D76" s="7">
-        <v>-22.54</v>
-      </c>
-      <c r="E76" s="9">
-        <v>20.92</v>
+        <v>17.23</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-117.17</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-9.59</v>
+        <v>-8.58</v>
       </c>
       <c r="D77" s="7">
-        <v>1261.35</v>
-      </c>
-      <c r="E77" s="9">
-        <v>1270.94</v>
+        <v>-32.04</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-23.46</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-6.02</v>
+        <v>-41.4</v>
       </c>
       <c r="D78" s="7">
-        <v>6.61</v>
+        <v>122.35</v>
       </c>
       <c r="E78" s="9">
-        <v>12.63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-64.08</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-81.06</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-16.98</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-32.45</v>
-      </c>
-      <c r="D80" s="7">
-        <v>134.4</v>
-      </c>
-      <c r="E80" s="9">
-        <v>166.85</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-17.63</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-8.58</v>
-      </c>
-      <c r="E81" s="9">
-        <v>9.050000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>33.62</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-41.4</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-75.02</v>
+        <v>163.75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3524,28 +3457,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3559,16 +3492,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>56.4</v>
+        <v>55.3</v>
       </c>
       <c r="E2" s="12">
         <v>90</v>
       </c>
       <c r="F2" s="12">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G2" s="12">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3705,31 +3638,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4088000000000001</v>
+        <v>0.4133</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3717</v>
+        <v>0.3659000000000001</v>
       </c>
       <c r="C2" s="15">
-        <v>0.304</v>
+        <v>0.3051</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2377</v>
+        <v>0.2341</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1905</v>
+        <v>0.1911</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1475</v>
+        <v>0.1449</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1447</v>
+        <v>0.132</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0301</v>
+        <v>-0.0246</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0683</v>
+        <v>-0.0701</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,31 +196,40 @@
     <t>RSI Overbought Exit</t>
   </si>
   <si>
-    <t>74.1 → 62.3</t>
+    <t>71.3 → 65.0</t>
   </si>
   <si>
     <t>🔵 COOLING</t>
   </si>
   <si>
-    <t>74.1</t>
-  </si>
-  <si>
-    <t>62.3</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.3 → 71.3</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.3</t>
-  </si>
-  <si>
     <t>71.3</t>
+  </si>
+  <si>
+    <t>65.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.7 → 46.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>46.1</t>
+  </si>
+  <si>
+    <t>51.1 → 40.6</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>40.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -272,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,13 +322,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -333,7 +335,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,12 +363,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,11 +456,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -473,7 +469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -831,8 +827,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -972,10 +968,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>677.3</v>
+        <v>671.3</v>
       </c>
       <c r="D2">
-        <v>0.24</v>
+        <v>-0.89</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -984,46 +980,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.78</v>
+        <v>-33.38</v>
       </c>
       <c r="H2">
-        <v>84.45</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="I2">
-        <v>-0.9399999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="J2">
-        <v>1.61</v>
+        <v>3.04</v>
       </c>
       <c r="K2">
-        <v>-9.93</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L2">
-        <v>16.44</v>
+        <v>15.52</v>
       </c>
       <c r="M2">
-        <v>-7.01</v>
+        <v>-7.17</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>681.65</v>
+        <v>681.4400000000001</v>
       </c>
       <c r="Q2">
-        <v>658.1900000000001</v>
+        <v>659.9400000000001</v>
       </c>
       <c r="R2">
-        <v>651.85</v>
+        <v>652.86</v>
       </c>
       <c r="S2">
-        <v>626.4299999999999</v>
+        <v>627.1799999999999</v>
       </c>
       <c r="T2">
-        <v>8.119999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1038,34 +1034,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>55.51</v>
+        <v>53.4</v>
       </c>
       <c r="Z2">
-        <v>10.22</v>
+        <v>9.48</v>
       </c>
       <c r="AA2">
-        <v>6.99</v>
+        <v>7.48</v>
       </c>
       <c r="AB2">
-        <v>3.23</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>55.18</v>
+        <v>47.8</v>
       </c>
       <c r="AD2">
-        <v>64.66</v>
+        <v>57.04</v>
       </c>
       <c r="AE2">
-        <v>25.33</v>
+        <v>25.22</v>
       </c>
       <c r="AF2">
-        <v>-81.14</v>
+        <v>-61.91</v>
       </c>
       <c r="AG2">
-        <v>705</v>
+        <v>705.91</v>
       </c>
       <c r="AH2">
-        <v>611.38</v>
+        <v>613.97</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1074,7 +1070,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>51.57</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1085,10 +1081,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>317.5</v>
+        <v>311.95</v>
       </c>
       <c r="D3">
-        <v>1.86</v>
+        <v>-1.75</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1097,46 +1093,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
       <c r="H3">
-        <v>107.2</v>
+        <v>103.58</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J3">
-        <v>17.79</v>
+        <v>17.98</v>
       </c>
       <c r="K3">
-        <v>33.12</v>
+        <v>26.65</v>
       </c>
       <c r="L3">
-        <v>58.2</v>
+        <v>55.96</v>
       </c>
       <c r="M3">
-        <v>41.33</v>
+        <v>40.81</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>310.33</v>
+        <v>311.66</v>
       </c>
       <c r="Q3">
-        <v>295.72</v>
+        <v>297.96</v>
       </c>
       <c r="R3">
-        <v>276.48</v>
+        <v>277.5</v>
       </c>
       <c r="S3">
-        <v>218.71</v>
+        <v>219.47</v>
       </c>
       <c r="T3">
-        <v>45.17</v>
+        <v>42.14</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1151,34 +1147,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>71.29000000000001</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="Z3">
-        <v>11.92</v>
+        <v>11.53</v>
       </c>
       <c r="AA3">
-        <v>11.28</v>
+        <v>11.33</v>
       </c>
       <c r="AB3">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="AC3">
-        <v>68.47</v>
+        <v>60.94</v>
       </c>
       <c r="AD3">
-        <v>65.58</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AE3">
-        <v>10.59</v>
+        <v>10.72</v>
       </c>
       <c r="AF3">
-        <v>10.01</v>
+        <v>-40.98</v>
       </c>
       <c r="AG3">
-        <v>332.52</v>
+        <v>332.84</v>
       </c>
       <c r="AH3">
-        <v>258.91</v>
+        <v>263.08</v>
       </c>
       <c r="AI3">
         <v>282.53</v>
@@ -1187,7 +1183,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>40.34</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1198,10 +1194,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1137</v>
+        <v>1120.5</v>
       </c>
       <c r="D4">
-        <v>-0.83</v>
+        <v>-1.45</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1210,46 +1206,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.78</v>
+        <v>-13.06</v>
       </c>
       <c r="H4">
-        <v>15.31</v>
+        <v>13.64</v>
       </c>
       <c r="I4">
-        <v>-0.7</v>
+        <v>-3.82</v>
       </c>
       <c r="J4">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>-2.52</v>
       </c>
       <c r="L4">
-        <v>9.16</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M4">
-        <v>23.41</v>
+        <v>23.04</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O4">
         <v>61</v>
       </c>
       <c r="P4">
-        <v>1146.54</v>
+        <v>1137.64</v>
       </c>
       <c r="Q4">
-        <v>1143.2</v>
+        <v>1144.65</v>
       </c>
       <c r="R4">
-        <v>1097.27</v>
+        <v>1098.6</v>
       </c>
       <c r="S4">
-        <v>1130.3</v>
+        <v>1130.78</v>
       </c>
       <c r="T4">
-        <v>0.59</v>
+        <v>-0.91</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1261,37 +1257,37 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.73</v>
+        <v>46.15</v>
       </c>
       <c r="Z4">
-        <v>12.12</v>
+        <v>9.07</v>
       </c>
       <c r="AA4">
-        <v>16.63</v>
+        <v>15.12</v>
       </c>
       <c r="AB4">
-        <v>-4.51</v>
+        <v>-6.05</v>
       </c>
       <c r="AC4">
         <v>4.21</v>
       </c>
       <c r="AD4">
-        <v>6.36</v>
+        <v>4.21</v>
       </c>
       <c r="AE4">
-        <v>27.35</v>
+        <v>31.04</v>
       </c>
       <c r="AF4">
-        <v>-26.32</v>
+        <v>-27.64</v>
       </c>
       <c r="AG4">
-        <v>1200.36</v>
+        <v>1197.61</v>
       </c>
       <c r="AH4">
-        <v>1086.03</v>
+        <v>1091.68</v>
       </c>
       <c r="AI4">
         <v>1106.3</v>
@@ -1300,7 +1296,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.54</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1311,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>762.15</v>
+        <v>756.1</v>
       </c>
       <c r="D5">
-        <v>-2.7</v>
+        <v>-0.79</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1323,46 +1319,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-11.85</v>
+        <v>-12.55</v>
       </c>
       <c r="H5">
-        <v>15.15</v>
+        <v>14.23</v>
       </c>
       <c r="I5">
-        <v>3.22</v>
+        <v>2.47</v>
       </c>
       <c r="J5">
-        <v>3.29</v>
+        <v>2.81</v>
       </c>
       <c r="K5">
-        <v>9.73</v>
+        <v>7.84</v>
       </c>
       <c r="L5">
-        <v>1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="M5">
-        <v>36.59</v>
+        <v>36.35</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>751.77</v>
+        <v>755.42</v>
       </c>
       <c r="Q5">
-        <v>727.35</v>
+        <v>728.27</v>
       </c>
       <c r="R5">
-        <v>726.14</v>
+        <v>727.3</v>
       </c>
       <c r="S5">
-        <v>748.85</v>
+        <v>748.9</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>0.96</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1377,34 +1373,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>62.33</v>
+        <v>59.43</v>
       </c>
       <c r="Z5">
-        <v>8.619999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="AA5">
-        <v>2.87</v>
+        <v>4.14</v>
       </c>
       <c r="AB5">
-        <v>5.75</v>
+        <v>5.08</v>
       </c>
       <c r="AC5">
-        <v>89.43000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="AD5">
-        <v>95.19</v>
+        <v>88.08</v>
       </c>
       <c r="AE5">
-        <v>20.44</v>
+        <v>20.8</v>
       </c>
       <c r="AF5">
-        <v>27.16</v>
+        <v>108.15</v>
       </c>
       <c r="AG5">
-        <v>770.97</v>
+        <v>773.54</v>
       </c>
       <c r="AH5">
-        <v>683.73</v>
+        <v>682.99</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1413,7 +1409,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>39.31</v>
+        <v>38.42</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1424,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>530.45</v>
+        <v>526.45</v>
       </c>
       <c r="D6">
-        <v>-0.8100000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1436,25 +1432,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-11.59</v>
+        <v>-12.26</v>
       </c>
       <c r="H6">
-        <v>20.95</v>
+        <v>20.04</v>
       </c>
       <c r="I6">
-        <v>-1.68</v>
+        <v>-2.48</v>
       </c>
       <c r="J6">
-        <v>-5.06</v>
+        <v>-5.76</v>
       </c>
       <c r="K6">
-        <v>-5.17</v>
+        <v>-7.03</v>
       </c>
       <c r="L6">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="M6">
-        <v>13.2</v>
+        <v>13.02</v>
       </c>
       <c r="N6">
         <v>23</v>
@@ -1463,19 +1459,19 @@
         <v>51</v>
       </c>
       <c r="P6">
-        <v>532.3200000000001</v>
+        <v>529.64</v>
       </c>
       <c r="Q6">
-        <v>539.39</v>
+        <v>537.71</v>
       </c>
       <c r="R6">
-        <v>548.5700000000001</v>
+        <v>548.1</v>
       </c>
       <c r="S6">
-        <v>520.9</v>
+        <v>521.16</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1490,34 +1486,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.6</v>
+        <v>40.47</v>
       </c>
       <c r="Z6">
-        <v>-6.36</v>
+        <v>-6.57</v>
       </c>
       <c r="AA6">
-        <v>-6.08</v>
+        <v>-6.18</v>
       </c>
       <c r="AB6">
-        <v>-0.28</v>
+        <v>-0.39</v>
       </c>
       <c r="AC6">
-        <v>76.81</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="AD6">
-        <v>75.04000000000001</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AE6">
-        <v>12.25</v>
+        <v>11.92</v>
       </c>
       <c r="AF6">
-        <v>-51.97</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="AG6">
-        <v>560.63</v>
+        <v>557.34</v>
       </c>
       <c r="AH6">
-        <v>518.15</v>
+        <v>518.09</v>
       </c>
       <c r="AI6">
         <v>555.41</v>
@@ -1526,7 +1522,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.87</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1537,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11444</v>
+        <v>11449</v>
       </c>
       <c r="D7">
-        <v>0.88</v>
+        <v>0.04</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1549,22 +1545,22 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.37</v>
+        <v>-48.35</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.45</v>
       </c>
       <c r="I7">
-        <v>-1.26</v>
+        <v>-0.2</v>
       </c>
       <c r="J7">
-        <v>-1.11</v>
+        <v>-1.89</v>
       </c>
       <c r="K7">
-        <v>-6.63</v>
+        <v>-7.83</v>
       </c>
       <c r="L7">
-        <v>-39.75</v>
+        <v>-39.05</v>
       </c>
       <c r="M7">
         <v>19.11</v>
@@ -1573,22 +1569,22 @@
         <v>12</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P7">
-        <v>11419.6</v>
+        <v>11415</v>
       </c>
       <c r="Q7">
-        <v>11547.2</v>
+        <v>11525.95</v>
       </c>
       <c r="R7">
-        <v>11491.86</v>
+        <v>11474.02</v>
       </c>
       <c r="S7">
-        <v>14654.84</v>
+        <v>14619.24</v>
       </c>
       <c r="T7">
-        <v>-21.91</v>
+        <v>-21.69</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1603,34 +1599,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.56</v>
+        <v>47.67</v>
       </c>
       <c r="Z7">
-        <v>-49.09</v>
+        <v>-49.96</v>
       </c>
       <c r="AA7">
-        <v>-25.72</v>
+        <v>-30.57</v>
       </c>
       <c r="AB7">
-        <v>-23.37</v>
+        <v>-19.39</v>
       </c>
       <c r="AC7">
-        <v>37.12</v>
+        <v>29.55</v>
       </c>
       <c r="AD7">
-        <v>36.01</v>
+        <v>33.37</v>
       </c>
       <c r="AE7">
-        <v>385.44</v>
+        <v>389.05</v>
       </c>
       <c r="AF7">
-        <v>-1.96</v>
+        <v>-33.79</v>
       </c>
       <c r="AG7">
-        <v>12001.75</v>
+        <v>11955.21</v>
       </c>
       <c r="AH7">
-        <v>11092.65</v>
+        <v>11096.69</v>
       </c>
       <c r="AI7">
         <v>12426.6</v>
@@ -1639,7 +1635,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>21.61</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1650,10 +1646,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>342.45</v>
+        <v>343.15</v>
       </c>
       <c r="D8">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1662,46 +1658,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.49</v>
+        <v>-2.29</v>
       </c>
       <c r="H8">
-        <v>46.15</v>
+        <v>46.45</v>
       </c>
       <c r="I8">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="J8">
-        <v>-1.2</v>
+        <v>0.53</v>
       </c>
       <c r="K8">
-        <v>17.68</v>
+        <v>16.54</v>
       </c>
       <c r="L8">
-        <v>13.68</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M8">
-        <v>30.51</v>
+        <v>30.56</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>335.94</v>
+        <v>337.97</v>
       </c>
       <c r="Q8">
-        <v>336.47</v>
+        <v>336.67</v>
       </c>
       <c r="R8">
-        <v>333.46</v>
+        <v>333.81</v>
       </c>
       <c r="S8">
-        <v>286.96</v>
+        <v>287.34</v>
       </c>
       <c r="T8">
-        <v>19.34</v>
+        <v>19.42</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1716,34 +1712,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.39</v>
+        <v>57.97</v>
       </c>
       <c r="Z8">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AA8">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB8">
-        <v>-0.23</v>
+        <v>0.12</v>
       </c>
       <c r="AC8">
-        <v>52.88</v>
+        <v>77.41</v>
       </c>
       <c r="AD8">
-        <v>28.26</v>
+        <v>52.39</v>
       </c>
       <c r="AE8">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="AF8">
-        <v>17.23</v>
+        <v>37.04</v>
       </c>
       <c r="AG8">
-        <v>346.8</v>
+        <v>347.36</v>
       </c>
       <c r="AH8">
-        <v>326.14</v>
+        <v>325.97</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1752,7 +1748,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.2</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1763,10 +1759,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="D9">
-        <v>-0.46</v>
+        <v>-2.99</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1775,46 +1771,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-2.76</v>
+        <v>-5.67</v>
       </c>
       <c r="H9">
-        <v>20.82</v>
+        <v>17.21</v>
       </c>
       <c r="I9">
-        <v>-0.31</v>
+        <v>-4.53</v>
       </c>
       <c r="J9">
-        <v>2.75</v>
+        <v>-0.78</v>
       </c>
       <c r="K9">
-        <v>0.49</v>
+        <v>-2.43</v>
       </c>
       <c r="L9">
-        <v>18.39</v>
+        <v>14.53</v>
       </c>
       <c r="M9">
-        <v>14.49</v>
+        <v>13.78</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P9">
-        <v>1307.66</v>
+        <v>1295.66</v>
       </c>
       <c r="Q9">
-        <v>1306.44</v>
+        <v>1306.19</v>
       </c>
       <c r="R9">
-        <v>1279.13</v>
+        <v>1279.83</v>
       </c>
       <c r="S9">
-        <v>1228.63</v>
+        <v>1229.39</v>
       </c>
       <c r="T9">
-        <v>6.13</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1829,34 +1825,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>51.11</v>
+        <v>40.61</v>
       </c>
       <c r="Z9">
-        <v>7.02</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>10.11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB9">
-        <v>-3.09</v>
+        <v>-5.65</v>
       </c>
       <c r="AC9">
         <v>11.55</v>
       </c>
       <c r="AD9">
-        <v>12.82</v>
+        <v>10.29</v>
       </c>
       <c r="AE9">
-        <v>24.8</v>
+        <v>25.81</v>
       </c>
       <c r="AF9">
-        <v>-32.04</v>
+        <v>-3.26</v>
       </c>
       <c r="AG9">
-        <v>1348.48</v>
+        <v>1349.19</v>
       </c>
       <c r="AH9">
-        <v>1264.4</v>
+        <v>1263.19</v>
       </c>
       <c r="AI9">
         <v>1264.89</v>
@@ -1865,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1876,10 +1872,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>85.44</v>
+        <v>85.73</v>
       </c>
       <c r="D10">
-        <v>1.88</v>
+        <v>0.34</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1888,25 +1884,25 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-6.57</v>
+        <v>-6.25</v>
       </c>
       <c r="H10">
-        <v>136.81</v>
+        <v>137.61</v>
       </c>
       <c r="I10">
-        <v>4.77</v>
+        <v>0.3</v>
       </c>
       <c r="J10">
-        <v>3.06</v>
+        <v>-1.51</v>
       </c>
       <c r="K10">
-        <v>64.81</v>
+        <v>63.02</v>
       </c>
       <c r="L10">
-        <v>17.36</v>
+        <v>16.77</v>
       </c>
       <c r="M10">
-        <v>-2.46</v>
+        <v>-2.39</v>
       </c>
       <c r="N10">
         <v>88</v>
@@ -1915,19 +1911,19 @@
         <v>88</v>
       </c>
       <c r="P10">
-        <v>84.56</v>
+        <v>84.61</v>
       </c>
       <c r="Q10">
-        <v>83.27</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="R10">
-        <v>73.14</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="S10">
-        <v>60.16</v>
+        <v>60.26</v>
       </c>
       <c r="T10">
-        <v>42.01</v>
+        <v>42.27</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1942,34 +1938,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.28</v>
+        <v>59.72</v>
       </c>
       <c r="Z10">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AA10">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AB10">
-        <v>-0.41</v>
+        <v>-0.29</v>
       </c>
       <c r="AC10">
-        <v>76.05</v>
+        <v>84.63</v>
       </c>
       <c r="AD10">
-        <v>71.53</v>
+        <v>76.91</v>
       </c>
       <c r="AE10">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="AF10">
-        <v>122.35</v>
+        <v>-27.03</v>
       </c>
       <c r="AG10">
-        <v>90.59999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="AH10">
-        <v>75.93000000000001</v>
+        <v>76.59</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1978,7 +1974,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>13.94</v>
+        <v>13.47</v>
       </c>
     </row>
   </sheetData>
@@ -2119,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2159,7 +2155,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2179,7 +2175,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>62</v>
@@ -2197,1243 +2193,1331 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>7.34</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.61</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-5.73</v>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>13.95</v>
+        <v>1.61</v>
       </c>
       <c r="D9" s="7">
-        <v>17.79</v>
-      </c>
-      <c r="E9" s="9">
-        <v>3.84</v>
+        <v>3.04</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>4.7</v>
+        <v>17.79</v>
       </c>
       <c r="D10" s="7">
-        <v>2.25</v>
+        <v>17.98</v>
       </c>
       <c r="E10" s="8">
-        <v>-2.45</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>8.029999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="D11" s="7">
-        <v>3.29</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-4.74</v>
+        <v>1.87</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-5.01</v>
+        <v>3.29</v>
       </c>
       <c r="D12" s="7">
-        <v>-5.06</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.05</v>
+        <v>2.81</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-5</v>
+        <v>-5.06</v>
       </c>
       <c r="D13" s="7">
-        <v>-1.11</v>
+        <v>-5.76</v>
       </c>
       <c r="E13" s="9">
-        <v>3.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-0.13</v>
+        <v>-1.11</v>
       </c>
       <c r="D14" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.07</v>
+        <v>-1.89</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>2.07</v>
+        <v>-1.2</v>
       </c>
       <c r="D15" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.68</v>
+        <v>0.53</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-0.01</v>
+        <v>2.75</v>
       </c>
       <c r="D16" s="7">
-        <v>3.06</v>
+        <v>-0.78</v>
       </c>
       <c r="E16" s="9">
-        <v>3.07</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-1.54</v>
+        <v>3.06</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="E17" s="9">
-        <v>0.6</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>0.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D18" s="7">
-        <v>2.14</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.32</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-1.11</v>
+        <v>2.14</v>
       </c>
       <c r="D19" s="7">
-        <v>-0.7</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.41</v>
+        <v>2.18</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>6.59</v>
+        <v>-0.7</v>
       </c>
       <c r="D20" s="7">
-        <v>3.22</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-3.37</v>
+        <v>-3.82</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-0.93</v>
+        <v>3.22</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.68</v>
-      </c>
-      <c r="E21" s="8">
+        <v>2.47</v>
+      </c>
+      <c r="E21" s="9">
         <v>-0.75</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-0.85</v>
+        <v>-1.68</v>
       </c>
       <c r="D22" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.41</v>
+        <v>-2.48</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>2.8</v>
+        <v>-1.26</v>
       </c>
       <c r="D23" s="7">
-        <v>2.5</v>
+        <v>-0.2</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.3</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>0.31</v>
+        <v>2.5</v>
       </c>
       <c r="D24" s="7">
-        <v>-0.31</v>
+        <v>3.05</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.62</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>7.97</v>
+        <v>-0.31</v>
       </c>
       <c r="D25" s="7">
-        <v>4.77</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-3.2</v>
+        <v>-4.53</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-4.22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>17.17</v>
+        <v>4.77</v>
       </c>
       <c r="D26" s="7">
-        <v>16.44</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.73</v>
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-4.47</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>56.56</v>
+        <v>16.44</v>
       </c>
       <c r="D27" s="7">
-        <v>58.2</v>
+        <v>15.52</v>
       </c>
       <c r="E27" s="9">
-        <v>1.64</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>10.79</v>
+        <v>58.2</v>
       </c>
       <c r="D28" s="7">
-        <v>9.16</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.63</v>
+        <v>55.96</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>3.78</v>
+        <v>9.16</v>
       </c>
       <c r="D29" s="7">
-        <v>1.92</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.86</v>
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>6.45</v>
+        <v>1.92</v>
       </c>
       <c r="D30" s="7">
-        <v>4.32</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.13</v>
+        <v>-1.56</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-39.9</v>
+        <v>4.32</v>
       </c>
       <c r="D31" s="7">
-        <v>-39.75</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.15</v>
+        <v>4.38</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>13.76</v>
+        <v>-39.75</v>
       </c>
       <c r="D32" s="7">
-        <v>13.68</v>
+        <v>-39.05</v>
       </c>
       <c r="E32" s="8">
-        <v>-0.08</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>22.08</v>
+        <v>13.68</v>
       </c>
       <c r="D33" s="7">
-        <v>18.39</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-3.69</v>
+        <v>9.619999999999999</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-4.06</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>15.54</v>
+        <v>18.39</v>
       </c>
       <c r="D34" s="7">
-        <v>17.36</v>
+        <v>14.53</v>
       </c>
       <c r="E34" s="9">
-        <v>1.82</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>-7.66</v>
+        <v>17.36</v>
       </c>
       <c r="D35" s="7">
-        <v>-9.93</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.27</v>
+        <v>16.77</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>39.47</v>
+        <v>-9.93</v>
       </c>
       <c r="D36" s="7">
-        <v>33.12</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="E36" s="8">
-        <v>-6.35</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>2.25</v>
+        <v>33.12</v>
       </c>
       <c r="D37" s="7">
-        <v>-1</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-3.25</v>
+        <v>26.65</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-6.47</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>15.3</v>
+        <v>-1</v>
       </c>
       <c r="D38" s="7">
-        <v>9.73</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-5.57</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-3.16</v>
+        <v>9.73</v>
       </c>
       <c r="D39" s="7">
-        <v>-5.17</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.01</v>
+        <v>7.84</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-5.95</v>
+        <v>-5.17</v>
       </c>
       <c r="D40" s="7">
-        <v>-6.63</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.68</v>
+        <v>-7.03</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>23.94</v>
+        <v>-6.63</v>
       </c>
       <c r="D41" s="7">
-        <v>17.68</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-6.26</v>
+        <v>-7.83</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>2.16</v>
+        <v>17.68</v>
       </c>
       <c r="D42" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.67</v>
+        <v>16.54</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>63.69</v>
+        <v>0.49</v>
       </c>
       <c r="D43" s="7">
-        <v>64.81</v>
+        <v>-2.43</v>
       </c>
       <c r="E43" s="9">
-        <v>1.12</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>-32.94</v>
+        <v>64.81</v>
       </c>
       <c r="D44" s="7">
-        <v>-32.78</v>
+        <v>63.02</v>
       </c>
       <c r="E44" s="9">
-        <v>0.16</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-11.04</v>
+        <v>-32.78</v>
       </c>
       <c r="D45" s="7">
-        <v>-11.78</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.74</v>
+        <v>-33.38</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-9.4</v>
+        <v>0</v>
       </c>
       <c r="D46" s="7">
-        <v>-11.85</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-2.45</v>
+        <v>-1.75</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-10.87</v>
+        <v>-11.78</v>
       </c>
       <c r="D47" s="7">
-        <v>-11.59</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.72</v>
+        <v>-13.06</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-48.82</v>
+        <v>-11.85</v>
       </c>
       <c r="D48" s="7">
-        <v>-48.37</v>
+        <v>-12.55</v>
       </c>
       <c r="E48" s="9">
-        <v>0.45</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-2.79</v>
+        <v>-11.59</v>
       </c>
       <c r="D49" s="7">
-        <v>-2.49</v>
+        <v>-12.26</v>
       </c>
       <c r="E49" s="9">
-        <v>0.3</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-2.31</v>
+        <v>-48.37</v>
       </c>
       <c r="D50" s="7">
-        <v>-2.76</v>
+        <v>-48.35</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.45</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-8.300000000000001</v>
+        <v>-2.49</v>
       </c>
       <c r="D51" s="7">
-        <v>-6.57</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.73</v>
+        <v>-2.29</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>675.7</v>
+        <v>-2.76</v>
       </c>
       <c r="D52" s="7">
-        <v>677.3</v>
+        <v>-5.67</v>
       </c>
       <c r="E52" s="9">
-        <v>1.6</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>311.7</v>
+        <v>-6.57</v>
       </c>
       <c r="D53" s="7">
-        <v>317.5</v>
-      </c>
-      <c r="E53" s="9">
-        <v>5.8</v>
+        <v>-6.25</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.32</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>1146.5</v>
+        <v>677.3</v>
       </c>
       <c r="D54" s="7">
-        <v>1137</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-9.5</v>
+        <v>671.3</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>783.3</v>
+        <v>317.5</v>
       </c>
       <c r="D55" s="7">
-        <v>762.15</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-21.15</v>
+        <v>311.95</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-5.55</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>534.8</v>
+        <v>1137</v>
       </c>
       <c r="D56" s="7">
-        <v>530.45</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-4.35</v>
+        <v>1120.5</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-16.5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>11344</v>
+        <v>762.15</v>
       </c>
       <c r="D57" s="7">
-        <v>11444</v>
+        <v>756.1</v>
       </c>
       <c r="E57" s="9">
-        <v>100</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>341.4</v>
+        <v>530.45</v>
       </c>
       <c r="D58" s="7">
-        <v>342.45</v>
+        <v>526.45</v>
       </c>
       <c r="E58" s="9">
-        <v>1.05</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>1310</v>
+        <v>11444</v>
       </c>
       <c r="D59" s="7">
-        <v>1304</v>
+        <v>11449</v>
       </c>
       <c r="E59" s="8">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>83.86</v>
+        <v>342.45</v>
       </c>
       <c r="D60" s="7">
-        <v>85.44</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.58</v>
+        <v>343.15</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>55.07</v>
+        <v>1304</v>
       </c>
       <c r="D61" s="7">
-        <v>55.51</v>
+        <v>1265</v>
       </c>
       <c r="E61" s="9">
-        <v>0.44</v>
+        <v>-39</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>68.31</v>
+        <v>85.44</v>
       </c>
       <c r="D62" s="7">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="E62" s="9">
-        <v>2.98</v>
+        <v>85.73</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="7">
-        <v>53.57</v>
+        <v>34</v>
       </c>
       <c r="D63" s="7">
-        <v>50.73</v>
+        <v>55</v>
       </c>
       <c r="E63" s="8">
-        <v>-2.84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>74.06999999999999</v>
+        <v>45</v>
       </c>
       <c r="D64" s="7">
-        <v>62.33</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11.74</v>
+        <v>34</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="7">
-        <v>44.99</v>
+        <v>55</v>
       </c>
       <c r="D65" s="7">
-        <v>42.6</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.39</v>
+        <v>45</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-10</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>45.39</v>
+        <v>55.51</v>
       </c>
       <c r="D66" s="7">
-        <v>47.56</v>
+        <v>53.4</v>
       </c>
       <c r="E66" s="9">
-        <v>2.17</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>56.54</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="D67" s="7">
-        <v>57.39</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E67" s="9">
-        <v>0.85</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>53.07</v>
+        <v>50.73</v>
       </c>
       <c r="D68" s="7">
-        <v>51.11</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.96</v>
+        <v>46.15</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-4.58</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>56.96</v>
+        <v>62.33</v>
       </c>
       <c r="D69" s="7">
-        <v>59.28</v>
+        <v>59.43</v>
       </c>
       <c r="E69" s="9">
-        <v>2.32</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>-72.45</v>
+        <v>42.6</v>
       </c>
       <c r="D70" s="7">
-        <v>-81.14</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-8.69</v>
+        <v>40.47</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>-33.94</v>
+        <v>47.56</v>
       </c>
       <c r="D71" s="7">
-        <v>10.01</v>
-      </c>
-      <c r="E71" s="9">
-        <v>43.95</v>
+        <v>47.67</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>-22.54</v>
+        <v>57.39</v>
       </c>
       <c r="D72" s="7">
-        <v>-26.32</v>
+        <v>57.97</v>
       </c>
       <c r="E72" s="8">
-        <v>-3.78</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>1261.35</v>
+        <v>51.11</v>
       </c>
       <c r="D73" s="7">
-        <v>27.16</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-1234.19</v>
+        <v>40.61</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>6.61</v>
+        <v>59.28</v>
       </c>
       <c r="D74" s="7">
-        <v>-51.97</v>
+        <v>59.72</v>
       </c>
       <c r="E74" s="8">
-        <v>-58.58</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-81.06</v>
+        <v>-81.14</v>
       </c>
       <c r="D75" s="7">
-        <v>-1.96</v>
-      </c>
-      <c r="E75" s="9">
-        <v>79.09999999999999</v>
+        <v>-61.91</v>
+      </c>
+      <c r="E75" s="8">
+        <v>19.23</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>134.4</v>
+        <v>10.01</v>
       </c>
       <c r="D76" s="7">
-        <v>17.23</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-117.17</v>
+        <v>-40.98</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-50.99</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-8.58</v>
+        <v>-26.32</v>
       </c>
       <c r="D77" s="7">
-        <v>-32.04</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-23.46</v>
+        <v>-27.64</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-41.4</v>
+        <v>27.16</v>
       </c>
       <c r="D78" s="7">
+        <v>108.15</v>
+      </c>
+      <c r="E78" s="8">
+        <v>80.98999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-51.97</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-70.95999999999999</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-18.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-1.96</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-33.79</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-31.83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>17.23</v>
+      </c>
+      <c r="D81" s="7">
+        <v>37.04</v>
+      </c>
+      <c r="E81" s="8">
+        <v>19.81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-32.04</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-3.26</v>
+      </c>
+      <c r="E82" s="8">
+        <v>28.78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
         <v>122.35</v>
       </c>
-      <c r="E78" s="9">
-        <v>163.75</v>
+      <c r="D83" s="7">
+        <v>-27.03</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-149.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3457,28 +3541,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3486,22 +3570,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>68.16</v>
+        <v>64.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>55.3</v>
+        <v>52.3</v>
       </c>
       <c r="E2" s="12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F2" s="12">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="G2" s="12">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3638,31 +3722,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4133</v>
+        <v>0.4081</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3659000000000001</v>
+        <v>0.3635</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3051</v>
+        <v>0.3056</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2341</v>
+        <v>0.2304</v>
       </c>
       <c r="E2" s="15">
         <v>0.1911</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1449</v>
+        <v>0.1378</v>
       </c>
       <c r="G2" s="15">
-        <v>0.132</v>
+        <v>0.1302</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0246</v>
+        <v>-0.0239</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0701</v>
+        <v>-0.0717</v>
       </c>
     </row>
   </sheetData>
